--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC19" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_LigaPro_Po" displayName="AveragesTable_LigaPro_Po" ref="A1:EC19" headerRowCount="1">
   <autoFilter ref="A1:EC19"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3883,139 +3883,139 @@
         <v>3.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>73.2</v>
+        <v>77.67</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AN8" t="n">
-        <v>49.8</v>
+        <v>49.33</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>5.67</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>48.4</v>
+        <v>47.83</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>14.4</v>
+        <v>13.17</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="BD8" t="n">
-        <v>21.2</v>
+        <v>22.83</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BH8" t="n">
         <v>9</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.2</v>
+        <v>5.09</v>
       </c>
       <c r="BR8" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BU8" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV8" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW8" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX8" t="n">
-        <v>30</v>
+        <v>36.36</v>
       </c>
       <c r="BY8" t="n">
         <v>1.93</v>
@@ -4027,19 +4027,19 @@
         <v>3.2</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="CE8" t="n">
         <v>1.41</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CG8" t="n">
         <v>2.69</v>
@@ -4048,49 +4048,49 @@
         <v>1.34</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.84</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CO8" t="n">
         <v>1.33</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="CR8" t="n">
         <v>1.43</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CU8" t="n">
         <v>1.36</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX8" t="n">
         <v>1.5</v>
@@ -4108,85 +4108,85 @@
         <v>1.36</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="DH8" t="n">
-        <v>85.90000000000001</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.8</v>
+        <v>3.63</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="DM8" t="n">
-        <v>58.9</v>
+        <v>57.82</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.1</v>
+        <v>14.91</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.9</v>
+        <v>6.18</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>52.6</v>
+        <v>51.91</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.7</v>
+        <v>14</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.9</v>
+        <v>9.18</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="EA8" t="n">
-        <v>24.7</v>
+        <v>25.27</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="9">
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
@@ -4208,82 +4208,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="H9" t="n">
-        <v>86.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="M9" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>17.6</v>
+        <v>16.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="R9" t="n">
-        <v>6.6</v>
+        <v>5.33</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>46.4</v>
+        <v>47.83</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.8</v>
+        <v>12.17</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.800000000000001</v>
+        <v>7.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>21.6</v>
+        <v>24</v>
       </c>
       <c r="AD9" t="n">
         <v>1.52</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4367,49 +4367,49 @@
         <v>2.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.2</v>
+        <v>10.09</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BL9" t="n">
         <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BU9" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4418,16 +4418,16 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CB9" t="n">
         <v>3.33</v>
@@ -4442,7 +4442,7 @@
         <v>1.42</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CG9" t="n">
         <v>2.73</v>
@@ -4457,31 +4457,31 @@
         <v>1.79</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CO9" t="n">
         <v>1.31</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="CR9" t="n">
         <v>1.42</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CT9" t="n">
         <v>2.88</v>
@@ -4490,10 +4490,10 @@
         <v>1.37</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX9" t="n">
         <v>1.5</v>
@@ -4508,88 +4508,88 @@
         <v>2.04</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="DH9" t="n">
-        <v>84.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.9</v>
+        <v>4.82</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.4</v>
+        <v>0.54</v>
       </c>
       <c r="DM9" t="n">
-        <v>58.3</v>
+        <v>59.55</v>
       </c>
       <c r="DN9" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DO9" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.3</v>
+        <v>15.82</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.1</v>
+        <v>15.82</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.2</v>
+        <v>6.45</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.2</v>
+        <v>51.54</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.5</v>
+        <v>13.09</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.4</v>
+        <v>8.82</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.4</v>
+        <v>21.82</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="10">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4689,130 +4689,130 @@
         <v>3.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AG10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>84.83</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>51.17</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP10" t="n">
         <v>2</v>
       </c>
-      <c r="AH10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>51</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AQ10" t="n">
-        <v>12.8</v>
+        <v>14.17</v>
       </c>
       <c r="AR10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.6</v>
+        <v>7.83</v>
       </c>
       <c r="AT10" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BN10" t="n">
         <v>1</v>
       </c>
-      <c r="AU10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BO10" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.2</v>
+        <v>4.64</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BT10" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BU10" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4821,7 +4821,7 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY10" t="n">
         <v>2.14</v>
@@ -4830,67 +4830,67 @@
         <v>2.24</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CC10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="CD10" t="n">
         <v>2.67</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>2.73</v>
       </c>
       <c r="CE10" t="n">
         <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CH10" t="n">
         <v>1.35</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.87</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="CR10" t="n">
         <v>1.45</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CV10" t="n">
         <v>1.94</v>
@@ -4911,88 +4911,88 @@
         <v>1.96</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DH10" t="n">
-        <v>80.40000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.5</v>
+        <v>5.27</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM10" t="n">
-        <v>53.4</v>
+        <v>53.27</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.3</v>
+        <v>14</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16.1</v>
+        <v>15.82</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.1</v>
+        <v>7.27</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.5</v>
+        <v>52.82</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.1</v>
+        <v>12.82</v>
       </c>
       <c r="DY10" t="n">
-        <v>10</v>
+        <v>9.18</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="11">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -5014,49 +5014,49 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="G11" t="n">
-        <v>1.67</v>
+        <v>2.43</v>
       </c>
       <c r="H11" t="n">
-        <v>94.83</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M11" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="O11" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M11" t="n">
-        <v>43.33</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.83</v>
-      </c>
       <c r="P11" t="n">
-        <v>12.5</v>
+        <v>12.29</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>16.14</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>8.43</v>
       </c>
       <c r="S11" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5068,28 +5068,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>48.33</v>
+        <v>49.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>12</v>
+        <v>12.43</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.67</v>
+        <v>7.71</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.33</v>
+        <v>4.71</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.17</v>
+        <v>22</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5173,70 +5173,70 @@
         <v>4.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.82</v>
+        <v>10.08</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="BN11" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="BO11" t="n">
         <v>1</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.18</v>
+        <v>5.5</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>90.91</v>
+        <v>83.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BV11" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX11" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CC11" t="n">
         <v>3.32</v>
@@ -5248,10 +5248,10 @@
         <v>1.44</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CH11" t="n">
         <v>1.33</v>
@@ -5260,40 +5260,40 @@
         <v>1.87</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CL11" t="n">
         <v>1.7</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CO11" t="n">
         <v>1.34</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="CR11" t="n">
         <v>1.45</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CV11" t="n">
         <v>1.95</v>
@@ -5314,55 +5314,55 @@
         <v>1.97</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="DH11" t="n">
-        <v>88</v>
+        <v>88.5</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.27</v>
+        <v>3.09</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.73</v>
+        <v>4.25</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.27</v>
+        <v>45.16</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="DO11" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.36</v>
+        <v>13.17</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.64</v>
+        <v>17.17</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.27</v>
+        <v>7.5</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>47.54</v>
+        <v>48.08</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.09</v>
+        <v>11.42</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.46</v>
+        <v>7.5</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.63</v>
+        <v>3.91</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.18</v>
+        <v>20.75</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="12">

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -4725,10 +4725,10 @@
         <v>14.17</v>
       </c>
       <c r="AR10" t="n">
-        <v>15.5</v>
+        <v>15.17</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.83</v>
+        <v>9.83</v>
       </c>
       <c r="AT10" t="n">
         <v>0.83</v>
@@ -4746,25 +4746,25 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>46.33</v>
+        <v>46.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.33</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.5</v>
+        <v>11.17</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="BD10" t="n">
         <v>19.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BF10" t="n">
         <v>2.17</v>
@@ -4956,10 +4956,10 @@
         <v>14</v>
       </c>
       <c r="DQ10" t="n">
-        <v>15.82</v>
+        <v>15.64</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.27</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS10" t="n">
         <v>0.09</v>
@@ -4971,19 +4971,19 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>52.82</v>
+        <v>52.91</v>
       </c>
       <c r="DW10" t="n">
         <v>0.18</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.82</v>
+        <v>13.18</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.18</v>
+        <v>9.73</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.64</v>
+        <v>3.46</v>
       </c>
       <c r="EA10" t="n">
         <v>20</v>
@@ -5047,10 +5047,10 @@
         <v>12.29</v>
       </c>
       <c r="Q11" t="n">
-        <v>16.14</v>
+        <v>16</v>
       </c>
       <c r="R11" t="n">
-        <v>8.43</v>
+        <v>9</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
@@ -5068,25 +5068,25 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>49.14</v>
+        <v>49</v>
       </c>
       <c r="Y11" t="n">
         <v>0.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.43</v>
+        <v>12.86</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.71</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.71</v>
+        <v>4.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>22</v>
+        <v>21.86</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
         <v>1.57</v>
@@ -5359,10 +5359,10 @@
         <v>13.17</v>
       </c>
       <c r="DQ11" t="n">
-        <v>17.17</v>
+        <v>17.08</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.5</v>
+        <v>7.83</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,25 +5374,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.08</v>
+        <v>48</v>
       </c>
       <c r="DW11" t="n">
         <v>0.25</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.42</v>
+        <v>11.67</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.5</v>
+        <v>7.84</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.75</v>
+        <v>20.67</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="EC11" t="n">
         <v>2.75</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -2588,61 +2588,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="F5" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="H5" t="n">
-        <v>98.67</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="L5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>63.83</v>
+        <v>63.71</v>
       </c>
       <c r="N5" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="P5" t="n">
-        <v>15.5</v>
+        <v>15.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.67</v>
+        <v>14.71</v>
       </c>
       <c r="R5" t="n">
-        <v>5.83</v>
+        <v>4.86</v>
       </c>
       <c r="S5" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T5" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>56.5</v>
+        <v>57.86</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>15</v>
+        <v>14.43</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.5</v>
+        <v>5.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>22.83</v>
+        <v>24</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="AF5" t="n">
         <v>0.2</v>
@@ -2759,49 +2759,49 @@
         <v>4</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.91</v>
+        <v>8.83</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BT5" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BU5" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2810,19 +2810,19 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="CA5" t="n">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="CC5" t="n">
         <v>2.19</v>
@@ -2837,28 +2837,28 @@
         <v>2.66</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CO5" t="n">
         <v>1.2</v>
@@ -2867,22 +2867,22 @@
         <v>1.87</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CR5" t="n">
         <v>1.43</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW5" t="n">
         <v>1.92</v>
@@ -2891,97 +2891,97 @@
         <v>1.48</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.59</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC5" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>87.08</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>4</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>5</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>55.91</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DO5" t="n">
         <v>2.16</v>
       </c>
-      <c r="DD5" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>87.37</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="DK5" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>55.27</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>2.09</v>
-      </c>
       <c r="DP5" t="n">
-        <v>16.18</v>
+        <v>16</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.55</v>
+        <v>15.08</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.27</v>
+        <v>5.67</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.55</v>
+        <v>56.42</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.64</v>
+        <v>14.33</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.449999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="EA5" t="n">
-        <v>24</v>
+        <v>24.58</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="EC5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AI6" t="n">
-        <v>77.17</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AL6" t="n">
         <v>4</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN6" t="n">
-        <v>42.17</v>
+        <v>40.43</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ6" t="n">
-        <v>17</v>
+        <v>17.43</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.83</v>
+        <v>16</v>
       </c>
       <c r="AS6" t="n">
-        <v>13.67</v>
+        <v>11.57</v>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.33</v>
+        <v>10.29</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.83</v>
+        <v>5.86</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="BD6" t="n">
-        <v>23.33</v>
+        <v>23.86</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.09</v>
+        <v>9.92</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.64</v>
+        <v>5.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BS6" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BY6" t="n">
         <v>2.93</v>
@@ -3222,52 +3222,52 @@
         <v>3.38</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.53</v>
+        <v>3.58</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.58</v>
+        <v>4.71</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.9</v>
+        <v>5.13</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ6" t="n">
         <v>3.03</v>
@@ -3276,16 +3276,16 @@
         <v>1.4</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CU6" t="n">
         <v>1.39</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW6" t="n">
         <v>1.87</v>
@@ -3296,91 +3296,91 @@
       </c>
       <c r="CZ6" t="inlineStr"/>
       <c r="DA6" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DB6" t="n">
         <v>1.31</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="DH6" t="n">
-        <v>76.73</v>
+        <v>74.75</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.46</v>
+        <v>42.33</v>
       </c>
       <c r="DN6" t="n">
         <v>1.09</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.18</v>
+        <v>14.67</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.36</v>
+        <v>13.67</v>
       </c>
       <c r="DR6" t="n">
-        <v>11.46</v>
+        <v>10.42</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>42.27</v>
+        <v>41.58</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.18</v>
+        <v>9.67</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.27</v>
+        <v>5.75</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.27</v>
+        <v>20.83</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="EC6" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="7">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
@@ -4611,82 +4611,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="G10" t="n">
         <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>75.2</v>
+        <v>76.17</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="K10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M10" t="n">
-        <v>55.8</v>
+        <v>55.67</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="O10" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.2</v>
+        <v>15.67</v>
       </c>
       <c r="R10" t="n">
-        <v>6.6</v>
+        <v>5.33</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>60.6</v>
+        <v>59.17</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>15.6</v>
+        <v>13.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.4</v>
+        <v>10.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.6</v>
+        <v>19.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="AF10" t="n">
         <v>0.33</v>
@@ -4770,49 +4770,49 @@
         <v>2.17</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.64</v>
+        <v>10.08</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BN10" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.27</v>
+        <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="BR10" t="n">
-        <v>100</v>
+        <v>91.67</v>
       </c>
       <c r="BS10" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BU10" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4821,19 +4821,19 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CA10" t="n">
         <v>3.15</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CC10" t="n">
         <v>2.6</v>
@@ -4845,25 +4845,25 @@
         <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CG10" t="n">
         <v>2.66</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI10" t="n">
         <v>1.88</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM10" t="n">
         <v>2.58</v>
@@ -4872,127 +4872,127 @@
         <v>1.97</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="CR10" t="n">
         <v>1.45</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX10" t="n">
         <v>1.51</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.51</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DB10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>53.42</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>52.84</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="EB10" t="n">
         <v>1.38</v>
       </c>
-      <c r="DC10" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="DD10" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="DE10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DF10" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG10" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="DH10" t="n">
-        <v>80.45</v>
-      </c>
-      <c r="DI10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DJ10" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="DK10" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="DL10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DM10" t="n">
-        <v>53.27</v>
-      </c>
-      <c r="DN10" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="DO10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="DP10" t="n">
-        <v>14</v>
-      </c>
-      <c r="DQ10" t="n">
-        <v>15.64</v>
-      </c>
-      <c r="DR10" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="DS10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DT10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV10" t="n">
-        <v>52.91</v>
-      </c>
-      <c r="DW10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DX10" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="DY10" t="n">
-        <v>9.73</v>
-      </c>
-      <c r="DZ10" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="EA10" t="n">
-        <v>20</v>
-      </c>
-      <c r="EB10" t="n">
-        <v>1.45</v>
-      </c>
       <c r="EC10" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="11">
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
         <v>0.33</v>
@@ -6301,139 +6301,139 @@
         <v>2.67</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" t="n">
-        <v>67.5</v>
+        <v>69</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AN14" t="n">
         <v>34</v>
       </c>
       <c r="AO14" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.75</v>
+        <v>12.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>15.25</v>
+        <v>17</v>
       </c>
       <c r="AS14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>49.25</v>
+        <v>49.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.75</v>
+        <v>9.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="BD14" t="n">
         <v>17</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="BH14" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BL14" t="n">
         <v>1</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.7</v>
+        <v>5.64</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>90</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BU14" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV14" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>90</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BY14" t="n">
         <v>2.68</v>
@@ -6442,16 +6442,16 @@
         <v>2.77</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.92</v>
+        <v>3.82</v>
       </c>
       <c r="CE14" t="n">
         <v>1.38</v>
@@ -6460,7 +6460,7 @@
         <v>2.85</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CH14" t="n">
         <v>1.4</v>
@@ -6472,22 +6472,22 @@
         <v>1.73</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CO14" t="n">
         <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CQ14" t="n">
         <v>3.17</v>
@@ -6496,7 +6496,7 @@
         <v>1.39</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CT14" t="n">
         <v>3</v>
@@ -6516,88 +6516,88 @@
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DB14" t="n">
         <v>1.31</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="DG14" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DH14" t="n">
-        <v>71.3</v>
+        <v>71.63</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.5</v>
+        <v>5.27</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.2</v>
+        <v>45.09</v>
       </c>
       <c r="DN14" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.6</v>
+        <v>14.64</v>
       </c>
       <c r="DQ14" t="n">
-        <v>16.2</v>
+        <v>16.91</v>
       </c>
       <c r="DR14" t="n">
-        <v>10.3</v>
+        <v>9.27</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.8</v>
+        <v>50.82</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.4</v>
+        <v>13.91</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.1</v>
+        <v>8.82</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.3</v>
+        <v>5.09</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.1</v>
+        <v>20.73</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="EC14" t="n">
         <v>3</v>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>5</v>
@@ -6622,55 +6622,55 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H15" t="n">
-        <v>62.8</v>
+        <v>64</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>3.67</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M15" t="n">
-        <v>31</v>
+        <v>31.17</v>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8</v>
+        <v>1.33</v>
       </c>
       <c r="P15" t="n">
-        <v>14.8</v>
+        <v>16.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="R15" t="n">
-        <v>10.2</v>
+        <v>8.33</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -6679,25 +6679,25 @@
         <v>49</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.4</v>
+        <v>10.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.4</v>
+        <v>17.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE15" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6781,70 +6781,70 @@
         <v>2.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.6</v>
+        <v>10.64</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.2</v>
+        <v>4.36</v>
       </c>
       <c r="BQ15" t="n">
         <v>5</v>
       </c>
       <c r="BR15" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS15" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BT15" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BU15" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV15" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.28</v>
+        <v>3.06</v>
       </c>
       <c r="CA15" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="CC15" t="n">
         <v>3.64</v>
@@ -6853,37 +6853,37 @@
         <v>4.2</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.67</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP15" t="n">
         <v>1.85</v>
@@ -6895,111 +6895,111 @@
         <v>1.4</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CU15" t="n">
         <v>1.39</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CX15" t="inlineStr"/>
       <c r="CY15" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="CZ15" t="inlineStr"/>
       <c r="DA15" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="DB15" t="n">
         <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="DH15" t="n">
-        <v>65.7</v>
+        <v>66.09</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.4</v>
+        <v>4.73</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="DM15" t="n">
-        <v>39.9</v>
+        <v>39.18</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.5</v>
+        <v>15.27</v>
       </c>
       <c r="DQ15" t="n">
-        <v>16</v>
+        <v>15.91</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.5</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>49.7</v>
+        <v>49.64</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.2</v>
+        <v>11.09</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.8</v>
+        <v>7.55</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.5</v>
+        <v>19.46</v>
       </c>
       <c r="EB15" t="n">
         <v>1.23</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="16">
@@ -7009,13 +7009,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7102,136 +7102,136 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>51</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="BE16" t="n">
         <v>1.4</v>
       </c>
-      <c r="AH16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>56</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BF16" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.9</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="BR16" t="n">
-        <v>100</v>
+        <v>90.91</v>
       </c>
       <c r="BS16" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BU16" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV16" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BY16" t="n">
         <v>2.32</v>
@@ -7243,28 +7243,28 @@
         <v>3.18</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="CE16" t="n">
         <v>1.41</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.83</v>
@@ -7273,19 +7273,19 @@
         <v>1.32</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ16" t="n">
         <v>3.5</v>
@@ -7294,7 +7294,7 @@
         <v>1.42</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CT16" t="n">
         <v>2.88</v>
@@ -7303,106 +7303,106 @@
         <v>1.37</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX16" t="n">
         <v>1.57</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.35</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="DB16" t="n">
         <v>1.35</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DH16" t="n">
-        <v>87.3</v>
+        <v>86.91</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.1</v>
+        <v>4.73</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="DM16" t="n">
-        <v>54.2</v>
+        <v>53.55</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DO16" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DP16" t="n">
-        <v>15.2</v>
+        <v>14.82</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.4</v>
+        <v>13.55</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.4</v>
+        <v>6.64</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53</v>
+        <v>52.55</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX16" t="n">
-        <v>14.5</v>
+        <v>13.91</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.1</v>
+        <v>7.82</v>
       </c>
       <c r="DZ16" t="n">
-        <v>6.4</v>
+        <v>6.09</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.9</v>
+        <v>18.91</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="EC16" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -2633,10 +2633,10 @@
         <v>15.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.71</v>
+        <v>14.57</v>
       </c>
       <c r="R5" t="n">
-        <v>4.86</v>
+        <v>5.29</v>
       </c>
       <c r="S5" t="n">
         <v>1.14</v>
@@ -2654,25 +2654,25 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>57.86</v>
+        <v>58.29</v>
       </c>
       <c r="Y5" t="n">
         <v>0.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.43</v>
+        <v>15.29</v>
       </c>
       <c r="AA5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.43</v>
+        <v>5.29</v>
       </c>
       <c r="AC5" t="n">
         <v>24</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AE5" t="n">
         <v>3.14</v>
@@ -2945,10 +2945,10 @@
         <v>16</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.08</v>
+        <v>15</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.67</v>
+        <v>5.92</v>
       </c>
       <c r="DS5" t="n">
         <v>0.17</v>
@@ -2960,25 +2960,25 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.42</v>
+        <v>56.67</v>
       </c>
       <c r="DW5" t="n">
         <v>0.25</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.33</v>
+        <v>14.84</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.17</v>
+        <v>9.75</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.17</v>
+        <v>5.09</v>
       </c>
       <c r="EA5" t="n">
         <v>24.58</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="EC5" t="n">
         <v>3.5</v>
@@ -3117,10 +3117,10 @@
         <v>17.43</v>
       </c>
       <c r="AR6" t="n">
-        <v>16</v>
+        <v>15.71</v>
       </c>
       <c r="AS6" t="n">
-        <v>11.57</v>
+        <v>13.57</v>
       </c>
       <c r="AT6" t="n">
         <v>1.14</v>
@@ -3138,25 +3138,25 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>37</v>
+        <v>36.57</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.29</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.29</v>
+        <v>10.57</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.86</v>
+        <v>6</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.43</v>
+        <v>4.57</v>
       </c>
       <c r="BD6" t="n">
         <v>23.86</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BF6" t="n">
         <v>2.14</v>
@@ -3344,10 +3344,10 @@
         <v>14.67</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.67</v>
+        <v>13.5</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.42</v>
+        <v>11.58</v>
       </c>
       <c r="DS6" t="n">
         <v>0.25</v>
@@ -3359,25 +3359,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>41.58</v>
+        <v>41.33</v>
       </c>
       <c r="DW6" t="n">
         <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.67</v>
+        <v>9.83</v>
       </c>
       <c r="DY6" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="EA6" t="n">
         <v>20.83</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="EC6" t="n">
         <v>1.92</v>
@@ -4644,10 +4644,10 @@
         <v>13.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.67</v>
+        <v>15.5</v>
       </c>
       <c r="R10" t="n">
-        <v>5.33</v>
+        <v>6.83</v>
       </c>
       <c r="S10" t="n">
         <v>0.67</v>
@@ -4665,16 +4665,16 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>59.17</v>
+        <v>59.33</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.83</v>
+        <v>11.83</v>
       </c>
       <c r="AB10" t="n">
         <v>2.67</v>
@@ -4683,7 +4683,7 @@
         <v>19.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
         <v>2.67</v>
@@ -4956,10 +4956,10 @@
         <v>13.84</v>
       </c>
       <c r="DQ10" t="n">
-        <v>15.42</v>
+        <v>15.34</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.58</v>
+        <v>8.33</v>
       </c>
       <c r="DS10" t="n">
         <v>0.08</v>
@@ -4971,16 +4971,16 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>52.84</v>
+        <v>52.92</v>
       </c>
       <c r="DW10" t="n">
         <v>0.16</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.34</v>
+        <v>12.84</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.17</v>
+        <v>9.67</v>
       </c>
       <c r="DZ10" t="n">
         <v>3.17</v>
@@ -4989,7 +4989,7 @@
         <v>19.66</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="EC10" t="n">
         <v>2.42</v>
@@ -6337,10 +6337,10 @@
         <v>12.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="AT14" t="n">
         <v>2.4</v>
@@ -6358,16 +6358,16 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>49.6</v>
+        <v>50.2</v>
       </c>
       <c r="AZ14" t="n">
         <v>0.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BC14" t="n">
         <v>4.4</v>
@@ -6376,7 +6376,7 @@
         <v>17</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BF14" t="n">
         <v>3.4</v>
@@ -6564,10 +6564,10 @@
         <v>14.64</v>
       </c>
       <c r="DQ14" t="n">
-        <v>16.91</v>
+        <v>16.82</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.27</v>
+        <v>10</v>
       </c>
       <c r="DS14" t="n">
         <v>0.18</v>
@@ -6579,16 +6579,16 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.82</v>
+        <v>51.09</v>
       </c>
       <c r="DW14" t="n">
         <v>0.36</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.91</v>
+        <v>14.09</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.82</v>
+        <v>9</v>
       </c>
       <c r="DZ14" t="n">
         <v>5.09</v>
@@ -6597,7 +6597,7 @@
         <v>20.73</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="EC14" t="n">
         <v>3</v>
@@ -6658,7 +6658,7 @@
         <v>16</v>
       </c>
       <c r="R15" t="n">
-        <v>8.33</v>
+        <v>10.83</v>
       </c>
       <c r="S15" t="n">
         <v>1.17</v>
@@ -6676,16 +6676,16 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>49</v>
+        <v>48.5</v>
       </c>
       <c r="Y15" t="n">
         <v>0.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.33</v>
+        <v>10.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.67</v>
+        <v>6.83</v>
       </c>
       <c r="AB15" t="n">
         <v>3.67</v>
@@ -6694,7 +6694,7 @@
         <v>17.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE15" t="n">
         <v>3</v>
@@ -6966,7 +6966,7 @@
         <v>15.91</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.539999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="DS15" t="n">
         <v>0.09</v>
@@ -6978,16 +6978,16 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>49.64</v>
+        <v>49.36</v>
       </c>
       <c r="DW15" t="n">
         <v>0.18</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.09</v>
+        <v>11.18</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.55</v>
+        <v>7.63</v>
       </c>
       <c r="DZ15" t="n">
         <v>3.55</v>
@@ -6996,7 +6996,7 @@
         <v>19.46</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="EC15" t="n">
         <v>2.64</v>
@@ -7135,10 +7135,10 @@
         <v>14.17</v>
       </c>
       <c r="AR16" t="n">
-        <v>12.17</v>
+        <v>11.67</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.67</v>
+        <v>7.17</v>
       </c>
       <c r="AT16" t="n">
         <v>0.5</v>
@@ -7156,16 +7156,16 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>51</v>
+        <v>50.83</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.17</v>
       </c>
       <c r="BA16" t="n">
-        <v>12.17</v>
+        <v>12.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.83</v>
+        <v>9.17</v>
       </c>
       <c r="BC16" t="n">
         <v>3.33</v>
@@ -7174,7 +7174,7 @@
         <v>16.67</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BF16" t="n">
         <v>2</v>
@@ -7366,10 +7366,10 @@
         <v>14.82</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.55</v>
+        <v>13.27</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.64</v>
+        <v>7.46</v>
       </c>
       <c r="DS16" t="n">
         <v>0.27</v>
@@ -7381,16 +7381,16 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>52.55</v>
+        <v>52.45</v>
       </c>
       <c r="DW16" t="n">
         <v>0.18</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.91</v>
+        <v>14.09</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.82</v>
+        <v>8</v>
       </c>
       <c r="DZ16" t="n">
         <v>6.09</v>
@@ -7399,7 +7399,7 @@
         <v>18.91</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="EC16" t="n">
         <v>2.73</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
@@ -1391,49 +1391,49 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8</v>
+        <v>2.17</v>
       </c>
       <c r="H2" t="n">
-        <v>81</v>
+        <v>81.33</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>53.6</v>
+        <v>56.67</v>
       </c>
       <c r="N2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="P2" t="n">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.4</v>
+        <v>13.17</v>
       </c>
       <c r="R2" t="n">
-        <v>5.4</v>
+        <v>4.33</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>51.2</v>
+        <v>51.83</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.2</v>
+        <v>16.17</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.2</v>
+        <v>6.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AF2" t="n">
         <v>0.33</v>
@@ -1550,70 +1550,70 @@
         <v>2.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.449999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BN2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.18</v>
+        <v>3.75</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.55</v>
+        <v>4.08</v>
       </c>
       <c r="BR2" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS2" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT2" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BU2" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX2" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="CC2" t="n">
         <v>3.27</v>
@@ -1622,13 +1622,13 @@
         <v>3.28</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="CH2" t="n">
         <v>1.33</v>
@@ -1643,7 +1643,7 @@
         <v>1.4</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM2" t="n">
         <v>2.64</v>
@@ -1652,25 +1652,25 @@
         <v>2.02</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV2" t="n">
         <v>1.85</v>
@@ -1691,88 +1691,88 @@
         <v>2.02</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.26</v>
+        <v>4.2</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="DH2" t="n">
-        <v>77.91</v>
+        <v>78.33</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ2" t="n">
         <v>3</v>
       </c>
       <c r="DK2" t="n">
-        <v>5</v>
+        <v>5.34</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.91</v>
+        <v>0.75</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.82</v>
+        <v>51.67</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.82</v>
+        <v>14.66</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.27</v>
+        <v>12.67</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.37</v>
+        <v>5.75</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.91</v>
+        <v>50.33</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX2" t="n">
-        <v>15</v>
+        <v>15.08</v>
       </c>
       <c r="DY2" t="n">
         <v>9</v>
       </c>
       <c r="DZ2" t="n">
-        <v>6</v>
+        <v>6.08</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.64</v>
+        <v>23.33</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.57</v>
+        <v>2.12</v>
       </c>
       <c r="AI6" t="n">
-        <v>73.70999999999999</v>
+        <v>72.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AL6" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>40.43</v>
+        <v>40.75</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.43</v>
+        <v>1.12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>17.43</v>
+        <v>17</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.71</v>
+        <v>15.75</v>
       </c>
       <c r="AS6" t="n">
-        <v>13.57</v>
+        <v>11.75</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>36.57</v>
+        <v>37.62</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.57</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="BD6" t="n">
-        <v>23.86</v>
+        <v>23.88</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BG6" t="n">
         <v>1.92</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.92</v>
+        <v>10</v>
       </c>
       <c r="BI6" t="n">
         <v>1.92</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BR6" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT6" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BU6" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV6" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY6" t="n">
         <v>2.93</v>
@@ -3222,55 +3222,55 @@
         <v>3.38</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.71</v>
+        <v>4.8</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.13</v>
+        <v>5.14</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CI6" t="n">
         <v>1.75</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="CR6" t="n">
         <v>1.4</v>
@@ -3279,16 +3279,16 @@
         <v>2.99</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CU6" t="n">
         <v>1.39</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CX6" t="inlineStr"/>
       <c r="CY6" t="n">
@@ -3305,7 +3305,7 @@
         <v>2</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
@@ -3314,70 +3314,70 @@
         <v>0.92</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="DH6" t="n">
-        <v>74.75</v>
+        <v>74.08</v>
       </c>
       <c r="DI6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>42.38</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="DW6" t="n">
         <v>0.08</v>
       </c>
-      <c r="DJ6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>42.33</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DP6" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="DQ6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="DR6" t="n">
-        <v>11.58</v>
-      </c>
-      <c r="DS6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DT6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV6" t="n">
-        <v>41.33</v>
-      </c>
-      <c r="DW6" t="n">
-        <v>0.09</v>
-      </c>
       <c r="DX6" t="n">
-        <v>9.83</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DY6" t="n">
-        <v>5.83</v>
+        <v>5.54</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.83</v>
+        <v>21.08</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="EC6" t="n">
         <v>1.92</v>
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5095,49 +5095,49 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AI11" t="n">
-        <v>79.8</v>
+        <v>78.83</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AL11" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN11" t="n">
-        <v>41</v>
+        <v>40.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.4</v>
+        <v>15.33</v>
       </c>
       <c r="AR11" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AU11" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5149,82 +5149,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>46.6</v>
+        <v>47.83</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="BD11" t="n">
-        <v>19</v>
+        <v>21.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.08</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BL11" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BM11" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BN11" t="n">
         <v>2</v>
       </c>
       <c r="BO11" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.58</v>
+        <v>4.23</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.5</v>
+        <v>5.23</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU11" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BV11" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX11" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY11" t="n">
         <v>2.51</v>
@@ -5236,19 +5236,19 @@
         <v>3.11</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.32</v>
+        <v>3.17</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.54</v>
+        <v>3.37</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CG11" t="n">
         <v>2.64</v>
@@ -5257,7 +5257,7 @@
         <v>1.33</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.86</v>
@@ -5269,19 +5269,19 @@
         <v>1.7</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CO11" t="n">
         <v>1.34</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CR11" t="n">
         <v>1.45</v>
@@ -5296,7 +5296,7 @@
         <v>1.34</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW11" t="n">
         <v>1.88</v>
@@ -5305,64 +5305,64 @@
         <v>1.51</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.5</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DH11" t="n">
-        <v>88.5</v>
+        <v>87.38</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.09</v>
+        <v>3.31</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.25</v>
+        <v>4.08</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.16</v>
+        <v>44.61</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.17</v>
+        <v>13.69</v>
       </c>
       <c r="DQ11" t="n">
-        <v>17.08</v>
+        <v>17.15</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.83</v>
+        <v>7.15</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48</v>
+        <v>48.46</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.67</v>
+        <v>11.31</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.84</v>
+        <v>7.46</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.67</v>
+        <v>21.69</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="12">
@@ -7815,94 +7815,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F18" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="G18" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>80.5</v>
+        <v>76.86</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.83</v>
+        <v>3.29</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>48</v>
+        <v>46.43</v>
       </c>
       <c r="N18" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="P18" t="n">
-        <v>15</v>
+        <v>14.86</v>
       </c>
       <c r="Q18" t="n">
-        <v>15.5</v>
+        <v>16.86</v>
       </c>
       <c r="R18" t="n">
-        <v>12.67</v>
+        <v>10.71</v>
       </c>
       <c r="S18" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="U18" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V18" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>44.17</v>
+        <v>44.43</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>9.17</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.67</v>
+        <v>4.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="AC18" t="n">
-        <v>19.67</v>
+        <v>19.57</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7989,67 +7989,67 @@
         <v>2</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.09</v>
+        <v>9.42</v>
       </c>
       <c r="BI18" t="n">
         <v>2</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BP18" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="BR18" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS18" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BT18" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BU18" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV18" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY18" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="BZ18" t="n">
-        <v>3.57</v>
+        <v>3.48</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="CC18" t="n">
         <v>4.78</v>
@@ -8061,10 +8061,10 @@
         <v>1.36</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="CH18" t="n">
         <v>1.4</v>
@@ -8082,19 +8082,19 @@
         <v>1.75</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP18" t="n">
         <v>1.92</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="CR18" t="n">
         <v>1.39</v>
@@ -8124,91 +8124,91 @@
         <v>2.58</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DB18" t="n">
         <v>1.31</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="DH18" t="n">
-        <v>76.27</v>
+        <v>74.5</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.91</v>
+        <v>3.59</v>
       </c>
       <c r="DL18" t="n">
         <v>0</v>
       </c>
       <c r="DM18" t="n">
-        <v>46.64</v>
+        <v>45.83</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DP18" t="n">
-        <v>13.36</v>
+        <v>13.42</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.91</v>
+        <v>15.75</v>
       </c>
       <c r="DR18" t="n">
-        <v>10.46</v>
+        <v>9.5</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>44</v>
+        <v>44.17</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.460000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="DY18" t="n">
-        <v>5.55</v>
+        <v>5.42</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.91</v>
+        <v>4.08</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.18</v>
+        <v>19.17</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1391,10 +1391,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="G2" t="n">
-        <v>2.17</v>
+        <v>3.17</v>
       </c>
       <c r="H2" t="n">
         <v>81.33</v>
@@ -1403,13 +1403,13 @@
         <v>0.17</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="K2" t="n">
         <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="M2" t="n">
         <v>56.67</v>
@@ -1418,7 +1418,7 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="P2" t="n">
         <v>15</v>
@@ -1454,19 +1454,19 @@
         <v>16.17</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.83</v>
+        <v>9.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.33</v>
+        <v>6.67</v>
       </c>
       <c r="AC2" t="n">
         <v>26</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AF2" t="n">
         <v>0.33</v>
@@ -1553,7 +1553,7 @@
         <v>3.42</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.58</v>
+        <v>9.67</v>
       </c>
       <c r="BI2" t="n">
         <v>3.42</v>
@@ -1577,10 +1577,10 @@
         <v>1.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.08</v>
+        <v>4.67</v>
       </c>
       <c r="BR2" t="n">
         <v>91.67</v>
@@ -1607,13 +1607,13 @@
         <v>2.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CA2" t="n">
         <v>3.24</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="CC2" t="n">
         <v>3.27</v>
@@ -1661,7 +1661,7 @@
         <v>3.95</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS2" t="n">
         <v>3.2</v>
@@ -1670,7 +1670,7 @@
         <v>2.7</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CV2" t="n">
         <v>1.85</v>
@@ -1682,31 +1682,31 @@
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.51</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC2" t="n">
         <v>2.28</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.2</v>
+        <v>4.21</v>
       </c>
       <c r="DE2" t="n">
         <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.08</v>
+        <v>2.58</v>
       </c>
       <c r="DH2" t="n">
         <v>78.33</v>
@@ -1715,13 +1715,13 @@
         <v>0.08</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="DK2" t="n">
         <v>5.34</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="DM2" t="n">
         <v>51.67</v>
@@ -1730,7 +1730,7 @@
         <v>0.92</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.92</v>
+        <v>2.34</v>
       </c>
       <c r="DP2" t="n">
         <v>14.66</v>
@@ -1760,19 +1760,19 @@
         <v>15.08</v>
       </c>
       <c r="DY2" t="n">
-        <v>9</v>
+        <v>8.83</v>
       </c>
       <c r="DZ2" t="n">
-        <v>6.08</v>
+        <v>6.25</v>
       </c>
       <c r="EA2" t="n">
         <v>23.33</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,16 +1872,16 @@
         <v>3</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>73</v>
+        <v>71.17</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
@@ -1890,100 +1890,100 @@
         <v>3</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.4</v>
+        <v>4.83</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AN3" t="n">
-        <v>43.2</v>
+        <v>42.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15.4</v>
+        <v>14.67</v>
       </c>
       <c r="AR3" t="n">
-        <v>14</v>
+        <v>14.67</v>
       </c>
       <c r="AS3" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>41.2</v>
+        <v>42.33</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.6</v>
+        <v>10.17</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.6</v>
+        <v>6.17</v>
       </c>
       <c r="BC3" t="n">
         <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.91</v>
+        <v>11.75</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.09</v>
+        <v>4.92</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,19 +1992,19 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BU3" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW3" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BX3" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BY3" t="n">
         <v>2.05</v>
@@ -2016,67 +2016,67 @@
         <v>3.33</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.44</v>
+        <v>3.39</v>
       </c>
       <c r="CE3" t="n">
         <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CH3" t="n">
         <v>1.39</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CN3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP3" t="n">
         <v>1.93</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CR3" t="n">
         <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CT3" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CU3" t="n">
         <v>1.4</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW3" t="n">
         <v>1.78</v>
@@ -2085,97 +2085,97 @@
         <v>1.56</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="DG3" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="DH3" t="n">
-        <v>87.09</v>
+        <v>85</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="DK3" t="n">
-        <v>7.09</v>
+        <v>7.08</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DM3" t="n">
-        <v>60.82</v>
+        <v>59</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="DO3" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.73</v>
+        <v>14.42</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.91</v>
+        <v>14.25</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.359999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50.82</v>
+        <v>50.58</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DX3" t="n">
-        <v>15</v>
+        <v>14.84</v>
       </c>
       <c r="DY3" t="n">
-        <v>10</v>
+        <v>9.92</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="EA3" t="n">
-        <v>23.45</v>
+        <v>23.5</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>0.14</v>
@@ -2678,130 +2678,130 @@
         <v>3.14</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
-        <v>73.8</v>
+        <v>78.17</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.2</v>
+        <v>5.67</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AO5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>27.83</v>
+      </c>
+      <c r="BE5" t="n">
         <v>1.6</v>
       </c>
-      <c r="AP5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.58</v>
-      </c>
       <c r="BF5" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="BG5" t="n">
         <v>2</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.83</v>
+        <v>8.77</v>
       </c>
       <c r="BI5" t="n">
         <v>2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.83</v>
+        <v>3.69</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BT5" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BU5" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BY5" t="n">
         <v>2.06</v>
@@ -2819,49 +2819,49 @@
         <v>2.03</v>
       </c>
       <c r="CA5" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.07</v>
+        <v>2.84</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CK5" t="n">
         <v>1.28</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP5" t="n">
         <v>1.87</v>
@@ -2870,118 +2870,118 @@
         <v>3.22</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CU5" t="n">
         <v>1.37</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CX5" t="n">
         <v>1.48</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.59</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="DB5" t="n">
         <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.08</v>
+        <v>88.08</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DJ5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="DK5" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DM5" t="n">
-        <v>55.91</v>
+        <v>56.46</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="DP5" t="n">
-        <v>16</v>
+        <v>15.62</v>
       </c>
       <c r="DQ5" t="n">
         <v>15</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.92</v>
+        <v>5.39</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.67</v>
+        <v>56</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.84</v>
+        <v>14.85</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.75</v>
+        <v>9.85</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="EA5" t="n">
-        <v>24.58</v>
+        <v>25.77</v>
       </c>
       <c r="EB5" t="n">
         <v>1.7</v>
       </c>
       <c r="EC5" t="n">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="6">
@@ -3087,7 +3087,7 @@
         <v>1.12</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="AI6" t="n">
         <v>72.75</v>
@@ -3099,10 +3099,10 @@
         <v>2.62</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN6" t="n">
         <v>40.75</v>
@@ -3111,10 +3111,10 @@
         <v>1.25</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="AR6" t="n">
         <v>15.75</v>
@@ -3147,16 +3147,16 @@
         <v>9.880000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.38</v>
+        <v>4.25</v>
       </c>
       <c r="BD6" t="n">
         <v>23.88</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BF6" t="n">
         <v>2.12</v>
@@ -3165,7 +3165,7 @@
         <v>1.92</v>
       </c>
       <c r="BH6" t="n">
-        <v>10</v>
+        <v>10.08</v>
       </c>
       <c r="BI6" t="n">
         <v>1.92</v>
@@ -3189,10 +3189,10 @@
         <v>0.62</v>
       </c>
       <c r="BP6" t="n">
-        <v>3</v>
+        <v>3.54</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5</v>
+        <v>5.54</v>
       </c>
       <c r="BR6" t="n">
         <v>69.23</v>
@@ -3225,13 +3225,13 @@
         <v>3.48</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="CC6" t="n">
         <v>4.8</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
       <c r="CE6" t="n">
         <v>1.28</v>
@@ -3276,7 +3276,7 @@
         <v>1.4</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CT6" t="n">
         <v>2.96</v>
@@ -3302,10 +3302,10 @@
         <v>1.31</v>
       </c>
       <c r="DC6" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
         <v>0.92</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="DH6" t="n">
         <v>74.08</v>
@@ -3326,10 +3326,10 @@
         <v>2.23</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0.08</v>
+        <v>0.08</v>
       </c>
       <c r="DM6" t="n">
         <v>42.38</v>
@@ -3338,10 +3338,10 @@
         <v>1.08</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.62</v>
+        <v>14.77</v>
       </c>
       <c r="DQ6" t="n">
         <v>13.69</v>
@@ -3368,16 +3368,16 @@
         <v>9.460000000000001</v>
       </c>
       <c r="DY6" t="n">
-        <v>5.54</v>
+        <v>5.61</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.93</v>
+        <v>3.85</v>
       </c>
       <c r="EA6" t="n">
         <v>21.08</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="EC6" t="n">
         <v>1.92</v>
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3883,139 +3883,139 @@
         <v>3.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="AI8" t="n">
-        <v>77.67</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.83</v>
+        <v>5.43</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AN8" t="n">
-        <v>49.33</v>
+        <v>53.86</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
       </c>
       <c r="AP8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>48.86</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BN8" t="n">
         <v>1.33</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>47.83</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>22.83</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.27</v>
-      </c>
       <c r="BO8" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.91</v>
+        <v>4.25</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.09</v>
+        <v>4.83</v>
       </c>
       <c r="BR8" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS8" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BU8" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
       <c r="BV8" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX8" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BY8" t="n">
         <v>1.93</v>
@@ -4027,19 +4027,19 @@
         <v>3.2</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CG8" t="n">
         <v>2.69</v>
@@ -4054,16 +4054,16 @@
         <v>1.84</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO8" t="n">
         <v>1.33</v>
@@ -4072,7 +4072,7 @@
         <v>2.07</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="CR8" t="n">
         <v>1.43</v>
@@ -4090,19 +4090,19 @@
         <v>1.95</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="DB8" t="n">
         <v>1.36</v>
@@ -4114,79 +4114,79 @@
         <v>3.82</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="DH8" t="n">
-        <v>87.18000000000001</v>
+        <v>88.58</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.91</v>
+        <v>5.25</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="DM8" t="n">
-        <v>57.82</v>
+        <v>59.75</v>
       </c>
       <c r="DN8" t="n">
         <v>1</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.91</v>
+        <v>14.67</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14</v>
+        <v>13.83</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.18</v>
+        <v>5.58</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.91</v>
+        <v>52.17</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>14</v>
+        <v>13.83</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.18</v>
+        <v>9</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="EA8" t="n">
-        <v>25.27</v>
+        <v>25.92</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4689,130 +4689,130 @@
         <v>2.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AI10" t="n">
-        <v>84.83</v>
+        <v>85.86</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.67</v>
+        <v>3.14</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.17</v>
+        <v>4.43</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="AN10" t="n">
-        <v>51.17</v>
+        <v>53.57</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.17</v>
+        <v>14.57</v>
       </c>
       <c r="AR10" t="n">
-        <v>15.17</v>
+        <v>14.71</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.83</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>46.5</v>
+        <v>47.86</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.17</v>
+        <v>11.29</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.5</v>
+        <v>7.29</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.17</v>
+        <v>2.71</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BH10" t="n">
         <v>10.08</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BN10" t="n">
         <v>0.92</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BP10" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="BR10" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS10" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BT10" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BU10" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4821,7 +4821,7 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY10" t="n">
         <v>2.16</v>
@@ -4833,13 +4833,13 @@
         <v>3.15</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="CE10" t="n">
         <v>1.42</v>
@@ -4848,7 +4848,7 @@
         <v>3</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CH10" t="n">
         <v>1.34</v>
@@ -4863,22 +4863,22 @@
         <v>1.44</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CR10" t="n">
         <v>1.45</v>
@@ -4914,85 +4914,85 @@
         <v>1.37</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="DE10" t="n">
         <v>0.16</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DG10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>81.39</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>54.54</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DO10" t="n">
         <v>2.16</v>
       </c>
-      <c r="DH10" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="DI10" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DJ10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="DK10" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="DL10" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DM10" t="n">
-        <v>53.42</v>
-      </c>
-      <c r="DN10" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DO10" t="n">
-        <v>2</v>
-      </c>
       <c r="DP10" t="n">
-        <v>13.84</v>
+        <v>14.08</v>
       </c>
       <c r="DQ10" t="n">
-        <v>15.34</v>
+        <v>15.07</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.33</v>
+        <v>7.62</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>52.92</v>
+        <v>53.15</v>
       </c>
       <c r="DW10" t="n">
         <v>0.16</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.84</v>
+        <v>12.77</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.67</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.17</v>
+        <v>3.39</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.66</v>
+        <v>19.38</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.42</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="11">
@@ -5236,13 +5236,13 @@
         <v>3.11</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CC11" t="n">
         <v>3.17</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CE11" t="n">
         <v>1.43</v>
@@ -5287,13 +5287,13 @@
         <v>1.45</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV11" t="n">
         <v>1.96</v>
@@ -5305,13 +5305,13 @@
         <v>1.51</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.5</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="DB11" t="n">
         <v>1.37</v>
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
         <v>0.5</v>
@@ -5498,136 +5498,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AI12" t="n">
-        <v>73.2</v>
+        <v>77.83</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.2</v>
+        <v>3.67</v>
       </c>
       <c r="AL12" t="n">
-        <v>5.2</v>
+        <v>4.67</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN12" t="n">
-        <v>43.8</v>
+        <v>45.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.6</v>
+        <v>13.17</v>
       </c>
       <c r="AR12" t="n">
-        <v>15.2</v>
+        <v>15.17</v>
       </c>
       <c r="AS12" t="n">
-        <v>12</v>
+        <v>9.83</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>46.4</v>
+        <v>48.33</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.2</v>
+        <v>10.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.6</v>
+        <v>6.17</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.2</v>
+        <v>20.83</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.82</v>
+        <v>10.25</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.73</v>
+        <v>4.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.09</v>
+        <v>4.83</v>
       </c>
       <c r="BR12" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS12" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BV12" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BY12" t="n">
         <v>2.49</v>
@@ -5636,25 +5636,25 @@
         <v>2.9</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.41</v>
+        <v>3.29</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.82</v>
+        <v>3.62</v>
       </c>
       <c r="CE12" t="n">
         <v>1.42</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CH12" t="n">
         <v>1.34</v>
@@ -5663,19 +5663,19 @@
         <v>1.89</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="CO12" t="n">
         <v>1.34</v>
@@ -5684,22 +5684,22 @@
         <v>2.13</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CR12" t="n">
         <v>1.44</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW12" t="n">
         <v>1.9</v>
@@ -5726,79 +5726,79 @@
         <v>3.96</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="DH12" t="n">
-        <v>78.81999999999999</v>
+        <v>80.67</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.82</v>
+        <v>3.08</v>
       </c>
       <c r="DK12" t="n">
-        <v>6.45</v>
+        <v>6.08</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>52.27</v>
+        <v>52.42</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.73</v>
+        <v>14.42</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.82</v>
+        <v>14.84</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.09</v>
+        <v>8.25</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>51.82</v>
+        <v>52.33</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.37</v>
+        <v>12.84</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.91</v>
+        <v>8.5</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.64</v>
+        <v>21.42</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="13">
@@ -6211,94 +6211,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="G14" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="H14" t="n">
-        <v>73.83</v>
+        <v>74</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>6.71</v>
       </c>
       <c r="L14" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M14" t="n">
-        <v>54.33</v>
+        <v>52.57</v>
       </c>
       <c r="N14" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="O14" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="P14" t="n">
-        <v>16.5</v>
+        <v>15.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>16.83</v>
+        <v>16.57</v>
       </c>
       <c r="R14" t="n">
-        <v>7.83</v>
+        <v>6.57</v>
       </c>
       <c r="S14" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="U14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>51.83</v>
+        <v>51.86</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>17.5</v>
+        <v>16.29</v>
       </c>
       <c r="AA14" t="n">
-        <v>11.83</v>
+        <v>10.86</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.67</v>
+        <v>5.43</v>
       </c>
       <c r="AC14" t="n">
-        <v>23.83</v>
+        <v>24.43</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AF14" t="n">
         <v>0.4</v>
@@ -6382,70 +6382,70 @@
         <v>3.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BH14" t="n">
-        <v>12</v>
+        <v>11.67</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BL14" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.64</v>
+        <v>5.67</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV14" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="CC14" t="n">
         <v>3.25</v>
@@ -6457,13 +6457,13 @@
         <v>1.38</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI14" t="n">
         <v>2.01</v>
@@ -6472,16 +6472,16 @@
         <v>1.73</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CO14" t="n">
         <v>1.28</v>
@@ -6490,25 +6490,25 @@
         <v>1.92</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CR14" t="n">
         <v>1.39</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CT14" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CU14" t="n">
         <v>1.4</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
@@ -6525,82 +6525,82 @@
         <v>2</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DH14" t="n">
-        <v>71.63</v>
+        <v>71.92</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DM14" t="n">
-        <v>45.09</v>
+        <v>44.83</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.64</v>
+        <v>14.17</v>
       </c>
       <c r="DQ14" t="n">
-        <v>16.82</v>
+        <v>16.67</v>
       </c>
       <c r="DR14" t="n">
-        <v>10</v>
+        <v>9.08</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.09</v>
+        <v>51.17</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.09</v>
+        <v>13.67</v>
       </c>
       <c r="DY14" t="n">
-        <v>9</v>
+        <v>8.67</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.73</v>
+        <v>21.33</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="EC14" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="15">
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>5</v>
@@ -6622,82 +6622,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="H15" t="n">
-        <v>64</v>
+        <v>66.14</v>
       </c>
       <c r="I15" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="K15" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="L15" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="M15" t="n">
-        <v>31.17</v>
+        <v>33.86</v>
       </c>
       <c r="N15" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="O15" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="P15" t="n">
-        <v>16.17</v>
+        <v>15.86</v>
       </c>
       <c r="Q15" t="n">
-        <v>16</v>
+        <v>15.71</v>
       </c>
       <c r="R15" t="n">
-        <v>10.83</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="T15" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="U15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>48.5</v>
+        <v>47.57</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.5</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.83</v>
+        <v>6.29</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.67</v>
+        <v>17.86</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6781,70 +6781,70 @@
         <v>2.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.64</v>
+        <v>10.08</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.36</v>
+        <v>4.17</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="BR15" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS15" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BT15" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BU15" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BY15" t="n">
         <v>2.48</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="CC15" t="n">
         <v>3.64</v>
@@ -6853,61 +6853,61 @@
         <v>4.2</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CG15" t="n">
         <v>2.49</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="CR15" t="n">
         <v>1.4</v>
       </c>
       <c r="CS15" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="CU15" t="n">
         <v>1.39</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CX15" t="inlineStr"/>
       <c r="CY15" t="n">
@@ -6921,85 +6921,85 @@
         <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="DH15" t="n">
-        <v>66.09</v>
+        <v>67.17</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.73</v>
+        <v>4.5</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DM15" t="n">
-        <v>39.18</v>
+        <v>40.08</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.27</v>
+        <v>15.17</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.91</v>
+        <v>15.75</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.91</v>
+        <v>9</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>49.36</v>
+        <v>48.75</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.18</v>
+        <v>10.66</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.63</v>
+        <v>7.25</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.46</v>
+        <v>19.42</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="16">
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
@@ -7021,82 +7021,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H16" t="n">
-        <v>77.8</v>
+        <v>77.67</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="K16" t="n">
-        <v>5.6</v>
+        <v>4.83</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M16" t="n">
-        <v>52.4</v>
+        <v>50</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="O16" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>15.6</v>
+        <v>14.17</v>
       </c>
       <c r="Q16" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="R16" t="n">
-        <v>7.8</v>
+        <v>6.33</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>54.4</v>
+        <v>52.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>16</v>
+        <v>14.83</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.6</v>
+        <v>6.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>21.6</v>
+        <v>22.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="AE16" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7180,67 +7180,67 @@
         <v>2</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.359999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.82</v>
+        <v>4.17</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="BR16" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS16" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BT16" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BV16" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CB16" t="n">
         <v>3.28</v>
@@ -7258,7 +7258,7 @@
         <v>2.93</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CH16" t="n">
         <v>1.35</v>
@@ -7270,16 +7270,16 @@
         <v>1.83</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO16" t="n">
         <v>1.32</v>
@@ -7288,16 +7288,16 @@
         <v>2.04</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CR16" t="n">
         <v>1.42</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CU16" t="n">
         <v>1.37</v>
@@ -7309,13 +7309,13 @@
         <v>1.85</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="DA16" t="n">
         <v>1.92</v>
@@ -7324,7 +7324,7 @@
         <v>1.35</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DD16" t="n">
         <v>3.77</v>
@@ -7333,76 +7333,76 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="DG16" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DH16" t="n">
-        <v>86.91</v>
+        <v>86.08</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.73</v>
+        <v>4.42</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DM16" t="n">
-        <v>53.55</v>
+        <v>52.25</v>
       </c>
       <c r="DN16" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.82</v>
+        <v>14.17</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.27</v>
+        <v>13.34</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.46</v>
+        <v>6.75</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>52.45</v>
+        <v>51.83</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX16" t="n">
-        <v>14.09</v>
+        <v>13.66</v>
       </c>
       <c r="DY16" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="DZ16" t="n">
-        <v>6.09</v>
+        <v>5.92</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.91</v>
+        <v>19.5</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17">
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
@@ -7424,49 +7424,49 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="H17" t="n">
-        <v>84.59999999999999</v>
+        <v>81.67</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>50.2</v>
+        <v>48.67</v>
       </c>
       <c r="N17" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>11</v>
+        <v>12.33</v>
       </c>
       <c r="R17" t="n">
-        <v>8.4</v>
+        <v>6.83</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7478,28 +7478,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>48</v>
+        <v>47.33</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.8</v>
+        <v>12.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.2</v>
+        <v>8.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AC17" t="n">
-        <v>22.2</v>
+        <v>21.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AF17" t="n">
         <v>0.17</v>
@@ -7583,70 +7583,70 @@
         <v>2.83</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.73</v>
+        <v>9.75</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.27</v>
+        <v>4.42</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="BR17" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS17" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BT17" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BU17" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV17" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BW17" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX17" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="CA17" t="n">
         <v>3.11</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="CC17" t="n">
         <v>2.72</v>
@@ -7670,43 +7670,43 @@
         <v>1.91</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CM17" t="n">
         <v>2.76</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CO17" t="n">
         <v>1.33</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CR17" t="n">
         <v>1.42</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CU17" t="n">
         <v>1.38</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW17" t="n">
         <v>1.89</v>
@@ -7724,88 +7724,88 @@
         <v>2.13</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC17" t="n">
         <v>2.11</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF17" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="DH17" t="n">
-        <v>87.27</v>
+        <v>85.58</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.73</v>
+        <v>5.58</v>
       </c>
       <c r="DL17" t="n">
         <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>56</v>
+        <v>54.75</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.54</v>
+        <v>12.42</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.18</v>
+        <v>10.92</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.73</v>
+        <v>7</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.63</v>
+        <v>47.33</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.73</v>
+        <v>12.75</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.09</v>
+        <v>8.42</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.64</v>
+        <v>4.34</v>
       </c>
       <c r="EA17" t="n">
-        <v>22.64</v>
+        <v>22.17</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="18">
@@ -8043,13 +8043,13 @@
         <v>3.14</v>
       </c>
       <c r="BZ18" t="n">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="CA18" t="n">
         <v>3.54</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CC18" t="n">
         <v>4.78</v>
@@ -8100,16 +8100,16 @@
         <v>1.39</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CW18" t="n">
         <v>1.85</v>
@@ -8124,13 +8124,13 @@
         <v>2.58</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DB18" t="n">
         <v>1.31</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DD18" t="n">
         <v>3.48</v>
@@ -8218,61 +8218,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="G19" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>89.8</v>
+        <v>85.33</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="K19" t="n">
-        <v>7.4</v>
+        <v>6.67</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M19" t="n">
-        <v>69.2</v>
+        <v>62.83</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O19" t="n">
-        <v>4.2</v>
+        <v>3.67</v>
       </c>
       <c r="P19" t="n">
-        <v>12.8</v>
+        <v>13.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="R19" t="n">
-        <v>3.4</v>
+        <v>2.67</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8284,28 +8284,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>58.8</v>
+        <v>57.67</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>10.6</v>
+        <v>11.17</v>
       </c>
       <c r="AA19" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.6</v>
+        <v>4.83</v>
       </c>
       <c r="AC19" t="n">
-        <v>20.2</v>
+        <v>19.17</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8389,70 +8389,70 @@
         <v>4</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.27</v>
+        <v>11.17</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.82</v>
+        <v>5.92</v>
       </c>
       <c r="BR19" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS19" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT19" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BV19" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="CA19" t="n">
         <v>3.28</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CC19" t="n">
         <v>2.27</v>
@@ -8461,10 +8461,10 @@
         <v>2.54</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="CG19" t="n">
         <v>2.72</v>
@@ -8473,112 +8473,112 @@
         <v>1.37</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CN19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CP19" t="n">
         <v>2</v>
       </c>
-      <c r="CO19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CP19" t="n">
-        <v>2.01</v>
-      </c>
       <c r="CQ19" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="CR19" t="n">
         <v>1.41</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CU19" t="n">
         <v>1.38</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.42</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DG19" t="n">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="DH19" t="n">
-        <v>85.09</v>
+        <v>83.25</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="DK19" t="n">
-        <v>6.46</v>
+        <v>6.17</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DM19" t="n">
-        <v>58.45</v>
+        <v>56.16</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.45</v>
+        <v>14.75</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.73</v>
+        <v>15.42</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.09</v>
+        <v>5.5</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8590,28 +8590,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>56.45</v>
+        <v>56.08</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.82</v>
+        <v>11.08</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.55</v>
+        <v>6.66</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.27</v>
+        <v>4.42</v>
       </c>
       <c r="EA19" t="n">
-        <v>22.18</v>
+        <v>21.5</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1424,10 +1424,10 @@
         <v>15</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.17</v>
+        <v>13</v>
       </c>
       <c r="R2" t="n">
-        <v>4.33</v>
+        <v>5.17</v>
       </c>
       <c r="S2" t="n">
         <v>0.83</v>
@@ -1445,25 +1445,25 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>51.83</v>
+        <v>52</v>
       </c>
       <c r="Y2" t="n">
         <v>0.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.17</v>
+        <v>16.83</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.5</v>
+        <v>10.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.67</v>
+        <v>6.17</v>
       </c>
       <c r="AC2" t="n">
         <v>26</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AE2" t="n">
         <v>2.5</v>
@@ -1736,10 +1736,10 @@
         <v>14.66</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.67</v>
+        <v>12.58</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.75</v>
+        <v>6.17</v>
       </c>
       <c r="DS2" t="n">
         <v>0.08</v>
@@ -1751,19 +1751,19 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.33</v>
+        <v>50.42</v>
       </c>
       <c r="DW2" t="n">
         <v>0.25</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.08</v>
+        <v>15.42</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.83</v>
+        <v>9.42</v>
       </c>
       <c r="DZ2" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="EA2" t="n">
         <v>23.33</v>
@@ -1911,7 +1911,7 @@
         <v>14.67</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>11.33</v>
       </c>
       <c r="AT3" t="n">
         <v>1.67</v>
@@ -1929,16 +1929,16 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>42.33</v>
+        <v>42</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.33</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.17</v>
+        <v>10.67</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.17</v>
+        <v>6.67</v>
       </c>
       <c r="BC3" t="n">
         <v>4</v>
@@ -1947,7 +1947,7 @@
         <v>22.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BF3" t="n">
         <v>2.5</v>
@@ -2142,7 +2142,7 @@
         <v>14.25</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.5</v>
+        <v>9.17</v>
       </c>
       <c r="DS3" t="n">
         <v>0.08</v>
@@ -2154,16 +2154,16 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50.58</v>
+        <v>50.42</v>
       </c>
       <c r="DW3" t="n">
         <v>0.25</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.84</v>
+        <v>15.08</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.92</v>
+        <v>10.17</v>
       </c>
       <c r="DZ3" t="n">
         <v>4.92</v>
@@ -2172,7 +2172,7 @@
         <v>23.5</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="EC3" t="n">
         <v>2.75</v>
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,52 +2275,52 @@
         <v>3.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AI4" t="n">
-        <v>62.67</v>
+        <v>63.14</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.33</v>
+        <v>5.29</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AN4" t="n">
-        <v>35.67</v>
+        <v>36.86</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.83</v>
+        <v>15.57</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.33</v>
+        <v>10</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.5</v>
+        <v>6.29</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>43.33</v>
+        <v>44.71</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.17</v>
+        <v>10.71</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.17</v>
+        <v>6.57</v>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="BD4" t="n">
-        <v>21.83</v>
+        <v>21.43</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="BG4" t="n">
         <v>2</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.27</v>
+        <v>10.08</v>
       </c>
       <c r="BI4" t="n">
         <v>2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="BR4" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BS4" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BU4" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV4" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BY4" t="n">
         <v>2.37</v>
@@ -2416,55 +2416,55 @@
         <v>2.51</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.32</v>
+        <v>3.44</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.96</v>
+        <v>4.25</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF4" t="n">
         <v>2.8</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK4" t="n">
         <v>1.32</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP4" t="n">
         <v>1.96</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="CR4" t="n">
         <v>1.46</v>
@@ -2479,10 +2479,10 @@
         <v>1.34</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CX4" t="n">
         <v>1.51</v>
@@ -2497,88 +2497,88 @@
         <v>1.98</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
       <c r="DE4" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DH4" t="n">
-        <v>72.91</v>
+        <v>72.33</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.18</v>
+        <v>6.09</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DM4" t="n">
-        <v>49.91</v>
+        <v>49.42</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="DP4" t="n">
-        <v>15.36</v>
+        <v>16.25</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12</v>
+        <v>12.17</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.27</v>
+        <v>6.59</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.36</v>
+        <v>47.83</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>13</v>
+        <v>13.08</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.73</v>
+        <v>8.75</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="EA4" t="n">
-        <v>25.18</v>
+        <v>24.67</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="5">
@@ -2714,10 +2714,10 @@
         <v>16</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.5</v>
+        <v>14.67</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AT5" t="n">
         <v>0.17</v>
@@ -2735,16 +2735,16 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>53.33</v>
+        <v>53.17</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.17</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.33</v>
+        <v>14.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.67</v>
+        <v>9.83</v>
       </c>
       <c r="BC5" t="n">
         <v>4.67</v>
@@ -2753,7 +2753,7 @@
         <v>27.83</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BF5" t="n">
         <v>3.33</v>
@@ -2945,10 +2945,10 @@
         <v>15.62</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15</v>
+        <v>14.62</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.39</v>
+        <v>5.85</v>
       </c>
       <c r="DS5" t="n">
         <v>0.15</v>
@@ -2960,16 +2960,16 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56</v>
+        <v>55.93</v>
       </c>
       <c r="DW5" t="n">
         <v>0.31</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.85</v>
+        <v>14.93</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.85</v>
+        <v>9.92</v>
       </c>
       <c r="DZ5" t="n">
         <v>5</v>
@@ -2978,7 +2978,7 @@
         <v>25.77</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="EC5" t="n">
         <v>3.23</v>
@@ -3117,10 +3117,10 @@
         <v>17.25</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.75</v>
+        <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>11.75</v>
+        <v>13.12</v>
       </c>
       <c r="AT6" t="n">
         <v>1.25</v>
@@ -3138,16 +3138,16 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>37.62</v>
+        <v>37.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.25</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.880000000000001</v>
+        <v>10.38</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.62</v>
+        <v>6.12</v>
       </c>
       <c r="BC6" t="n">
         <v>4.25</v>
@@ -3156,7 +3156,7 @@
         <v>23.88</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BF6" t="n">
         <v>2.12</v>
@@ -3344,10 +3344,10 @@
         <v>14.77</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.69</v>
+        <v>13.54</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.62</v>
+        <v>11.46</v>
       </c>
       <c r="DS6" t="n">
         <v>0.23</v>
@@ -3359,16 +3359,16 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>41.61</v>
+        <v>41.54</v>
       </c>
       <c r="DW6" t="n">
         <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.460000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="DY6" t="n">
-        <v>5.61</v>
+        <v>5.92</v>
       </c>
       <c r="DZ6" t="n">
         <v>3.85</v>
@@ -3377,7 +3377,7 @@
         <v>21.08</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="EC6" t="n">
         <v>1.92</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -3402,49 +3402,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="H7" t="n">
-        <v>86</v>
+        <v>83.17</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>61.2</v>
+        <v>58</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="P7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="R7" t="n">
-        <v>7.6</v>
+        <v>6.17</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3456,28 +3456,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>57.2</v>
+        <v>55.5</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.6</v>
+        <v>15.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.2</v>
+        <v>9.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.4</v>
+        <v>5.83</v>
       </c>
       <c r="AC7" t="n">
-        <v>21.4</v>
+        <v>20.17</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3561,49 +3561,49 @@
         <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.27</v>
+        <v>10.08</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.73</v>
+        <v>3.83</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3612,19 +3612,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="CC7" t="n">
         <v>2.29</v>
@@ -3636,25 +3636,25 @@
         <v>1.38</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CH7" t="n">
         <v>1.4</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CK7" t="n">
         <v>1.36</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CM7" t="n">
         <v>2.8</v>
@@ -3669,7 +3669,7 @@
         <v>1.92</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="CR7" t="n">
         <v>1.39</v>
@@ -3684,10 +3684,10 @@
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="CX7" t="n">
         <v>1.48</v>
@@ -3702,88 +3702,88 @@
         <v>2.15</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.81999999999999</v>
+        <v>79.83</v>
       </c>
       <c r="DI7" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>4.18</v>
+        <v>4.08</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.54</v>
+        <v>4.42</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>53.09</v>
+        <v>52.16</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="DO7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>8</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="EB7" t="n">
         <v>1.63</v>
       </c>
-      <c r="DP7" t="n">
-        <v>15</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>15.73</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV7" t="n">
-        <v>54.36</v>
-      </c>
-      <c r="DW7" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DX7" t="n">
-        <v>14.64</v>
-      </c>
-      <c r="DY7" t="n">
-        <v>9.369999999999999</v>
-      </c>
-      <c r="DZ7" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="EA7" t="n">
-        <v>19.82</v>
-      </c>
-      <c r="EB7" t="n">
-        <v>1.67</v>
-      </c>
       <c r="EC7" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="8">
@@ -3919,10 +3919,10 @@
         <v>15</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.71</v>
+        <v>6.14</v>
       </c>
       <c r="AT8" t="n">
         <v>0.86</v>
@@ -3940,25 +3940,25 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>48.86</v>
+        <v>49</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.289999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.71</v>
+        <v>4.86</v>
       </c>
       <c r="BD8" t="n">
         <v>24.29</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="BF8" t="n">
         <v>3.29</v>
@@ -4150,10 +4150,10 @@
         <v>14.67</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.83</v>
+        <v>13.42</v>
       </c>
       <c r="DR8" t="n">
-        <v>5.58</v>
+        <v>6.41</v>
       </c>
       <c r="DS8" t="n">
         <v>0.08</v>
@@ -4165,25 +4165,25 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>52.17</v>
+        <v>52.25</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.83</v>
+        <v>14.42</v>
       </c>
       <c r="DY8" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.83</v>
+        <v>4.92</v>
       </c>
       <c r="EA8" t="n">
         <v>25.92</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="EC8" t="n">
         <v>3.5</v>
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4289,127 +4289,127 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AI9" t="n">
-        <v>83.40000000000001</v>
+        <v>85.17</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AK9" t="n">
         <v>3</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN9" t="n">
-        <v>56.6</v>
+        <v>56.83</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15</v>
+        <v>14.33</v>
       </c>
       <c r="AR9" t="n">
-        <v>16.8</v>
+        <v>17.33</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.8</v>
+        <v>6.33</v>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA9" t="n">
-        <v>14.2</v>
+        <v>14.83</v>
       </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.2</v>
+        <v>19.33</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.09</v>
+        <v>9.75</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="BL9" t="n">
         <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="BO9" t="n">
         <v>1</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BU9" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4418,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BY9" t="n">
         <v>2.15</v>
@@ -4427,61 +4427,61 @@
         <v>2.16</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CB9" t="n">
         <v>3.33</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="CE9" t="n">
         <v>1.42</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI9" t="n">
         <v>1.91</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CK9" t="n">
         <v>1.41</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CO9" t="n">
         <v>1.31</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="CR9" t="n">
         <v>1.42</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CT9" t="n">
         <v>2.88</v>
@@ -4490,106 +4490,106 @@
         <v>1.37</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX9" t="n">
         <v>1.5</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.54</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DB9" t="n">
         <v>1.34</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DH9" t="n">
-        <v>90</v>
+        <v>90.34</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM9" t="n">
-        <v>59.55</v>
+        <v>59.42</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DP9" t="n">
-        <v>15.82</v>
+        <v>15.42</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.82</v>
+        <v>16.16</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.45</v>
+        <v>5.83</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.54</v>
+        <v>52.16</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.09</v>
+        <v>13.5</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.82</v>
+        <v>8.83</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.27</v>
+        <v>4.66</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.82</v>
+        <v>21.67</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -4725,10 +4725,10 @@
         <v>14.57</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.71</v>
+        <v>14.57</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.289999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="AT10" t="n">
         <v>0.71</v>
@@ -4746,25 +4746,25 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>47.86</v>
+        <v>49.43</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.29</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.29</v>
+        <v>12</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.29</v>
+        <v>7.86</v>
       </c>
       <c r="BC10" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="BD10" t="n">
         <v>19</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BF10" t="n">
         <v>2.71</v>
@@ -4956,10 +4956,10 @@
         <v>14.08</v>
       </c>
       <c r="DQ10" t="n">
-        <v>15.07</v>
+        <v>15</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.62</v>
+        <v>8.23</v>
       </c>
       <c r="DS10" t="n">
         <v>0.15</v>
@@ -4971,25 +4971,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.15</v>
+        <v>54</v>
       </c>
       <c r="DW10" t="n">
         <v>0.16</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.77</v>
+        <v>13.15</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.390000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.39</v>
+        <v>3.46</v>
       </c>
       <c r="EA10" t="n">
         <v>19.38</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="EC10" t="n">
         <v>2.69</v>
@@ -5128,10 +5128,10 @@
         <v>15.33</v>
       </c>
       <c r="AR11" t="n">
-        <v>18.5</v>
+        <v>17.83</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>6.33</v>
       </c>
       <c r="AT11" t="n">
         <v>1.83</v>
@@ -5149,25 +5149,25 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.83</v>
+        <v>47.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
         <v>3</v>
       </c>
       <c r="BD11" t="n">
-        <v>21.5</v>
+        <v>21.33</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BF11" t="n">
         <v>4.5</v>
@@ -5359,10 +5359,10 @@
         <v>13.69</v>
       </c>
       <c r="DQ11" t="n">
-        <v>17.15</v>
+        <v>16.84</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.15</v>
+        <v>7.77</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,25 +5374,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.46</v>
+        <v>48.31</v>
       </c>
       <c r="DW11" t="n">
         <v>0.31</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.31</v>
+        <v>11.54</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.46</v>
+        <v>7.69</v>
       </c>
       <c r="DZ11" t="n">
         <v>3.85</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.69</v>
+        <v>21.62</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC11" t="n">
         <v>2.92</v>
@@ -5534,7 +5534,7 @@
         <v>15.17</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.83</v>
+        <v>11.17</v>
       </c>
       <c r="AT12" t="n">
         <v>2</v>
@@ -5552,25 +5552,25 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>48.33</v>
+        <v>47.83</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.5</v>
+        <v>11.17</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.17</v>
+        <v>6.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.33</v>
+        <v>4.67</v>
       </c>
       <c r="BD12" t="n">
         <v>20.83</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BF12" t="n">
         <v>3</v>
@@ -5765,7 +5765,7 @@
         <v>14.84</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.25</v>
+        <v>8.92</v>
       </c>
       <c r="DS12" t="n">
         <v>0.08</v>
@@ -5777,25 +5777,25 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.33</v>
+        <v>52.08</v>
       </c>
       <c r="DW12" t="n">
         <v>0.25</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.84</v>
+        <v>13.17</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.5</v>
+        <v>8.67</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="EA12" t="n">
         <v>21.42</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="EC12" t="n">
         <v>2.75</v>
@@ -5808,10 +5808,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
@@ -5820,82 +5820,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>79.8</v>
+        <v>80.83</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="M13" t="n">
-        <v>54.8</v>
+        <v>51.83</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O13" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="P13" t="n">
-        <v>15.6</v>
+        <v>16</v>
       </c>
       <c r="Q13" t="n">
-        <v>16.6</v>
+        <v>16.33</v>
       </c>
       <c r="R13" t="n">
-        <v>7.8</v>
+        <v>6.33</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>38.8</v>
+        <v>39.17</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.8</v>
+        <v>11.67</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.800000000000001</v>
+        <v>7.67</v>
       </c>
       <c r="AB13" t="n">
         <v>4</v>
       </c>
       <c r="AC13" t="n">
-        <v>21.2</v>
+        <v>21.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5979,70 +5979,70 @@
         <v>2.17</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.73</v>
+        <v>9.42</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.36</v>
+        <v>4.25</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.27</v>
+        <v>5.08</v>
       </c>
       <c r="BR13" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BS13" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT13" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BU13" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BV13" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.17</v>
+        <v>3.22</v>
       </c>
       <c r="CA13" t="n">
         <v>3.29</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CC13" t="n">
         <v>4.28</v>
@@ -6054,49 +6054,49 @@
         <v>1.43</v>
       </c>
       <c r="CF13" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI13" t="n">
         <v>1.82</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CO13" t="n">
         <v>1.34</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="CR13" t="n">
         <v>1.42</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CU13" t="n">
         <v>1.37</v>
@@ -6111,19 +6111,19 @@
         <v>1.52</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.46</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DB13" t="n">
         <v>1.37</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DD13" t="n">
         <v>3.93</v>
@@ -6132,76 +6132,76 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DH13" t="n">
-        <v>78.45</v>
+        <v>79.08</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.63</v>
+        <v>3.42</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM13" t="n">
-        <v>45.09</v>
+        <v>44.42</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.73</v>
+        <v>15</v>
       </c>
       <c r="DQ13" t="n">
-        <v>18.09</v>
+        <v>17.83</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.36</v>
+        <v>9.42</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>42.45</v>
+        <v>42.34</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.36</v>
+        <v>10</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.55</v>
+        <v>7.08</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.18</v>
+        <v>21.5</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="EC13" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="14">
@@ -6256,10 +6256,10 @@
         <v>15.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>16.57</v>
+        <v>16.29</v>
       </c>
       <c r="R14" t="n">
-        <v>6.57</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="S14" t="n">
         <v>1.29</v>
@@ -6277,7 +6277,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>51.86</v>
+        <v>52</v>
       </c>
       <c r="Y14" t="n">
         <v>0.29</v>
@@ -6286,16 +6286,16 @@
         <v>16.29</v>
       </c>
       <c r="AA14" t="n">
-        <v>10.86</v>
+        <v>11</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.43</v>
+        <v>5.29</v>
       </c>
       <c r="AC14" t="n">
         <v>24.43</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AE14" t="n">
         <v>2.43</v>
@@ -6564,10 +6564,10 @@
         <v>14.17</v>
       </c>
       <c r="DQ14" t="n">
-        <v>16.67</v>
+        <v>16.5</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.08</v>
+        <v>10.33</v>
       </c>
       <c r="DS14" t="n">
         <v>0.16</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.17</v>
+        <v>51.25</v>
       </c>
       <c r="DW14" t="n">
         <v>0.34</v>
@@ -6588,10 +6588,10 @@
         <v>13.67</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.67</v>
+        <v>8.75</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="EA14" t="n">
         <v>21.33</v>
@@ -6655,10 +6655,10 @@
         <v>15.86</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.71</v>
+        <v>15.29</v>
       </c>
       <c r="R15" t="n">
-        <v>9.140000000000001</v>
+        <v>10.14</v>
       </c>
       <c r="S15" t="n">
         <v>1.29</v>
@@ -6676,25 +6676,25 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>47.57</v>
+        <v>48</v>
       </c>
       <c r="Y15" t="n">
         <v>0.43</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.710000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.29</v>
+        <v>6.43</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.43</v>
+        <v>3.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.86</v>
+        <v>18</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE15" t="n">
         <v>2.86</v>
@@ -6963,10 +6963,10 @@
         <v>15.17</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.75</v>
+        <v>15.5</v>
       </c>
       <c r="DR15" t="n">
-        <v>9</v>
+        <v>9.58</v>
       </c>
       <c r="DS15" t="n">
         <v>0.08</v>
@@ -6978,25 +6978,25 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>48.75</v>
+        <v>49</v>
       </c>
       <c r="DW15" t="n">
         <v>0.25</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.66</v>
+        <v>10.83</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.25</v>
+        <v>7.33</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.42</v>
+        <v>19.5</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="EC15" t="n">
         <v>2.58</v>
@@ -7054,10 +7054,10 @@
         <v>14.17</v>
       </c>
       <c r="Q16" t="n">
-        <v>15</v>
+        <v>14.67</v>
       </c>
       <c r="R16" t="n">
-        <v>6.33</v>
+        <v>8</v>
       </c>
       <c r="S16" t="n">
         <v>0.67</v>
@@ -7075,25 +7075,25 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>52.83</v>
+        <v>52.67</v>
       </c>
       <c r="Y16" t="n">
         <v>0.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>14.83</v>
+        <v>15.17</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.33</v>
+        <v>6.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.5</v>
+        <v>8.33</v>
       </c>
       <c r="AC16" t="n">
         <v>22.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -7366,10 +7366,10 @@
         <v>14.17</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.34</v>
+        <v>13.17</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.75</v>
+        <v>7.58</v>
       </c>
       <c r="DS16" t="n">
         <v>0.25</v>
@@ -7381,19 +7381,19 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.83</v>
+        <v>51.75</v>
       </c>
       <c r="DW16" t="n">
         <v>0.17</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.66</v>
+        <v>13.84</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.92</v>
+        <v>5.83</v>
       </c>
       <c r="EA16" t="n">
         <v>19.5</v>
@@ -7457,10 +7457,10 @@
         <v>12.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.33</v>
+        <v>12</v>
       </c>
       <c r="R17" t="n">
-        <v>6.83</v>
+        <v>8.67</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -7478,25 +7478,25 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>47.33</v>
+        <v>45.5</v>
       </c>
       <c r="Y17" t="n">
         <v>0.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.67</v>
+        <v>13.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.67</v>
+        <v>9.17</v>
       </c>
       <c r="AB17" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="AC17" t="n">
         <v>21.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE17" t="n">
         <v>2.17</v>
@@ -7769,10 +7769,10 @@
         <v>12.42</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.92</v>
+        <v>10.75</v>
       </c>
       <c r="DR17" t="n">
-        <v>7</v>
+        <v>7.92</v>
       </c>
       <c r="DS17" t="n">
         <v>0.16</v>
@@ -7784,25 +7784,25 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.33</v>
+        <v>46.42</v>
       </c>
       <c r="DW17" t="n">
         <v>0.42</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.75</v>
+        <v>13.08</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.42</v>
+        <v>8.67</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.34</v>
+        <v>4.42</v>
       </c>
       <c r="EA17" t="n">
         <v>22.17</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="EC17" t="n">
         <v>2.5</v>
@@ -7860,10 +7860,10 @@
         <v>14.86</v>
       </c>
       <c r="Q18" t="n">
-        <v>16.86</v>
+        <v>16.14</v>
       </c>
       <c r="R18" t="n">
-        <v>10.71</v>
+        <v>11.71</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -7881,16 +7881,16 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>44.43</v>
+        <v>44.71</v>
       </c>
       <c r="Y18" t="n">
         <v>0.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>9.289999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.57</v>
+        <v>5</v>
       </c>
       <c r="AB18" t="n">
         <v>4.71</v>
@@ -7899,7 +7899,7 @@
         <v>19.57</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="n">
         <v>2.71</v>
@@ -8172,10 +8172,10 @@
         <v>13.42</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.75</v>
+        <v>15.33</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.5</v>
+        <v>10.08</v>
       </c>
       <c r="DS18" t="n">
         <v>0.17</v>
@@ -8187,16 +8187,16 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>44.17</v>
+        <v>44.33</v>
       </c>
       <c r="DW18" t="n">
         <v>0.17</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="DY18" t="n">
-        <v>5.42</v>
+        <v>5.67</v>
       </c>
       <c r="DZ18" t="n">
         <v>4.08</v>
@@ -8205,7 +8205,7 @@
         <v>19.17</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="EC18" t="n">
         <v>2.58</v>
@@ -8263,10 +8263,10 @@
         <v>13.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>13.5</v>
+        <v>13.33</v>
       </c>
       <c r="R19" t="n">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="S19" t="n">
         <v>1.33</v>
@@ -8284,25 +8284,25 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>57.67</v>
+        <v>58</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.17</v>
+        <v>11.33</v>
       </c>
       <c r="AA19" t="n">
         <v>6.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="AC19" t="n">
         <v>19.17</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE19" t="n">
         <v>1.67</v>
@@ -8575,10 +8575,10 @@
         <v>14.75</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.42</v>
+        <v>15.33</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.5</v>
+        <v>6.16</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8590,19 +8590,19 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>56.08</v>
+        <v>56.25</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.08</v>
+        <v>11.16</v>
       </c>
       <c r="DY19" t="n">
         <v>6.66</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.42</v>
+        <v>4.5</v>
       </c>
       <c r="EA19" t="n">
         <v>21.5</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -2314,7 +2314,7 @@
         <v>10</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.29</v>
+        <v>7.71</v>
       </c>
       <c r="AT4" t="n">
         <v>1.14</v>
@@ -2332,25 +2332,25 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>44.71</v>
+        <v>42.71</v>
       </c>
       <c r="AZ4" t="n">
         <v>-0.14</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.71</v>
+        <v>10.86</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.57</v>
+        <v>6.86</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="BD4" t="n">
         <v>21.43</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BF4" t="n">
         <v>2.29</v>
@@ -2545,7 +2545,7 @@
         <v>12.17</v>
       </c>
       <c r="DR4" t="n">
-        <v>6.59</v>
+        <v>7.41</v>
       </c>
       <c r="DS4" t="n">
         <v>0.17</v>
@@ -2557,25 +2557,25 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.83</v>
+        <v>46.66</v>
       </c>
       <c r="DW4" t="n">
         <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.08</v>
+        <v>13.17</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.75</v>
+        <v>8.92</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="EA4" t="n">
         <v>24.67</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="EC4" t="n">
         <v>2.67</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
@@ -3003,49 +3003,49 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="H6" t="n">
-        <v>76.2</v>
+        <v>79.83</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>45.17</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="P6" t="n">
-        <v>10.8</v>
+        <v>12</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.4</v>
+        <v>10.33</v>
       </c>
       <c r="R6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.17</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>48</v>
+        <v>47.83</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>16.6</v>
+        <v>17.17</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,67 +3162,67 @@
         <v>2.12</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.08</v>
+        <v>10.29</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.54</v>
+        <v>3.86</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.54</v>
+        <v>5.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BU6" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.38</v>
+        <v>3.49</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="CB6" t="n">
         <v>3.58</v>
@@ -3234,10 +3234,10 @@
         <v>5.12</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CG6" t="n">
         <v>2.61</v>
@@ -3246,31 +3246,31 @@
         <v>1.28</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.7</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CO6" t="n">
         <v>1.19</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CR6" t="n">
         <v>1.4</v>
@@ -3285,18 +3285,18 @@
         <v>1.39</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CW6" t="n">
         <v>1.88</v>
       </c>
       <c r="CX6" t="inlineStr"/>
       <c r="CY6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CZ6" t="inlineStr"/>
       <c r="DA6" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DB6" t="n">
         <v>1.31</v>
@@ -3311,76 +3311,76 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="DG6" t="n">
         <v>2.08</v>
       </c>
       <c r="DH6" t="n">
-        <v>74.08</v>
+        <v>75.78</v>
       </c>
       <c r="DI6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="DK6" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM6" t="n">
-        <v>42.38</v>
+        <v>42.64</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.77</v>
+        <v>15</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.54</v>
+        <v>13.28</v>
       </c>
       <c r="DR6" t="n">
-        <v>11.46</v>
+        <v>10.57</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>41.54</v>
+        <v>41.93</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.77</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DY6" t="n">
-        <v>5.92</v>
+        <v>5.93</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.85</v>
+        <v>3.93</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.08</v>
+        <v>21</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3435,10 +3435,10 @@
         <v>16.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>17.83</v>
       </c>
       <c r="R7" t="n">
-        <v>6.17</v>
+        <v>7.33</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -3456,25 +3456,25 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>55.5</v>
+        <v>57.83</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.5</v>
+        <v>15.33</v>
       </c>
       <c r="AA7" t="n">
         <v>9.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.83</v>
+        <v>5.67</v>
       </c>
       <c r="AC7" t="n">
         <v>20.17</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AE7" t="n">
         <v>2.67</v>
@@ -3747,10 +3747,10 @@
         <v>14.92</v>
       </c>
       <c r="DQ7" t="n">
-        <v>16.67</v>
+        <v>16.58</v>
       </c>
       <c r="DR7" t="n">
-        <v>8</v>
+        <v>8.58</v>
       </c>
       <c r="DS7" t="n">
         <v>0.16</v>
@@ -3762,25 +3762,25 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.75</v>
+        <v>54.92</v>
       </c>
       <c r="DW7" t="n">
         <v>0.25</v>
       </c>
       <c r="DX7" t="n">
-        <v>14.25</v>
+        <v>14.16</v>
       </c>
       <c r="DY7" t="n">
         <v>9.17</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="EA7" t="n">
         <v>19.34</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="EC7" t="n">
         <v>3.83</v>
@@ -4325,7 +4325,7 @@
         <v>17.33</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.33</v>
+        <v>7.33</v>
       </c>
       <c r="AT9" t="n">
         <v>1.83</v>
@@ -4343,25 +4343,25 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>56.5</v>
+        <v>54.83</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.17</v>
       </c>
       <c r="BA9" t="n">
-        <v>14.83</v>
+        <v>15.67</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.83</v>
+        <v>10.83</v>
       </c>
       <c r="BC9" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.33</v>
+        <v>19.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="BF9" t="n">
         <v>2.83</v>
@@ -4556,7 +4556,7 @@
         <v>16.16</v>
       </c>
       <c r="DR9" t="n">
-        <v>5.83</v>
+        <v>6.33</v>
       </c>
       <c r="DS9" t="n">
         <v>0.25</v>
@@ -4568,25 +4568,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52.16</v>
+        <v>51.33</v>
       </c>
       <c r="DW9" t="n">
         <v>0.17</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.5</v>
+        <v>13.92</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.83</v>
+        <v>9.33</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.66</v>
+        <v>4.58</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.67</v>
+        <v>21.75</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="EC9" t="n">
         <v>2.5</v>
@@ -5853,10 +5853,10 @@
         <v>16</v>
       </c>
       <c r="Q13" t="n">
-        <v>16.33</v>
+        <v>15.83</v>
       </c>
       <c r="R13" t="n">
-        <v>6.33</v>
+        <v>8.33</v>
       </c>
       <c r="S13" t="n">
         <v>1.17</v>
@@ -5874,25 +5874,25 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>39.17</v>
+        <v>40.83</v>
       </c>
       <c r="Y13" t="n">
         <v>0.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>11.67</v>
+        <v>12.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.67</v>
+        <v>8.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="AC13" t="n">
         <v>21.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="n">
         <v>2.17</v>
@@ -6165,10 +6165,10 @@
         <v>15</v>
       </c>
       <c r="DQ13" t="n">
-        <v>17.83</v>
+        <v>17.58</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.42</v>
+        <v>10.42</v>
       </c>
       <c r="DS13" t="n">
         <v>0.08</v>
@@ -6180,25 +6180,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>42.34</v>
+        <v>43.16</v>
       </c>
       <c r="DW13" t="n">
         <v>0.34</v>
       </c>
       <c r="DX13" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.08</v>
+        <v>7.5</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="EA13" t="n">
         <v>21.5</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="EC13" t="n">
         <v>2.17</v>
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
         <v>0.17</v>
@@ -8311,49 +8311,49 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="AI19" t="n">
-        <v>81.17</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.67</v>
+        <v>5.86</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AN19" t="n">
-        <v>49.5</v>
+        <v>54.57</v>
       </c>
       <c r="AO19" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15.83</v>
+        <v>14.71</v>
       </c>
       <c r="AR19" t="n">
-        <v>17.33</v>
+        <v>17.57</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.33</v>
+        <v>7</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8365,82 +8365,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>54.5</v>
+        <v>54.29</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>11</v>
+        <v>11.29</v>
       </c>
       <c r="BB19" t="n">
         <v>7</v>
       </c>
       <c r="BC19" t="n">
-        <v>4</v>
+        <v>4.29</v>
       </c>
       <c r="BD19" t="n">
-        <v>23.83</v>
+        <v>23.43</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="BF19" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.17</v>
+        <v>11.31</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.25</v>
+        <v>5.46</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.92</v>
+        <v>5.85</v>
       </c>
       <c r="BR19" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS19" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU19" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV19" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BY19" t="n">
         <v>2.11</v>
@@ -8449,34 +8449,34 @@
         <v>2.26</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CH19" t="n">
         <v>1.37</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK19" t="n">
         <v>1.41</v>
@@ -8485,10 +8485,10 @@
         <v>1.86</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CO19" t="n">
         <v>1.3</v>
@@ -8497,13 +8497,13 @@
         <v>2</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CR19" t="n">
         <v>1.41</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CT19" t="n">
         <v>2.92</v>
@@ -8512,7 +8512,7 @@
         <v>1.38</v>
       </c>
       <c r="CV19" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CW19" t="n">
         <v>1.84</v>
@@ -8521,64 +8521,64 @@
         <v>1.55</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.42</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DB19" t="n">
         <v>1.34</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="DE19" t="n">
         <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="DG19" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="DH19" t="n">
-        <v>83.25</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="DK19" t="n">
-        <v>6.17</v>
+        <v>6.23</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM19" t="n">
-        <v>56.16</v>
+        <v>58.38</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.75</v>
+        <v>14.23</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.33</v>
+        <v>15.61</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.16</v>
+        <v>5.62</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8590,28 +8590,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>56.25</v>
+        <v>56</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.16</v>
+        <v>11.31</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.66</v>
+        <v>6.69</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.5</v>
+        <v>4.62</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.5</v>
+        <v>21.46</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,139 +1469,139 @@
         <v>2.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG2" t="n">
         <v>2</v>
       </c>
       <c r="AH2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>47.14</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>49.14</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BN2" t="n">
         <v>2</v>
       </c>
-      <c r="AI2" t="n">
-        <v>75.33</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>46.67</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>48.83</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>20.67</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>2.17</v>
-      </c>
       <c r="BO2" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.67</v>
+        <v>4.92</v>
       </c>
       <c r="BR2" t="n">
-        <v>91.67</v>
+        <v>84.62</v>
       </c>
       <c r="BS2" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BT2" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU2" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BV2" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX2" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BY2" t="n">
         <v>2.04</v>
@@ -1610,37 +1610,37 @@
         <v>2.03</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CH2" t="n">
         <v>1.33</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.91</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CL2" t="n">
         <v>1.81</v>
@@ -1658,13 +1658,13 @@
         <v>2.13</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="CR2" t="n">
         <v>1.47</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CT2" t="n">
         <v>2.7</v>
@@ -1682,22 +1682,22 @@
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.51</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="DB2" t="n">
         <v>1.41</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.21</v>
+        <v>4.22</v>
       </c>
       <c r="DE2" t="n">
         <v>0.16</v>
@@ -1706,40 +1706,40 @@
         <v>1.92</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="DH2" t="n">
-        <v>78.33</v>
+        <v>77.92</v>
       </c>
       <c r="DI2" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.34</v>
+        <v>5.31</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.67</v>
+        <v>51.54</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.66</v>
+        <v>14.54</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.58</v>
+        <v>12.39</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.17</v>
+        <v>5.62</v>
       </c>
       <c r="DS2" t="n">
         <v>0.08</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.42</v>
+        <v>50.46</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.42</v>
+        <v>15.15</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.42</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>6</v>
+        <v>5.77</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.33</v>
+        <v>22.93</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>3.29</v>
       </c>
       <c r="H3" t="n">
-        <v>98.83</v>
+        <v>94.86</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="J3" t="n">
-        <v>3.17</v>
+        <v>2.71</v>
       </c>
       <c r="K3" t="n">
-        <v>9.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="M3" t="n">
-        <v>75.5</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="O3" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="P3" t="n">
-        <v>14.17</v>
+        <v>14.29</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.83</v>
+        <v>14.29</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>5.86</v>
       </c>
       <c r="S3" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="T3" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>58.83</v>
+        <v>58.14</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>19.5</v>
+        <v>19.43</v>
       </c>
       <c r="AA3" t="n">
-        <v>13.67</v>
+        <v>13.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.83</v>
+        <v>6.29</v>
       </c>
       <c r="AC3" t="n">
-        <v>24.5</v>
+        <v>23.57</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="AF3" t="n">
         <v>0.17</v>
@@ -1953,37 +1953,37 @@
         <v>2.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.75</v>
+        <v>11.92</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BL3" t="n">
         <v>0.92</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.92</v>
+        <v>4.46</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.17</v>
+        <v>4.69</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,31 +1992,31 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV3" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW3" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX3" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.47</v>
+        <v>3.51</v>
       </c>
       <c r="CC3" t="n">
         <v>2.91</v>
@@ -2025,10 +2025,10 @@
         <v>3.39</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CG3" t="n">
         <v>2.85</v>
@@ -2037,28 +2037,28 @@
         <v>1.39</v>
       </c>
       <c r="CI3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CQ3" t="n">
         <v>3.18</v>
@@ -2067,16 +2067,16 @@
         <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CW3" t="n">
         <v>1.78</v>
@@ -2085,13 +2085,13 @@
         <v>1.56</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="DB3" t="n">
         <v>1.3</v>
@@ -2100,49 +2100,49 @@
         <v>1.98</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="DE3" t="n">
         <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.17</v>
+        <v>2.85</v>
       </c>
       <c r="DH3" t="n">
-        <v>85</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.08</v>
+        <v>2.84</v>
       </c>
       <c r="DK3" t="n">
-        <v>7.08</v>
+        <v>7.15</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="DM3" t="n">
-        <v>59</v>
+        <v>59.31</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.92</v>
+        <v>2.61</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.42</v>
+        <v>14.47</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.25</v>
+        <v>14.47</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.17</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS3" t="n">
         <v>0.08</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50.42</v>
+        <v>50.69</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.08</v>
+        <v>15.39</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.17</v>
+        <v>10.15</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.92</v>
+        <v>5.23</v>
       </c>
       <c r="EA3" t="n">
-        <v>23.5</v>
+        <v>23.08</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="H4" t="n">
-        <v>85.2</v>
+        <v>83.33</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="K4" t="n">
-        <v>7.2</v>
+        <v>7.17</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="M4" t="n">
-        <v>67</v>
+        <v>65.17</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="P4" t="n">
-        <v>17.2</v>
+        <v>15.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.2</v>
+        <v>14.83</v>
       </c>
       <c r="R4" t="n">
-        <v>7</v>
+        <v>5.67</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>52.2</v>
+        <v>51.67</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.4</v>
+        <v>16.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.8</v>
+        <v>11.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>29.2</v>
+        <v>27.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="AF4" t="n">
         <v>0.14</v>
@@ -2356,70 +2356,70 @@
         <v>2.29</v>
       </c>
       <c r="BG4" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.08</v>
+        <v>10.23</v>
       </c>
       <c r="BI4" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.75</v>
+        <v>4.69</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="BR4" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BT4" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BU4" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV4" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.37</v>
+        <v>2.61</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.51</v>
+        <v>2.69</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CC4" t="n">
         <v>3.44</v>
@@ -2428,55 +2428,55 @@
         <v>4.25</v>
       </c>
       <c r="CE4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CK4" t="n">
         <v>1.33</v>
       </c>
-      <c r="CF4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>1.32</v>
-      </c>
       <c r="CL4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.43</v>
+        <v>3.48</v>
       </c>
       <c r="CR4" t="n">
         <v>1.46</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CV4" t="n">
         <v>1.89</v>
@@ -2488,97 +2488,97 @@
         <v>1.51</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.52</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.06</v>
+        <v>4.09</v>
       </c>
       <c r="DE4" t="n">
         <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DG4" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="DH4" t="n">
-        <v>72.33</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.09</v>
+        <v>6.16</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DM4" t="n">
-        <v>49.42</v>
+        <v>49.93</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="DP4" t="n">
-        <v>16.25</v>
+        <v>15.69</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.17</v>
+        <v>12.23</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.41</v>
+        <v>6.77</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.66</v>
+        <v>46.85</v>
       </c>
       <c r="DW4" t="n">
         <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.17</v>
+        <v>13.31</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.92</v>
+        <v>9.15</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="EA4" t="n">
-        <v>24.67</v>
+        <v>24.23</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5">
@@ -2588,25 +2588,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F5" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="G5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="H5" t="n">
-        <v>96.56999999999999</v>
+        <v>96.38</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2615,34 +2615,34 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.14</v>
+        <v>4.38</v>
       </c>
       <c r="L5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>63.71</v>
+        <v>65.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="P5" t="n">
-        <v>15.29</v>
+        <v>14.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.57</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
-        <v>5.29</v>
+        <v>4.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58.29</v>
+        <v>58.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.29</v>
+        <v>15.62</v>
       </c>
       <c r="AA5" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.29</v>
+        <v>5.75</v>
       </c>
       <c r="AC5" t="n">
         <v>24</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AF5" t="n">
         <v>0.17</v>
@@ -2762,46 +2762,46 @@
         <v>2</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.77</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI5" t="n">
         <v>2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BU5" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2810,19 +2810,19 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CA5" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CC5" t="n">
         <v>2.18</v>
@@ -2831,31 +2831,31 @@
         <v>2.84</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CN5" t="n">
         <v>1.89</v>
@@ -2864,10 +2864,10 @@
         <v>1.21</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CR5" t="n">
         <v>1.42</v>
@@ -2876,7 +2876,7 @@
         <v>3.09</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CU5" t="n">
         <v>1.37</v>
@@ -2885,19 +2885,19 @@
         <v>1.94</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="DB5" t="n">
         <v>1.35</v>
@@ -2909,79 +2909,79 @@
         <v>3.76</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.08</v>
+        <v>88.58</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.85</v>
+        <v>4.93</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DM5" t="n">
-        <v>56.46</v>
+        <v>57.86</v>
       </c>
       <c r="DN5" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.62</v>
+        <v>15.21</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.62</v>
+        <v>14.86</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.85</v>
+        <v>5.36</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.93</v>
+        <v>56.22</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.93</v>
+        <v>15.14</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.92</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5</v>
+        <v>5.29</v>
       </c>
       <c r="EA5" t="n">
-        <v>25.77</v>
+        <v>25.64</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="EC5" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="6">
@@ -3219,7 +3219,7 @@
         <v>2.94</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.49</v>
+        <v>3.46</v>
       </c>
       <c r="CA6" t="n">
         <v>3.46</v>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
@@ -4208,82 +4208,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="G9" t="n">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="H9" t="n">
-        <v>95.5</v>
+        <v>101.43</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="K9" t="n">
-        <v>4.83</v>
+        <v>5.14</v>
       </c>
       <c r="L9" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="M9" t="n">
-        <v>62</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="P9" t="n">
-        <v>16.5</v>
+        <v>15.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>16.29</v>
       </c>
       <c r="R9" t="n">
-        <v>5.33</v>
+        <v>4.43</v>
       </c>
       <c r="S9" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="U9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>47.83</v>
+        <v>48.14</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.17</v>
+        <v>12.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.83</v>
+        <v>8</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.33</v>
+        <v>4.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>24</v>
+        <v>23.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4367,49 +4367,49 @@
         <v>2.83</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.75</v>
+        <v>9.92</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL9" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BO9" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.5</v>
+        <v>4.69</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT9" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU9" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4418,19 +4418,19 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY9" t="n">
         <v>2.15</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CA9" t="n">
         <v>3.04</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="CC9" t="n">
         <v>2.93</v>
@@ -4442,16 +4442,16 @@
         <v>1.42</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CH9" t="n">
         <v>1.34</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.8</v>
@@ -4460,13 +4460,13 @@
         <v>1.41</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO9" t="n">
         <v>1.31</v>
@@ -4475,13 +4475,13 @@
         <v>2.06</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="CR9" t="n">
         <v>1.42</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CT9" t="n">
         <v>2.88</v>
@@ -4490,106 +4490,106 @@
         <v>1.37</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX9" t="n">
         <v>1.5</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.54</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="DB9" t="n">
         <v>1.34</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="DH9" t="n">
-        <v>90.34</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM9" t="n">
-        <v>59.42</v>
+        <v>61</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DP9" t="n">
-        <v>15.42</v>
+        <v>15</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.16</v>
+        <v>16.77</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.33</v>
+        <v>5.77</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.33</v>
+        <v>51.23</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.92</v>
+        <v>13.77</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.33</v>
+        <v>9.31</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.58</v>
+        <v>4.46</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.75</v>
+        <v>21.69</v>
       </c>
       <c r="EB9" t="n">
         <v>1.62</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="10">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
@@ -4611,82 +4611,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="G10" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="H10" t="n">
+        <v>75.14</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>53.29</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P10" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>57.86</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="AB10" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="n">
-        <v>76.17</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M10" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>59.33</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.67</v>
-      </c>
       <c r="AC10" t="n">
-        <v>19.83</v>
+        <v>19.57</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="AF10" t="n">
         <v>0.29</v>
@@ -4770,49 +4770,49 @@
         <v>2.71</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.08</v>
+        <v>10.14</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.15</v>
+        <v>3.79</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.46</v>
+        <v>4.07</v>
       </c>
       <c r="BR10" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS10" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BU10" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4821,19 +4821,19 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="CC10" t="n">
         <v>2.65</v>
@@ -4848,34 +4848,34 @@
         <v>3</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CH10" t="n">
         <v>1.34</v>
       </c>
       <c r="CI10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CJ10" t="n">
         <v>1.88</v>
       </c>
-      <c r="CJ10" t="n">
-        <v>1.86</v>
-      </c>
       <c r="CK10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CO10" t="n">
         <v>1.36</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CQ10" t="n">
         <v>3.74</v>
@@ -4893,10 +4893,10 @@
         <v>1.35</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CX10" t="n">
         <v>1.51</v>
@@ -4914,85 +4914,85 @@
         <v>1.37</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF10" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="DH10" t="n">
-        <v>81.39</v>
+        <v>80.5</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="DM10" t="n">
-        <v>54.54</v>
+        <v>53.43</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.08</v>
+        <v>13.57</v>
       </c>
       <c r="DQ10" t="n">
-        <v>15</v>
+        <v>14.86</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.23</v>
+        <v>7.57</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54</v>
+        <v>53.64</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.15</v>
+        <v>13.07</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.69</v>
+        <v>9.5</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.46</v>
+        <v>3.57</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.38</v>
+        <v>19.28</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="11">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
@@ -5014,82 +5014,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="H11" t="n">
-        <v>94.70999999999999</v>
+        <v>97</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="K11" t="n">
-        <v>4.43</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="M11" t="n">
-        <v>48.14</v>
+        <v>53.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="O11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE11" t="n">
         <v>2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>16</v>
-      </c>
-      <c r="R11" t="n">
-        <v>9</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>49</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>12.86</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>21.86</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5173,67 +5173,67 @@
         <v>4.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.460000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BN11" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.23</v>
+        <v>4.14</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.23</v>
+        <v>5.29</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BV11" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BX11" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CB11" t="n">
         <v>3.14</v>
@@ -5245,34 +5245,34 @@
         <v>3.36</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CH11" t="n">
         <v>1.33</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO11" t="n">
         <v>1.34</v>
@@ -5281,7 +5281,7 @@
         <v>2.12</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CR11" t="n">
         <v>1.45</v>
@@ -5305,13 +5305,13 @@
         <v>1.51</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.5</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB11" t="n">
         <v>1.37</v>
@@ -5320,49 +5320,49 @@
         <v>2.21</v>
       </c>
       <c r="DD11" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="DH11" t="n">
-        <v>87.38</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.31</v>
+        <v>3.43</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.08</v>
+        <v>4.43</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.61</v>
+        <v>48.07</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.69</v>
+        <v>13.71</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.84</v>
+        <v>16.93</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.77</v>
+        <v>7.14</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.31</v>
+        <v>48.86</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.54</v>
+        <v>12.22</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.69</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.85</v>
+        <v>4.07</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.62</v>
+        <v>21.57</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.92</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="12">
@@ -5405,61 +5405,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="F12" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>3.29</v>
       </c>
       <c r="H12" t="n">
-        <v>83.5</v>
+        <v>81.86</v>
       </c>
       <c r="I12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="K12" t="n">
-        <v>7.5</v>
+        <v>7.29</v>
       </c>
       <c r="L12" t="n">
-        <v>0.83</v>
+        <v>0.57</v>
       </c>
       <c r="M12" t="n">
-        <v>59.33</v>
+        <v>57.57</v>
       </c>
       <c r="N12" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>2.86</v>
       </c>
       <c r="P12" t="n">
-        <v>15.67</v>
+        <v>16.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.5</v>
+        <v>14.29</v>
       </c>
       <c r="R12" t="n">
-        <v>6.67</v>
+        <v>5.57</v>
       </c>
       <c r="S12" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5471,28 +5471,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>56.33</v>
+        <v>55.14</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.17</v>
+        <v>14.43</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.83</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.33</v>
+        <v>4.71</v>
       </c>
       <c r="AC12" t="n">
-        <v>22</v>
+        <v>21.57</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5576,70 +5576,70 @@
         <v>3</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.25</v>
+        <v>10.08</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.5</v>
+        <v>4.08</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.83</v>
+        <v>4.38</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS12" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT12" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU12" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BV12" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="CA12" t="n">
         <v>3.17</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CC12" t="n">
         <v>3.29</v>
@@ -5648,34 +5648,34 @@
         <v>3.62</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF12" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CH12" t="n">
         <v>1.34</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CL12" t="n">
         <v>1.72</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="CO12" t="n">
         <v>1.34</v>
@@ -5684,22 +5684,22 @@
         <v>2.13</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="CR12" t="n">
         <v>1.44</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CW12" t="n">
         <v>1.9</v>
@@ -5708,64 +5708,64 @@
         <v>1.49</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.56</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="DB12" t="n">
         <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="DH12" t="n">
-        <v>80.67</v>
+        <v>80</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="DK12" t="n">
         <v>6.08</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="DM12" t="n">
-        <v>52.42</v>
+        <v>52</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.58</v>
+        <v>2.31</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.42</v>
+        <v>15.08</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.84</v>
+        <v>14.7</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.92</v>
+        <v>8.15</v>
       </c>
       <c r="DS12" t="n">
         <v>0.08</v>
@@ -5777,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.08</v>
+        <v>51.77</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.17</v>
+        <v>12.93</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.67</v>
+        <v>8.23</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.5</v>
+        <v>4.69</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.42</v>
+        <v>21.23</v>
       </c>
       <c r="EB12" t="n">
         <v>1.52</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="13">
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5901,49 +5901,49 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AI13" t="n">
-        <v>77.33</v>
+        <v>77</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.33</v>
+        <v>3.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="AN13" t="n">
-        <v>37</v>
+        <v>38.14</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>13.71</v>
       </c>
       <c r="AR13" t="n">
-        <v>19.33</v>
+        <v>17.86</v>
       </c>
       <c r="AS13" t="n">
-        <v>12.5</v>
+        <v>10.57</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5955,82 +5955,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>45.5</v>
+        <v>46.29</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.5</v>
+        <v>6.14</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="BD13" t="n">
-        <v>21.17</v>
+        <v>22.86</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.42</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BJ13" t="n">
         <v>0.92</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BO13" t="n">
         <v>1.08</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.25</v>
+        <v>3.85</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.08</v>
+        <v>4.62</v>
       </c>
       <c r="BR13" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT13" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV13" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY13" t="n">
         <v>2.88</v>
@@ -6039,31 +6039,31 @@
         <v>3.22</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.28</v>
+        <v>4.48</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.03</v>
+        <v>5.19</v>
       </c>
       <c r="CE13" t="n">
         <v>1.43</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.91</v>
@@ -6072,10 +6072,10 @@
         <v>1.39</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CN13" t="n">
         <v>2.04</v>
@@ -6084,7 +6084,7 @@
         <v>1.34</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CQ13" t="n">
         <v>3.7</v>
@@ -6102,10 +6102,10 @@
         <v>1.37</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CX13" t="n">
         <v>1.52</v>
@@ -6126,49 +6126,49 @@
         <v>2.17</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="DH13" t="n">
-        <v>79.08</v>
+        <v>78.77</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.42</v>
+        <v>3.61</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="DM13" t="n">
-        <v>44.42</v>
+        <v>44.46</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="DP13" t="n">
-        <v>15</v>
+        <v>14.77</v>
       </c>
       <c r="DQ13" t="n">
-        <v>17.58</v>
+        <v>16.92</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.42</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DS13" t="n">
         <v>0.08</v>
@@ -6180,28 +6180,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>43.16</v>
+        <v>43.77</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.33</v>
+        <v>10</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.5</v>
+        <v>7.23</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.5</v>
+        <v>22.38</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="14">
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>0.29</v>
@@ -6301,139 +6301,139 @@
         <v>2.43</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AI14" t="n">
-        <v>69</v>
+        <v>69.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>4.2</v>
+        <v>3.67</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="AN14" t="n">
-        <v>34</v>
+        <v>33.67</v>
       </c>
       <c r="AO14" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>16.8</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
-        <v>12.6</v>
+        <v>10.33</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>50.2</v>
+        <v>50.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.6</v>
+        <v>5.33</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="BD14" t="n">
-        <v>17</v>
+        <v>17.17</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.67</v>
+        <v>11.38</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BL14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM14" t="n">
         <v>0.92</v>
       </c>
-      <c r="BM14" t="n">
-        <v>0.83</v>
-      </c>
       <c r="BN14" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="BO14" t="n">
         <v>1.08</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.33</v>
+        <v>3.92</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.67</v>
+        <v>5.15</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU14" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV14" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BY14" t="n">
         <v>2.75</v>
@@ -6442,22 +6442,22 @@
         <v>2.94</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CE14" t="n">
         <v>1.38</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CG14" t="n">
         <v>2.81</v>
@@ -6475,44 +6475,44 @@
         <v>1.23</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="CN14" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="CO14" t="n">
         <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CR14" t="n">
         <v>1.39</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CU14" t="n">
         <v>1.4</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
@@ -6525,16 +6525,16 @@
         <v>2</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DG14" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="DH14" t="n">
         <v>71.92</v>
@@ -6543,64 +6543,64 @@
         <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.42</v>
+        <v>3.23</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="DM14" t="n">
-        <v>44.83</v>
+        <v>43.85</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.17</v>
+        <v>13.85</v>
       </c>
       <c r="DQ14" t="n">
-        <v>16.5</v>
+        <v>17.08</v>
       </c>
       <c r="DR14" t="n">
-        <v>10.33</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.25</v>
+        <v>51.31</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.67</v>
+        <v>13.23</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.75</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.33</v>
+        <v>21.08</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="15">
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6703,136 +6703,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>68.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AL15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AN15" t="n">
-        <v>48.8</v>
+        <v>46.17</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14.2</v>
+        <v>14.17</v>
       </c>
       <c r="AR15" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.800000000000001</v>
+        <v>7.17</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.6</v>
+        <v>1.17</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>50.4</v>
+        <v>49.33</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>12</v>
+        <v>11.33</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.4</v>
+        <v>3.83</v>
       </c>
       <c r="BD15" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.25</v>
+        <v>2.54</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.08</v>
+        <v>10</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.25</v>
+        <v>2.54</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN15" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="BR15" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS15" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BT15" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU15" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV15" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BX15" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BY15" t="n">
         <v>2.48</v>
@@ -6844,19 +6844,19 @@
         <v>3.04</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.64</v>
+        <v>3.53</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.2</v>
+        <v>4.11</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="CG15" t="n">
         <v>2.49</v>
@@ -6868,28 +6868,28 @@
         <v>1.76</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="CR15" t="n">
         <v>1.4</v>
@@ -6911,20 +6911,20 @@
       </c>
       <c r="CX15" t="inlineStr"/>
       <c r="CY15" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CZ15" t="inlineStr"/>
       <c r="DA15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="DB15" t="n">
         <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
@@ -6933,73 +6933,73 @@
         <v>2</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="DH15" t="n">
-        <v>67.17</v>
+        <v>67.23</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="DM15" t="n">
-        <v>40.08</v>
+        <v>39.54</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.17</v>
+        <v>15.08</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.5</v>
+        <v>15.62</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.58</v>
+        <v>8.77</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>49</v>
+        <v>48.61</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.83</v>
+        <v>10.61</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.33</v>
+        <v>6.92</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.5</v>
+        <v>19.62</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="16">
@@ -7009,13 +7009,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7102,136 +7102,136 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="AI16" t="n">
-        <v>94.5</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.17</v>
+        <v>2.71</v>
       </c>
       <c r="AL16" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AN16" t="n">
-        <v>54.5</v>
+        <v>51.86</v>
       </c>
       <c r="AO16" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ16" t="n">
-        <v>14.17</v>
+        <v>14.71</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.67</v>
+        <v>11.71</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.17</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>50.83</v>
+        <v>50.71</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA16" t="n">
-        <v>12.5</v>
+        <v>11.57</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.17</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.67</v>
+        <v>18.43</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="BF16" t="n">
-        <v>2</v>
+        <v>2.57</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.42</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.17</v>
+        <v>4.23</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.08</v>
+        <v>3.38</v>
       </c>
       <c r="BR16" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS16" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU16" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV16" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BY16" t="n">
         <v>2.35</v>
@@ -7243,19 +7243,19 @@
         <v>3.19</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CE16" t="n">
         <v>1.41</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG16" t="n">
         <v>2.69</v>
@@ -7264,22 +7264,22 @@
         <v>1.35</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CL16" t="n">
         <v>1.83</v>
       </c>
-      <c r="CK16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>1.82</v>
-      </c>
       <c r="CM16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CO16" t="n">
         <v>1.32</v>
@@ -7288,121 +7288,121 @@
         <v>2.04</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CR16" t="n">
         <v>1.42</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CU16" t="n">
         <v>1.37</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CW16" t="n">
         <v>1.85</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="DA16" t="n">
         <v>1.92</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="DH16" t="n">
-        <v>86.08</v>
+        <v>86.23</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM16" t="n">
-        <v>52.25</v>
+        <v>51</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.17</v>
+        <v>14.46</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.17</v>
+        <v>13.08</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.58</v>
+        <v>6.92</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.75</v>
+        <v>51.61</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.84</v>
+        <v>13.23</v>
       </c>
       <c r="DY16" t="n">
-        <v>8</v>
+        <v>7.62</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.83</v>
+        <v>5.62</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.5</v>
+        <v>20.23</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="17">
@@ -7412,13 +7412,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7502,139 +7502,139 @@
         <v>2.17</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.83</v>
+        <v>3.57</v>
       </c>
       <c r="AI17" t="n">
-        <v>89.5</v>
+        <v>87.14</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="AL17" t="n">
-        <v>6.17</v>
+        <v>5.57</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>60.83</v>
+        <v>56.43</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.33</v>
+        <v>12.57</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.17</v>
+        <v>6</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>47.33</v>
+        <v>46.29</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BA17" t="n">
-        <v>12.83</v>
+        <v>11.71</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.17</v>
+        <v>7.57</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.67</v>
+        <v>4.14</v>
       </c>
       <c r="BD17" t="n">
-        <v>23</v>
+        <v>22.29</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.75</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="BR17" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS17" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BT17" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU17" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV17" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX17" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BY17" t="n">
         <v>1.67</v>
@@ -7643,16 +7643,16 @@
         <v>1.98</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CB17" t="n">
         <v>3.46</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="CE17" t="n">
         <v>1.41</v>
@@ -7667,31 +7667,31 @@
         <v>1.35</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO17" t="n">
         <v>1.33</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CR17" t="n">
         <v>1.42</v>
@@ -7703,7 +7703,7 @@
         <v>2.88</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV17" t="n">
         <v>1.96</v>
@@ -7712,22 +7712,22 @@
         <v>1.89</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.37</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="DB17" t="n">
         <v>1.35</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD17" t="n">
         <v>3.77</v>
@@ -7736,43 +7736,43 @@
         <v>0.08</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="DH17" t="n">
-        <v>85.58</v>
+        <v>84.62</v>
       </c>
       <c r="DI17" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.58</v>
+        <v>5.31</v>
       </c>
       <c r="DL17" t="n">
         <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>54.75</v>
+        <v>52.85</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.42</v>
+        <v>12.54</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.75</v>
+        <v>10.92</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.92</v>
+        <v>7.23</v>
       </c>
       <c r="DS17" t="n">
         <v>0.16</v>
@@ -7784,28 +7784,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>46.42</v>
+        <v>45.93</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.08</v>
+        <v>12.46</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.67</v>
+        <v>8.31</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.42</v>
+        <v>4.15</v>
       </c>
       <c r="EA17" t="n">
-        <v>22.17</v>
+        <v>21.85</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="18">
@@ -7815,13 +7815,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
         <v>0.14</v>
@@ -7908,49 +7908,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>71.2</v>
+        <v>69.17</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AL18" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="AN18" t="n">
-        <v>45</v>
+        <v>44.67</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="AP18" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.4</v>
+        <v>11.67</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.2</v>
+        <v>14.83</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.8</v>
+        <v>6.33</v>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7962,82 +7962,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>43.8</v>
+        <v>44.17</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.6</v>
+        <v>6.83</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="BD18" t="n">
-        <v>18.6</v>
+        <v>18.83</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BG18" t="n">
         <v>2</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.42</v>
+        <v>9.77</v>
       </c>
       <c r="BI18" t="n">
         <v>2</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BP18" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.25</v>
+        <v>3.85</v>
       </c>
       <c r="BR18" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS18" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BT18" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BU18" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV18" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY18" t="n">
         <v>3.14</v>
@@ -8046,22 +8046,22 @@
         <v>3.51</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.78</v>
+        <v>4.82</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.12</v>
+        <v>5.22</v>
       </c>
       <c r="CE18" t="n">
         <v>1.36</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CG18" t="n">
         <v>2.91</v>
@@ -8070,7 +8070,7 @@
         <v>1.4</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.76</v>
@@ -8079,37 +8079,37 @@
         <v>1.32</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP18" t="n">
         <v>1.92</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CR18" t="n">
         <v>1.39</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CU18" t="n">
         <v>1.4</v>
       </c>
       <c r="CV18" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW18" t="n">
         <v>1.85</v>
@@ -8118,97 +8118,97 @@
         <v>1.48</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.58</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="DB18" t="n">
         <v>1.31</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="DE18" t="n">
         <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="DH18" t="n">
-        <v>74.5</v>
+        <v>73.31</v>
       </c>
       <c r="DI18" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.59</v>
+        <v>3.77</v>
       </c>
       <c r="DL18" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="DM18" t="n">
-        <v>45.83</v>
+        <v>45.62</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
       <c r="DP18" t="n">
-        <v>13.42</v>
+        <v>13.39</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.33</v>
+        <v>15.54</v>
       </c>
       <c r="DR18" t="n">
-        <v>10.08</v>
+        <v>9.23</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>44.33</v>
+        <v>44.46</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.75</v>
+        <v>9.69</v>
       </c>
       <c r="DY18" t="n">
-        <v>5.67</v>
+        <v>5.84</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.08</v>
+        <v>3.84</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.17</v>
+        <v>19.23</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="19">
@@ -8458,7 +8458,7 @@
         <v>2.22</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CE19" t="n">
         <v>1.4</v>
@@ -8503,7 +8503,7 @@
         <v>1.41</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CT19" t="n">
         <v>2.92</v>
@@ -8512,7 +8512,7 @@
         <v>1.38</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CW19" t="n">
         <v>1.84</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1827,10 +1827,10 @@
         <v>14.29</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.29</v>
+        <v>13.71</v>
       </c>
       <c r="R3" t="n">
-        <v>5.86</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
         <v>1.57</v>
@@ -1848,25 +1848,25 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>58.14</v>
+        <v>57.43</v>
       </c>
       <c r="Y3" t="n">
         <v>0.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>19.43</v>
+        <v>20.14</v>
       </c>
       <c r="AA3" t="n">
-        <v>13.14</v>
+        <v>14.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.29</v>
+        <v>6</v>
       </c>
       <c r="AC3" t="n">
         <v>23.57</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AE3" t="n">
         <v>2.57</v>
@@ -1956,7 +1956,7 @@
         <v>3.15</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.92</v>
+        <v>12</v>
       </c>
       <c r="BI3" t="n">
         <v>3.15</v>
@@ -2139,10 +2139,10 @@
         <v>14.47</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.47</v>
+        <v>14.15</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.380000000000001</v>
+        <v>9</v>
       </c>
       <c r="DS3" t="n">
         <v>0.08</v>
@@ -2154,25 +2154,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50.69</v>
+        <v>50.31</v>
       </c>
       <c r="DW3" t="n">
         <v>0.23</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.39</v>
+        <v>15.77</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.15</v>
+        <v>10.69</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.23</v>
+        <v>5.08</v>
       </c>
       <c r="EA3" t="n">
         <v>23.08</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="EC3" t="n">
         <v>2.54</v>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>3.83</v>
@@ -2209,7 +2209,7 @@
         <v>0.33</v>
       </c>
       <c r="J4" t="n">
-        <v>3.67</v>
+        <v>3.83</v>
       </c>
       <c r="K4" t="n">
         <v>7.17</v>
@@ -2272,7 +2272,7 @@
         <v>1.79</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.17</v>
+        <v>3.33</v>
       </c>
       <c r="AF4" t="n">
         <v>0.14</v>
@@ -2509,7 +2509,7 @@
         <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="DG4" t="n">
         <v>2.15</v>
@@ -2521,7 +2521,7 @@
         <v>0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="DK4" t="n">
         <v>6.16</v>
@@ -2578,7 +2578,7 @@
         <v>1.52</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="5">
@@ -3036,10 +3036,10 @@
         <v>12</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.33</v>
+        <v>10.17</v>
       </c>
       <c r="R6" t="n">
-        <v>7.17</v>
+        <v>9</v>
       </c>
       <c r="S6" t="n">
         <v>0.5</v>
@@ -3057,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>47.83</v>
+        <v>46.5</v>
       </c>
       <c r="Y6" t="n">
         <v>-0.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.17</v>
+        <v>9.83</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.67</v>
+        <v>6.33</v>
       </c>
       <c r="AB6" t="n">
         <v>3.5</v>
@@ -3075,7 +3075,7 @@
         <v>17.17</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
         <v>1.83</v>
@@ -3344,10 +3344,10 @@
         <v>15</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.28</v>
+        <v>13.22</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.57</v>
+        <v>11.35</v>
       </c>
       <c r="DS6" t="n">
         <v>0.22</v>
@@ -3359,16 +3359,16 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>41.93</v>
+        <v>41.36</v>
       </c>
       <c r="DW6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.859999999999999</v>
+        <v>10.14</v>
       </c>
       <c r="DY6" t="n">
-        <v>5.93</v>
+        <v>6.21</v>
       </c>
       <c r="DZ6" t="n">
         <v>3.93</v>
@@ -3377,7 +3377,7 @@
         <v>21</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="EC6" t="n">
         <v>2</v>
@@ -3390,13 +3390,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3483,127 +3483,127 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AI7" t="n">
-        <v>76.5</v>
+        <v>80.86</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>5.5</v>
+        <v>5.43</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.33</v>
+        <v>4.14</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AN7" t="n">
-        <v>46.33</v>
+        <v>49</v>
       </c>
       <c r="AO7" t="n">
         <v>2</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.33</v>
+        <v>12.86</v>
       </c>
       <c r="AR7" t="n">
-        <v>15.33</v>
+        <v>16.14</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.83</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AT7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AU7" t="n">
         <v>1</v>
       </c>
-      <c r="AU7" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AV7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>52</v>
+        <v>53.57</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BA7" t="n">
         <v>13</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.33</v>
+        <v>4.29</v>
       </c>
       <c r="BD7" t="n">
-        <v>18.5</v>
+        <v>20.86</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="BF7" t="n">
         <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.08</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL7" t="n">
         <v>0.92</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.83</v>
+        <v>3.69</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.5</v>
+        <v>4.31</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT7" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU7" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3612,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BY7" t="n">
         <v>1.71</v>
@@ -3621,28 +3621,28 @@
         <v>1.79</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.46</v>
+        <v>3.42</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="CE7" t="n">
         <v>1.38</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI7" t="n">
         <v>1.94</v>
@@ -3654,37 +3654,37 @@
         <v>1.36</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CM7" t="n">
         <v>2.8</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP7" t="n">
         <v>1.92</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CW7" t="n">
         <v>1.84</v>
@@ -3699,58 +3699,58 @@
         <v>2.56</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC7" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DH7" t="n">
-        <v>79.83</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="DI7" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>4.08</v>
+        <v>4.16</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.42</v>
+        <v>4.31</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.16</v>
+        <v>53.15</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.92</v>
+        <v>14.54</v>
       </c>
       <c r="DQ7" t="n">
-        <v>16.58</v>
+        <v>16.92</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.58</v>
+        <v>7.85</v>
       </c>
       <c r="DS7" t="n">
         <v>0.16</v>
@@ -3762,28 +3762,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.92</v>
+        <v>55.54</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX7" t="n">
-        <v>14.16</v>
+        <v>14.08</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.17</v>
+        <v>9.15</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.34</v>
+        <v>20.54</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.83</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="8">
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -3808,10 +3808,10 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="H8" t="n">
-        <v>98.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3820,34 +3820,34 @@
         <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="M8" t="n">
-        <v>68</v>
+        <v>62.17</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>14.2</v>
+        <v>15.17</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.2</v>
+        <v>11.83</v>
       </c>
       <c r="R8" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3859,28 +3859,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>56.8</v>
+        <v>53.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>14.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>10</v>
+        <v>9.33</v>
       </c>
       <c r="AB8" t="n">
         <v>5</v>
       </c>
       <c r="AC8" t="n">
-        <v>28.2</v>
+        <v>25.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="AF8" t="n">
         <v>0.14</v>
@@ -3964,67 +3964,67 @@
         <v>3.29</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.08</v>
+        <v>8.69</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BO8" t="n">
         <v>1.08</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.25</v>
+        <v>4.08</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.83</v>
+        <v>4.62</v>
       </c>
       <c r="BR8" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS8" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT8" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BU8" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV8" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX8" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CB8" t="n">
         <v>3.38</v>
@@ -4039,37 +4039,37 @@
         <v>1.42</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CH8" t="n">
         <v>1.34</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO8" t="n">
         <v>1.33</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CQ8" t="n">
         <v>3.55</v>
@@ -4081,7 +4081,7 @@
         <v>3.15</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CU8" t="n">
         <v>1.36</v>
@@ -4096,64 +4096,64 @@
         <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.48</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DB8" t="n">
         <v>1.36</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="DE8" t="n">
         <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.09</v>
+        <v>2.85</v>
       </c>
       <c r="DH8" t="n">
-        <v>88.58</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.59</v>
+        <v>3.62</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.25</v>
+        <v>4.92</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DM8" t="n">
-        <v>59.75</v>
+        <v>57.7</v>
       </c>
       <c r="DN8" t="n">
         <v>1</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.67</v>
+        <v>15.08</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.42</v>
+        <v>13.15</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.41</v>
+        <v>5.84</v>
       </c>
       <c r="DS8" t="n">
         <v>0.08</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>52.25</v>
+        <v>51.08</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.42</v>
+        <v>14.15</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.5</v>
+        <v>9.23</v>
       </c>
       <c r="DZ8" t="n">
         <v>4.92</v>
       </c>
       <c r="EA8" t="n">
-        <v>25.92</v>
+        <v>24.85</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="9">
@@ -4241,10 +4241,10 @@
         <v>15.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.29</v>
+        <v>15.57</v>
       </c>
       <c r="R9" t="n">
-        <v>4.43</v>
+        <v>5.43</v>
       </c>
       <c r="S9" t="n">
         <v>1.29</v>
@@ -4262,19 +4262,19 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>48.14</v>
+        <v>49.14</v>
       </c>
       <c r="Y9" t="n">
         <v>0.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.14</v>
+        <v>12.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>8</v>
+        <v>8.43</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="AC9" t="n">
         <v>23.57</v>
@@ -4553,10 +4553,10 @@
         <v>15</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.77</v>
+        <v>16.38</v>
       </c>
       <c r="DR9" t="n">
-        <v>5.77</v>
+        <v>6.31</v>
       </c>
       <c r="DS9" t="n">
         <v>0.23</v>
@@ -4568,19 +4568,19 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.23</v>
+        <v>51.77</v>
       </c>
       <c r="DW9" t="n">
         <v>0.23</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.77</v>
+        <v>13.93</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.31</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.46</v>
+        <v>4.38</v>
       </c>
       <c r="EA9" t="n">
         <v>21.69</v>
@@ -4614,7 +4614,7 @@
         <v>1.71</v>
       </c>
       <c r="G10" t="n">
-        <v>2.43</v>
+        <v>3.14</v>
       </c>
       <c r="H10" t="n">
         <v>75.14</v>
@@ -4629,7 +4629,7 @@
         <v>5.86</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="M10" t="n">
         <v>53.29</v>
@@ -4638,16 +4638,16 @@
         <v>0.86</v>
       </c>
       <c r="O10" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="P10" t="n">
         <v>12.57</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.14</v>
+        <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>5.71</v>
+        <v>6.86</v>
       </c>
       <c r="S10" t="n">
         <v>0.57</v>
@@ -4665,25 +4665,25 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57.86</v>
+        <v>57.57</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.14</v>
+        <v>14.86</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.14</v>
+        <v>11.86</v>
       </c>
       <c r="AB10" t="n">
         <v>3</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.57</v>
+        <v>19.86</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE10" t="n">
         <v>2.57</v>
@@ -4797,10 +4797,10 @@
         <v>0.86</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.79</v>
+        <v>4.07</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.07</v>
+        <v>4.71</v>
       </c>
       <c r="BR10" t="n">
         <v>92.86</v>
@@ -4926,7 +4926,7 @@
         <v>1.92</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="DH10" t="n">
         <v>80.5</v>
@@ -4941,7 +4941,7 @@
         <v>5.14</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="DM10" t="n">
         <v>53.43</v>
@@ -4950,16 +4950,16 @@
         <v>0.86</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="DP10" t="n">
         <v>13.57</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.86</v>
+        <v>14.78</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.57</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS10" t="n">
         <v>0.14</v>
@@ -4971,25 +4971,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.64</v>
+        <v>53.5</v>
       </c>
       <c r="DW10" t="n">
         <v>0.14</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.07</v>
+        <v>13.43</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.5</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DZ10" t="n">
         <v>3.57</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.28</v>
+        <v>19.43</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="EC10" t="n">
         <v>2.64</v>
@@ -5047,10 +5047,10 @@
         <v>12.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>16.25</v>
+        <v>15.88</v>
       </c>
       <c r="R11" t="n">
-        <v>7.75</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="S11" t="n">
         <v>2.25</v>
@@ -5068,25 +5068,25 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>49.88</v>
+        <v>50.38</v>
       </c>
       <c r="Y11" t="n">
         <v>0.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.88</v>
+        <v>14.12</v>
       </c>
       <c r="AA11" t="n">
-        <v>9</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.88</v>
+        <v>4.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.75</v>
+        <v>21.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -5359,10 +5359,10 @@
         <v>13.71</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.93</v>
+        <v>16.72</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.14</v>
+        <v>7.5</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,25 +5374,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.86</v>
+        <v>49.15</v>
       </c>
       <c r="DW11" t="n">
         <v>0.28</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.22</v>
+        <v>12.35</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.140000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.57</v>
+        <v>21.5</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC11" t="n">
         <v>3.07</v>
@@ -5417,10 +5417,10 @@
         <v>0.43</v>
       </c>
       <c r="F12" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="G12" t="n">
-        <v>3.29</v>
+        <v>3.57</v>
       </c>
       <c r="H12" t="n">
         <v>81.86</v>
@@ -5429,13 +5429,13 @@
         <v>0.14</v>
       </c>
       <c r="J12" t="n">
-        <v>2.43</v>
+        <v>2.57</v>
       </c>
       <c r="K12" t="n">
         <v>7.29</v>
       </c>
       <c r="L12" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="M12" t="n">
         <v>57.57</v>
@@ -5444,7 +5444,7 @@
         <v>0.71</v>
       </c>
       <c r="O12" t="n">
-        <v>2.86</v>
+        <v>3.57</v>
       </c>
       <c r="P12" t="n">
         <v>16.71</v>
@@ -5492,7 +5492,7 @@
         <v>1.65</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.43</v>
+        <v>2.57</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5603,10 +5603,10 @@
         <v>1.46</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.08</v>
+        <v>4.46</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.38</v>
+        <v>4.69</v>
       </c>
       <c r="BR12" t="n">
         <v>92.31</v>
@@ -5729,10 +5729,10 @@
         <v>0.23</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="DH12" t="n">
         <v>80</v>
@@ -5741,13 +5741,13 @@
         <v>0.23</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="DK12" t="n">
         <v>6.08</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="DM12" t="n">
         <v>52</v>
@@ -5756,7 +5756,7 @@
         <v>1.07</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.31</v>
+        <v>2.69</v>
       </c>
       <c r="DP12" t="n">
         <v>15.08</v>
@@ -5798,7 +5798,7 @@
         <v>1.52</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="13">
@@ -5904,7 +5904,7 @@
         <v>1.43</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.14</v>
+        <v>1.86</v>
       </c>
       <c r="AI13" t="n">
         <v>77</v>
@@ -5919,7 +5919,7 @@
         <v>3.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.14</v>
+        <v>0.29</v>
       </c>
       <c r="AN13" t="n">
         <v>38.14</v>
@@ -5928,7 +5928,7 @@
         <v>0.71</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.29</v>
+        <v>1.71</v>
       </c>
       <c r="AQ13" t="n">
         <v>13.71</v>
@@ -5937,7 +5937,7 @@
         <v>17.86</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.57</v>
+        <v>12.57</v>
       </c>
       <c r="AT13" t="n">
         <v>1.57</v>
@@ -5955,25 +5955,25 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>46.29</v>
+        <v>46.57</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.14</v>
       </c>
       <c r="BA13" t="n">
-        <v>8</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.14</v>
+        <v>6.86</v>
       </c>
       <c r="BC13" t="n">
         <v>1.86</v>
       </c>
       <c r="BD13" t="n">
-        <v>22.86</v>
+        <v>22.57</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="BF13" t="n">
         <v>2</v>
@@ -6006,10 +6006,10 @@
         <v>1.08</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.62</v>
+        <v>5.31</v>
       </c>
       <c r="BR13" t="n">
         <v>76.92</v>
@@ -6135,7 +6135,7 @@
         <v>1.69</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="DH13" t="n">
         <v>78.77</v>
@@ -6150,7 +6150,7 @@
         <v>3.61</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="DM13" t="n">
         <v>44.46</v>
@@ -6159,7 +6159,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="DP13" t="n">
         <v>14.77</v>
@@ -6168,7 +6168,7 @@
         <v>16.92</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.539999999999999</v>
+        <v>10.61</v>
       </c>
       <c r="DS13" t="n">
         <v>0.08</v>
@@ -6180,25 +6180,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>43.77</v>
+        <v>43.92</v>
       </c>
       <c r="DW13" t="n">
         <v>0.31</v>
       </c>
       <c r="DX13" t="n">
-        <v>10</v>
+        <v>10.38</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.23</v>
+        <v>7.62</v>
       </c>
       <c r="DZ13" t="n">
         <v>2.77</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.38</v>
+        <v>22.23</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="EC13" t="n">
         <v>2.08</v>
@@ -6307,7 +6307,7 @@
         <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" t="n">
         <v>69.5</v>
@@ -6322,7 +6322,7 @@
         <v>3</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="AN14" t="n">
         <v>33.67</v>
@@ -6331,7 +6331,7 @@
         <v>2.17</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AQ14" t="n">
         <v>12</v>
@@ -6409,10 +6409,10 @@
         <v>1.08</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.92</v>
+        <v>4.31</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.15</v>
+        <v>5.46</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
@@ -6534,7 +6534,7 @@
         <v>1.31</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="DH14" t="n">
         <v>71.92</v>
@@ -6549,7 +6549,7 @@
         <v>5</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="DM14" t="n">
         <v>43.85</v>
@@ -6558,7 +6558,7 @@
         <v>1.7</v>
       </c>
       <c r="DO14" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DP14" t="n">
         <v>13.85</v>
@@ -6736,10 +6736,10 @@
         <v>14.17</v>
       </c>
       <c r="AR15" t="n">
-        <v>16</v>
+        <v>15.67</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.17</v>
+        <v>9.67</v>
       </c>
       <c r="AT15" t="n">
         <v>1.83</v>
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>49.33</v>
+        <v>48.67</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
@@ -6963,10 +6963,10 @@
         <v>15.08</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.62</v>
+        <v>15.47</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.77</v>
+        <v>9.92</v>
       </c>
       <c r="DS15" t="n">
         <v>0.15</v>
@@ -6978,7 +6978,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>48.61</v>
+        <v>48.31</v>
       </c>
       <c r="DW15" t="n">
         <v>0.23</v>
@@ -7135,10 +7135,10 @@
         <v>14.71</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.71</v>
+        <v>11.86</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AT16" t="n">
         <v>0.43</v>
@@ -7156,25 +7156,25 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>50.71</v>
+        <v>49.71</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.14</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.57</v>
+        <v>11.86</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.289999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="BC16" t="n">
         <v>3.29</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.43</v>
+        <v>18.29</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF16" t="n">
         <v>2.57</v>
@@ -7366,10 +7366,10 @@
         <v>14.46</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.08</v>
+        <v>13.16</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.92</v>
+        <v>8.16</v>
       </c>
       <c r="DS16" t="n">
         <v>0.23</v>
@@ -7381,22 +7381,22 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.61</v>
+        <v>51.08</v>
       </c>
       <c r="DW16" t="n">
         <v>0.15</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.23</v>
+        <v>13.39</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.62</v>
+        <v>7.77</v>
       </c>
       <c r="DZ16" t="n">
         <v>5.62</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.23</v>
+        <v>20.15</v>
       </c>
       <c r="EB16" t="n">
         <v>1.6</v>
@@ -7923,7 +7923,7 @@
         <v>2.33</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AM18" t="n">
         <v>-0.17</v>
@@ -7941,10 +7941,10 @@
         <v>11.67</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.83</v>
+        <v>14.67</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.33</v>
+        <v>8.5</v>
       </c>
       <c r="AT18" t="n">
         <v>1.17</v>
@@ -7962,25 +7962,25 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>44.17</v>
+        <v>45</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.67</v>
+        <v>10</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.83</v>
+        <v>7</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="BD18" t="n">
         <v>18.83</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="BF18" t="n">
         <v>2.33</v>
@@ -7989,7 +7989,7 @@
         <v>2</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.77</v>
+        <v>9.85</v>
       </c>
       <c r="BI18" t="n">
         <v>2</v>
@@ -8154,7 +8154,7 @@
         <v>2.69</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.77</v>
+        <v>3.85</v>
       </c>
       <c r="DL18" t="n">
         <v>-0.08</v>
@@ -8172,10 +8172,10 @@
         <v>13.39</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.54</v>
+        <v>15.46</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.23</v>
+        <v>10.23</v>
       </c>
       <c r="DS18" t="n">
         <v>0.16</v>
@@ -8187,25 +8187,25 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>44.46</v>
+        <v>44.84</v>
       </c>
       <c r="DW18" t="n">
         <v>0.16</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.69</v>
+        <v>9.84</v>
       </c>
       <c r="DY18" t="n">
-        <v>5.84</v>
+        <v>5.92</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="EA18" t="n">
         <v>19.23</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="EC18" t="n">
         <v>2.53</v>
@@ -8344,10 +8344,10 @@
         <v>14.71</v>
       </c>
       <c r="AR19" t="n">
-        <v>17.57</v>
+        <v>17.43</v>
       </c>
       <c r="AS19" t="n">
-        <v>7</v>
+        <v>7.86</v>
       </c>
       <c r="AT19" t="n">
         <v>0.86</v>
@@ -8365,25 +8365,25 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>54.29</v>
+        <v>55.43</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>11.29</v>
+        <v>12</v>
       </c>
       <c r="BB19" t="n">
-        <v>7</v>
+        <v>7.71</v>
       </c>
       <c r="BC19" t="n">
         <v>4.29</v>
       </c>
       <c r="BD19" t="n">
-        <v>23.43</v>
+        <v>23.29</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="BF19" t="n">
         <v>3.57</v>
@@ -8575,10 +8575,10 @@
         <v>14.23</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.61</v>
+        <v>15.54</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.62</v>
+        <v>6.08</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8590,25 +8590,25 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>56</v>
+        <v>56.62</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.31</v>
+        <v>11.69</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.69</v>
+        <v>7.07</v>
       </c>
       <c r="DZ19" t="n">
         <v>4.62</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.46</v>
+        <v>21.39</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="EC19" t="n">
         <v>2.69</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1505,10 +1505,10 @@
         <v>14.14</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.86</v>
+        <v>12.14</v>
       </c>
       <c r="AS2" t="n">
-        <v>6</v>
+        <v>7.43</v>
       </c>
       <c r="AT2" t="n">
         <v>1.57</v>
@@ -1526,25 +1526,25 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>49.14</v>
+        <v>49.71</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.14</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.71</v>
+        <v>14.29</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.289999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BC2" t="n">
         <v>5.43</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.29</v>
+        <v>20.57</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BF2" t="n">
         <v>2.57</v>
@@ -1736,10 +1736,10 @@
         <v>14.54</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.39</v>
+        <v>12.54</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.62</v>
+        <v>6.39</v>
       </c>
       <c r="DS2" t="n">
         <v>0.08</v>
@@ -1751,25 +1751,25 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.46</v>
+        <v>50.77</v>
       </c>
       <c r="DW2" t="n">
         <v>0.23</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.15</v>
+        <v>15.46</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.390000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DZ2" t="n">
         <v>5.77</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.93</v>
+        <v>23.08</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="EC2" t="n">
         <v>2.54</v>
@@ -2230,10 +2230,10 @@
         <v>15.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.83</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
-        <v>5.67</v>
+        <v>7.67</v>
       </c>
       <c r="S4" t="n">
         <v>0.83</v>
@@ -2251,25 +2251,25 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>51.67</v>
+        <v>51</v>
       </c>
       <c r="Y4" t="n">
         <v>0.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.17</v>
+        <v>16.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.83</v>
+        <v>12.17</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>27.5</v>
+        <v>28.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AE4" t="n">
         <v>3.33</v>
@@ -2542,10 +2542,10 @@
         <v>15.69</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.23</v>
+        <v>12.31</v>
       </c>
       <c r="DR4" t="n">
-        <v>6.77</v>
+        <v>7.69</v>
       </c>
       <c r="DS4" t="n">
         <v>0.15</v>
@@ -2557,25 +2557,25 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.85</v>
+        <v>46.54</v>
       </c>
       <c r="DW4" t="n">
         <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.31</v>
+        <v>13.54</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.15</v>
+        <v>9.31</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.15</v>
+        <v>4.23</v>
       </c>
       <c r="EA4" t="n">
-        <v>24.23</v>
+        <v>24.69</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="EC4" t="n">
         <v>2.77</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AI6" t="n">
-        <v>72.75</v>
+        <v>74.78</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.88</v>
+        <v>4.11</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>40.75</v>
+        <v>43.44</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AQ6" t="n">
-        <v>17.25</v>
+        <v>16.78</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.5</v>
+        <v>15.56</v>
       </c>
       <c r="AS6" t="n">
-        <v>13.12</v>
+        <v>11.56</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>37.5</v>
+        <v>38.67</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.38</v>
+        <v>10.56</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.12</v>
+        <v>6.67</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.25</v>
+        <v>3.89</v>
       </c>
       <c r="BD6" t="n">
-        <v>23.88</v>
+        <v>24.11</v>
       </c>
       <c r="BE6" t="n">
         <v>1.25</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.29</v>
+        <v>10.4</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="BR6" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BS6" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BT6" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BU6" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY6" t="n">
         <v>2.94</v>
@@ -3222,70 +3222,70 @@
         <v>3.46</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.12</v>
+        <v>4.94</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CG6" t="n">
         <v>2.61</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="CR6" t="n">
         <v>1.4</v>
       </c>
       <c r="CS6" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CU6" t="n">
         <v>1.39</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW6" t="n">
         <v>1.88</v>
@@ -3296,85 +3296,85 @@
       </c>
       <c r="CZ6" t="inlineStr"/>
       <c r="DA6" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.49</v>
+        <v>3.52</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DH6" t="n">
-        <v>75.78</v>
+        <v>76.8</v>
       </c>
       <c r="DI6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.15</v>
+        <v>4.27</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DM6" t="n">
-        <v>42.64</v>
+        <v>44.13</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="DP6" t="n">
-        <v>15</v>
+        <v>14.87</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.22</v>
+        <v>13.4</v>
       </c>
       <c r="DR6" t="n">
-        <v>11.35</v>
+        <v>10.54</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>41.36</v>
+        <v>41.8</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.14</v>
+        <v>10.27</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.21</v>
+        <v>6.53</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.93</v>
+        <v>3.73</v>
       </c>
       <c r="EA6" t="n">
-        <v>21</v>
+        <v>21.33</v>
       </c>
       <c r="EB6" t="n">
         <v>1.25</v>
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4689,139 +4689,139 @@
         <v>2.57</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>85.86</v>
+        <v>84.25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>53.57</v>
+        <v>53.25</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.57</v>
+        <v>14.88</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.57</v>
+        <v>14.62</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.43</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>49.43</v>
+        <v>49.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA10" t="n">
-        <v>12</v>
+        <v>11.88</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.86</v>
+        <v>7.12</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.14</v>
+        <v>4.75</v>
       </c>
       <c r="BD10" t="n">
-        <v>19</v>
+        <v>18.88</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.14</v>
+        <v>10.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="BN10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BO10" t="n">
         <v>0.93</v>
       </c>
-      <c r="BO10" t="n">
-        <v>0.86</v>
-      </c>
       <c r="BP10" t="n">
-        <v>4.07</v>
+        <v>4.2</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.71</v>
+        <v>4.73</v>
       </c>
       <c r="BR10" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS10" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BU10" t="n">
-        <v>7.14</v>
+        <v>13.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BY10" t="n">
         <v>2.07</v>
@@ -4830,43 +4830,43 @@
         <v>2.13</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CB10" t="n">
         <v>3.28</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="CE10" t="n">
         <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI10" t="n">
         <v>1.87</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CK10" t="n">
         <v>1.43</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CN10" t="n">
         <v>1.99</v>
@@ -4920,79 +4920,79 @@
         <v>3.94</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DH10" t="n">
-        <v>80.5</v>
+        <v>80</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM10" t="n">
-        <v>53.43</v>
+        <v>53.27</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.57</v>
+        <v>13.8</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.78</v>
+        <v>14.8</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.140000000000001</v>
+        <v>7.53</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.5</v>
+        <v>53.27</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.43</v>
+        <v>13.27</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.859999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.57</v>
+        <v>3.93</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.43</v>
+        <v>19.34</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="11">
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -6622,82 +6622,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="G15" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="H15" t="n">
-        <v>66.14</v>
+        <v>70.12</v>
       </c>
       <c r="I15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J15" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="L15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M15" t="n">
-        <v>33.86</v>
+        <v>37</v>
       </c>
       <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P15" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.14</v>
       </c>
-      <c r="O15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P15" t="n">
-        <v>15.86</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>15.29</v>
-      </c>
-      <c r="R15" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>48</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AE15" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6781,67 +6781,67 @@
         <v>2.17</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="BH15" t="n">
-        <v>10</v>
+        <v>10.14</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.08</v>
+        <v>4.21</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.85</v>
+        <v>4.93</v>
       </c>
       <c r="BR15" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS15" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BT15" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU15" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV15" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX15" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="CB15" t="n">
         <v>3.41</v>
@@ -6853,55 +6853,55 @@
         <v>4.11</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CL15" t="n">
         <v>1.65</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP15" t="n">
         <v>1.9</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV15" t="n">
         <v>1.97</v>
@@ -6918,88 +6918,88 @@
         <v>2.12</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC15" t="n">
         <v>2.11</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="DH15" t="n">
-        <v>67.23</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.15</v>
+        <v>4.29</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DM15" t="n">
-        <v>39.54</v>
+        <v>40.93</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.08</v>
+        <v>14.86</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.47</v>
+        <v>15.57</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.92</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>48.31</v>
+        <v>48.57</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.61</v>
+        <v>10.35</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.92</v>
+        <v>6.64</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.62</v>
+        <v>19.93</v>
       </c>
       <c r="EB15" t="n">
         <v>1.21</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="16">
@@ -7815,25 +7815,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="F18" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="H18" t="n">
-        <v>76.86</v>
+        <v>78</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -7842,67 +7842,67 @@
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.29</v>
+        <v>3.62</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M18" t="n">
-        <v>46.43</v>
+        <v>47.38</v>
       </c>
       <c r="N18" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O18" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="P18" t="n">
-        <v>14.86</v>
+        <v>14.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>16.14</v>
+        <v>16.62</v>
       </c>
       <c r="R18" t="n">
-        <v>11.71</v>
+        <v>10.12</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="U18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>44.71</v>
+        <v>45.38</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>9.710000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA18" t="n">
-        <v>5</v>
+        <v>5.38</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>19.57</v>
+        <v>19.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7986,70 +7986,70 @@
         <v>2.33</v>
       </c>
       <c r="BG18" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.85</v>
+        <v>9.93</v>
       </c>
       <c r="BI18" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="BP18" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.85</v>
+        <v>3.93</v>
       </c>
       <c r="BR18" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BU18" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV18" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BY18" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="BZ18" t="n">
-        <v>3.51</v>
+        <v>3.55</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="CC18" t="n">
         <v>4.82</v>
@@ -8058,13 +8058,13 @@
         <v>5.22</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="CH18" t="n">
         <v>1.4</v>
@@ -8073,37 +8073,37 @@
         <v>1.95</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CL18" t="n">
         <v>1.73</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="CR18" t="n">
         <v>1.39</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="CU18" t="n">
         <v>1.4</v>
@@ -8112,7 +8112,7 @@
         <v>1.99</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX18" t="n">
         <v>1.48</v>
@@ -8127,88 +8127,88 @@
         <v>2.23</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DH18" t="n">
-        <v>73.31</v>
+        <v>74.22</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="DL18" t="n">
-        <v>-0.08</v>
+        <v>-0</v>
       </c>
       <c r="DM18" t="n">
-        <v>45.62</v>
+        <v>46.22</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.54</v>
+        <v>0.72</v>
       </c>
       <c r="DP18" t="n">
-        <v>13.39</v>
+        <v>13.43</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.46</v>
+        <v>15.78</v>
       </c>
       <c r="DR18" t="n">
-        <v>10.23</v>
+        <v>9.43</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>44.84</v>
+        <v>45.22</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.84</v>
+        <v>10</v>
       </c>
       <c r="DY18" t="n">
-        <v>5.92</v>
+        <v>6.07</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.23</v>
+        <v>19.14</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
@@ -1391,82 +1391,82 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>80.56999999999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M2" t="n">
+        <v>54.43</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P2" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>51</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.83</v>
       </c>
-      <c r="G2" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="H2" t="n">
-        <v>81.33</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>56.67</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P2" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>13</v>
-      </c>
-      <c r="R2" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>52</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>16.83</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AE2" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AF2" t="n">
         <v>0.29</v>
@@ -1550,67 +1550,67 @@
         <v>2.57</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.85</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BN2" t="n">
         <v>2</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.31</v>
+        <v>4.21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.92</v>
+        <v>5.07</v>
       </c>
       <c r="BR2" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BV2" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX2" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CB2" t="n">
         <v>3.28</v>
@@ -1625,7 +1625,7 @@
         <v>1.45</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CG2" t="n">
         <v>2.62</v>
@@ -1634,16 +1634,16 @@
         <v>1.33</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CK2" t="n">
         <v>1.39</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CM2" t="n">
         <v>2.64</v>
@@ -1658,7 +1658,7 @@
         <v>2.13</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="CR2" t="n">
         <v>1.47</v>
@@ -1673,10 +1673,10 @@
         <v>1.34</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX2" t="n">
         <v>1.51</v>
@@ -1691,7 +1691,7 @@
         <v>2.05</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC2" t="n">
         <v>2.29</v>
@@ -1700,79 +1700,79 @@
         <v>4.22</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="DH2" t="n">
-        <v>77.92</v>
+        <v>77.78</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ2" t="n">
         <v>3</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.31</v>
+        <v>5.21</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.54</v>
+        <v>50.78</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.54</v>
+        <v>14.22</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.54</v>
+        <v>12.86</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.39</v>
+        <v>5.86</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.77</v>
+        <v>50.36</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.46</v>
+        <v>15.22</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.77</v>
+        <v>5.71</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.08</v>
+        <v>22.36</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="3">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,52 +2275,52 @@
         <v>3.33</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.71</v>
+        <v>1.62</v>
       </c>
       <c r="AI4" t="n">
-        <v>63.14</v>
+        <v>63.88</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.29</v>
+        <v>6</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AN4" t="n">
-        <v>36.86</v>
+        <v>41.12</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.57</v>
+        <v>15.12</v>
       </c>
       <c r="AR4" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.71</v>
+        <v>6.62</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>42.71</v>
+        <v>43.88</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.86</v>
+        <v>12.12</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.86</v>
+        <v>7.38</v>
       </c>
       <c r="BC4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>4</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BR4" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="BU4" t="n">
         <v>21.43</v>
       </c>
-      <c r="BE4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>10.23</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>69.23</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>61.54</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>23.08</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>15.38</v>
-      </c>
       <c r="BV4" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BY4" t="n">
         <v>2.61</v>
@@ -2416,46 +2416,46 @@
         <v>2.69</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK4" t="n">
         <v>1.33</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CO4" t="n">
         <v>1.25</v>
@@ -2467,118 +2467,118 @@
         <v>3.48</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CX4" t="n">
         <v>1.51</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.52</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.09</v>
+        <v>4.18</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.15</v>
+        <v>2.57</v>
       </c>
       <c r="DH4" t="n">
-        <v>72.45999999999999</v>
+        <v>72.22</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ4" t="n">
         <v>3</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.16</v>
+        <v>6.5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DM4" t="n">
-        <v>49.93</v>
+        <v>51.43</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DP4" t="n">
-        <v>15.69</v>
+        <v>15.42</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.31</v>
+        <v>12</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.69</v>
+        <v>7.07</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.54</v>
+        <v>46.93</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.54</v>
+        <v>14.07</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.31</v>
+        <v>9.43</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.23</v>
+        <v>4.64</v>
       </c>
       <c r="EA4" t="n">
-        <v>24.69</v>
+        <v>24.57</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="5">
@@ -3114,7 +3114,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ6" t="n">
-        <v>16.78</v>
+        <v>17.11</v>
       </c>
       <c r="AR6" t="n">
         <v>15.56</v>
@@ -3231,7 +3231,7 @@
         <v>4.65</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.94</v>
+        <v>4.92</v>
       </c>
       <c r="CE6" t="n">
         <v>1.3</v>
@@ -3305,7 +3305,7 @@
         <v>2.02</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
@@ -3341,7 +3341,7 @@
         <v>1.74</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.87</v>
+        <v>15.07</v>
       </c>
       <c r="DQ6" t="n">
         <v>13.4</v>
@@ -3390,13 +3390,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3483,127 +3483,127 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AI7" t="n">
-        <v>80.86</v>
+        <v>79.25</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>5.43</v>
+        <v>5.62</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.14</v>
+        <v>3.75</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AN7" t="n">
-        <v>49</v>
+        <v>47.88</v>
       </c>
       <c r="AO7" t="n">
         <v>2</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.86</v>
+        <v>12.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>16.14</v>
+        <v>16.25</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.289999999999999</v>
+        <v>7.12</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="n">
         <v>1</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>53.57</v>
+        <v>50.75</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>13</v>
+        <v>12.62</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.710000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="BD7" t="n">
-        <v>20.86</v>
+        <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BF7" t="n">
         <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.619999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU7" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3612,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY7" t="n">
         <v>1.71</v>
@@ -3621,22 +3621,22 @@
         <v>1.79</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CG7" t="n">
         <v>2.83</v>
@@ -3645,28 +3645,28 @@
         <v>1.39</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CK7" t="n">
         <v>1.36</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CN7" t="n">
         <v>2.12</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CQ7" t="n">
         <v>3.31</v>
@@ -3675,7 +3675,7 @@
         <v>1.4</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CT7" t="n">
         <v>2.99</v>
@@ -3705,85 +3705,85 @@
         <v>1.32</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="DH7" t="n">
-        <v>81.93000000000001</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ7" t="n">
-        <v>4.16</v>
+        <v>4.36</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.31</v>
+        <v>4.07</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>53.15</v>
+        <v>52.22</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.54</v>
+        <v>14.21</v>
       </c>
       <c r="DQ7" t="n">
-        <v>16.92</v>
+        <v>16.93</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.85</v>
+        <v>7.21</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>55.54</v>
+        <v>53.78</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="DX7" t="n">
-        <v>14.08</v>
+        <v>13.78</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.15</v>
+        <v>8.93</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.93</v>
+        <v>4.86</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.54</v>
+        <v>20.07</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3883,139 +3883,139 @@
         <v>3.83</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>81.43000000000001</v>
+        <v>84.75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.43</v>
+        <v>5.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AN8" t="n">
-        <v>53.86</v>
+        <v>53.88</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR8" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="BU8" t="n">
         <v>14.29</v>
       </c>
-      <c r="AS8" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>49</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>24.29</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>84.62</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>84.62</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>30.77</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>15.38</v>
-      </c>
       <c r="BV8" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX8" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY8" t="n">
         <v>2.02</v>
@@ -4027,19 +4027,19 @@
         <v>3.19</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="CE8" t="n">
         <v>1.42</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CG8" t="n">
         <v>2.68</v>
@@ -4051,34 +4051,34 @@
         <v>1.88</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK8" t="n">
         <v>1.29</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CM8" t="n">
         <v>2.56</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="CR8" t="n">
         <v>1.43</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CT8" t="n">
         <v>2.83</v>
@@ -4087,10 +4087,10 @@
         <v>1.36</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX8" t="n">
         <v>1.51</v>
@@ -4102,91 +4102,91 @@
         <v>2.48</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB8" t="n">
         <v>1.36</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="DH8" t="n">
-        <v>86.54000000000001</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.62</v>
+        <v>3.57</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="DM8" t="n">
-        <v>57.7</v>
+        <v>57.43</v>
       </c>
       <c r="DN8" t="n">
         <v>1</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.08</v>
+        <v>14.5</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.15</v>
+        <v>13.78</v>
       </c>
       <c r="DR8" t="n">
-        <v>5.84</v>
+        <v>5.36</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.08</v>
+        <v>51.36</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.15</v>
+        <v>13.43</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.23</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.92</v>
+        <v>4.71</v>
       </c>
       <c r="EA8" t="n">
-        <v>24.85</v>
+        <v>24.5</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4289,136 +4289,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="AI9" t="n">
-        <v>85.17</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AK9" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN9" t="n">
-        <v>56.83</v>
+        <v>55.43</v>
       </c>
       <c r="AO9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AU9" t="n">
         <v>1</v>
       </c>
-      <c r="AP9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>17.33</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AV9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>54.83</v>
+        <v>54.71</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA9" t="n">
-        <v>15.67</v>
+        <v>15.29</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.83</v>
+        <v>10.14</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.83</v>
+        <v>5.14</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.54</v>
+        <v>2.71</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.92</v>
+        <v>9.93</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.54</v>
+        <v>2.71</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.54</v>
+        <v>4.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT9" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BU9" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY9" t="n">
         <v>2.15</v>
@@ -4427,16 +4427,16 @@
         <v>2.17</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CB9" t="n">
         <v>3.34</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CD9" t="n">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="CE9" t="n">
         <v>1.42</v>
@@ -4448,7 +4448,7 @@
         <v>2.73</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI9" t="n">
         <v>1.92</v>
@@ -4457,31 +4457,31 @@
         <v>1.8</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CN9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CP9" t="n">
         <v>2.05</v>
       </c>
-      <c r="CO9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>2.06</v>
-      </c>
       <c r="CQ9" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="CR9" t="n">
         <v>1.42</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CT9" t="n">
         <v>2.88</v>
@@ -4514,82 +4514,82 @@
         <v>2.11</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="DH9" t="n">
-        <v>93.93000000000001</v>
+        <v>93.36</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.84</v>
+        <v>2.64</v>
       </c>
       <c r="DK9" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DM9" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DP9" t="n">
-        <v>15</v>
+        <v>14.72</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.38</v>
+        <v>16.64</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.31</v>
+        <v>5.78</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.77</v>
+        <v>51.92</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.93</v>
+        <v>13.86</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.539999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.38</v>
+        <v>4.57</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.69</v>
+        <v>21.78</v>
       </c>
       <c r="EB9" t="n">
         <v>1.62</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="10">
@@ -4839,7 +4839,7 @@
         <v>2.55</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CE10" t="n">
         <v>1.42</v>
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5095,49 +5095,49 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="AI11" t="n">
-        <v>78.83</v>
+        <v>75.86</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>40.5</v>
+        <v>39.29</v>
       </c>
       <c r="AO11" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15.33</v>
+        <v>15.29</v>
       </c>
       <c r="AR11" t="n">
-        <v>17.83</v>
+        <v>17.71</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.33</v>
+        <v>5.29</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5149,49 +5149,49 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.5</v>
+        <v>47.57</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BA11" t="n">
-        <v>10</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>6.14</v>
       </c>
       <c r="BC11" t="n">
-        <v>3</v>
+        <v>3.57</v>
       </c>
       <c r="BD11" t="n">
-        <v>21.33</v>
+        <v>22.43</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.43</v>
+        <v>9.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM11" t="n">
         <v>1.07</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1</v>
       </c>
       <c r="BN11" t="n">
         <v>2.07</v>
@@ -5200,31 +5200,31 @@
         <v>1.07</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.14</v>
+        <v>3.8</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.29</v>
+        <v>4.87</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU11" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV11" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW11" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX11" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY11" t="n">
         <v>2.45</v>
@@ -5236,28 +5236,28 @@
         <v>3.1</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.17</v>
+        <v>3.09</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.36</v>
+        <v>3.29</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CG11" t="n">
         <v>2.63</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.85</v>
@@ -5269,37 +5269,37 @@
         <v>1.72</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CO11" t="n">
         <v>1.34</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CU11" t="n">
         <v>1.35</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX11" t="n">
         <v>1.51</v>
@@ -5317,52 +5317,52 @@
         <v>1.37</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="DH11" t="n">
-        <v>89.20999999999999</v>
+        <v>87.13</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="DM11" t="n">
-        <v>48.07</v>
+        <v>47</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="DO11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.71</v>
+        <v>13.8</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.72</v>
+        <v>16.73</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.5</v>
+        <v>6.94</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,25 +5374,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.15</v>
+        <v>49.07</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.35</v>
+        <v>12.06</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.359999999999999</v>
+        <v>7.87</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="EC11" t="n">
         <v>3.07</v>
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>0.43</v>
@@ -5498,136 +5498,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH12" t="n">
         <v>2</v>
       </c>
-      <c r="AH12" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AI12" t="n">
-        <v>77.83</v>
+        <v>77</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.67</v>
+        <v>4.43</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN12" t="n">
-        <v>45.5</v>
+        <v>44</v>
       </c>
       <c r="AO12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BN12" t="n">
         <v>1.5</v>
       </c>
-      <c r="AP12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>15.17</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>47.83</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>20.83</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BO12" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.46</v>
+        <v>4.29</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.69</v>
+        <v>4.57</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS12" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU12" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BV12" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="BX12" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BY12" t="n">
         <v>2.43</v>
@@ -5636,25 +5636,25 @@
         <v>2.79</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.29</v>
+        <v>3.14</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.62</v>
+        <v>3.46</v>
       </c>
       <c r="CE12" t="n">
         <v>1.41</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CH12" t="n">
         <v>1.34</v>
@@ -5666,37 +5666,37 @@
         <v>1.85</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CL12" t="n">
         <v>1.72</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CO12" t="n">
         <v>1.34</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="CR12" t="n">
         <v>1.44</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV12" t="n">
         <v>1.94</v>
@@ -5708,97 +5708,97 @@
         <v>1.49</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DB12" t="n">
         <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="DH12" t="n">
-        <v>80</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="DK12" t="n">
-        <v>6.08</v>
+        <v>5.86</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DM12" t="n">
-        <v>52</v>
+        <v>50.78</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.08</v>
+        <v>15.14</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.7</v>
+        <v>15.29</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.15</v>
+        <v>7.5</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>51.77</v>
+        <v>51.57</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.93</v>
+        <v>13</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.23</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.69</v>
+        <v>4.85</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.23</v>
+        <v>20.86</v>
       </c>
       <c r="EB12" t="n">
         <v>1.52</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="13">
@@ -5808,10 +5808,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>7</v>
@@ -5820,13 +5820,13 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>80.83</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -5835,67 +5835,67 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="L13" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M13" t="n">
-        <v>51.83</v>
+        <v>51.71</v>
       </c>
       <c r="N13" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="P13" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="Q13" t="n">
         <v>16</v>
       </c>
-      <c r="Q13" t="n">
-        <v>15.83</v>
-      </c>
       <c r="R13" t="n">
-        <v>8.33</v>
+        <v>7</v>
       </c>
       <c r="S13" t="n">
-        <v>1.17</v>
+        <v>1.71</v>
       </c>
       <c r="T13" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="U13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>40.83</v>
+        <v>42.29</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.33</v>
+        <v>12.71</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.5</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="AC13" t="n">
-        <v>21.83</v>
+        <v>21.71</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5979,70 +5979,70 @@
         <v>2</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.46</v>
+        <v>2.71</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.539999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.46</v>
+        <v>2.71</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.15</v>
+        <v>0.36</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.31</v>
+        <v>5.14</v>
       </c>
       <c r="BR13" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU13" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV13" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="BX13" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="CC13" t="n">
         <v>4.48</v>
@@ -6057,13 +6057,13 @@
         <v>3</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.91</v>
@@ -6072,49 +6072,49 @@
         <v>1.39</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CN13" t="n">
         <v>2.04</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW13" t="n">
         <v>1.97</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="DA13" t="n">
         <v>2.03</v>
@@ -6123,85 +6123,85 @@
         <v>1.37</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DH13" t="n">
-        <v>78.77</v>
+        <v>78.72</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="DM13" t="n">
-        <v>44.46</v>
+        <v>44.92</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.77</v>
+        <v>15.14</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.92</v>
+        <v>16.93</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.61</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>43.92</v>
+        <v>44.43</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.38</v>
+        <v>10.71</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.62</v>
+        <v>7.79</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.23</v>
+        <v>22.14</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="14">
@@ -6211,67 +6211,67 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F14" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="H14" t="n">
-        <v>74</v>
+        <v>76.12</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="K14" t="n">
-        <v>6.71</v>
+        <v>6.5</v>
       </c>
       <c r="L14" t="n">
-        <v>0.57</v>
+        <v>0.38</v>
       </c>
       <c r="M14" t="n">
-        <v>52.57</v>
+        <v>52.5</v>
       </c>
       <c r="N14" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.71</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
-        <v>15.43</v>
+        <v>15.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>16.29</v>
+        <v>16.5</v>
       </c>
       <c r="R14" t="n">
-        <v>8.710000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="S14" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T14" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="U14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -6280,25 +6280,25 @@
         <v>52</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.29</v>
+        <v>15.62</v>
       </c>
       <c r="AA14" t="n">
-        <v>11</v>
+        <v>10.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.29</v>
+        <v>5.38</v>
       </c>
       <c r="AC14" t="n">
-        <v>24.43</v>
+        <v>24.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AF14" t="n">
         <v>0.33</v>
@@ -6385,67 +6385,67 @@
         <v>3</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.38</v>
+        <v>11.21</v>
       </c>
       <c r="BI14" t="n">
         <v>3</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL14" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BM14" t="n">
         <v>1</v>
       </c>
-      <c r="BM14" t="n">
-        <v>0.92</v>
-      </c>
       <c r="BN14" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.31</v>
+        <v>3.93</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.46</v>
+        <v>5</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU14" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV14" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BY14" t="n">
         <v>2.75</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="CC14" t="n">
         <v>3.27</v>
@@ -6457,10 +6457,10 @@
         <v>1.38</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CH14" t="n">
         <v>1.39</v>
@@ -6472,25 +6472,25 @@
         <v>1.73</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CO14" t="n">
         <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CR14" t="n">
         <v>1.39</v>
@@ -6508,7 +6508,7 @@
         <v>2.06</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
@@ -6525,82 +6525,82 @@
         <v>2</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="DG14" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="DH14" t="n">
-        <v>71.92</v>
+        <v>73.28</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.23</v>
+        <v>3.36</v>
       </c>
       <c r="DK14" t="n">
         <v>5</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="DM14" t="n">
-        <v>43.85</v>
+        <v>44.43</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.85</v>
+        <v>13.86</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.08</v>
+        <v>17.14</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.460000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.31</v>
+        <v>51.36</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.23</v>
+        <v>13.07</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.380000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.85</v>
+        <v>4.93</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.08</v>
+        <v>21.5</v>
       </c>
       <c r="EB14" t="n">
         <v>1.49</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="15">
@@ -6652,7 +6652,7 @@
         <v>1.38</v>
       </c>
       <c r="P15" t="n">
-        <v>15.38</v>
+        <v>15.5</v>
       </c>
       <c r="Q15" t="n">
         <v>15.5</v>
@@ -6682,10 +6682,10 @@
         <v>0.38</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.619999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="AB15" t="n">
         <v>3.62</v>
@@ -6838,13 +6838,13 @@
         <v>2.44</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CA15" t="n">
         <v>3.07</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CC15" t="n">
         <v>3.53</v>
@@ -6960,7 +6960,7 @@
         <v>1.65</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.86</v>
+        <v>14.93</v>
       </c>
       <c r="DQ15" t="n">
         <v>15.57</v>
@@ -6984,10 +6984,10 @@
         <v>0.22</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.35</v>
+        <v>10.43</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.64</v>
+        <v>6.71</v>
       </c>
       <c r="DZ15" t="n">
         <v>3.71</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -7021,82 +7021,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="H16" t="n">
-        <v>77.67</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J16" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="K16" t="n">
-        <v>4.83</v>
+        <v>5.29</v>
       </c>
       <c r="L16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M16" t="n">
-        <v>50</v>
+        <v>54.29</v>
       </c>
       <c r="N16" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O16" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="P16" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>14</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="T16" t="n">
         <v>2</v>
       </c>
-      <c r="P16" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="R16" t="n">
-        <v>8</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.33</v>
-      </c>
       <c r="U16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>52.67</v>
+        <v>55</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.17</v>
+        <v>14.43</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.83</v>
+        <v>6.57</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.33</v>
+        <v>7.86</v>
       </c>
       <c r="AC16" t="n">
-        <v>22.33</v>
+        <v>22.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AE16" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7180,64 +7180,64 @@
         <v>2.57</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.619999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.23</v>
+        <v>4.29</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.38</v>
+        <v>3.43</v>
       </c>
       <c r="BR16" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS16" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BT16" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU16" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV16" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CA16" t="n">
         <v>3.19</v>
@@ -7255,16 +7255,16 @@
         <v>1.41</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CH16" t="n">
         <v>1.35</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.82</v>
@@ -7276,19 +7276,19 @@
         <v>1.83</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP16" t="n">
         <v>2.04</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CR16" t="n">
         <v>1.42</v>
@@ -7306,7 +7306,7 @@
         <v>2</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX16" t="n">
         <v>1.55</v>
@@ -7327,82 +7327,82 @@
         <v>2.12</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DG16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>86.14</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>53.08</v>
+      </c>
+      <c r="DN16" t="n">
         <v>1</v>
       </c>
-      <c r="DH16" t="n">
-        <v>86.23</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>3</v>
-      </c>
-      <c r="DK16" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="DL16" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="DM16" t="n">
-        <v>51</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>1.08</v>
-      </c>
       <c r="DO16" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.46</v>
+        <v>14.64</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.16</v>
+        <v>12.93</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.16</v>
+        <v>7.5</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.08</v>
+        <v>52.36</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.39</v>
+        <v>13.14</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.77</v>
+        <v>7.57</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.62</v>
+        <v>5.58</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.15</v>
+        <v>20.57</v>
       </c>
       <c r="EB16" t="n">
         <v>1.6</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="17">
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
@@ -7424,13 +7424,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="G17" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="H17" t="n">
-        <v>81.67</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -7439,34 +7439,34 @@
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="M17" t="n">
-        <v>48.67</v>
+        <v>49</v>
       </c>
       <c r="N17" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="O17" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>12.5</v>
+        <v>11.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>12</v>
+        <v>12.29</v>
       </c>
       <c r="R17" t="n">
-        <v>8.67</v>
+        <v>7.29</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7478,28 +7478,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>45.5</v>
+        <v>45.86</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="Z17" t="n">
-        <v>13.33</v>
+        <v>13</v>
       </c>
       <c r="AA17" t="n">
-        <v>9.17</v>
+        <v>8.57</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.17</v>
+        <v>4.43</v>
       </c>
       <c r="AC17" t="n">
-        <v>21.33</v>
+        <v>20</v>
       </c>
       <c r="AD17" t="n">
         <v>1.48</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
         <v>0.14</v>
@@ -7583,70 +7583,70 @@
         <v>2.86</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.619999999999999</v>
+        <v>10</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.38</v>
+        <v>4.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.54</v>
+        <v>4.86</v>
       </c>
       <c r="BR17" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS17" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BU17" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV17" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX17" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="CC17" t="n">
         <v>2.86</v>
@@ -7658,10 +7658,10 @@
         <v>1.41</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CH17" t="n">
         <v>1.35</v>
@@ -7670,16 +7670,16 @@
         <v>1.92</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK17" t="n">
         <v>1.39</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CN17" t="n">
         <v>2.07</v>
@@ -7691,121 +7691,121 @@
         <v>2.04</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="CU17" t="n">
         <v>1.37</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CX17" t="n">
         <v>1.56</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.37</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.77</v>
+        <v>3.88</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="DG17" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="DH17" t="n">
-        <v>84.62</v>
+        <v>82.92</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.31</v>
+        <v>5.22</v>
       </c>
       <c r="DL17" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM17" t="n">
-        <v>52.85</v>
+        <v>52.72</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.54</v>
+        <v>12.07</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.92</v>
+        <v>11.14</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.23</v>
+        <v>6.64</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>45.93</v>
+        <v>46.08</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.46</v>
+        <v>12.36</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.31</v>
+        <v>8.07</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.15</v>
+        <v>4.28</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.85</v>
+        <v>21.14</v>
       </c>
       <c r="EB17" t="n">
         <v>1.46</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="18">
@@ -8049,7 +8049,7 @@
         <v>3.52</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="CC18" t="n">
         <v>4.82</v>
@@ -8109,7 +8109,7 @@
         <v>1.4</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW18" t="n">
         <v>1.86</v>
@@ -8218,61 +8218,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F19" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="H19" t="n">
-        <v>85.33</v>
+        <v>83.14</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="J19" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="K19" t="n">
-        <v>6.67</v>
+        <v>6.29</v>
       </c>
       <c r="L19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M19" t="n">
-        <v>62.83</v>
+        <v>60.71</v>
       </c>
       <c r="N19" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="O19" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="P19" t="n">
-        <v>13.67</v>
+        <v>14.29</v>
       </c>
       <c r="Q19" t="n">
-        <v>13.33</v>
+        <v>13</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>3.29</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8284,28 +8284,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>58</v>
+        <v>56.29</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.33</v>
+        <v>11.29</v>
       </c>
       <c r="AA19" t="n">
-        <v>6.33</v>
+        <v>6.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="AC19" t="n">
-        <v>19.17</v>
+        <v>19.71</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8389,61 +8389,61 @@
         <v>3.57</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.31</v>
+        <v>11.21</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.46</v>
+        <v>5.36</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="BR19" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV19" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="BZ19" t="n">
         <v>2.26</v>
@@ -8452,7 +8452,7 @@
         <v>3.27</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CC19" t="n">
         <v>2.22</v>
@@ -8473,37 +8473,37 @@
         <v>1.37</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL19" t="n">
         <v>1.86</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP19" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="CR19" t="n">
         <v>1.41</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CT19" t="n">
         <v>2.92</v>
@@ -8512,13 +8512,13 @@
         <v>1.38</v>
       </c>
       <c r="CV19" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CW19" t="n">
         <v>1.84</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY19" t="n">
         <v>1.79</v>
@@ -8539,46 +8539,46 @@
         <v>3.7</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DG19" t="n">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="DH19" t="n">
-        <v>87.45999999999999</v>
+        <v>86.22</v>
       </c>
       <c r="DI19" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="DK19" t="n">
-        <v>6.23</v>
+        <v>6.08</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM19" t="n">
-        <v>58.38</v>
+        <v>57.64</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.23</v>
+        <v>14.5</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.54</v>
+        <v>15.22</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.08</v>
+        <v>5.58</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8590,28 +8590,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>56.62</v>
+        <v>55.86</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.69</v>
+        <v>11.64</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.07</v>
+        <v>6.92</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.62</v>
+        <v>4.71</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.39</v>
+        <v>21.5</v>
       </c>
       <c r="EB19" t="n">
         <v>1.48</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1424,10 +1424,10 @@
         <v>14.29</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.57</v>
+        <v>13</v>
       </c>
       <c r="R2" t="n">
-        <v>4.29</v>
+        <v>5.86</v>
       </c>
       <c r="S2" t="n">
         <v>0.71</v>
@@ -1445,25 +1445,25 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>51</v>
+        <v>50.86</v>
       </c>
       <c r="Y2" t="n">
         <v>0.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.14</v>
+        <v>16.29</v>
       </c>
       <c r="AA2" t="n">
         <v>10.14</v>
       </c>
       <c r="AB2" t="n">
-        <v>6</v>
+        <v>6.14</v>
       </c>
       <c r="AC2" t="n">
         <v>24.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AE2" t="n">
         <v>2.57</v>
@@ -1736,10 +1736,10 @@
         <v>14.22</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.86</v>
+        <v>12.57</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.86</v>
+        <v>6.64</v>
       </c>
       <c r="DS2" t="n">
         <v>0.07000000000000001</v>
@@ -1751,25 +1751,25 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.36</v>
+        <v>50.28</v>
       </c>
       <c r="DW2" t="n">
         <v>0.22</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.22</v>
+        <v>15.29</v>
       </c>
       <c r="DY2" t="n">
         <v>9.5</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.71</v>
+        <v>5.78</v>
       </c>
       <c r="EA2" t="n">
         <v>22.36</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="EC2" t="n">
         <v>2.57</v>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,118 +1872,118 @@
         <v>2.57</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AI3" t="n">
-        <v>71.17</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.83</v>
+        <v>4.86</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>42.5</v>
+        <v>42.57</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.67</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.67</v>
+        <v>15.86</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.33</v>
+        <v>9.57</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>42</v>
+        <v>42.71</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.67</v>
+        <v>10.29</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.67</v>
+        <v>6.29</v>
       </c>
       <c r="BC3" t="n">
         <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>22.5</v>
+        <v>22.86</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="BH3" t="n">
-        <v>12</v>
+        <v>11.79</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.69</v>
+        <v>4.64</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,19 +1992,19 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV3" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW3" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX3" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BY3" t="n">
         <v>1.99</v>
@@ -2013,16 +2013,16 @@
         <v>2.13</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.51</v>
+        <v>3.55</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.39</v>
+        <v>3.63</v>
       </c>
       <c r="CE3" t="n">
         <v>1.37</v>
@@ -2031,13 +2031,13 @@
         <v>2.74</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CH3" t="n">
         <v>1.39</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.78</v>
@@ -2046,13 +2046,13 @@
         <v>1.4</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
@@ -2064,13 +2064,13 @@
         <v>3.18</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CU3" t="n">
         <v>1.41</v>
@@ -2091,91 +2091,91 @@
         <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DB3" t="n">
         <v>1.3</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="DH3" t="n">
-        <v>83.93000000000001</v>
+        <v>83.08</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="DK3" t="n">
-        <v>7.15</v>
+        <v>7</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DM3" t="n">
-        <v>59.31</v>
+        <v>58.14</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.47</v>
+        <v>14.64</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.15</v>
+        <v>14.78</v>
       </c>
       <c r="DR3" t="n">
-        <v>9</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50.31</v>
+        <v>50.07</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.77</v>
+        <v>15.22</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.69</v>
+        <v>10.22</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="EA3" t="n">
-        <v>23.08</v>
+        <v>23.22</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="4">
@@ -2311,10 +2311,10 @@
         <v>15.12</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.75</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.62</v>
+        <v>7.88</v>
       </c>
       <c r="AT4" t="n">
         <v>1.25</v>
@@ -2341,16 +2341,16 @@
         <v>12.12</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.38</v>
+        <v>7.62</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="BD4" t="n">
         <v>21.62</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BF4" t="n">
         <v>2.38</v>
@@ -2542,10 +2542,10 @@
         <v>15.42</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12</v>
+        <v>11.93</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.07</v>
+        <v>7.79</v>
       </c>
       <c r="DS4" t="n">
         <v>0.14</v>
@@ -2566,16 +2566,16 @@
         <v>14.07</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.43</v>
+        <v>9.57</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="EA4" t="n">
         <v>24.57</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="EC4" t="n">
         <v>2.79</v>
@@ -2588,25 +2588,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F5" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="G5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H5" t="n">
-        <v>96.38</v>
+        <v>94.22</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2615,34 +2615,34 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="L5" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>65.25</v>
+        <v>63.22</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="P5" t="n">
-        <v>14.62</v>
+        <v>15.11</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>15.22</v>
       </c>
       <c r="R5" t="n">
-        <v>4.5</v>
+        <v>3.89</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58.5</v>
+        <v>57.89</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.62</v>
+        <v>14.78</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.880000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.75</v>
+        <v>5.56</v>
       </c>
       <c r="AC5" t="n">
-        <v>24</v>
+        <v>23.89</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AF5" t="n">
         <v>0.17</v>
@@ -2762,31 +2762,31 @@
         <v>2</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.710000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="BI5" t="n">
         <v>2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="BQ5" t="n">
         <v>3.93</v>
@@ -2795,13 +2795,13 @@
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BU5" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2810,19 +2810,19 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.47</v>
+        <v>3.52</v>
       </c>
       <c r="CC5" t="n">
         <v>2.18</v>
@@ -2834,34 +2834,34 @@
         <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CL5" t="n">
         <v>1.69</v>
       </c>
-      <c r="CK5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>1.67</v>
-      </c>
       <c r="CM5" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CN5" t="n">
         <v>1.89</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP5" t="n">
         <v>1.88</v>
@@ -2870,22 +2870,22 @@
         <v>3.23</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX5" t="n">
         <v>1.51</v>
@@ -2897,91 +2897,91 @@
         <v>2.51</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.76</v>
+        <v>3.71</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="DG5" t="n">
         <v>1.93</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.58</v>
+        <v>87.8</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="DK5" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>57.13</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>15</v>
+      </c>
+      <c r="DR5" t="n">
         <v>4.93</v>
       </c>
-      <c r="DL5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DP5" t="n">
-        <v>15.21</v>
-      </c>
-      <c r="DQ5" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="DR5" t="n">
-        <v>5.36</v>
-      </c>
       <c r="DS5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.22</v>
+        <v>56</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="DX5" t="n">
-        <v>15.14</v>
+        <v>14.67</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.859999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.29</v>
+        <v>5.2</v>
       </c>
       <c r="EA5" t="n">
-        <v>25.64</v>
+        <v>25.47</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="EC5" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -3117,10 +3117,10 @@
         <v>17.11</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.56</v>
+        <v>15.33</v>
       </c>
       <c r="AS6" t="n">
-        <v>11.56</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
         <v>1.22</v>
@@ -3138,16 +3138,16 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>38.67</v>
+        <v>39.44</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.22</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.56</v>
+        <v>10.67</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.67</v>
+        <v>6.78</v>
       </c>
       <c r="BC6" t="n">
         <v>3.89</v>
@@ -3156,7 +3156,7 @@
         <v>24.11</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BF6" t="n">
         <v>2.11</v>
@@ -3344,10 +3344,10 @@
         <v>15.07</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.4</v>
+        <v>13.27</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.54</v>
+        <v>10.8</v>
       </c>
       <c r="DS6" t="n">
         <v>0.2</v>
@@ -3359,16 +3359,16 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>41.8</v>
+        <v>42.26</v>
       </c>
       <c r="DW6" t="n">
         <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.27</v>
+        <v>10.33</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.53</v>
+        <v>6.6</v>
       </c>
       <c r="DZ6" t="n">
         <v>3.73</v>
@@ -3377,7 +3377,7 @@
         <v>21.33</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="EC6" t="n">
         <v>2</v>
@@ -3919,10 +3919,10 @@
         <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.25</v>
+        <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.25</v>
+        <v>6.62</v>
       </c>
       <c r="AT8" t="n">
         <v>1.12</v>
@@ -3940,16 +3940,16 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>49.75</v>
+        <v>49.88</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.75</v>
+        <v>13</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="BC8" t="n">
         <v>4.5</v>
@@ -3958,7 +3958,7 @@
         <v>23.75</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="BF8" t="n">
         <v>3.25</v>
@@ -4150,10 +4150,10 @@
         <v>14.5</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.78</v>
+        <v>13.64</v>
       </c>
       <c r="DR8" t="n">
-        <v>5.36</v>
+        <v>6.14</v>
       </c>
       <c r="DS8" t="n">
         <v>0.07000000000000001</v>
@@ -4165,16 +4165,16 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.36</v>
+        <v>51.43</v>
       </c>
       <c r="DW8" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.43</v>
+        <v>13.57</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.710000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ8" t="n">
         <v>4.71</v>
@@ -4183,7 +4183,7 @@
         <v>24.5</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="EC8" t="n">
         <v>3.5</v>
@@ -4322,10 +4322,10 @@
         <v>13.86</v>
       </c>
       <c r="AR9" t="n">
-        <v>17.71</v>
+        <v>17.43</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.14</v>
+        <v>7.57</v>
       </c>
       <c r="AT9" t="n">
         <v>1.86</v>
@@ -4343,25 +4343,25 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>54.71</v>
+        <v>54</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.14</v>
       </c>
       <c r="BA9" t="n">
-        <v>15.29</v>
+        <v>16</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.14</v>
+        <v>10.71</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.14</v>
+        <v>5.29</v>
       </c>
       <c r="BD9" t="n">
         <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="BF9" t="n">
         <v>2.43</v>
@@ -4553,10 +4553,10 @@
         <v>14.72</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.64</v>
+        <v>16.5</v>
       </c>
       <c r="DR9" t="n">
-        <v>5.78</v>
+        <v>6.5</v>
       </c>
       <c r="DS9" t="n">
         <v>0.22</v>
@@ -4568,25 +4568,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.92</v>
+        <v>51.57</v>
       </c>
       <c r="DW9" t="n">
         <v>0.22</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.86</v>
+        <v>14.22</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.279999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="EA9" t="n">
         <v>21.78</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="EC9" t="n">
         <v>2.28</v>
@@ -4725,10 +4725,10 @@
         <v>14.88</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.62</v>
+        <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.119999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT10" t="n">
         <v>0.88</v>
@@ -4746,7 +4746,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>49.5</v>
+        <v>49.38</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.25</v>
@@ -4755,16 +4755,16 @@
         <v>11.88</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.12</v>
+        <v>7.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.88</v>
+        <v>18.75</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BF10" t="n">
         <v>2.88</v>
@@ -4956,10 +4956,10 @@
         <v>13.8</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.8</v>
+        <v>14.73</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.53</v>
+        <v>8</v>
       </c>
       <c r="DS10" t="n">
         <v>0.2</v>
@@ -4971,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.27</v>
+        <v>53.2</v>
       </c>
       <c r="DW10" t="n">
         <v>0.13</v>
@@ -4980,16 +4980,16 @@
         <v>13.27</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.33</v>
+        <v>9.4</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.93</v>
+        <v>3.86</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.34</v>
+        <v>19.27</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="EC10" t="n">
         <v>2.74</v>
@@ -5098,7 +5098,7 @@
         <v>2.71</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
         <v>75.86</v>
@@ -5113,7 +5113,7 @@
         <v>3.71</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AN11" t="n">
         <v>39.29</v>
@@ -5122,16 +5122,16 @@
         <v>2.14</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AQ11" t="n">
         <v>15.29</v>
       </c>
       <c r="AR11" t="n">
-        <v>17.71</v>
+        <v>17.14</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.29</v>
+        <v>6.71</v>
       </c>
       <c r="AT11" t="n">
         <v>1.71</v>
@@ -5149,16 +5149,16 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.57</v>
+        <v>47.14</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.57</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.710000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.14</v>
+        <v>6.43</v>
       </c>
       <c r="BC11" t="n">
         <v>3.57</v>
@@ -5167,7 +5167,7 @@
         <v>22.43</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BF11" t="n">
         <v>4.29</v>
@@ -5200,10 +5200,10 @@
         <v>1.07</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.87</v>
+        <v>5.2</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
@@ -5329,7 +5329,7 @@
         <v>1.8</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="DH11" t="n">
         <v>87.13</v>
@@ -5344,7 +5344,7 @@
         <v>4.4</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="DM11" t="n">
         <v>47</v>
@@ -5353,16 +5353,16 @@
         <v>1.6</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="DP11" t="n">
         <v>13.8</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.73</v>
+        <v>16.47</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.94</v>
+        <v>7.6</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,16 +5374,16 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.07</v>
+        <v>48.87</v>
       </c>
       <c r="DW11" t="n">
         <v>0.33</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.06</v>
+        <v>12.2</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.87</v>
+        <v>8</v>
       </c>
       <c r="DZ11" t="n">
         <v>4.2</v>
@@ -5558,10 +5558,10 @@
         <v>0.43</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.57</v>
+        <v>11.29</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.57</v>
+        <v>6.29</v>
       </c>
       <c r="BC12" t="n">
         <v>5</v>
@@ -5570,7 +5570,7 @@
         <v>20.14</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BF12" t="n">
         <v>2.71</v>
@@ -5639,13 +5639,13 @@
         <v>3.16</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CC12" t="n">
         <v>3.14</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CE12" t="n">
         <v>1.41</v>
@@ -5690,10 +5690,10 @@
         <v>1.44</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CU12" t="n">
         <v>1.35</v>
@@ -5702,7 +5702,7 @@
         <v>1.94</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX12" t="n">
         <v>1.49</v>
@@ -5723,7 +5723,7 @@
         <v>2.2</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="DE12" t="n">
         <v>0.22</v>
@@ -5783,10 +5783,10 @@
         <v>0.22</v>
       </c>
       <c r="DX12" t="n">
-        <v>13</v>
+        <v>12.86</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="DZ12" t="n">
         <v>4.85</v>
@@ -5880,19 +5880,19 @@
         <v>0.43</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.71</v>
+        <v>12.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.710000000000001</v>
+        <v>8</v>
       </c>
       <c r="AB13" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="AC13" t="n">
         <v>21.71</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
         <v>2.29</v>
@@ -6036,13 +6036,13 @@
         <v>2.92</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CA13" t="n">
         <v>3.3</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="CC13" t="n">
         <v>4.48</v>
@@ -6093,7 +6093,7 @@
         <v>1.43</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CT13" t="n">
         <v>2.85</v>
@@ -6108,7 +6108,7 @@
         <v>1.97</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY13" t="n">
         <v>1.79</v>
@@ -6126,7 +6126,7 @@
         <v>2.18</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
@@ -6186,13 +6186,13 @@
         <v>0.28</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.71</v>
+        <v>10.42</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.79</v>
+        <v>7.43</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="EA13" t="n">
         <v>22.14</v>
@@ -6226,7 +6226,7 @@
         <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="H14" t="n">
         <v>76.12</v>
@@ -6241,7 +6241,7 @@
         <v>6.5</v>
       </c>
       <c r="L14" t="n">
-        <v>0.38</v>
+        <v>0.62</v>
       </c>
       <c r="M14" t="n">
         <v>52.5</v>
@@ -6250,16 +6250,16 @@
         <v>1.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="P14" t="n">
         <v>15.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>16.5</v>
+        <v>16.38</v>
       </c>
       <c r="R14" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="S14" t="n">
         <v>1.38</v>
@@ -6277,25 +6277,25 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>52</v>
+        <v>52.38</v>
       </c>
       <c r="Y14" t="n">
         <v>0.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.62</v>
+        <v>16.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>10.25</v>
+        <v>11.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.38</v>
+        <v>5.25</v>
       </c>
       <c r="AC14" t="n">
         <v>24.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="n">
         <v>2.62</v>
@@ -6409,10 +6409,10 @@
         <v>1.07</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.93</v>
+        <v>4.36</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5</v>
+        <v>5.36</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
@@ -6534,7 +6534,7 @@
         <v>1.36</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="DH14" t="n">
         <v>73.28</v>
@@ -6549,7 +6549,7 @@
         <v>5</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="DM14" t="n">
         <v>44.43</v>
@@ -6558,16 +6558,16 @@
         <v>1.79</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="DP14" t="n">
         <v>13.86</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.14</v>
+        <v>17.07</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.710000000000001</v>
+        <v>9</v>
       </c>
       <c r="DS14" t="n">
         <v>0.21</v>
@@ -6579,25 +6579,25 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.36</v>
+        <v>51.57</v>
       </c>
       <c r="DW14" t="n">
         <v>0.36</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.07</v>
+        <v>13.72</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.140000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.93</v>
+        <v>4.86</v>
       </c>
       <c r="EA14" t="n">
         <v>21.5</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="EC14" t="n">
         <v>2.78</v>
@@ -6655,10 +6655,10 @@
         <v>15.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.5</v>
+        <v>15.38</v>
       </c>
       <c r="R15" t="n">
-        <v>8.75</v>
+        <v>10.12</v>
       </c>
       <c r="S15" t="n">
         <v>1.12</v>
@@ -6676,16 +6676,16 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>48.5</v>
+        <v>47.62</v>
       </c>
       <c r="Y15" t="n">
         <v>0.38</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.75</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.12</v>
+        <v>6.25</v>
       </c>
       <c r="AB15" t="n">
         <v>3.62</v>
@@ -6694,7 +6694,7 @@
         <v>18.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE15" t="n">
         <v>3</v>
@@ -6963,10 +6963,10 @@
         <v>14.93</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.57</v>
+        <v>15.5</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.140000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="DS15" t="n">
         <v>0.14</v>
@@ -6978,16 +6978,16 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>48.57</v>
+        <v>48.07</v>
       </c>
       <c r="DW15" t="n">
         <v>0.22</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.43</v>
+        <v>10.5</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.71</v>
+        <v>6.79</v>
       </c>
       <c r="DZ15" t="n">
         <v>3.71</v>
@@ -6996,7 +6996,7 @@
         <v>19.93</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="EC15" t="n">
         <v>2.64</v>
@@ -7457,10 +7457,10 @@
         <v>11.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.29</v>
+        <v>12</v>
       </c>
       <c r="R17" t="n">
-        <v>7.29</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>1.29</v>
@@ -7484,19 +7484,19 @@
         <v>0.57</v>
       </c>
       <c r="Z17" t="n">
-        <v>13</v>
+        <v>12.71</v>
       </c>
       <c r="AA17" t="n">
         <v>8.57</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.43</v>
+        <v>4.14</v>
       </c>
       <c r="AC17" t="n">
         <v>20</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -7769,10 +7769,10 @@
         <v>12.07</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.14</v>
+        <v>11</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.64</v>
+        <v>7.43</v>
       </c>
       <c r="DS17" t="n">
         <v>0.14</v>
@@ -7790,19 +7790,19 @@
         <v>0.5</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.36</v>
+        <v>12.21</v>
       </c>
       <c r="DY17" t="n">
         <v>8.07</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.28</v>
+        <v>4.14</v>
       </c>
       <c r="EA17" t="n">
         <v>21.14</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="EC17" t="n">
         <v>2.43</v>
@@ -7860,10 +7860,10 @@
         <v>14.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>16.62</v>
+        <v>16.38</v>
       </c>
       <c r="R18" t="n">
-        <v>10.12</v>
+        <v>10.62</v>
       </c>
       <c r="S18" t="n">
         <v>1.25</v>
@@ -7881,25 +7881,25 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>45.38</v>
+        <v>45.5</v>
       </c>
       <c r="Y18" t="n">
         <v>0.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.38</v>
+        <v>5.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.62</v>
+        <v>4.75</v>
       </c>
       <c r="AC18" t="n">
         <v>19.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE18" t="n">
         <v>2.75</v>
@@ -8172,10 +8172,10 @@
         <v>13.43</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.78</v>
+        <v>15.65</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.43</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DS18" t="n">
         <v>0.14</v>
@@ -8187,25 +8187,25 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>45.22</v>
+        <v>45.29</v>
       </c>
       <c r="DW18" t="n">
         <v>0.14</v>
       </c>
       <c r="DX18" t="n">
-        <v>10</v>
+        <v>10.14</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.07</v>
+        <v>6.14</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="EA18" t="n">
         <v>19.14</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="EC18" t="n">
         <v>2.57</v>
@@ -8266,7 +8266,7 @@
         <v>13</v>
       </c>
       <c r="R19" t="n">
-        <v>3.29</v>
+        <v>5.14</v>
       </c>
       <c r="S19" t="n">
         <v>1.57</v>
@@ -8284,7 +8284,7 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>56.29</v>
+        <v>57</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -8293,16 +8293,16 @@
         <v>11.29</v>
       </c>
       <c r="AA19" t="n">
-        <v>6.14</v>
+        <v>6.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.14</v>
+        <v>4.71</v>
       </c>
       <c r="AC19" t="n">
         <v>19.71</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AE19" t="n">
         <v>1.71</v>
@@ -8578,7 +8578,7 @@
         <v>15.22</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.58</v>
+        <v>6.5</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8590,7 +8590,7 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.86</v>
+        <v>56.22</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
@@ -8599,16 +8599,16 @@
         <v>11.64</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.92</v>
+        <v>7.14</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.71</v>
+        <v>4.5</v>
       </c>
       <c r="EA19" t="n">
         <v>21.5</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="EC19" t="n">
         <v>2.64</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1908,10 +1908,10 @@
         <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.86</v>
+        <v>15.57</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.57</v>
+        <v>10.86</v>
       </c>
       <c r="AT3" t="n">
         <v>1.57</v>
@@ -1929,16 +1929,16 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>42.71</v>
+        <v>42.29</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.29</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.29</v>
+        <v>10.57</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.29</v>
+        <v>6.57</v>
       </c>
       <c r="BC3" t="n">
         <v>4</v>
@@ -1947,7 +1947,7 @@
         <v>22.86</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="BF3" t="n">
         <v>2.86</v>
@@ -2139,10 +2139,10 @@
         <v>14.64</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.78</v>
+        <v>14.64</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.279999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="DS3" t="n">
         <v>0.07000000000000001</v>
@@ -2154,16 +2154,16 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50.07</v>
+        <v>49.86</v>
       </c>
       <c r="DW3" t="n">
         <v>0.22</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.22</v>
+        <v>15.36</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.22</v>
+        <v>10.36</v>
       </c>
       <c r="DZ3" t="n">
         <v>5</v>
@@ -2172,7 +2172,7 @@
         <v>23.22</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="EC3" t="n">
         <v>2.72</v>
@@ -2636,7 +2636,7 @@
         <v>15.22</v>
       </c>
       <c r="R5" t="n">
-        <v>3.89</v>
+        <v>4.78</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -2654,19 +2654,19 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>57.89</v>
+        <v>58.22</v>
       </c>
       <c r="Y5" t="n">
         <v>0.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.78</v>
+        <v>15</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.220000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.56</v>
+        <v>5.44</v>
       </c>
       <c r="AC5" t="n">
         <v>23.89</v>
@@ -2948,7 +2948,7 @@
         <v>15</v>
       </c>
       <c r="DR5" t="n">
-        <v>4.93</v>
+        <v>5.47</v>
       </c>
       <c r="DS5" t="n">
         <v>0.13</v>
@@ -2960,19 +2960,19 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56</v>
+        <v>56.2</v>
       </c>
       <c r="DW5" t="n">
         <v>0.33</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.67</v>
+        <v>14.8</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.460000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.2</v>
+        <v>5.13</v>
       </c>
       <c r="EA5" t="n">
         <v>25.47</v>
@@ -5531,10 +5531,10 @@
         <v>13.57</v>
       </c>
       <c r="AR12" t="n">
-        <v>16.29</v>
+        <v>15.86</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.43</v>
+        <v>10.57</v>
       </c>
       <c r="AT12" t="n">
         <v>1.86</v>
@@ -5552,16 +5552,16 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>48</v>
+        <v>47.29</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.43</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.29</v>
+        <v>11.57</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.29</v>
+        <v>6.57</v>
       </c>
       <c r="BC12" t="n">
         <v>5</v>
@@ -5570,7 +5570,7 @@
         <v>20.14</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BF12" t="n">
         <v>2.71</v>
@@ -5762,10 +5762,10 @@
         <v>15.14</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15.29</v>
+        <v>15.08</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.5</v>
+        <v>8.07</v>
       </c>
       <c r="DS12" t="n">
         <v>0.07000000000000001</v>
@@ -5777,16 +5777,16 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>51.57</v>
+        <v>51.22</v>
       </c>
       <c r="DW12" t="n">
         <v>0.22</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.86</v>
+        <v>13</v>
       </c>
       <c r="DY12" t="n">
-        <v>8</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ12" t="n">
         <v>4.85</v>
@@ -5853,10 +5853,10 @@
         <v>16.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>15.86</v>
       </c>
       <c r="R13" t="n">
-        <v>7</v>
+        <v>7.86</v>
       </c>
       <c r="S13" t="n">
         <v>1.71</v>
@@ -5874,16 +5874,16 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>42.29</v>
+        <v>43</v>
       </c>
       <c r="Y13" t="n">
         <v>0.43</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.14</v>
+        <v>12.57</v>
       </c>
       <c r="AA13" t="n">
-        <v>8</v>
+        <v>8.43</v>
       </c>
       <c r="AB13" t="n">
         <v>4.14</v>
@@ -5892,7 +5892,7 @@
         <v>21.71</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE13" t="n">
         <v>2.29</v>
@@ -6165,10 +6165,10 @@
         <v>15.14</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.93</v>
+        <v>16.86</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.779999999999999</v>
+        <v>10.22</v>
       </c>
       <c r="DS13" t="n">
         <v>0.07000000000000001</v>
@@ -6180,16 +6180,16 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.43</v>
+        <v>44.78</v>
       </c>
       <c r="DW13" t="n">
         <v>0.28</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.42</v>
+        <v>10.64</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.43</v>
+        <v>7.64</v>
       </c>
       <c r="DZ13" t="n">
         <v>3</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,139 +1469,139 @@
         <v>2.57</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>75.75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>47.14</v>
+        <v>48.62</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.14</v>
+        <v>14.38</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.14</v>
+        <v>14</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.43</v>
+        <v>6.38</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>49.71</v>
+        <v>50.38</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA2" t="n">
-        <v>14.29</v>
+        <v>13.12</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.859999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.43</v>
+        <v>4.75</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.57</v>
+        <v>22.12</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.859999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN2" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="BR2" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS2" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT2" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU2" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BV2" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX2" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY2" t="n">
         <v>2.07</v>
@@ -1613,28 +1613,28 @@
         <v>3.24</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="CE2" t="n">
         <v>1.45</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CH2" t="n">
         <v>1.33</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.89</v>
@@ -1643,19 +1643,19 @@
         <v>1.39</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CN2" t="n">
         <v>2.02</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CQ2" t="n">
         <v>3.95</v>
@@ -1682,7 +1682,7 @@
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.51</v>
@@ -1694,85 +1694,85 @@
         <v>1.4</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF2" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="DH2" t="n">
-        <v>77.78</v>
+        <v>78</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.78</v>
+        <v>51.33</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.22</v>
+        <v>14.34</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.57</v>
+        <v>13.53</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.64</v>
+        <v>6.14</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.28</v>
+        <v>50.6</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.29</v>
+        <v>14.6</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.78</v>
+        <v>5.4</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.36</v>
+        <v>23.06</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.57</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="3">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="G4" t="n">
-        <v>3.83</v>
+        <v>3.14</v>
       </c>
       <c r="H4" t="n">
-        <v>83.33</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="J4" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="K4" t="n">
-        <v>7.17</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>0.83</v>
+        <v>0.57</v>
       </c>
       <c r="M4" t="n">
-        <v>65.17</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O4" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="P4" t="n">
-        <v>15.83</v>
+        <v>16</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>15.43</v>
       </c>
       <c r="R4" t="n">
-        <v>7.67</v>
+        <v>6.43</v>
       </c>
       <c r="S4" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="T4" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>51</v>
+        <v>51.86</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.67</v>
+        <v>17.57</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.17</v>
+        <v>13.14</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="AC4" t="n">
-        <v>28.5</v>
+        <v>29.29</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="AF4" t="n">
         <v>0.12</v>
@@ -2356,70 +2356,70 @@
         <v>2.38</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.57</v>
+        <v>10.27</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.79</v>
+        <v>4.4</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="BR4" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BS4" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BT4" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV4" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.61</v>
+        <v>2.51</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="CA4" t="n">
         <v>3.2</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CC4" t="n">
         <v>3.42</v>
@@ -2428,10 +2428,10 @@
         <v>4.15</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CG4" t="n">
         <v>2.44</v>
@@ -2443,28 +2443,28 @@
         <v>1.7</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CN4" t="n">
         <v>1.83</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="CR4" t="n">
         <v>1.47</v>
@@ -2479,73 +2479,73 @@
         <v>1.34</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="CY4" t="n">
         <v>1.77</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DB4" t="n">
         <v>1.4</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.18</v>
+        <v>4.2</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.57</v>
+        <v>2.33</v>
       </c>
       <c r="DH4" t="n">
-        <v>72.22</v>
+        <v>72.47</v>
       </c>
       <c r="DI4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.5</v>
+        <v>6.47</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="DM4" t="n">
-        <v>51.43</v>
+        <v>52.93</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="DP4" t="n">
-        <v>15.42</v>
+        <v>15.53</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.93</v>
+        <v>12.33</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.79</v>
+        <v>7.2</v>
       </c>
       <c r="DS4" t="n">
         <v>0.14</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.93</v>
+        <v>47.6</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>14.07</v>
+        <v>14.66</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.57</v>
+        <v>10.2</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="EA4" t="n">
-        <v>24.57</v>
+        <v>25.2</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>0.11</v>
@@ -2678,139 +2678,139 @@
         <v>3.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AH5" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AI5" t="n">
-        <v>78.17</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.67</v>
+        <v>5.57</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN5" t="n">
-        <v>48</v>
+        <v>49.14</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16</v>
+        <v>16.43</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.67</v>
+        <v>15.71</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.5</v>
+        <v>5.43</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>53.17</v>
+        <v>53.86</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.5</v>
+        <v>13.57</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.83</v>
+        <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.67</v>
+        <v>4.57</v>
       </c>
       <c r="BD5" t="n">
-        <v>27.83</v>
+        <v>27.14</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="BG5" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.73</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.93</v>
+        <v>1.12</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.73</v>
+        <v>3.56</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.93</v>
+        <v>4.06</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BU5" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BY5" t="n">
         <v>2.02</v>
@@ -2828,13 +2828,13 @@
         <v>2.18</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CG5" t="n">
         <v>2.53</v>
@@ -2846,10 +2846,10 @@
         <v>1.77</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CL5" t="n">
         <v>1.69</v>
@@ -2858,16 +2858,16 @@
         <v>2.49</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO5" t="n">
         <v>1.22</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
@@ -2891,64 +2891,64 @@
         <v>1.51</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DB5" t="n">
         <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.8</v>
+        <v>88.19</v>
       </c>
       <c r="DI5" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.87</v>
+        <v>3.75</v>
       </c>
       <c r="DK5" t="n">
         <v>4.87</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM5" t="n">
-        <v>57.13</v>
+        <v>57.06</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.47</v>
+        <v>15.69</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15</v>
+        <v>15.43</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.47</v>
+        <v>5.06</v>
       </c>
       <c r="DS5" t="n">
         <v>0.13</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.2</v>
+        <v>56.31</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.8</v>
+        <v>14.37</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.67</v>
+        <v>9.32</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
       <c r="EA5" t="n">
-        <v>25.47</v>
+        <v>25.31</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="EC5" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="6">
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
@@ -3402,49 +3402,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G7" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="H7" t="n">
-        <v>83.17</v>
+        <v>81</v>
       </c>
       <c r="I7" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="J7" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="L7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>58</v>
+        <v>56.29</v>
       </c>
       <c r="N7" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="P7" t="n">
-        <v>16.5</v>
+        <v>17.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.83</v>
+        <v>18</v>
       </c>
       <c r="R7" t="n">
-        <v>7.33</v>
+        <v>6.14</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3456,28 +3456,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>57.83</v>
+        <v>56</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.33</v>
+        <v>13.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.67</v>
+        <v>8.43</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.67</v>
+        <v>5</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.17</v>
+        <v>20</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3561,49 +3561,49 @@
         <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.57</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="BR7" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS7" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3612,19 +3612,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CC7" t="n">
         <v>2.42</v>
@@ -3636,7 +3636,7 @@
         <v>1.39</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="CG7" t="n">
         <v>2.83</v>
@@ -3645,43 +3645,43 @@
         <v>1.39</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CK7" t="n">
         <v>1.36</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CM7" t="n">
         <v>2.79</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP7" t="n">
         <v>1.93</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="CR7" t="n">
         <v>1.4</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV7" t="n">
         <v>2.01</v>
@@ -3693,7 +3693,7 @@
         <v>1.48</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.56</v>
@@ -3705,82 +3705,82 @@
         <v>1.32</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.49</v>
+        <v>3.52</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.93000000000001</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="DJ7" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.22</v>
+        <v>51.8</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.21</v>
+        <v>14.93</v>
       </c>
       <c r="DQ7" t="n">
-        <v>16.93</v>
+        <v>17.07</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.21</v>
+        <v>6.66</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.78</v>
+        <v>53.2</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.78</v>
+        <v>13</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.93</v>
+        <v>8.4</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.86</v>
+        <v>4.6</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.07</v>
+        <v>20</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="EC7" t="n">
         <v>4</v>
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -3805,49 +3805,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="G8" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="H8" t="n">
-        <v>92.5</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="K8" t="n">
-        <v>4.33</v>
+        <v>5.29</v>
       </c>
       <c r="L8" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="M8" t="n">
-        <v>62.17</v>
+        <v>63.43</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>2.57</v>
       </c>
       <c r="P8" t="n">
-        <v>15.17</v>
+        <v>14.43</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.83</v>
+        <v>13.71</v>
       </c>
       <c r="R8" t="n">
-        <v>5.5</v>
+        <v>4.57</v>
       </c>
       <c r="S8" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3859,28 +3859,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>53.5</v>
+        <v>53.86</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.33</v>
+        <v>14.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AB8" t="n">
         <v>5</v>
       </c>
       <c r="AC8" t="n">
-        <v>25.5</v>
+        <v>24.57</v>
       </c>
       <c r="AD8" t="n">
         <v>1.7</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.83</v>
+        <v>3.57</v>
       </c>
       <c r="AF8" t="n">
         <v>0.12</v>
@@ -3964,70 +3964,70 @@
         <v>3.25</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.789999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>4</v>
+        <v>4.27</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="BR8" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS8" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT8" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU8" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV8" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX8" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CC8" t="n">
         <v>2.5</v>
@@ -4036,13 +4036,13 @@
         <v>2.65</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CH8" t="n">
         <v>1.34</v>
@@ -4057,13 +4057,13 @@
         <v>1.29</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO8" t="n">
         <v>1.32</v>
@@ -4072,7 +4072,7 @@
         <v>2.06</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="CR8" t="n">
         <v>1.43</v>
@@ -4096,13 +4096,13 @@
         <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.48</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="DB8" t="n">
         <v>1.36</v>
@@ -4114,79 +4114,79 @@
         <v>3.86</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="DG8" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="DH8" t="n">
-        <v>88.06999999999999</v>
+        <v>88.27</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.57</v>
+        <v>3.46</v>
       </c>
       <c r="DK8" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="DM8" t="n">
-        <v>57.43</v>
+        <v>58.34</v>
       </c>
       <c r="DN8" t="n">
         <v>1</v>
       </c>
       <c r="DO8" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.64</v>
+        <v>14.4</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.14</v>
+        <v>5.66</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.43</v>
+        <v>51.74</v>
       </c>
       <c r="DW8" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.57</v>
+        <v>13.53</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.859999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.71</v>
+        <v>4.73</v>
       </c>
       <c r="EA8" t="n">
-        <v>24.5</v>
+        <v>24.13</v>
       </c>
       <c r="EB8" t="n">
         <v>1.6</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -4208,82 +4208,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="G9" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
-        <v>101.43</v>
+        <v>95.75</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="K9" t="n">
-        <v>5.14</v>
+        <v>5.88</v>
       </c>
       <c r="L9" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="M9" t="n">
-        <v>64.56999999999999</v>
+        <v>64.38</v>
       </c>
       <c r="N9" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O9" t="n">
-        <v>2.86</v>
+        <v>3.38</v>
       </c>
       <c r="P9" t="n">
-        <v>15.57</v>
+        <v>14.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.57</v>
+        <v>15.38</v>
       </c>
       <c r="R9" t="n">
-        <v>5.43</v>
+        <v>4.62</v>
       </c>
       <c r="S9" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="T9" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="U9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>49.14</v>
+        <v>51.12</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.43</v>
+        <v>12.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.43</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>4</v>
+        <v>4.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>23.57</v>
+        <v>23.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4367,70 +4367,70 @@
         <v>2.43</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.93</v>
+        <v>10.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BO9" t="n">
         <v>1.07</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.5</v>
+        <v>4.73</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.79</v>
+        <v>4.87</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT9" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU9" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CC9" t="n">
         <v>2.95</v>
@@ -4442,10 +4442,10 @@
         <v>1.42</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH9" t="n">
         <v>1.35</v>
@@ -4460,10 +4460,10 @@
         <v>1.4</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CN9" t="n">
         <v>2.06</v>
@@ -4472,19 +4472,19 @@
         <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CQ9" t="n">
         <v>3.57</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS9" t="n">
         <v>3.09</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CU9" t="n">
         <v>1.37</v>
@@ -4511,85 +4511,85 @@
         <v>1.34</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="DH9" t="n">
-        <v>93.36</v>
+        <v>90.87</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.07</v>
+        <v>5.47</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="DM9" t="n">
-        <v>60</v>
+        <v>60.2</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.22</v>
+        <v>2.54</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.72</v>
+        <v>14.4</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.5</v>
+        <v>16.34</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.57</v>
+        <v>52.46</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.22</v>
+        <v>14.13</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.57</v>
+        <v>9.33</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.78</v>
+        <v>21.93</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="10">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
@@ -4611,82 +4611,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="G10" t="n">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="H10" t="n">
-        <v>75.14</v>
+        <v>79.62</v>
       </c>
       <c r="I10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J10" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="K10" t="n">
-        <v>5.86</v>
+        <v>6.12</v>
       </c>
       <c r="L10" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>53.29</v>
+        <v>55.88</v>
       </c>
       <c r="N10" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O10" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="P10" t="n">
-        <v>12.57</v>
+        <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>15.38</v>
       </c>
       <c r="R10" t="n">
-        <v>6.86</v>
+        <v>5.88</v>
       </c>
       <c r="S10" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="T10" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="U10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57.57</v>
+        <v>57.25</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.86</v>
+        <v>15.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.86</v>
+        <v>12.12</v>
       </c>
       <c r="AB10" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.86</v>
+        <v>20.62</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AF10" t="n">
         <v>0.25</v>
@@ -4770,70 +4770,70 @@
         <v>2.88</v>
       </c>
       <c r="BG10" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
       <c r="BI10" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.73</v>
+        <v>4.38</v>
       </c>
       <c r="BR10" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BU10" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BZ10" t="n">
         <v>2.07</v>
       </c>
-      <c r="BZ10" t="n">
-        <v>2.13</v>
-      </c>
       <c r="CA10" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.28</v>
+        <v>3.33</v>
       </c>
       <c r="CC10" t="n">
         <v>2.55</v>
@@ -4848,7 +4848,7 @@
         <v>2.99</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CH10" t="n">
         <v>1.35</v>
@@ -4860,34 +4860,34 @@
         <v>1.87</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="CU10" t="n">
         <v>1.35</v>
@@ -4902,97 +4902,97 @@
         <v>1.51</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.51</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="DB10" t="n">
         <v>1.37</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="DH10" t="n">
-        <v>80</v>
+        <v>81.94</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.13</v>
+        <v>5.31</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="DM10" t="n">
-        <v>53.27</v>
+        <v>54.56</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.8</v>
+        <v>13.94</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.73</v>
+        <v>14.94</v>
       </c>
       <c r="DR10" t="n">
-        <v>8</v>
+        <v>7.44</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.2</v>
+        <v>53.32</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.27</v>
+        <v>13.57</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.4</v>
+        <v>9.68</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.27</v>
+        <v>19.69</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="11">
@@ -5002,61 +5002,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="G11" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="H11" t="n">
-        <v>97</v>
+        <v>95.56</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="L11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M11" t="n">
-        <v>53.75</v>
+        <v>52.89</v>
       </c>
       <c r="N11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="O11" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>12.5</v>
+        <v>12.89</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.88</v>
+        <v>16.33</v>
       </c>
       <c r="R11" t="n">
-        <v>8.380000000000001</v>
+        <v>7.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="T11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5068,28 +5068,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>50.38</v>
+        <v>49.44</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.12</v>
+        <v>13.67</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.380000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.75</v>
+        <v>4.89</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.62</v>
+        <v>22</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5173,70 +5173,70 @@
         <v>4.29</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.4</v>
+        <v>9.25</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="BL11" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BN11" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU11" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BV11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BW11" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.61</v>
+        <v>2.82</v>
       </c>
       <c r="CA11" t="n">
         <v>3.1</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="CC11" t="n">
         <v>3.09</v>
@@ -5263,7 +5263,7 @@
         <v>1.85</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CL11" t="n">
         <v>1.72</v>
@@ -5281,16 +5281,16 @@
         <v>2.11</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CR11" t="n">
         <v>1.44</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CU11" t="n">
         <v>1.35</v>
@@ -5308,61 +5308,61 @@
         <v>1.84</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB11" t="n">
         <v>1.37</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="DH11" t="n">
-        <v>87.13</v>
+        <v>86.94</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM11" t="n">
-        <v>47</v>
+        <v>46.94</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.8</v>
+        <v>13.94</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.47</v>
+        <v>16.68</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.6</v>
+        <v>7.06</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.87</v>
+        <v>48.43</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.2</v>
+        <v>12.06</v>
       </c>
       <c r="DY11" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.2</v>
+        <v>4.31</v>
       </c>
       <c r="EA11" t="n">
-        <v>22</v>
+        <v>22.19</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC11" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="12">
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5901,136 +5901,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>77</v>
+        <v>74.5</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.71</v>
+        <v>3.25</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.29</v>
+        <v>0.12</v>
       </c>
       <c r="AN13" t="n">
-        <v>38.14</v>
+        <v>37.12</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.71</v>
+        <v>13.62</v>
       </c>
       <c r="AR13" t="n">
-        <v>17.86</v>
+        <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>12.57</v>
+        <v>10.88</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>46.57</v>
+        <v>46.12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.710000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.86</v>
+        <v>6.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="BD13" t="n">
-        <v>22.57</v>
+        <v>22.38</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="BF13" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.210000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BP13" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.14</v>
+        <v>4.73</v>
       </c>
       <c r="BR13" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS13" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU13" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV13" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX13" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY13" t="n">
         <v>2.92</v>
@@ -6039,31 +6039,31 @@
         <v>3.22</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CB13" t="n">
         <v>3.5</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.48</v>
+        <v>4.4</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.19</v>
+        <v>5.16</v>
       </c>
       <c r="CE13" t="n">
         <v>1.43</v>
       </c>
       <c r="CF13" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CH13" t="n">
         <v>1.34</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.91</v>
@@ -6072,22 +6072,22 @@
         <v>1.39</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.71</v>
+        <v>3.79</v>
       </c>
       <c r="CR13" t="n">
         <v>1.43</v>
@@ -6102,106 +6102,106 @@
         <v>1.36</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="CY13" t="n">
         <v>1.79</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DB13" t="n">
         <v>1.37</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="DH13" t="n">
-        <v>78.72</v>
+        <v>77.27</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="DM13" t="n">
-        <v>44.92</v>
+        <v>43.93</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.14</v>
+        <v>15</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.86</v>
+        <v>17</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.22</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.78</v>
+        <v>44.66</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.64</v>
+        <v>10.4</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.64</v>
+        <v>7.4</v>
       </c>
       <c r="DZ13" t="n">
         <v>3</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.14</v>
+        <v>22.07</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14">
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>0.25</v>
@@ -6301,139 +6301,139 @@
         <v>2.62</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AI14" t="n">
-        <v>69.5</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="AL14" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="AN14" t="n">
-        <v>33.67</v>
+        <v>35.29</v>
       </c>
       <c r="AO14" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>12.71</v>
       </c>
       <c r="AR14" t="n">
-        <v>18</v>
+        <v>18.43</v>
       </c>
       <c r="AS14" t="n">
-        <v>10.33</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>50.5</v>
+        <v>49.71</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.67</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.33</v>
+        <v>5.29</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.17</v>
+        <v>18.29</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BF14" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="BG14" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.21</v>
+        <v>11.13</v>
       </c>
       <c r="BI14" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BM14" t="n">
         <v>1</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.36</v>
+        <v>4.93</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT14" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV14" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BY14" t="n">
         <v>2.75</v>
@@ -6442,16 +6442,16 @@
         <v>2.9</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.27</v>
+        <v>3.49</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.81</v>
+        <v>4.04</v>
       </c>
       <c r="CE14" t="n">
         <v>1.38</v>
@@ -6466,19 +6466,19 @@
         <v>1.39</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK14" t="n">
         <v>1.24</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CN14" t="n">
         <v>2.04</v>
@@ -6487,16 +6487,16 @@
         <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CR14" t="n">
         <v>1.39</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CT14" t="n">
         <v>3</v>
@@ -6508,7 +6508,7 @@
         <v>2.06</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
@@ -6525,82 +6525,82 @@
         <v>2</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="DH14" t="n">
-        <v>73.28</v>
+        <v>74</v>
       </c>
       <c r="DI14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.36</v>
+        <v>3.47</v>
       </c>
       <c r="DK14" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DM14" t="n">
-        <v>44.43</v>
+        <v>44.47</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.86</v>
+        <v>14.06</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.07</v>
+        <v>17.34</v>
       </c>
       <c r="DR14" t="n">
-        <v>9</v>
+        <v>8.33</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.57</v>
+        <v>51.13</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.72</v>
+        <v>13.27</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.859999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.86</v>
+        <v>4.67</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.5</v>
+        <v>21.74</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.78</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="15">
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6703,136 +6703,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AH15" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AI15" t="n">
-        <v>68.5</v>
+        <v>65.14</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
-        <v>5</v>
+        <v>4.71</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AN15" t="n">
-        <v>46.17</v>
+        <v>45</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14.17</v>
+        <v>14.14</v>
       </c>
       <c r="AR15" t="n">
-        <v>15.67</v>
+        <v>15.14</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.67</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>48.67</v>
+        <v>46.71</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BA15" t="n">
-        <v>11.33</v>
+        <v>11</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.5</v>
+        <v>7.14</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="BD15" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.14</v>
+        <v>10.4</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN15" t="n">
         <v>1.07</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.21</v>
+        <v>4.47</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.93</v>
+        <v>5</v>
       </c>
       <c r="BR15" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS15" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BT15" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU15" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV15" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX15" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY15" t="n">
         <v>2.44</v>
@@ -6841,34 +6841,34 @@
         <v>2.92</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="CE15" t="n">
         <v>1.32</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CI15" t="n">
         <v>1.78</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CK15" t="n">
         <v>1.28</v>
@@ -6877,19 +6877,19 @@
         <v>1.65</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CO15" t="n">
         <v>1.22</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
@@ -6918,88 +6918,88 @@
         <v>2.12</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC15" t="n">
         <v>2.11</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DH15" t="n">
-        <v>69.43000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.29</v>
+        <v>4.2</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DM15" t="n">
-        <v>40.93</v>
+        <v>40.73</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.93</v>
+        <v>14.87</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.5</v>
+        <v>15.27</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.93</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>48.07</v>
+        <v>47.2</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.79</v>
+        <v>6.67</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.93</v>
+        <v>20.27</v>
       </c>
       <c r="EB15" t="n">
         <v>1.22</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="16">
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>0.14</v>
@@ -8311,46 +8311,46 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.71</v>
+        <v>3.25</v>
       </c>
       <c r="AI19" t="n">
-        <v>89.29000000000001</v>
+        <v>86.88</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.86</v>
+        <v>5.38</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN19" t="n">
-        <v>54.57</v>
+        <v>52.75</v>
       </c>
       <c r="AO19" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14.71</v>
+        <v>15.62</v>
       </c>
       <c r="AR19" t="n">
-        <v>17.43</v>
+        <v>16.75</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.86</v>
+        <v>6.75</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AU19" t="n">
         <v>1</v>
@@ -8365,82 +8365,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>55.43</v>
+        <v>54</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>12</v>
+        <v>12.38</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.71</v>
+        <v>7.62</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.29</v>
+        <v>4.75</v>
       </c>
       <c r="BD19" t="n">
-        <v>23.29</v>
+        <v>22.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.21</v>
+        <v>11.33</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.36</v>
+        <v>5.53</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.86</v>
+        <v>5.8</v>
       </c>
       <c r="BR19" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS19" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV19" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY19" t="n">
         <v>2.15</v>
@@ -8449,22 +8449,22 @@
         <v>2.26</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="CE19" t="n">
         <v>1.4</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CG19" t="n">
         <v>2.71</v>
@@ -8485,10 +8485,10 @@
         <v>1.86</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CO19" t="n">
         <v>1.29</v>
@@ -8497,7 +8497,7 @@
         <v>1.99</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="CR19" t="n">
         <v>1.41</v>
@@ -8512,22 +8512,22 @@
         <v>1.38</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX19" t="n">
         <v>1.54</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.42</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="DB19" t="n">
         <v>1.34</v>
@@ -8545,40 +8545,40 @@
         <v>1.14</v>
       </c>
       <c r="DG19" t="n">
-        <v>3.28</v>
+        <v>3.07</v>
       </c>
       <c r="DH19" t="n">
-        <v>86.22</v>
+        <v>85.13</v>
       </c>
       <c r="DI19" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="DK19" t="n">
-        <v>6.08</v>
+        <v>5.8</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM19" t="n">
-        <v>57.64</v>
+        <v>56.46</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.22</v>
+        <v>15</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8590,28 +8590,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>56.22</v>
+        <v>55.4</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.64</v>
+        <v>11.87</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.14</v>
+        <v>7.13</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.5</v>
+        <v>4.73</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.5</v>
+        <v>21.33</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1505,10 +1505,10 @@
         <v>14.38</v>
       </c>
       <c r="AR2" t="n">
-        <v>14</v>
+        <v>13.62</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.38</v>
+        <v>6.75</v>
       </c>
       <c r="AT2" t="n">
         <v>1.38</v>
@@ -1526,25 +1526,25 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>50.38</v>
+        <v>50.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.12</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.12</v>
+        <v>13.88</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.380000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.75</v>
+        <v>4.88</v>
       </c>
       <c r="BD2" t="n">
-        <v>22.12</v>
+        <v>21.88</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="BF2" t="n">
         <v>2.88</v>
@@ -1736,10 +1736,10 @@
         <v>14.34</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.53</v>
+        <v>13.33</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.14</v>
+        <v>6.33</v>
       </c>
       <c r="DS2" t="n">
         <v>0.06</v>
@@ -1751,25 +1751,25 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.6</v>
+        <v>50.67</v>
       </c>
       <c r="DW2" t="n">
         <v>0.2</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.4</v>
+        <v>5.47</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.06</v>
+        <v>22.93</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="EC2" t="n">
         <v>2.74</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="H3" t="n">
-        <v>94.86</v>
+        <v>94.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="J3" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="K3" t="n">
-        <v>9.140000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>73.70999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="N3" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="O3" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="P3" t="n">
-        <v>14.29</v>
+        <v>13.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.71</v>
+        <v>15</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="T3" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>57.43</v>
+        <v>57.88</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>20.14</v>
+        <v>18.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>14.14</v>
+        <v>12.62</v>
       </c>
       <c r="AB3" t="n">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>23.57</v>
+        <v>23.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AF3" t="n">
         <v>0.14</v>
@@ -1953,70 +1953,70 @@
         <v>2.86</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.79</v>
+        <v>11.67</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.64</v>
+        <v>4.73</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU3" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV3" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW3" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX3" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="CA3" t="n">
         <v>3.35</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CC3" t="n">
         <v>3.08</v>
@@ -2049,19 +2049,19 @@
         <v>1.83</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2076,7 +2076,7 @@
         <v>1.41</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW3" t="n">
         <v>1.78</v>
@@ -2085,13 +2085,13 @@
         <v>1.56</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="DB3" t="n">
         <v>1.3</v>
@@ -2100,82 +2100,82 @@
         <v>1.96</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="DE3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.79</v>
+        <v>2.94</v>
       </c>
       <c r="DH3" t="n">
-        <v>83.08</v>
+        <v>83.67</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="DK3" t="n">
         <v>7</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM3" t="n">
-        <v>58.14</v>
+        <v>59.07</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.64</v>
+        <v>14.26</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.64</v>
+        <v>15.27</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.93</v>
+        <v>8.27</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>49.86</v>
+        <v>50.6</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.36</v>
+        <v>14.93</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5</v>
+        <v>5.13</v>
       </c>
       <c r="EA3" t="n">
-        <v>23.22</v>
+        <v>23.2</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="4">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -3003,49 +3003,49 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="G6" t="n">
-        <v>1.67</v>
+        <v>2.43</v>
       </c>
       <c r="H6" t="n">
-        <v>79.83</v>
+        <v>83.29000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>5.14</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>45.17</v>
+        <v>52.29</v>
       </c>
       <c r="N6" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O6" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="P6" t="n">
-        <v>12</v>
+        <v>12.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.17</v>
+        <v>11.14</v>
       </c>
       <c r="R6" t="n">
-        <v>9</v>
+        <v>7.57</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="T6" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>46.5</v>
+        <v>47.71</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.83</v>
+        <v>11.14</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.33</v>
+        <v>7.43</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.17</v>
+        <v>18.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>2.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.4</v>
+        <v>10.69</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BP6" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.53</v>
+        <v>5.75</v>
       </c>
       <c r="BR6" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BS6" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BT6" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BU6" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.46</v>
+        <v>3.37</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CC6" t="n">
         <v>4.65</v>
@@ -3234,10 +3234,10 @@
         <v>4.92</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CG6" t="n">
         <v>2.61</v>
@@ -3246,49 +3246,49 @@
         <v>1.29</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CN6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CP6" t="n">
         <v>1.85</v>
       </c>
-      <c r="CO6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>1.84</v>
-      </c>
       <c r="CQ6" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX6" t="inlineStr"/>
       <c r="CY6" t="n">
@@ -3302,85 +3302,85 @@
         <v>1.32</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.07</v>
+        <v>2.37</v>
       </c>
       <c r="DH6" t="n">
-        <v>76.8</v>
+        <v>78.5</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.27</v>
+        <v>4.56</v>
       </c>
       <c r="DL6" t="n">
         <v>0.06</v>
       </c>
       <c r="DM6" t="n">
-        <v>44.13</v>
+        <v>47.31</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.07</v>
+        <v>15.12</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.27</v>
+        <v>13.5</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.8</v>
+        <v>10.06</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>42.26</v>
+        <v>43.06</v>
       </c>
       <c r="DW6" t="n">
         <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.33</v>
+        <v>10.88</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.6</v>
+        <v>7.06</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.73</v>
+        <v>3.81</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.33</v>
+        <v>21.62</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="EC6" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="7">
@@ -3435,10 +3435,10 @@
         <v>17.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>17.86</v>
       </c>
       <c r="R7" t="n">
-        <v>6.14</v>
+        <v>7.43</v>
       </c>
       <c r="S7" t="n">
         <v>0.86</v>
@@ -3456,25 +3456,25 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>56</v>
+        <v>55.86</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.43</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.43</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AB7" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="AC7" t="n">
         <v>20</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AE7" t="n">
         <v>2.86</v>
@@ -3747,10 +3747,10 @@
         <v>14.93</v>
       </c>
       <c r="DQ7" t="n">
-        <v>17.07</v>
+        <v>17</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.66</v>
+        <v>7.26</v>
       </c>
       <c r="DS7" t="n">
         <v>0.13</v>
@@ -3762,25 +3762,25 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.2</v>
+        <v>53.13</v>
       </c>
       <c r="DW7" t="n">
         <v>0.27</v>
       </c>
       <c r="DX7" t="n">
-        <v>13</v>
+        <v>13.26</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.4</v>
+        <v>8.73</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.6</v>
+        <v>4.53</v>
       </c>
       <c r="EA7" t="n">
         <v>20</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="EC7" t="n">
         <v>4</v>
@@ -4075,13 +4075,13 @@
         <v>3.58</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CU8" t="n">
         <v>1.36</v>
@@ -5026,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="K11" t="n">
         <v>4.67</v>
@@ -5038,7 +5038,7 @@
         <v>52.89</v>
       </c>
       <c r="N11" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
@@ -5089,7 +5089,7 @@
         <v>1.59</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5338,7 +5338,7 @@
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="DK11" t="n">
         <v>4.25</v>
@@ -5350,7 +5350,7 @@
         <v>46.94</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="DO11" t="n">
         <v>1.87</v>
@@ -5395,7 +5395,7 @@
         <v>1.41</v>
       </c>
       <c r="EC11" t="n">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="12">
@@ -5405,61 +5405,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F12" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="G12" t="n">
-        <v>3.57</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>81.86</v>
+        <v>86.62</v>
       </c>
       <c r="I12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J12" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>7.29</v>
+        <v>6.5</v>
       </c>
       <c r="L12" t="n">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="M12" t="n">
-        <v>57.57</v>
+        <v>56.12</v>
       </c>
       <c r="N12" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="O12" t="n">
-        <v>3.57</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>16.71</v>
+        <v>16.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.29</v>
+        <v>14.88</v>
       </c>
       <c r="R12" t="n">
-        <v>5.57</v>
+        <v>4.75</v>
       </c>
       <c r="S12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T12" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5471,28 +5471,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>55.14</v>
+        <v>52.88</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.43</v>
+        <v>13.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.710000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.71</v>
+        <v>4.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>21.57</v>
+        <v>20.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5576,70 +5576,70 @@
         <v>2.71</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.710000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.29</v>
+        <v>3.93</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.57</v>
+        <v>4.2</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS12" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT12" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU12" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV12" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX12" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.79</v>
+        <v>2.69</v>
       </c>
       <c r="CA12" t="n">
         <v>3.16</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CC12" t="n">
         <v>3.14</v>
@@ -5651,10 +5651,10 @@
         <v>1.41</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CH12" t="n">
         <v>1.34</v>
@@ -5672,19 +5672,19 @@
         <v>1.72</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="CO12" t="n">
         <v>1.34</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="CR12" t="n">
         <v>1.44</v>
@@ -5708,64 +5708,64 @@
         <v>1.49</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.55</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DB12" t="n">
         <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.78</v>
+        <v>2.53</v>
       </c>
       <c r="DH12" t="n">
-        <v>79.43000000000001</v>
+        <v>82.13</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.86</v>
+        <v>5.53</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.42</v>
+        <v>0.33</v>
       </c>
       <c r="DM12" t="n">
-        <v>50.78</v>
+        <v>50.46</v>
       </c>
       <c r="DN12" t="n">
         <v>1</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.14</v>
+        <v>14.93</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15.08</v>
+        <v>15.34</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.07</v>
+        <v>7.47</v>
       </c>
       <c r="DS12" t="n">
         <v>0.07000000000000001</v>
@@ -5777,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>51.22</v>
+        <v>50.27</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DX12" t="n">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.85</v>
+        <v>4.6</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.86</v>
+        <v>20.53</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="13">
@@ -6703,7 +6703,7 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AH15" t="n">
         <v>2.86</v>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AL15" t="n">
         <v>4.71</v>
@@ -6778,7 +6778,7 @@
         <v>1.29</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="BG15" t="n">
         <v>2.4</v>
@@ -6930,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="DG15" t="n">
         <v>2.27</v>
@@ -6942,7 +6942,7 @@
         <v>0.13</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="DK15" t="n">
         <v>4.2</v>
@@ -6999,7 +6999,7 @@
         <v>1.22</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="16">
@@ -7009,13 +7009,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7102,136 +7102,136 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AI16" t="n">
-        <v>93.56999999999999</v>
+        <v>88.38</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.71</v>
+        <v>3.12</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>51.86</v>
+        <v>49.75</v>
       </c>
       <c r="AO16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>48.38</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="BE16" t="n">
         <v>1.29</v>
       </c>
-      <c r="AP16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>14.71</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>11.86</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>49.71</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>11.86</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>18.29</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.35</v>
-      </c>
       <c r="BF16" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.57</v>
+        <v>9.6</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BO16" t="n">
         <v>1.07</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.43</v>
+        <v>3.6</v>
       </c>
       <c r="BR16" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS16" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BT16" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU16" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV16" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BY16" t="n">
         <v>2.36</v>
@@ -7246,28 +7246,28 @@
         <v>3.29</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK16" t="n">
         <v>1.35</v>
@@ -7276,19 +7276,19 @@
         <v>1.83</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CO16" t="n">
         <v>1.31</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CR16" t="n">
         <v>1.42</v>
@@ -7303,106 +7303,106 @@
         <v>1.37</v>
       </c>
       <c r="CV16" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CX16" t="n">
         <v>1.55</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.4</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="DB16" t="n">
         <v>1.34</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="DH16" t="n">
-        <v>86.14</v>
+        <v>83.87</v>
       </c>
       <c r="DI16" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.92</v>
+        <v>3.13</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.71</v>
+        <v>4.6</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM16" t="n">
-        <v>53.08</v>
+        <v>51.87</v>
       </c>
       <c r="DN16" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.64</v>
+        <v>15.27</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.93</v>
+        <v>12.67</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.5</v>
+        <v>6.93</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>52.36</v>
+        <v>51.47</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.14</v>
+        <v>12.6</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.57</v>
+        <v>7.13</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.58</v>
+        <v>5.47</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.57</v>
+        <v>20.93</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -7412,13 +7412,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7502,139 +7502,139 @@
         <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="AI17" t="n">
-        <v>87.14</v>
+        <v>85.88</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.57</v>
+        <v>5.62</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AN17" t="n">
-        <v>56.43</v>
+        <v>56.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.86</v>
+        <v>1.25</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.57</v>
+        <v>13.12</v>
       </c>
       <c r="AR17" t="n">
-        <v>10</v>
+        <v>11.25</v>
       </c>
       <c r="AS17" t="n">
-        <v>6</v>
+        <v>5.12</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>46.29</v>
+        <v>46.12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.71</v>
+        <v>11.12</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.57</v>
+        <v>7.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="BD17" t="n">
-        <v>22.29</v>
+        <v>21.62</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="BH17" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.86</v>
+        <v>5.13</v>
       </c>
       <c r="BR17" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS17" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BT17" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU17" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV17" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX17" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY17" t="n">
         <v>1.72</v>
@@ -7646,28 +7646,28 @@
         <v>3.15</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="CE17" t="n">
         <v>1.41</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CH17" t="n">
         <v>1.35</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.84</v>
@@ -7676,7 +7676,7 @@
         <v>1.39</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM17" t="n">
         <v>2.73</v>
@@ -7691,7 +7691,7 @@
         <v>2.04</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="CR17" t="n">
         <v>1.43</v>
@@ -7706,10 +7706,10 @@
         <v>1.37</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX17" t="n">
         <v>1.56</v>
@@ -7727,85 +7727,85 @@
         <v>1.36</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="DH17" t="n">
-        <v>82.92</v>
+        <v>82.53</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.22</v>
+        <v>5.27</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DM17" t="n">
-        <v>52.72</v>
+        <v>53</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="DO17" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.07</v>
+        <v>12.4</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.43</v>
+        <v>6.87</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>46.08</v>
+        <v>46</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.21</v>
+        <v>11.86</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.07</v>
+        <v>7.87</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.14</v>
+        <v>20.86</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="18">
@@ -7815,13 +7815,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
         <v>0.25</v>
@@ -7908,136 +7908,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AH18" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>84.14</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>52</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AT18" t="n">
         <v>1</v>
       </c>
-      <c r="AI18" t="n">
-        <v>69.17</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>44.67</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AP18" t="n">
+      <c r="AU18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BL18" t="n">
         <v>0.67</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>45</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>18.83</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0.71</v>
-      </c>
       <c r="BM18" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BP18" t="n">
-        <v>2.29</v>
+        <v>2.07</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.93</v>
+        <v>3.6</v>
       </c>
       <c r="BR18" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS18" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BT18" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BU18" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV18" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY18" t="n">
         <v>3.25</v>
@@ -8046,16 +8046,16 @@
         <v>3.55</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.82</v>
+        <v>4.64</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.22</v>
+        <v>5.03</v>
       </c>
       <c r="CE18" t="n">
         <v>1.37</v>
@@ -8064,7 +8064,7 @@
         <v>2.72</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CH18" t="n">
         <v>1.4</v>
@@ -8073,7 +8073,7 @@
         <v>1.95</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK18" t="n">
         <v>1.33</v>
@@ -8082,10 +8082,10 @@
         <v>1.73</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CO18" t="n">
         <v>1.28</v>
@@ -8133,82 +8133,82 @@
         <v>2.03</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="DH18" t="n">
-        <v>74.22</v>
+        <v>80.87</v>
       </c>
       <c r="DI18" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="DK18" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="DL18" t="n">
-        <v>-0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DM18" t="n">
-        <v>46.22</v>
+        <v>49.54</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="DP18" t="n">
-        <v>13.43</v>
+        <v>13.6</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.65</v>
+        <v>15.47</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.710000000000001</v>
+        <v>9</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>45.29</v>
+        <v>46.47</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX18" t="n">
-        <v>10.14</v>
+        <v>10.8</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.14</v>
+        <v>6.53</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4</v>
+        <v>4.26</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.14</v>
+        <v>18.8</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="19">
@@ -8503,10 +8503,10 @@
         <v>1.41</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CU19" t="n">
         <v>1.38</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1830,7 +1830,7 @@
         <v>15</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="S3" t="n">
         <v>1.38</v>
@@ -1848,25 +1848,25 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>57.88</v>
+        <v>57.75</v>
       </c>
       <c r="Y3" t="n">
         <v>0.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>18.75</v>
+        <v>19.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.62</v>
+        <v>13.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.12</v>
+        <v>6.25</v>
       </c>
       <c r="AC3" t="n">
         <v>23.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="AE3" t="n">
         <v>2.5</v>
@@ -2142,7 +2142,7 @@
         <v>15.27</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.27</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DS3" t="n">
         <v>0.13</v>
@@ -2154,25 +2154,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50.6</v>
+        <v>50.54</v>
       </c>
       <c r="DW3" t="n">
         <v>0.2</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.93</v>
+        <v>15.47</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.27</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.13</v>
+        <v>5.2</v>
       </c>
       <c r="EA3" t="n">
         <v>23.2</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="EC3" t="n">
         <v>2.67</v>
@@ -2714,10 +2714,10 @@
         <v>16.43</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.71</v>
+        <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.43</v>
+        <v>6.29</v>
       </c>
       <c r="AT5" t="n">
         <v>0.29</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>53.86</v>
+        <v>52.29</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.14</v>
@@ -2744,16 +2744,16 @@
         <v>13.57</v>
       </c>
       <c r="BB5" t="n">
-        <v>9</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.57</v>
+        <v>4.43</v>
       </c>
       <c r="BD5" t="n">
         <v>27.14</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="BF5" t="n">
         <v>3.14</v>
@@ -2945,10 +2945,10 @@
         <v>15.69</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.43</v>
+        <v>15.12</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.06</v>
+        <v>5.44</v>
       </c>
       <c r="DS5" t="n">
         <v>0.13</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.31</v>
+        <v>55.63</v>
       </c>
       <c r="DW5" t="n">
         <v>0.31</v>
@@ -2969,10 +2969,10 @@
         <v>14.37</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.32</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="EA5" t="n">
         <v>25.31</v>
@@ -3039,7 +3039,7 @@
         <v>11.14</v>
       </c>
       <c r="R6" t="n">
-        <v>7.57</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>0.43</v>
@@ -3057,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>47.71</v>
+        <v>49.29</v>
       </c>
       <c r="Y6" t="n">
         <v>-0.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.14</v>
+        <v>11.29</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.43</v>
+        <v>7.57</v>
       </c>
       <c r="AB6" t="n">
         <v>3.71</v>
@@ -3075,7 +3075,7 @@
         <v>18.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -3347,7 +3347,7 @@
         <v>13.5</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.06</v>
+        <v>10.81</v>
       </c>
       <c r="DS6" t="n">
         <v>0.19</v>
@@ -3359,16 +3359,16 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>43.06</v>
+        <v>43.75</v>
       </c>
       <c r="DW6" t="n">
         <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.88</v>
+        <v>10.94</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.06</v>
+        <v>7.13</v>
       </c>
       <c r="DZ6" t="n">
         <v>3.81</v>
@@ -3838,10 +3838,10 @@
         <v>14.43</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.71</v>
+        <v>13.43</v>
       </c>
       <c r="R8" t="n">
-        <v>4.57</v>
+        <v>5.57</v>
       </c>
       <c r="S8" t="n">
         <v>1.57</v>
@@ -3859,25 +3859,25 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>53.86</v>
+        <v>54</v>
       </c>
       <c r="Y8" t="n">
         <v>0.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.14</v>
+        <v>14.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.140000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="AC8" t="n">
         <v>24.57</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AE8" t="n">
         <v>3.57</v>
@@ -4150,10 +4150,10 @@
         <v>14.2</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.4</v>
+        <v>14.27</v>
       </c>
       <c r="DR8" t="n">
-        <v>5.66</v>
+        <v>6.13</v>
       </c>
       <c r="DS8" t="n">
         <v>0.06</v>
@@ -4165,25 +4165,25 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.74</v>
+        <v>51.8</v>
       </c>
       <c r="DW8" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.53</v>
+        <v>13.67</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.73</v>
+        <v>4.8</v>
       </c>
       <c r="EA8" t="n">
         <v>24.13</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="EC8" t="n">
         <v>3.4</v>
@@ -4244,7 +4244,7 @@
         <v>15.38</v>
       </c>
       <c r="R9" t="n">
-        <v>4.62</v>
+        <v>5.88</v>
       </c>
       <c r="S9" t="n">
         <v>1.12</v>
@@ -4262,25 +4262,25 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>51.12</v>
+        <v>50.62</v>
       </c>
       <c r="Y9" t="n">
         <v>0.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.119999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.38</v>
+        <v>4.25</v>
       </c>
       <c r="AC9" t="n">
         <v>23.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AE9" t="n">
         <v>1.88</v>
@@ -4556,7 +4556,7 @@
         <v>16.34</v>
       </c>
       <c r="DR9" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="DS9" t="n">
         <v>0.2</v>
@@ -4568,25 +4568,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52.46</v>
+        <v>52.2</v>
       </c>
       <c r="DW9" t="n">
         <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.13</v>
+        <v>14.67</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.33</v>
+        <v>9.93</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.8</v>
+        <v>4.74</v>
       </c>
       <c r="EA9" t="n">
         <v>21.93</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="EC9" t="n">
         <v>2.14</v>
@@ -5047,10 +5047,10 @@
         <v>12.89</v>
       </c>
       <c r="Q11" t="n">
-        <v>16.33</v>
+        <v>16.22</v>
       </c>
       <c r="R11" t="n">
-        <v>7.33</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>2.44</v>
@@ -5068,7 +5068,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>49.44</v>
+        <v>50.67</v>
       </c>
       <c r="Y11" t="n">
         <v>0.11</v>
@@ -5359,10 +5359,10 @@
         <v>13.94</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.68</v>
+        <v>16.62</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.06</v>
+        <v>7.5</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.43</v>
+        <v>49.13</v>
       </c>
       <c r="DW11" t="n">
         <v>0.31</v>
@@ -5432,7 +5432,7 @@
         <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>6.5</v>
+        <v>6.62</v>
       </c>
       <c r="L12" t="n">
         <v>0.5</v>
@@ -5450,10 +5450,10 @@
         <v>16.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.88</v>
+        <v>14.62</v>
       </c>
       <c r="R12" t="n">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="S12" t="n">
         <v>1.25</v>
@@ -5471,25 +5471,25 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.88</v>
+        <v>52.38</v>
       </c>
       <c r="Y12" t="n">
         <v>0.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.5</v>
+        <v>13.88</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.25</v>
+        <v>9.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.88</v>
+        <v>21.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AE12" t="n">
         <v>2.25</v>
@@ -5579,7 +5579,7 @@
         <v>3</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.33</v>
+        <v>9.4</v>
       </c>
       <c r="BI12" t="n">
         <v>3</v>
@@ -5744,7 +5744,7 @@
         <v>2.87</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.53</v>
+        <v>5.6</v>
       </c>
       <c r="DL12" t="n">
         <v>0.33</v>
@@ -5762,10 +5762,10 @@
         <v>14.93</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15.34</v>
+        <v>15.2</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.47</v>
+        <v>8.27</v>
       </c>
       <c r="DS12" t="n">
         <v>0.07000000000000001</v>
@@ -5777,25 +5777,25 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.27</v>
+        <v>50</v>
       </c>
       <c r="DW12" t="n">
         <v>0.26</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="DY12" t="n">
-        <v>8</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.53</v>
+        <v>20.66</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="EC12" t="n">
         <v>2.46</v>
@@ -6736,10 +6736,10 @@
         <v>14.14</v>
       </c>
       <c r="AR15" t="n">
-        <v>15.14</v>
+        <v>14.86</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.140000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="AT15" t="n">
         <v>1.86</v>
@@ -6757,25 +6757,25 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>46.71</v>
+        <v>47.29</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.14</v>
       </c>
       <c r="BA15" t="n">
-        <v>11</v>
+        <v>11.71</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.14</v>
+        <v>7.71</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="BD15" t="n">
         <v>22</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="BF15" t="n">
         <v>2</v>
@@ -6963,10 +6963,10 @@
         <v>14.87</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.27</v>
+        <v>15.14</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DS15" t="n">
         <v>0.13</v>
@@ -6978,25 +6978,25 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.2</v>
+        <v>47.47</v>
       </c>
       <c r="DW15" t="n">
         <v>0.27</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.4</v>
+        <v>10.73</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.67</v>
+        <v>6.93</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.73</v>
+        <v>3.8</v>
       </c>
       <c r="EA15" t="n">
         <v>20.27</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="EC15" t="n">
         <v>2.53</v>
@@ -7138,7 +7138,7 @@
         <v>11.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.12</v>
+        <v>8</v>
       </c>
       <c r="AT16" t="n">
         <v>0.5</v>
@@ -7156,25 +7156,25 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>48.38</v>
+        <v>48.5</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.38</v>
       </c>
       <c r="BA16" t="n">
-        <v>11</v>
+        <v>11.38</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.62</v>
+        <v>8</v>
       </c>
       <c r="BC16" t="n">
         <v>3.38</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.25</v>
+        <v>19.12</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="BF16" t="n">
         <v>2.75</v>
@@ -7369,7 +7369,7 @@
         <v>12.67</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.93</v>
+        <v>7.4</v>
       </c>
       <c r="DS16" t="n">
         <v>0.2</v>
@@ -7381,25 +7381,25 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.47</v>
+        <v>51.53</v>
       </c>
       <c r="DW16" t="n">
         <v>0.27</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.13</v>
+        <v>7.33</v>
       </c>
       <c r="DZ16" t="n">
         <v>5.47</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.93</v>
+        <v>20.87</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="EC16" t="n">
         <v>2.8</v>
@@ -7538,10 +7538,10 @@
         <v>13.12</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.25</v>
+        <v>10.88</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.12</v>
+        <v>6.38</v>
       </c>
       <c r="AT17" t="n">
         <v>1.25</v>
@@ -7559,19 +7559,19 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>46.12</v>
+        <v>44.75</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.62</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.12</v>
+        <v>11.25</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="BD17" t="n">
         <v>21.62</v>
@@ -7769,10 +7769,10 @@
         <v>12.4</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.87</v>
+        <v>7.54</v>
       </c>
       <c r="DS17" t="n">
         <v>0.13</v>
@@ -7784,19 +7784,19 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>46</v>
+        <v>45.27</v>
       </c>
       <c r="DW17" t="n">
         <v>0.6</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.86</v>
+        <v>11.93</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.87</v>
+        <v>8</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="EA17" t="n">
         <v>20.86</v>
@@ -7944,7 +7944,7 @@
         <v>14.43</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.14</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AT18" t="n">
         <v>1</v>
@@ -7962,25 +7962,25 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>47.57</v>
+        <v>48.14</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.43</v>
+        <v>12</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.71</v>
+        <v>8.43</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.71</v>
+        <v>3.57</v>
       </c>
       <c r="BD18" t="n">
-        <v>18.14</v>
+        <v>18.43</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="BF18" t="n">
         <v>2.14</v>
@@ -7989,7 +7989,7 @@
         <v>2.13</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.529999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BI18" t="n">
         <v>2.13</v>
@@ -8175,7 +8175,7 @@
         <v>15.47</v>
       </c>
       <c r="DR18" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DS18" t="n">
         <v>0.13</v>
@@ -8187,25 +8187,25 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.47</v>
+        <v>46.73</v>
       </c>
       <c r="DW18" t="n">
         <v>0.13</v>
       </c>
       <c r="DX18" t="n">
-        <v>10.8</v>
+        <v>11.07</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.53</v>
+        <v>6.87</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.26</v>
+        <v>4.2</v>
       </c>
       <c r="EA18" t="n">
-        <v>18.8</v>
+        <v>18.94</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="EC18" t="n">
         <v>2.47</v>
@@ -8344,10 +8344,10 @@
         <v>15.62</v>
       </c>
       <c r="AR19" t="n">
-        <v>16.75</v>
+        <v>16.62</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.75</v>
+        <v>7.62</v>
       </c>
       <c r="AT19" t="n">
         <v>0.75</v>
@@ -8365,25 +8365,25 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>54</v>
+        <v>53.88</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.38</v>
+        <v>12</v>
       </c>
       <c r="BB19" t="n">
         <v>7.62</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.75</v>
+        <v>4.38</v>
       </c>
       <c r="BD19" t="n">
         <v>22.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="BF19" t="n">
         <v>3.38</v>
@@ -8575,10 +8575,10 @@
         <v>15</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15</v>
+        <v>14.93</v>
       </c>
       <c r="DR19" t="n">
-        <v>6</v>
+        <v>6.46</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8590,25 +8590,25 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.4</v>
+        <v>55.34</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.87</v>
+        <v>11.67</v>
       </c>
       <c r="DY19" t="n">
         <v>7.13</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.73</v>
+        <v>4.53</v>
       </c>
       <c r="EA19" t="n">
         <v>21.33</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="EC19" t="n">
         <v>2.6</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.38</v>
+        <v>52.5</v>
       </c>
       <c r="Y12" t="n">
         <v>0.12</v>
@@ -5777,7 +5777,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50</v>
+        <v>50.07</v>
       </c>
       <c r="DW12" t="n">
         <v>0.26</v>
@@ -7962,7 +7962,7 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>48.14</v>
+        <v>48</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -7971,16 +7971,16 @@
         <v>12</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.43</v>
+        <v>8.57</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.57</v>
+        <v>3.43</v>
       </c>
       <c r="BD18" t="n">
         <v>18.43</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="BF18" t="n">
         <v>2.14</v>
@@ -8187,7 +8187,7 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.73</v>
+        <v>46.67</v>
       </c>
       <c r="DW18" t="n">
         <v>0.13</v>
@@ -8196,16 +8196,16 @@
         <v>11.07</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.87</v>
+        <v>6.93</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.2</v>
+        <v>4.13</v>
       </c>
       <c r="EA18" t="n">
         <v>18.94</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="EC18" t="n">
         <v>2.47</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
@@ -1394,46 +1394,46 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="H2" t="n">
-        <v>80.56999999999999</v>
+        <v>82.75</v>
       </c>
       <c r="I2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J2" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>5.29</v>
+        <v>5.88</v>
       </c>
       <c r="L2" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="M2" t="n">
-        <v>54.43</v>
+        <v>57.12</v>
       </c>
       <c r="N2" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O2" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>14.29</v>
+        <v>13.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>12.62</v>
       </c>
       <c r="R2" t="n">
-        <v>5.86</v>
+        <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>50.86</v>
+        <v>51.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.29</v>
+        <v>16.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.14</v>
+        <v>10.38</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.14</v>
+        <v>5.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.14</v>
+        <v>23.62</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AF2" t="n">
         <v>0.25</v>
@@ -1550,70 +1550,70 @@
         <v>2.88</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.73</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.2</v>
+        <v>4.31</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="BR2" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS2" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT2" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BV2" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX2" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="CC2" t="n">
         <v>3.07</v>
@@ -1622,13 +1622,13 @@
         <v>3.11</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="CH2" t="n">
         <v>1.33</v>
@@ -1637,7 +1637,7 @@
         <v>1.83</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK2" t="n">
         <v>1.39</v>
@@ -1646,100 +1646,100 @@
         <v>1.81</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CO2" t="n">
         <v>1.35</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CU2" t="n">
         <v>1.34</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CX2" t="n">
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.51</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="DB2" t="n">
         <v>1.4</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF2" t="n">
         <v>2.06</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.53</v>
+        <v>2.68</v>
       </c>
       <c r="DH2" t="n">
-        <v>78</v>
+        <v>79.25</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.33</v>
+        <v>52.87</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.34</v>
+        <v>13.82</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.33</v>
+        <v>13.12</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.33</v>
+        <v>6.38</v>
       </c>
       <c r="DS2" t="n">
         <v>0.06</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.67</v>
+        <v>51.12</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DX2" t="n">
-        <v>15</v>
+        <v>15.07</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.529999999999999</v>
+        <v>9.69</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.47</v>
+        <v>5.38</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.93</v>
+        <v>22.75</v>
       </c>
       <c r="EB2" t="n">
         <v>1.7</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,139 +1872,139 @@
         <v>2.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AI3" t="n">
-        <v>71.29000000000001</v>
+        <v>74.12</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.86</v>
+        <v>4.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>42.57</v>
+        <v>42.62</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>14.38</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.57</v>
+        <v>14.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.86</v>
+        <v>10.88</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>42.29</v>
+        <v>42.25</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.57</v>
+        <v>10.12</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.57</v>
+        <v>6.38</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BD3" t="n">
-        <v>22.86</v>
+        <v>22.62</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.67</v>
+        <v>11.69</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.73</v>
+        <v>4.81</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT3" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV3" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BY3" t="n">
         <v>2.03</v>
@@ -2019,19 +2019,19 @@
         <v>3.54</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="CE3" t="n">
         <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CH3" t="n">
         <v>1.39</v>
@@ -2043,16 +2043,16 @@
         <v>1.78</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
@@ -2061,7 +2061,7 @@
         <v>1.91</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2070,7 +2070,7 @@
         <v>2.91</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CU3" t="n">
         <v>1.41</v>
@@ -2085,13 +2085,13 @@
         <v>1.56</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="DB3" t="n">
         <v>1.3</v>
@@ -2100,82 +2100,82 @@
         <v>1.96</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="DH3" t="n">
-        <v>83.67</v>
+        <v>84.31</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="DK3" t="n">
-        <v>7</v>
+        <v>6.69</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DM3" t="n">
-        <v>59.07</v>
+        <v>58.06</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.26</v>
+        <v>14</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.27</v>
+        <v>14.75</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.529999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50.54</v>
+        <v>50</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.47</v>
+        <v>14.93</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.27</v>
+        <v>9.94</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="EA3" t="n">
-        <v>23.2</v>
+        <v>23.06</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3883,139 +3883,139 @@
         <v>3.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AI8" t="n">
-        <v>84.75</v>
+        <v>82.67</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.5</v>
+        <v>5.78</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AN8" t="n">
-        <v>53.88</v>
+        <v>52.11</v>
       </c>
       <c r="AO8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT8" t="n">
         <v>1</v>
       </c>
-      <c r="AP8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AU8" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>49.88</v>
+        <v>49.56</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>13</v>
+        <v>13.44</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="BD8" t="n">
-        <v>23.75</v>
+        <v>22.78</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.07</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BO8" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.27</v>
+        <v>4.19</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.8</v>
+        <v>5.19</v>
       </c>
       <c r="BR8" t="n">
-        <v>86.67</v>
+        <v>81.25</v>
       </c>
       <c r="BS8" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT8" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU8" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX8" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY8" t="n">
         <v>2.03</v>
@@ -4024,22 +4024,22 @@
         <v>2.15</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CB8" t="n">
         <v>3.35</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="CG8" t="n">
         <v>2.67</v>
@@ -4054,10 +4054,10 @@
         <v>1.82</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM8" t="n">
         <v>2.57</v>
@@ -4072,7 +4072,7 @@
         <v>2.06</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="CR8" t="n">
         <v>1.44</v>
@@ -4096,19 +4096,19 @@
         <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.48</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DB8" t="n">
         <v>1.36</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DD8" t="n">
         <v>3.86</v>
@@ -4117,43 +4117,43 @@
         <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.13</v>
+        <v>3.44</v>
       </c>
       <c r="DH8" t="n">
-        <v>88.27</v>
+        <v>86.88</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.46</v>
+        <v>3.37</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.4</v>
+        <v>5.57</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DM8" t="n">
-        <v>58.34</v>
+        <v>57.06</v>
       </c>
       <c r="DN8" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.2</v>
+        <v>13.87</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.27</v>
+        <v>14.5</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.13</v>
+        <v>6.37</v>
       </c>
       <c r="DS8" t="n">
         <v>0.06</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.67</v>
+        <v>13.87</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.869999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="EA8" t="n">
-        <v>24.13</v>
+        <v>23.56</v>
       </c>
       <c r="EB8" t="n">
         <v>1.61</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="9">
@@ -5808,10 +5808,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
@@ -5820,82 +5820,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="H13" t="n">
-        <v>80.43000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="K13" t="n">
-        <v>3.29</v>
+        <v>3.62</v>
       </c>
       <c r="L13" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="M13" t="n">
-        <v>51.71</v>
+        <v>51.75</v>
       </c>
       <c r="N13" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="O13" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="P13" t="n">
-        <v>16.57</v>
+        <v>16.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.86</v>
+        <v>15.12</v>
       </c>
       <c r="R13" t="n">
-        <v>7.86</v>
+        <v>7.5</v>
       </c>
       <c r="S13" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>43</v>
+        <v>44.25</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.57</v>
+        <v>13.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.43</v>
+        <v>9</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.14</v>
+        <v>4.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>21.71</v>
+        <v>21.62</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5979,70 +5979,70 @@
         <v>2.12</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="BH13" t="n">
-        <v>9</v>
+        <v>9.31</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.73</v>
+        <v>5.12</v>
       </c>
       <c r="BR13" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BS13" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BT13" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV13" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX13" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.92</v>
+        <v>3.06</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.22</v>
+        <v>3.33</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CC13" t="n">
         <v>4.4</v>
@@ -6054,7 +6054,7 @@
         <v>1.43</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CG13" t="n">
         <v>2.64</v>
@@ -6063,19 +6063,19 @@
         <v>1.34</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CN13" t="n">
         <v>2.03</v>
@@ -6084,10 +6084,10 @@
         <v>1.36</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.79</v>
+        <v>3.81</v>
       </c>
       <c r="CR13" t="n">
         <v>1.43</v>
@@ -6105,25 +6105,25 @@
         <v>1.87</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX13" t="n">
         <v>1.5</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.51</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB13" t="n">
         <v>1.37</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DD13" t="n">
         <v>3.97</v>
@@ -6132,76 +6132,76 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="DH13" t="n">
-        <v>77.27</v>
+        <v>76</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.27</v>
+        <v>3.44</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.93</v>
+        <v>44.44</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="DP13" t="n">
-        <v>15</v>
+        <v>15.18</v>
       </c>
       <c r="DQ13" t="n">
-        <v>17</v>
+        <v>16.56</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.470000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.66</v>
+        <v>45.18</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.4</v>
+        <v>7.75</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.07</v>
+        <v>22</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="14">

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -3919,7 +3919,7 @@
         <v>13.44</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.33</v>
+        <v>15.44</v>
       </c>
       <c r="AS8" t="n">
         <v>7</v>
@@ -3940,16 +3940,16 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>49.56</v>
+        <v>49.78</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.44</v>
+        <v>13.33</v>
       </c>
       <c r="BB8" t="n">
-        <v>9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BC8" t="n">
         <v>4.44</v>
@@ -4150,7 +4150,7 @@
         <v>13.87</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.5</v>
+        <v>14.56</v>
       </c>
       <c r="DR8" t="n">
         <v>6.37</v>
@@ -4165,16 +4165,16 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.5</v>
+        <v>51.63</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.87</v>
+        <v>13.81</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.130000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="DZ8" t="n">
         <v>4.75</v>
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0.38</v>
@@ -5498,136 +5498,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AI12" t="n">
-        <v>77</v>
+        <v>74.25</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>44</v>
+        <v>43.88</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.57</v>
+        <v>13.25</v>
       </c>
       <c r="AR12" t="n">
-        <v>15.86</v>
+        <v>15.12</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.57</v>
+        <v>10.75</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>47.29</v>
+        <v>45.88</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.57</v>
+        <v>11.38</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.57</v>
+        <v>6.62</v>
       </c>
       <c r="BC12" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="BD12" t="n">
-        <v>20.14</v>
+        <v>20.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="BG12" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.4</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="BR12" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU12" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV12" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX12" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BY12" t="n">
         <v>2.35</v>
@@ -5636,31 +5636,31 @@
         <v>2.69</v>
       </c>
       <c r="CA12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="CC12" t="n">
         <v>3.16</v>
-      </c>
-      <c r="CB12" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="CC12" t="n">
-        <v>3.14</v>
       </c>
       <c r="CD12" t="n">
         <v>3.45</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CH12" t="n">
         <v>1.34</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.85</v>
@@ -5672,10 +5672,10 @@
         <v>1.72</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO12" t="n">
         <v>1.34</v>
@@ -5684,7 +5684,7 @@
         <v>2.13</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="CR12" t="n">
         <v>1.44</v>
@@ -5702,7 +5702,7 @@
         <v>1.94</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX12" t="n">
         <v>1.49</v>
@@ -5726,79 +5726,79 @@
         <v>3.93</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="DH12" t="n">
-        <v>82.13</v>
+        <v>80.44</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.6</v>
+        <v>5.56</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DM12" t="n">
-        <v>50.46</v>
+        <v>50</v>
       </c>
       <c r="DN12" t="n">
         <v>1</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.93</v>
+        <v>14.68</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15.2</v>
+        <v>14.87</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.27</v>
+        <v>8.5</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.07</v>
+        <v>49.19</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.8</v>
+        <v>12.63</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.130000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.67</v>
+        <v>4.56</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.66</v>
+        <v>20.81</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -5874,7 +5874,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>44.25</v>
+        <v>44</v>
       </c>
       <c r="Y13" t="n">
         <v>0.38</v>
@@ -6180,7 +6180,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45.18</v>
+        <v>45.06</v>
       </c>
       <c r="DW13" t="n">
         <v>0.32</v>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
@@ -7424,13 +7424,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="G17" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="H17" t="n">
-        <v>78.70999999999999</v>
+        <v>81.88</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -7439,34 +7439,34 @@
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="L17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M17" t="n">
-        <v>49</v>
+        <v>54.12</v>
       </c>
       <c r="N17" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="P17" t="n">
-        <v>11.57</v>
+        <v>11.38</v>
       </c>
       <c r="Q17" t="n">
         <v>12</v>
       </c>
       <c r="R17" t="n">
-        <v>8.859999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T17" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7478,28 +7478,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>45.86</v>
+        <v>48.12</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.71</v>
+        <v>13.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.57</v>
+        <v>8.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.14</v>
+        <v>4.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>20</v>
+        <v>21.62</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AF17" t="n">
         <v>0.12</v>
@@ -7583,70 +7583,70 @@
         <v>3</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.33</v>
+        <v>10.25</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
       <c r="BR17" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS17" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BT17" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV17" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW17" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX17" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CC17" t="n">
         <v>2.79</v>
@@ -7658,16 +7658,16 @@
         <v>1.41</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH17" t="n">
         <v>1.35</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.84</v>
@@ -7676,7 +7676,7 @@
         <v>1.39</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM17" t="n">
         <v>2.73</v>
@@ -7688,10 +7688,10 @@
         <v>1.33</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="CR17" t="n">
         <v>1.43</v>
@@ -7706,10 +7706,10 @@
         <v>1.37</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CX17" t="n">
         <v>1.56</v>
@@ -7736,76 +7736,76 @@
         <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="DH17" t="n">
-        <v>82.53</v>
+        <v>83.88</v>
       </c>
       <c r="DI17" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.27</v>
+        <v>5.18</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM17" t="n">
-        <v>53</v>
+        <v>55.31</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.4</v>
+        <v>12.25</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.4</v>
+        <v>11.44</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.54</v>
+        <v>7.38</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>45.27</v>
+        <v>46.44</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.93</v>
+        <v>12.25</v>
       </c>
       <c r="DY17" t="n">
-        <v>8</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.93</v>
+        <v>4.12</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.86</v>
+        <v>21.62</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F4" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="G4" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>82.29000000000001</v>
+        <v>81.38</v>
       </c>
       <c r="I4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J4" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>66.43000000000001</v>
+        <v>65.25</v>
       </c>
       <c r="N4" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="O4" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
         <v>16</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.43</v>
+        <v>15.25</v>
       </c>
       <c r="R4" t="n">
-        <v>6.43</v>
+        <v>5.5</v>
       </c>
       <c r="S4" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="U4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>51.86</v>
+        <v>51.38</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.57</v>
+        <v>17.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.14</v>
+        <v>13</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>29.29</v>
+        <v>28.62</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AF4" t="n">
         <v>0.12</v>
@@ -2356,70 +2356,70 @@
         <v>2.38</v>
       </c>
       <c r="BG4" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.27</v>
+        <v>10.12</v>
       </c>
       <c r="BI4" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.67</v>
+        <v>3.56</v>
       </c>
       <c r="BR4" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BS4" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BU4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CC4" t="n">
         <v>3.42</v>
@@ -2431,52 +2431,52 @@
         <v>1.36</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="CG4" t="n">
         <v>2.44</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CI4" t="n">
         <v>1.7</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK4" t="n">
         <v>1.34</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="CR4" t="n">
         <v>1.47</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CV4" t="n">
         <v>1.86</v>
@@ -2494,7 +2494,7 @@
         <v>2.55</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DB4" t="n">
         <v>1.4</v>
@@ -2503,82 +2503,82 @@
         <v>2.29</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="DE4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>72.63</v>
+      </c>
+      <c r="DI4" t="n">
         <v>0.06</v>
       </c>
-      <c r="DF4" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="DG4" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="DH4" t="n">
-        <v>72.47</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="DJ4" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.47</v>
+        <v>6.38</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DM4" t="n">
-        <v>52.93</v>
+        <v>53.18</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DP4" t="n">
-        <v>15.53</v>
+        <v>15.56</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.33</v>
+        <v>12.43</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.2</v>
+        <v>6.69</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.6</v>
+        <v>47.63</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX4" t="n">
-        <v>14.66</v>
+        <v>14.81</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.2</v>
+        <v>10.31</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="EA4" t="n">
-        <v>25.2</v>
+        <v>25.12</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="5">
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
@@ -3805,49 +3805,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="G8" t="n">
-        <v>2.71</v>
+        <v>3.5</v>
       </c>
       <c r="H8" t="n">
-        <v>92.29000000000001</v>
+        <v>92.38</v>
       </c>
       <c r="I8" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="J8" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="K8" t="n">
-        <v>5.29</v>
+        <v>6.12</v>
       </c>
       <c r="L8" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="M8" t="n">
-        <v>63.43</v>
+        <v>66.25</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>14.43</v>
+        <v>14.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.43</v>
+        <v>12.88</v>
       </c>
       <c r="R8" t="n">
-        <v>5.57</v>
+        <v>4.75</v>
       </c>
       <c r="S8" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3859,28 +3859,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>54</v>
+        <v>53.25</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.43</v>
+        <v>15.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.289999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.14</v>
+        <v>5.38</v>
       </c>
       <c r="AC8" t="n">
-        <v>24.57</v>
+        <v>24.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="AF8" t="n">
         <v>0.11</v>
@@ -3964,70 +3964,70 @@
         <v>3.11</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.380000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.19</v>
+        <v>4.29</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.19</v>
+        <v>5.47</v>
       </c>
       <c r="BR8" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BT8" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BU8" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV8" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX8" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="CC8" t="n">
         <v>2.42</v>
@@ -4039,10 +4039,10 @@
         <v>1.42</v>
       </c>
       <c r="CF8" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CH8" t="n">
         <v>1.34</v>
@@ -4051,7 +4051,7 @@
         <v>1.88</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CK8" t="n">
         <v>1.31</v>
@@ -4060,28 +4060,28 @@
         <v>1.72</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CO8" t="n">
         <v>1.32</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CU8" t="n">
         <v>1.36</v>
@@ -4096,64 +4096,64 @@
         <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.48</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB8" t="n">
         <v>1.36</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="DE8" t="n">
         <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.44</v>
+        <v>3.76</v>
       </c>
       <c r="DH8" t="n">
-        <v>86.88</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.57</v>
+        <v>5.94</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="DM8" t="n">
-        <v>57.06</v>
+        <v>58.76</v>
       </c>
       <c r="DN8" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.87</v>
+        <v>14.12</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.56</v>
+        <v>14.24</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.37</v>
+        <v>5.94</v>
       </c>
       <c r="DS8" t="n">
         <v>0.06</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.63</v>
+        <v>51.41</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.81</v>
+        <v>14.35</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.07</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.75</v>
+        <v>4.88</v>
       </c>
       <c r="EA8" t="n">
-        <v>23.56</v>
+        <v>23.65</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="9">
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -4208,82 +4208,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>3.44</v>
       </c>
       <c r="H9" t="n">
-        <v>95.75</v>
+        <v>92.78</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="K9" t="n">
-        <v>5.88</v>
+        <v>6.56</v>
       </c>
       <c r="L9" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="M9" t="n">
-        <v>64.38</v>
+        <v>63.56</v>
       </c>
       <c r="N9" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="O9" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="P9" t="n">
-        <v>14.88</v>
+        <v>14.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.38</v>
+        <v>14.33</v>
       </c>
       <c r="R9" t="n">
-        <v>5.88</v>
+        <v>5.11</v>
       </c>
       <c r="S9" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="U9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>50.62</v>
+        <v>50.56</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.25</v>
+        <v>9.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.25</v>
+        <v>4.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>23.62</v>
+        <v>24.22</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4367,70 +4367,70 @@
         <v>2.43</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.2</v>
+        <v>10.44</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.73</v>
+        <v>4.56</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.87</v>
+        <v>5.31</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV9" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="CC9" t="n">
         <v>2.95</v>
@@ -4439,43 +4439,43 @@
         <v>2.98</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF9" t="n">
         <v>2.94</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CH9" t="n">
         <v>1.35</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CL9" t="n">
         <v>1.73</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO9" t="n">
         <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="CR9" t="n">
         <v>1.41</v>
@@ -4490,10 +4490,10 @@
         <v>1.37</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX9" t="n">
         <v>1.5</v>
@@ -4514,82 +4514,82 @@
         <v>2.1</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.53</v>
+        <v>3.06</v>
       </c>
       <c r="DH9" t="n">
-        <v>90.87</v>
+        <v>89.5</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.47</v>
+        <v>5.88</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM9" t="n">
-        <v>60.2</v>
+        <v>60</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.4</v>
+        <v>14.32</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.34</v>
+        <v>15.69</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.67</v>
+        <v>6.19</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52.2</v>
+        <v>52.06</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.67</v>
+        <v>14.88</v>
       </c>
       <c r="DY9" t="n">
         <v>9.93</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.74</v>
+        <v>4.94</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.93</v>
+        <v>22.37</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="10">
@@ -5528,7 +5528,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.25</v>
+        <v>13.38</v>
       </c>
       <c r="AR12" t="n">
         <v>15.12</v>
@@ -5759,7 +5759,7 @@
         <v>2.56</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.68</v>
+        <v>14.75</v>
       </c>
       <c r="DQ12" t="n">
         <v>14.87</v>
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0.25</v>
@@ -6301,139 +6301,139 @@
         <v>2.62</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>71.56999999999999</v>
+        <v>72.62</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN14" t="n">
-        <v>35.29</v>
+        <v>37.75</v>
       </c>
       <c r="AO14" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AP14" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.71</v>
+        <v>12.25</v>
       </c>
       <c r="AR14" t="n">
-        <v>18.43</v>
+        <v>18.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.710000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>49.71</v>
+        <v>50</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.289999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.29</v>
+        <v>6</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BD14" t="n">
-        <v>18.29</v>
+        <v>19.62</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.13</v>
+        <v>11.44</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM14" t="n">
         <v>1</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="BO14" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP14" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.93</v>
+        <v>5.25</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT14" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV14" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BY14" t="n">
         <v>2.75</v>
@@ -6442,22 +6442,22 @@
         <v>2.9</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.49</v>
+        <v>3.6</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.04</v>
+        <v>4.14</v>
       </c>
       <c r="CE14" t="n">
         <v>1.38</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CG14" t="n">
         <v>2.8</v>
@@ -6469,28 +6469,28 @@
         <v>2</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CO14" t="n">
         <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CR14" t="n">
         <v>1.39</v>
@@ -6505,10 +6505,10 @@
         <v>1.4</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
@@ -6528,79 +6528,79 @@
         <v>3.46</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="DH14" t="n">
-        <v>74</v>
+        <v>74.37</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.47</v>
+        <v>3.31</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DM14" t="n">
-        <v>44.47</v>
+        <v>45.12</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="DO14" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.06</v>
+        <v>13.75</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.34</v>
+        <v>17.44</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.33</v>
+        <v>7.75</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.13</v>
+        <v>51.19</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.27</v>
+        <v>13.25</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.6</v>
+        <v>8.75</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.74</v>
+        <v>22.18</v>
       </c>
       <c r="EB14" t="n">
         <v>1.48</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="15">
@@ -7815,13 +7815,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>0.25</v>
@@ -7908,49 +7908,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>84.14</v>
+        <v>81.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0.29</v>
+        <v>-0.12</v>
       </c>
       <c r="AN18" t="n">
-        <v>52</v>
+        <v>50.38</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.29</v>
+        <v>11.38</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.43</v>
+        <v>14.88</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.859999999999999</v>
+        <v>7.62</v>
       </c>
       <c r="AT18" t="n">
         <v>1</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7962,82 +7962,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>48</v>
+        <v>48.25</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>12</v>
+        <v>11.88</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.57</v>
+        <v>8.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="BD18" t="n">
-        <v>18.43</v>
+        <v>20</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.6</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BP18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.6</v>
+        <v>4.12</v>
       </c>
       <c r="BR18" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS18" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BT18" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BU18" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV18" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY18" t="n">
         <v>3.25</v>
@@ -8046,43 +8046,43 @@
         <v>3.55</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CB18" t="n">
         <v>3.62</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.64</v>
+        <v>4.61</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.03</v>
+        <v>5.07</v>
       </c>
       <c r="CE18" t="n">
         <v>1.37</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CH18" t="n">
         <v>1.4</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CL18" t="n">
         <v>1.73</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CN18" t="n">
         <v>2.2</v>
@@ -8136,79 +8136,79 @@
         <v>3.5</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="DH18" t="n">
-        <v>80.87</v>
+        <v>79.75</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.93</v>
+        <v>3.81</v>
       </c>
       <c r="DL18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="DM18" t="n">
-        <v>49.54</v>
+        <v>48.88</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DP18" t="n">
-        <v>13.6</v>
+        <v>13.07</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.47</v>
+        <v>15.63</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.67</v>
+        <v>46.88</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX18" t="n">
         <v>11.07</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.93</v>
+        <v>7</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="EA18" t="n">
-        <v>18.94</v>
+        <v>19.69</v>
       </c>
       <c r="EB18" t="n">
         <v>1.34</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="19">
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>0.14</v>
@@ -8311,136 +8311,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="AI19" t="n">
-        <v>86.88</v>
+        <v>85</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.38</v>
+        <v>5.11</v>
       </c>
       <c r="AM19" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>53.67</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BK19" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN19" t="n">
-        <v>52.75</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>15.62</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>16.62</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>53.88</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0.47</v>
-      </c>
       <c r="BL19" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.53</v>
+        <v>5.56</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.8</v>
+        <v>5.56</v>
       </c>
       <c r="BR19" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS19" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT19" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BV19" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY19" t="n">
         <v>2.15</v>
@@ -8449,34 +8449,34 @@
         <v>2.26</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CK19" t="n">
         <v>1.4</v>
@@ -8485,34 +8485,34 @@
         <v>1.86</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CN19" t="n">
         <v>2.04</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CV19" t="n">
         <v>1.99</v>
-      </c>
-      <c r="CQ19" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CS19" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="CT19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="CU19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CV19" t="n">
-        <v>2</v>
       </c>
       <c r="CW19" t="n">
         <v>1.85</v>
@@ -8533,52 +8533,52 @@
         <v>1.34</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="DG19" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="DH19" t="n">
-        <v>85.13</v>
+        <v>84.19</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.8</v>
+        <v>5.63</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DM19" t="n">
-        <v>56.46</v>
+        <v>56.06</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="DP19" t="n">
-        <v>15</v>
+        <v>14.75</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.93</v>
+        <v>15.37</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.46</v>
+        <v>6</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8590,28 +8590,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.34</v>
+        <v>55.13</v>
       </c>
       <c r="DW19" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.67</v>
+        <v>11.88</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.13</v>
+        <v>7.19</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.53</v>
+        <v>4.69</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.33</v>
+        <v>21.31</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="H2" t="n">
         <v>82.75</v>
@@ -1409,7 +1409,7 @@
         <v>5.88</v>
       </c>
       <c r="L2" t="n">
-        <v>0.62</v>
+        <v>0.75</v>
       </c>
       <c r="M2" t="n">
         <v>57.12</v>
@@ -1418,7 +1418,7 @@
         <v>0.88</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="P2" t="n">
         <v>13.25</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>51.75</v>
+        <v>52</v>
       </c>
       <c r="Y2" t="n">
         <v>0.38</v>
@@ -1469,139 +1469,139 @@
         <v>2.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="AI2" t="n">
-        <v>75.75</v>
+        <v>79.89</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.12</v>
+        <v>5.22</v>
       </c>
       <c r="AM2" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AN2" t="n">
-        <v>48.62</v>
+        <v>49.33</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AP2" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.38</v>
+        <v>14.33</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.62</v>
+        <v>14.22</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.75</v>
+        <v>5.89</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>50.5</v>
+        <v>50.44</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.88</v>
+        <v>13</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>8.33</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.88</v>
+        <v>4.67</v>
       </c>
       <c r="BD2" t="n">
-        <v>21.88</v>
+        <v>22.44</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BG2" t="n">
         <v>2.94</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.880000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI2" t="n">
         <v>2.94</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.31</v>
+        <v>4.24</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.06</v>
+        <v>5.47</v>
       </c>
       <c r="BR2" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT2" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV2" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX2" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY2" t="n">
         <v>2.04</v>
@@ -1610,31 +1610,31 @@
         <v>2.05</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CC2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CD2" t="n">
         <v>3.07</v>
       </c>
-      <c r="CD2" t="n">
-        <v>3.11</v>
-      </c>
       <c r="CE2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CH2" t="n">
         <v>1.33</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.88</v>
@@ -1643,7 +1643,7 @@
         <v>1.39</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM2" t="n">
         <v>2.67</v>
@@ -1655,16 +1655,16 @@
         <v>1.35</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="CR2" t="n">
         <v>1.46</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CT2" t="n">
         <v>2.72</v>
@@ -1703,43 +1703,43 @@
         <v>0.12</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.68</v>
+        <v>3.06</v>
       </c>
       <c r="DH2" t="n">
-        <v>79.25</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="DM2" t="n">
-        <v>52.87</v>
+        <v>53</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DP2" t="n">
         <v>13.82</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.12</v>
+        <v>13.47</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.38</v>
+        <v>5.94</v>
       </c>
       <c r="DS2" t="n">
         <v>0.06</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.12</v>
+        <v>51.17</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.07</v>
+        <v>14.53</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.69</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.38</v>
+        <v>5.24</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.75</v>
+        <v>23</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -1794,88 +1794,88 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="H3" t="n">
-        <v>94.5</v>
+        <v>92</v>
       </c>
       <c r="I3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="J3" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="K3" t="n">
-        <v>8.880000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="L3" t="n">
-        <v>0.12</v>
+        <v>0.67</v>
       </c>
       <c r="M3" t="n">
-        <v>73.5</v>
+        <v>71.11</v>
       </c>
       <c r="N3" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="O3" t="n">
-        <v>2.62</v>
+        <v>4.11</v>
       </c>
       <c r="P3" t="n">
-        <v>13.62</v>
+        <v>14</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>14.89</v>
       </c>
       <c r="R3" t="n">
-        <v>6.5</v>
+        <v>5.67</v>
       </c>
       <c r="S3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="U3" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="V3" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>57.75</v>
+        <v>56.78</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>19.75</v>
+        <v>18.22</v>
       </c>
       <c r="AA3" t="n">
-        <v>13.5</v>
+        <v>12.22</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AC3" t="n">
-        <v>23.5</v>
+        <v>23.56</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AF3" t="n">
         <v>0.12</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="AH3" t="n">
         <v>2.12</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.38</v>
+        <v>3.62</v>
       </c>
       <c r="AL3" t="n">
         <v>4.5</v>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>42.25</v>
+        <v>42.12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="BA3" t="n">
         <v>10.12</v>
@@ -1950,73 +1950,73 @@
         <v>1.21</v>
       </c>
       <c r="BF3" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.69</v>
+        <v>11.59</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.5</v>
+        <v>5.71</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.81</v>
+        <v>5.76</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU3" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV3" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW3" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX3" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="CC3" t="n">
         <v>3.22</v>
@@ -2040,19 +2040,19 @@
         <v>1.98</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
@@ -2061,7 +2061,7 @@
         <v>1.91</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2085,97 +2085,97 @@
         <v>1.56</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC3" t="n">
         <v>1.96</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.81</v>
+        <v>3.29</v>
       </c>
       <c r="DH3" t="n">
-        <v>84.31</v>
+        <v>83.59</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.69</v>
+        <v>6.65</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.25</v>
+        <v>0.53</v>
       </c>
       <c r="DM3" t="n">
-        <v>58.06</v>
+        <v>57.7</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.44</v>
+        <v>3.23</v>
       </c>
       <c r="DP3" t="n">
-        <v>14</v>
+        <v>14.18</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.75</v>
+        <v>14.71</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.69</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50</v>
+        <v>49.88</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.93</v>
+        <v>14.41</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.94</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="EA3" t="n">
-        <v>23.06</v>
+        <v>23.12</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="4">
@@ -2200,7 +2200,7 @@
         <v>2.88</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="n">
         <v>81.38</v>
@@ -2212,10 +2212,10 @@
         <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>6.75</v>
+        <v>6.88</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="M4" t="n">
         <v>65.25</v>
@@ -2224,16 +2224,16 @@
         <v>0.75</v>
       </c>
       <c r="O4" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
         <v>16</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.25</v>
+        <v>14.88</v>
       </c>
       <c r="R4" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -2251,124 +2251,124 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>51.38</v>
+        <v>51.75</v>
       </c>
       <c r="Y4" t="n">
         <v>0.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.5</v>
+        <v>17.88</v>
       </c>
       <c r="AA4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.5</v>
+        <v>4.38</v>
       </c>
       <c r="AC4" t="n">
         <v>28.62</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AE4" t="n">
         <v>3.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>63.88</v>
+        <v>72.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AL4" t="n">
         <v>6</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="n">
-        <v>41.12</v>
+        <v>47.62</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.62</v>
+        <v>0.88</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AQ4" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>42.62</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
         <v>15.12</v>
       </c>
-      <c r="AR4" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>43.88</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>12.12</v>
-      </c>
       <c r="BB4" t="n">
-        <v>7.62</v>
+        <v>10.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.5</v>
+        <v>4.88</v>
       </c>
       <c r="BD4" t="n">
-        <v>21.62</v>
+        <v>24.12</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.12</v>
+        <v>10.19</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL4" t="n">
         <v>0.75</v>
@@ -2380,22 +2380,22 @@
         <v>1.25</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.5</v>
+        <v>5.06</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.56</v>
+        <v>4.31</v>
       </c>
       <c r="BR4" t="n">
-        <v>75</v>
+        <v>81.25</v>
       </c>
       <c r="BS4" t="n">
-        <v>62.5</v>
+        <v>68.75</v>
       </c>
       <c r="BT4" t="n">
-        <v>31.25</v>
+        <v>37.5</v>
       </c>
       <c r="BU4" t="n">
         <v>25</v>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>43.75</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>2.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CA4" t="n">
         <v>3.19</v>
@@ -2467,13 +2467,13 @@
         <v>3.61</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS4" t="n">
         <v>3.29</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CU4" t="n">
         <v>1.33</v>
@@ -2488,64 +2488,64 @@
         <v>1.49</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.55</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
       <c r="DE4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>76.94</v>
+      </c>
+      <c r="DI4" t="n">
         <v>0.12</v>
       </c>
-      <c r="DF4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="DG4" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="DH4" t="n">
-        <v>72.63</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>0.06</v>
-      </c>
       <c r="DJ4" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DO4" t="n">
         <v>3.06</v>
       </c>
-      <c r="DK4" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>53.18</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>2.62</v>
-      </c>
       <c r="DP4" t="n">
-        <v>15.56</v>
+        <v>17.06</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.43</v>
+        <v>12.94</v>
       </c>
       <c r="DR4" t="n">
-        <v>6.69</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS4" t="n">
         <v>0.12</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.63</v>
+        <v>47.18</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="DX4" t="n">
-        <v>14.81</v>
+        <v>16.5</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.31</v>
+        <v>11.88</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.5</v>
+        <v>4.63</v>
       </c>
       <c r="EA4" t="n">
-        <v>25.12</v>
+        <v>26.37</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.82</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="5">
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="K5" t="n">
         <v>4.33</v>
@@ -2624,7 +2624,7 @@
         <v>63.22</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="O5" t="n">
         <v>2.33</v>
@@ -2633,10 +2633,10 @@
         <v>15.11</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.22</v>
+        <v>15.11</v>
       </c>
       <c r="R5" t="n">
-        <v>4.78</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58.22</v>
+        <v>58.33</v>
       </c>
       <c r="Y5" t="n">
         <v>0.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>15</v>
+        <v>15.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.56</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AB5" t="n">
         <v>5.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>23.89</v>
+        <v>23.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.11</v>
+        <v>3.22</v>
       </c>
       <c r="AF5" t="n">
         <v>0.29</v>
@@ -2753,7 +2753,7 @@
         <v>27.14</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="BF5" t="n">
         <v>3.14</v>
@@ -2924,7 +2924,7 @@
         <v>0.13</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.75</v>
+        <v>3.81</v>
       </c>
       <c r="DK5" t="n">
         <v>4.87</v>
@@ -2936,7 +2936,7 @@
         <v>57.06</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="DO5" t="n">
         <v>2</v>
@@ -2945,10 +2945,10 @@
         <v>15.69</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.12</v>
+        <v>15.06</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.44</v>
+        <v>5.56</v>
       </c>
       <c r="DS5" t="n">
         <v>0.13</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.63</v>
+        <v>55.69</v>
       </c>
       <c r="DW5" t="n">
         <v>0.31</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.37</v>
+        <v>14.56</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.380000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="DZ5" t="n">
         <v>5</v>
       </c>
       <c r="EA5" t="n">
-        <v>25.31</v>
+        <v>25.25</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="EC5" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -3003,79 +3003,79 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="G6" t="n">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="H6" t="n">
-        <v>83.29000000000001</v>
+        <v>95</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>5.14</v>
+        <v>5.62</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>52.29</v>
+        <v>60.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="O6" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="P6" t="n">
-        <v>12.57</v>
+        <v>14.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.14</v>
+        <v>14.75</v>
       </c>
       <c r="R6" t="n">
-        <v>9.289999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>0.43</v>
+        <v>0.88</v>
       </c>
       <c r="T6" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>49.29</v>
+        <v>50.62</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.29</v>
+        <v>12.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.57</v>
+        <v>8.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.71</v>
+        <v>4.12</v>
       </c>
       <c r="AC6" t="n">
-        <v>18.43</v>
+        <v>22.62</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
         <v>2.33</v>
@@ -3096,7 +3096,7 @@
         <v>0.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="AL6" t="n">
         <v>4.11</v>
@@ -3108,7 +3108,7 @@
         <v>43.44</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AP6" t="n">
         <v>1.78</v>
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>39.44</v>
+        <v>39.56</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.22</v>
@@ -3159,73 +3159,73 @@
         <v>1.26</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.11</v>
+        <v>2.33</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.69</v>
+        <v>10.82</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.12</v>
+        <v>4.41</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.75</v>
+        <v>6.41</v>
       </c>
       <c r="BR6" t="n">
-        <v>75</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>56.25</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>25</v>
+        <v>35.29</v>
       </c>
       <c r="BU6" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV6" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>31.25</v>
+        <v>41.18</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.37</v>
+        <v>3.21</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CC6" t="n">
         <v>4.65</v>
@@ -3237,49 +3237,49 @@
         <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CH6" t="n">
         <v>1.29</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.72</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CN6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CP6" t="n">
         <v>1.87</v>
       </c>
-      <c r="CO6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>1.85</v>
-      </c>
       <c r="CQ6" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="CR6" t="n">
         <v>1.41</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CU6" t="n">
         <v>1.38</v>
@@ -3288,7 +3288,7 @@
         <v>1.97</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CX6" t="inlineStr"/>
       <c r="CY6" t="n">
@@ -3305,82 +3305,82 @@
         <v>2.03</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.37</v>
+        <v>2.88</v>
       </c>
       <c r="DH6" t="n">
-        <v>78.5</v>
+        <v>84.3</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.56</v>
+        <v>4.82</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DM6" t="n">
-        <v>47.31</v>
+        <v>51.47</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.12</v>
+        <v>16.06</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.5</v>
+        <v>15.06</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.81</v>
+        <v>10.64</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>43.75</v>
+        <v>44.76</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.94</v>
+        <v>11.59</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.13</v>
+        <v>7.59</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.81</v>
+        <v>4</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.62</v>
+        <v>23.41</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="7">
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
@@ -3402,49 +3402,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="G7" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="H7" t="n">
-        <v>81</v>
+        <v>84.88</v>
       </c>
       <c r="I7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J7" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="K7" t="n">
-        <v>4.29</v>
+        <v>4.12</v>
       </c>
       <c r="L7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>56.29</v>
+        <v>57.62</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="O7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="P7" t="n">
-        <v>17.71</v>
+        <v>17</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.86</v>
+        <v>17.38</v>
       </c>
       <c r="R7" t="n">
-        <v>7.43</v>
+        <v>6.38</v>
       </c>
       <c r="S7" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="T7" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>55.86</v>
+        <v>55</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -3465,28 +3465,28 @@
         <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.140000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.86</v>
+        <v>5.25</v>
       </c>
       <c r="AC7" t="n">
         <v>20</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.12</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="n">
         <v>79.25</v>
@@ -3495,13 +3495,13 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>5.62</v>
+        <v>5.75</v>
       </c>
       <c r="AL7" t="n">
         <v>3.75</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
         <v>47.88</v>
@@ -3510,7 +3510,7 @@
         <v>2</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AQ7" t="n">
         <v>12.5</v>
@@ -3519,7 +3519,7 @@
         <v>16.25</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.12</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AT7" t="n">
         <v>1</v>
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>50.75</v>
+        <v>52.12</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.5</v>
@@ -3546,64 +3546,64 @@
         <v>12.62</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.380000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="BD7" t="n">
-        <v>20</v>
+        <v>19.88</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="BF7" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.470000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.8</v>
+        <v>4.31</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.27</v>
+        <v>4.75</v>
       </c>
       <c r="BR7" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS7" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BT7" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU7" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3612,19 +3612,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CA7" t="n">
         <v>3.39</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CC7" t="n">
         <v>2.42</v>
@@ -3636,55 +3636,55 @@
         <v>1.39</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.8</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CO7" t="n">
         <v>1.28</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="CR7" t="n">
         <v>1.4</v>
       </c>
       <c r="CS7" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CU7" t="n">
         <v>1.39</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CW7" t="n">
         <v>1.84</v>
@@ -3714,76 +3714,76 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.86</v>
+        <v>2.31</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.06999999999999</v>
+        <v>82.06</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ7" t="n">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="DK7" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DM7" t="n">
-        <v>51.8</v>
+        <v>52.75</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.93</v>
+        <v>14.75</v>
       </c>
       <c r="DQ7" t="n">
-        <v>17</v>
+        <v>16.81</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.26</v>
+        <v>8</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.13</v>
+        <v>53.56</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.26</v>
+        <v>13.31</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.73</v>
+        <v>8.5</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.53</v>
+        <v>4.81</v>
       </c>
       <c r="EA7" t="n">
-        <v>20</v>
+        <v>19.94</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="EC7" t="n">
-        <v>4</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="8">
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="G8" t="n">
         <v>3.5</v>
@@ -3817,7 +3817,7 @@
         <v>0.25</v>
       </c>
       <c r="J8" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
         <v>6.12</v>
@@ -3838,10 +3838,10 @@
         <v>14.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.88</v>
+        <v>13</v>
       </c>
       <c r="R8" t="n">
-        <v>4.75</v>
+        <v>5.88</v>
       </c>
       <c r="S8" t="n">
         <v>1.5</v>
@@ -3859,28 +3859,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>53.25</v>
+        <v>52.62</v>
       </c>
       <c r="Y8" t="n">
         <v>0.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.5</v>
+        <v>15.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.12</v>
+        <v>10</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.38</v>
+        <v>5.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>24.62</v>
+        <v>24.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="AF8" t="n">
         <v>0.11</v>
@@ -3919,10 +3919,10 @@
         <v>13.44</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.44</v>
+        <v>15.11</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>7.78</v>
       </c>
       <c r="AT8" t="n">
         <v>1</v>
@@ -3940,16 +3940,16 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>49.78</v>
+        <v>50.22</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.33</v>
+        <v>13.78</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.890000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="BC8" t="n">
         <v>4.44</v>
@@ -3958,7 +3958,7 @@
         <v>22.78</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="BF8" t="n">
         <v>3.11</v>
@@ -4027,7 +4027,7 @@
         <v>3.22</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CC8" t="n">
         <v>2.42</v>
@@ -4111,13 +4111,13 @@
         <v>2.14</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="DE8" t="n">
         <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="DG8" t="n">
         <v>3.76</v>
@@ -4129,7 +4129,7 @@
         <v>0.18</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="DK8" t="n">
         <v>5.94</v>
@@ -4150,10 +4150,10 @@
         <v>14.12</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.24</v>
+        <v>14.12</v>
       </c>
       <c r="DR8" t="n">
-        <v>5.94</v>
+        <v>6.89</v>
       </c>
       <c r="DS8" t="n">
         <v>0.06</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.41</v>
+        <v>51.35</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.35</v>
+        <v>14.47</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.470000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.88</v>
+        <v>4.82</v>
       </c>
       <c r="EA8" t="n">
-        <v>23.65</v>
+        <v>23.71</v>
       </c>
       <c r="EB8" t="n">
         <v>1.67</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="9">
@@ -4220,7 +4220,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.33</v>
+        <v>2.56</v>
       </c>
       <c r="K9" t="n">
         <v>6.56</v>
@@ -4232,7 +4232,7 @@
         <v>63.56</v>
       </c>
       <c r="N9" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>3.11</v>
@@ -4244,7 +4244,7 @@
         <v>14.33</v>
       </c>
       <c r="R9" t="n">
-        <v>5.11</v>
+        <v>6.11</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -4262,28 +4262,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>50.56</v>
+        <v>50.11</v>
       </c>
       <c r="Y9" t="n">
         <v>0.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>14</v>
+        <v>14.67</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.33</v>
+        <v>10.11</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.67</v>
+        <v>4.56</v>
       </c>
       <c r="AC9" t="n">
         <v>24.22</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4343,16 +4343,16 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>54</v>
+        <v>53.86</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.14</v>
       </c>
       <c r="BA9" t="n">
-        <v>16</v>
+        <v>15.71</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.71</v>
+        <v>10.43</v>
       </c>
       <c r="BC9" t="n">
         <v>5.29</v>
@@ -4361,7 +4361,7 @@
         <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="BF9" t="n">
         <v>2.43</v>
@@ -4490,31 +4490,31 @@
         <v>1.37</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX9" t="n">
         <v>1.5</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.54</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="DB9" t="n">
         <v>1.34</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
@@ -4532,7 +4532,7 @@
         <v>0.19</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="DK9" t="n">
         <v>5.88</v>
@@ -4544,7 +4544,7 @@
         <v>60</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO9" t="n">
         <v>2.44</v>
@@ -4556,7 +4556,7 @@
         <v>15.69</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.19</v>
+        <v>6.75</v>
       </c>
       <c r="DS9" t="n">
         <v>0.18</v>
@@ -4568,28 +4568,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52.06</v>
+        <v>51.75</v>
       </c>
       <c r="DW9" t="n">
         <v>0.18</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.88</v>
+        <v>15.12</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.93</v>
+        <v>10.25</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.94</v>
+        <v>4.88</v>
       </c>
       <c r="EA9" t="n">
         <v>22.37</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="10">
@@ -4611,10 +4611,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.62</v>
+        <v>3.88</v>
       </c>
       <c r="H10" t="n">
         <v>79.62</v>
@@ -4623,31 +4623,31 @@
         <v>0.12</v>
       </c>
       <c r="J10" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>6.12</v>
+        <v>6.25</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M10" t="n">
         <v>55.88</v>
       </c>
       <c r="N10" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="P10" t="n">
         <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.38</v>
+        <v>15.25</v>
       </c>
       <c r="R10" t="n">
-        <v>5.88</v>
+        <v>6.62</v>
       </c>
       <c r="S10" t="n">
         <v>0.62</v>
@@ -4665,28 +4665,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57.25</v>
+        <v>58.5</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>15.25</v>
+        <v>15.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.12</v>
+        <v>12.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="AC10" t="n">
         <v>20.62</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AF10" t="n">
         <v>0.25</v>
@@ -4695,7 +4695,7 @@
         <v>2.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AI10" t="n">
         <v>84.25</v>
@@ -4710,7 +4710,7 @@
         <v>4.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="AN10" t="n">
         <v>53.25</v>
@@ -4719,7 +4719,7 @@
         <v>0.88</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="AQ10" t="n">
         <v>14.88</v>
@@ -4746,7 +4746,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>49.38</v>
+        <v>49.12</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.25</v>
@@ -4773,7 +4773,7 @@
         <v>1.94</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.19</v>
+        <v>10.25</v>
       </c>
       <c r="BI10" t="n">
         <v>1.94</v>
@@ -4797,10 +4797,10 @@
         <v>0.88</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.88</v>
+        <v>4.19</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.38</v>
+        <v>5.38</v>
       </c>
       <c r="BR10" t="n">
         <v>93.75</v>
@@ -4923,10 +4923,10 @@
         <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.06</v>
+        <v>2.88</v>
       </c>
       <c r="DH10" t="n">
         <v>81.94</v>
@@ -4935,31 +4935,31 @@
         <v>0.12</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.31</v>
+        <v>5.38</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.19</v>
+        <v>0.31</v>
       </c>
       <c r="DM10" t="n">
         <v>54.56</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="DP10" t="n">
         <v>13.94</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.94</v>
+        <v>14.88</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.44</v>
+        <v>7.81</v>
       </c>
       <c r="DS10" t="n">
         <v>0.18</v>
@@ -4971,28 +4971,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.32</v>
+        <v>53.81</v>
       </c>
       <c r="DW10" t="n">
         <v>0.12</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.57</v>
+        <v>13.88</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.68</v>
+        <v>9.93</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="EA10" t="n">
         <v>19.69</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="11">
@@ -5068,25 +5068,25 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>50.67</v>
+        <v>50.89</v>
       </c>
       <c r="Y11" t="n">
         <v>0.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.67</v>
+        <v>13.44</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.779999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.89</v>
+        <v>4.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>22</v>
+        <v>21.89</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="n">
         <v>2.22</v>
@@ -5107,7 +5107,7 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="AL11" t="n">
         <v>3.71</v>
@@ -5119,7 +5119,7 @@
         <v>39.29</v>
       </c>
       <c r="AO11" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="AP11" t="n">
         <v>1.71</v>
@@ -5128,10 +5128,10 @@
         <v>15.29</v>
       </c>
       <c r="AR11" t="n">
-        <v>17.14</v>
+        <v>16.57</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.71</v>
+        <v>8.57</v>
       </c>
       <c r="AT11" t="n">
         <v>1.71</v>
@@ -5149,28 +5149,28 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.14</v>
+        <v>45.86</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.57</v>
       </c>
       <c r="BA11" t="n">
-        <v>10</v>
+        <v>10.57</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.43</v>
+        <v>6.86</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.57</v>
+        <v>3.71</v>
       </c>
       <c r="BD11" t="n">
-        <v>22.43</v>
+        <v>22.29</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.29</v>
+        <v>4.43</v>
       </c>
       <c r="BG11" t="n">
         <v>3.25</v>
@@ -5338,7 +5338,7 @@
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="DK11" t="n">
         <v>4.25</v>
@@ -5350,7 +5350,7 @@
         <v>46.94</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="DO11" t="n">
         <v>1.87</v>
@@ -5359,10 +5359,10 @@
         <v>13.94</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.62</v>
+        <v>16.37</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.5</v>
+        <v>8.31</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.13</v>
+        <v>48.69</v>
       </c>
       <c r="DW11" t="n">
         <v>0.31</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.06</v>
+        <v>12.18</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.75</v>
+        <v>7.88</v>
       </c>
       <c r="DZ11" t="n">
         <v>4.31</v>
       </c>
       <c r="EA11" t="n">
-        <v>22.19</v>
+        <v>22.06</v>
       </c>
       <c r="EB11" t="n">
         <v>1.41</v>
       </c>
       <c r="EC11" t="n">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="12">
@@ -5420,7 +5420,7 @@
         <v>1.62</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="H12" t="n">
         <v>86.62</v>
@@ -5435,7 +5435,7 @@
         <v>6.62</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="M12" t="n">
         <v>56.12</v>
@@ -5444,16 +5444,16 @@
         <v>0.75</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="P12" t="n">
         <v>16.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.62</v>
+        <v>14.12</v>
       </c>
       <c r="R12" t="n">
-        <v>6.25</v>
+        <v>7.75</v>
       </c>
       <c r="S12" t="n">
         <v>1.25</v>
@@ -5471,16 +5471,16 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.5</v>
+        <v>51.88</v>
       </c>
       <c r="Y12" t="n">
         <v>0.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.88</v>
+        <v>14.38</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AB12" t="n">
         <v>4.38</v>
@@ -5489,7 +5489,7 @@
         <v>21.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE12" t="n">
         <v>2.25</v>
@@ -5501,7 +5501,7 @@
         <v>1.88</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="AI12" t="n">
         <v>74.25</v>
@@ -5510,13 +5510,13 @@
         <v>0.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="AL12" t="n">
         <v>4.5</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="AN12" t="n">
         <v>43.88</v>
@@ -5525,7 +5525,7 @@
         <v>1.25</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AQ12" t="n">
         <v>13.38</v>
@@ -5603,10 +5603,10 @@
         <v>1.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>4</v>
+        <v>4.31</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.19</v>
+        <v>4.94</v>
       </c>
       <c r="BR12" t="n">
         <v>93.75</v>
@@ -5732,7 +5732,7 @@
         <v>1.75</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="DH12" t="n">
         <v>80.44</v>
@@ -5741,13 +5741,13 @@
         <v>0.18</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="DK12" t="n">
         <v>5.56</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
         <v>50</v>
@@ -5756,16 +5756,16 @@
         <v>1</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="DP12" t="n">
         <v>14.75</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.87</v>
+        <v>14.62</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.5</v>
+        <v>9.25</v>
       </c>
       <c r="DS12" t="n">
         <v>0.06</v>
@@ -5777,16 +5777,16 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.19</v>
+        <v>48.88</v>
       </c>
       <c r="DW12" t="n">
         <v>0.25</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.63</v>
+        <v>12.88</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.06</v>
+        <v>8.31</v>
       </c>
       <c r="DZ12" t="n">
         <v>4.56</v>
@@ -5795,7 +5795,7 @@
         <v>20.81</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="EC12" t="n">
         <v>2.5</v>
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5832,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="K13" t="n">
         <v>3.62</v>
@@ -5844,7 +5844,7 @@
         <v>51.75</v>
       </c>
       <c r="N13" t="n">
-        <v>0.62</v>
+        <v>0.75</v>
       </c>
       <c r="O13" t="n">
         <v>1.5</v>
@@ -5880,10 +5880,10 @@
         <v>0.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.5</v>
+        <v>13.62</v>
       </c>
       <c r="AA13" t="n">
-        <v>9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AB13" t="n">
         <v>4.5</v>
@@ -5895,142 +5895,142 @@
         <v>1.54</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" t="n">
-        <v>74.5</v>
+        <v>75.44</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>37.12</v>
+        <v>38.89</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.62</v>
+        <v>13.67</v>
       </c>
       <c r="AR13" t="n">
-        <v>18</v>
+        <v>18.11</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.88</v>
+        <v>11.78</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>46.12</v>
+        <v>46</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.5</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="BC13" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="BD13" t="n">
-        <v>22.38</v>
+        <v>21.78</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.31</v>
+        <v>9.59</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.62</v>
+        <v>3.88</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.12</v>
+        <v>5.59</v>
       </c>
       <c r="BR13" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BS13" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU13" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV13" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY13" t="n">
         <v>3.06</v>
@@ -6039,25 +6039,25 @@
         <v>3.33</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.16</v>
+        <v>5.02</v>
       </c>
       <c r="CE13" t="n">
         <v>1.43</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CH13" t="n">
         <v>1.34</v>
@@ -6075,13 +6075,13 @@
         <v>1.85</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CN13" t="n">
         <v>2.03</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP13" t="n">
         <v>2.1</v>
@@ -6093,16 +6093,16 @@
         <v>1.43</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CU13" t="n">
         <v>1.36</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW13" t="n">
         <v>1.97</v>
@@ -6126,55 +6126,55 @@
         <v>2.18</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="DH13" t="n">
-        <v>76</v>
+        <v>76.41</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.37</v>
+        <v>0.47</v>
       </c>
       <c r="DM13" t="n">
-        <v>44.44</v>
+        <v>44.94</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.62</v>
+        <v>0.82</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.18</v>
+        <v>15.12</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.56</v>
+        <v>16.7</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.19</v>
+        <v>9.77</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
@@ -6183,25 +6183,25 @@
         <v>45.06</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DX13" t="n">
-        <v>11</v>
+        <v>11.29</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="EA13" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="14">
@@ -6226,7 +6226,7 @@
         <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>2.12</v>
+        <v>3.25</v>
       </c>
       <c r="H14" t="n">
         <v>76.12</v>
@@ -6241,7 +6241,7 @@
         <v>6.5</v>
       </c>
       <c r="L14" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>52.5</v>
@@ -6250,7 +6250,7 @@
         <v>1.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
         <v>15.25</v>
@@ -6277,16 +6277,16 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>52.38</v>
+        <v>52.62</v>
       </c>
       <c r="Y14" t="n">
         <v>0.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.75</v>
+        <v>16.62</v>
       </c>
       <c r="AA14" t="n">
-        <v>11.5</v>
+        <v>11.38</v>
       </c>
       <c r="AB14" t="n">
         <v>5.25</v>
@@ -6295,7 +6295,7 @@
         <v>24.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AE14" t="n">
         <v>2.62</v>
@@ -6307,7 +6307,7 @@
         <v>1.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AI14" t="n">
         <v>72.62</v>
@@ -6322,7 +6322,7 @@
         <v>3</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.12</v>
+        <v>0.5</v>
       </c>
       <c r="AN14" t="n">
         <v>37.75</v>
@@ -6331,16 +6331,16 @@
         <v>2.12</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AQ14" t="n">
         <v>12.25</v>
       </c>
       <c r="AR14" t="n">
-        <v>18.5</v>
+        <v>18.12</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.5</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AT14" t="n">
         <v>1.88</v>
@@ -6358,25 +6358,25 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>50</v>
+        <v>49.38</v>
       </c>
       <c r="AZ14" t="n">
         <v>0.25</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="BD14" t="n">
         <v>19.62</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BF14" t="n">
         <v>3</v>
@@ -6385,7 +6385,7 @@
         <v>2.75</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.44</v>
+        <v>11.5</v>
       </c>
       <c r="BI14" t="n">
         <v>2.75</v>
@@ -6409,10 +6409,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.12</v>
+        <v>4.69</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.25</v>
+        <v>6.62</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
@@ -6445,13 +6445,13 @@
         <v>3.37</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="CC14" t="n">
         <v>3.6</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.14</v>
+        <v>4.18</v>
       </c>
       <c r="CE14" t="n">
         <v>1.38</v>
@@ -6525,7 +6525,7 @@
         <v>2</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="DE14" t="n">
         <v>0.25</v>
@@ -6534,7 +6534,7 @@
         <v>1.31</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.68</v>
+        <v>2.32</v>
       </c>
       <c r="DH14" t="n">
         <v>74.37</v>
@@ -6549,7 +6549,7 @@
         <v>4.75</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.37</v>
+        <v>0.75</v>
       </c>
       <c r="DM14" t="n">
         <v>45.12</v>
@@ -6558,16 +6558,16 @@
         <v>1.81</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="DP14" t="n">
         <v>13.75</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.44</v>
+        <v>17.25</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.75</v>
+        <v>8.94</v>
       </c>
       <c r="DS14" t="n">
         <v>0.18</v>
@@ -6579,19 +6579,19 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.19</v>
+        <v>51</v>
       </c>
       <c r="DW14" t="n">
         <v>0.32</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.25</v>
+        <v>13.31</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.75</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="EA14" t="n">
         <v>22.18</v>
@@ -6610,19 +6610,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="G15" t="n">
         <v>1.75</v>
@@ -6634,7 +6634,7 @@
         <v>0.25</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="K15" t="n">
         <v>3.75</v>
@@ -6676,7 +6676,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>47.62</v>
+        <v>47.5</v>
       </c>
       <c r="Y15" t="n">
         <v>0.38</v>
@@ -6694,145 +6694,145 @@
         <v>18.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AE15" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AI15" t="n">
-        <v>65.14</v>
+        <v>64.88</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="AM15" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AN15" t="n">
-        <v>45</v>
+        <v>44.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.29</v>
+        <v>0.75</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14.14</v>
+        <v>14.12</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.86</v>
+        <v>15.25</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.57</v>
+        <v>8.25</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AU15" t="n">
         <v>1</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>47.29</v>
+        <v>47.75</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA15" t="n">
-        <v>11.71</v>
+        <v>10.88</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.71</v>
+        <v>6.88</v>
       </c>
       <c r="BC15" t="n">
         <v>4</v>
       </c>
       <c r="BD15" t="n">
-        <v>22</v>
+        <v>21.88</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="BF15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.4</v>
+        <v>10.38</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.47</v>
+        <v>4.56</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="BR15" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS15" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV15" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX15" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BY15" t="n">
         <v>2.44</v>
@@ -6841,16 +6841,16 @@
         <v>2.92</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="CE15" t="n">
         <v>1.32</v>
@@ -6859,37 +6859,37 @@
         <v>2.69</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.71</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
@@ -6911,95 +6911,95 @@
       </c>
       <c r="CX15" t="inlineStr"/>
       <c r="CY15" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CZ15" t="inlineStr"/>
       <c r="DA15" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="DB15" t="n">
         <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.73</v>
+        <v>3.68</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DH15" t="n">
-        <v>67.8</v>
+        <v>67.5</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM15" t="n">
-        <v>40.73</v>
+        <v>40.75</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.87</v>
+        <v>14.81</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.14</v>
+        <v>15.32</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.859999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.47</v>
+        <v>47.62</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.73</v>
+        <v>10.38</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.93</v>
+        <v>6.56</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.27</v>
+        <v>20.31</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="16">
@@ -7009,94 +7009,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F16" t="n">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="G16" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="H16" t="n">
-        <v>78.70999999999999</v>
+        <v>81.62</v>
       </c>
       <c r="I16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J16" t="n">
-        <v>3.14</v>
+        <v>3.62</v>
       </c>
       <c r="K16" t="n">
-        <v>5.29</v>
+        <v>4.75</v>
       </c>
       <c r="L16" t="n">
-        <v>0.29</v>
+        <v>0.62</v>
       </c>
       <c r="M16" t="n">
-        <v>54.29</v>
+        <v>52.38</v>
       </c>
       <c r="N16" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="O16" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="P16" t="n">
-        <v>14.57</v>
+        <v>15.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>14</v>
+        <v>13.88</v>
       </c>
       <c r="R16" t="n">
-        <v>6.71</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="U16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>55</v>
+        <v>53.62</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z16" t="n">
-        <v>14.43</v>
+        <v>14.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.57</v>
+        <v>8</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.86</v>
+        <v>6.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>22.86</v>
+        <v>22.62</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.86</v>
+        <v>3.38</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7156,7 +7156,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>48.5</v>
+        <v>48.62</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.38</v>
@@ -7180,67 +7180,67 @@
         <v>2.75</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.6</v>
+        <v>9.44</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.6</v>
+        <v>4.19</v>
       </c>
       <c r="BR16" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS16" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BT16" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU16" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV16" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CB16" t="n">
         <v>3.29</v>
@@ -7252,19 +7252,19 @@
         <v>3.11</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CH16" t="n">
         <v>1.36</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.81</v>
@@ -7273,19 +7273,19 @@
         <v>1.35</v>
       </c>
       <c r="CL16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CN16" t="n">
         <v>1.83</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>1.82</v>
       </c>
       <c r="CO16" t="n">
         <v>1.31</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ16" t="n">
         <v>3.47</v>
@@ -7294,10 +7294,10 @@
         <v>1.42</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CU16" t="n">
         <v>1.37</v>
@@ -7306,7 +7306,7 @@
         <v>2.01</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX16" t="n">
         <v>1.55</v>
@@ -7324,85 +7324,85 @@
         <v>1.34</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="DE16" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DH16" t="n">
-        <v>83.87</v>
+        <v>85</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.13</v>
+        <v>3.37</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.6</v>
+        <v>4.38</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM16" t="n">
-        <v>51.87</v>
+        <v>51.06</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="DP16" t="n">
-        <v>15.27</v>
+        <v>15.5</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.67</v>
+        <v>12.69</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.4</v>
+        <v>8.06</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.53</v>
+        <v>51.12</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.8</v>
+        <v>12.94</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.33</v>
+        <v>8</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.47</v>
+        <v>4.94</v>
       </c>
       <c r="EA16" t="n">
         <v>20.87</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.8</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="17">
@@ -7412,13 +7412,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7478,7 +7478,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>48.12</v>
+        <v>48.38</v>
       </c>
       <c r="Y17" t="n">
         <v>0.5</v>
@@ -7502,139 +7502,139 @@
         <v>2.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="AI17" t="n">
-        <v>85.88</v>
+        <v>86.11</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.62</v>
+        <v>5.22</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN17" t="n">
-        <v>56.5</v>
+        <v>55.78</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.12</v>
+        <v>12.89</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.88</v>
+        <v>11.11</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.38</v>
+        <v>7.56</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>44.75</v>
+        <v>45.33</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.25</v>
+        <v>11.22</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.5</v>
+        <v>7.44</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="BD17" t="n">
-        <v>21.62</v>
+        <v>21.44</v>
       </c>
       <c r="BE17" t="n">
         <v>1.38</v>
       </c>
       <c r="BF17" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.25</v>
+        <v>9.94</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.62</v>
+        <v>4.53</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.06</v>
+        <v>4.88</v>
       </c>
       <c r="BR17" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS17" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BT17" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU17" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV17" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW17" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX17" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BY17" t="n">
         <v>1.78</v>
@@ -7643,16 +7643,16 @@
         <v>2.07</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="CE17" t="n">
         <v>1.41</v>
@@ -7661,37 +7661,37 @@
         <v>2.98</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CH17" t="n">
         <v>1.35</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.84</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CO17" t="n">
         <v>1.33</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="CR17" t="n">
         <v>1.43</v>
@@ -7727,52 +7727,52 @@
         <v>1.36</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="DE17" t="n">
         <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="DH17" t="n">
-        <v>83.88</v>
+        <v>84.12</v>
       </c>
       <c r="DI17" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.18</v>
+        <v>5</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM17" t="n">
-        <v>55.31</v>
+        <v>55</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DO17" t="n">
         <v>2</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.25</v>
+        <v>12.18</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.44</v>
+        <v>11.53</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.38</v>
+        <v>7.95</v>
       </c>
       <c r="DS17" t="n">
         <v>0.12</v>
@@ -7784,28 +7784,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>46.44</v>
+        <v>46.77</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.25</v>
+        <v>12.18</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.119999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="DZ17" t="n">
         <v>4.12</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.62</v>
+        <v>21.52</v>
       </c>
       <c r="EB17" t="n">
         <v>1.46</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="18">
@@ -7860,7 +7860,7 @@
         <v>14.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>16.38</v>
+        <v>16.5</v>
       </c>
       <c r="R18" t="n">
         <v>10.62</v>
@@ -7887,10 +7887,10 @@
         <v>0.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>10.25</v>
+        <v>10.38</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="AB18" t="n">
         <v>4.75</v>
@@ -7899,7 +7899,7 @@
         <v>19.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
         <v>2.75</v>
@@ -7908,10 +7908,10 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="n">
         <v>81.5</v>
@@ -7926,25 +7926,25 @@
         <v>4</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0.12</v>
+        <v>0.5</v>
       </c>
       <c r="AN18" t="n">
         <v>50.38</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="AQ18" t="n">
         <v>11.38</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.88</v>
+        <v>14.62</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.62</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AT18" t="n">
         <v>1</v>
@@ -7962,25 +7962,25 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>48.25</v>
+        <v>48.62</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.88</v>
+        <v>12.25</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="BD18" t="n">
         <v>20</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BF18" t="n">
         <v>2.12</v>
@@ -8013,10 +8013,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="BP18" t="n">
-        <v>2.06</v>
+        <v>3.19</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.12</v>
+        <v>5.62</v>
       </c>
       <c r="BR18" t="n">
         <v>87.5</v>
@@ -8109,40 +8109,40 @@
         <v>1.4</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX18" t="n">
         <v>1.48</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.58</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="DE18" t="n">
         <v>0.12</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.44</v>
+        <v>2.06</v>
       </c>
       <c r="DH18" t="n">
         <v>79.75</v>
@@ -8157,25 +8157,25 @@
         <v>3.81</v>
       </c>
       <c r="DL18" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="DM18" t="n">
         <v>48.88</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.62</v>
+        <v>1.38</v>
       </c>
       <c r="DP18" t="n">
         <v>13.07</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.63</v>
+        <v>15.56</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.119999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DS18" t="n">
         <v>0.12</v>
@@ -8187,25 +8187,25 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.88</v>
+        <v>47.06</v>
       </c>
       <c r="DW18" t="n">
         <v>0.12</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.07</v>
+        <v>11.32</v>
       </c>
       <c r="DY18" t="n">
-        <v>7</v>
+        <v>7.18</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.06</v>
+        <v>4.12</v>
       </c>
       <c r="EA18" t="n">
         <v>19.69</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EC18" t="n">
         <v>2.44</v>
@@ -8263,10 +8263,10 @@
         <v>14.29</v>
       </c>
       <c r="Q19" t="n">
-        <v>13</v>
+        <v>12.86</v>
       </c>
       <c r="R19" t="n">
-        <v>5.14</v>
+        <v>7.43</v>
       </c>
       <c r="S19" t="n">
         <v>1.57</v>
@@ -8284,25 +8284,25 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>57</v>
+        <v>57.43</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.29</v>
+        <v>13.29</v>
       </c>
       <c r="AA19" t="n">
-        <v>6.57</v>
+        <v>8.57</v>
       </c>
       <c r="AB19" t="n">
         <v>4.71</v>
       </c>
       <c r="AC19" t="n">
-        <v>19.71</v>
+        <v>19.86</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AE19" t="n">
         <v>1.71</v>
@@ -8371,10 +8371,10 @@
         <v>0.11</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.33</v>
+        <v>12.22</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.67</v>
+        <v>7.56</v>
       </c>
       <c r="BC19" t="n">
         <v>4.67</v>
@@ -8458,7 +8458,7 @@
         <v>2.37</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CE19" t="n">
         <v>1.41</v>
@@ -8506,37 +8506,37 @@
         <v>3.09</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CU19" t="n">
         <v>1.37</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX19" t="n">
         <v>1.54</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.42</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="DE19" t="n">
         <v>0.06</v>
@@ -8575,10 +8575,10 @@
         <v>14.75</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.37</v>
+        <v>15.31</v>
       </c>
       <c r="DR19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8590,25 +8590,25 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.13</v>
+        <v>55.32</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.88</v>
+        <v>12.69</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.19</v>
+        <v>8</v>
       </c>
       <c r="DZ19" t="n">
         <v>4.69</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.31</v>
+        <v>21.38</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="EC19" t="n">
         <v>2.62</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="G3" t="n">
         <v>4.33</v>
@@ -1806,7 +1806,7 @@
         <v>0.33</v>
       </c>
       <c r="J3" t="n">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
       <c r="K3" t="n">
         <v>8.56</v>
@@ -1869,7 +1869,7 @@
         <v>2.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="AF3" t="n">
         <v>0.12</v>
@@ -2106,7 +2106,7 @@
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="DG3" t="n">
         <v>3.29</v>
@@ -2118,7 +2118,7 @@
         <v>0.17</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="DK3" t="n">
         <v>6.65</v>
@@ -2175,7 +2175,7 @@
         <v>1.67</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="4">
@@ -6703,7 +6703,7 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="n">
         <v>2.75</v>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AL15" t="n">
         <v>4.62</v>
@@ -6778,7 +6778,7 @@
         <v>1.28</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BG15" t="n">
         <v>2.38</v>
@@ -6930,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DG15" t="n">
         <v>2.25</v>
@@ -6942,7 +6942,7 @@
         <v>0.12</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="DK15" t="n">
         <v>4.19</v>
@@ -6999,7 +6999,7 @@
         <v>1.16</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="16">

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1508,7 +1508,7 @@
         <v>14.22</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.89</v>
+        <v>6.44</v>
       </c>
       <c r="AT2" t="n">
         <v>1.33</v>
@@ -1526,25 +1526,25 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>50.44</v>
+        <v>49.78</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.11</v>
       </c>
       <c r="BA2" t="n">
-        <v>13</v>
+        <v>13.67</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.33</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.67</v>
+        <v>4.78</v>
       </c>
       <c r="BD2" t="n">
         <v>22.44</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BF2" t="n">
         <v>2.78</v>
@@ -1619,7 +1619,7 @@
         <v>3.01</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="CE2" t="n">
         <v>1.45</v>
@@ -1682,13 +1682,13 @@
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.51</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB2" t="n">
         <v>1.4</v>
@@ -1739,7 +1739,7 @@
         <v>13.47</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.94</v>
+        <v>6.23</v>
       </c>
       <c r="DS2" t="n">
         <v>0.06</v>
@@ -1751,25 +1751,25 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.17</v>
+        <v>50.82</v>
       </c>
       <c r="DW2" t="n">
         <v>0.24</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.53</v>
+        <v>14.88</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.289999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.24</v>
+        <v>5.3</v>
       </c>
       <c r="EA2" t="n">
         <v>23</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="EC2" t="n">
         <v>2.65</v>
@@ -1830,7 +1830,7 @@
         <v>14.89</v>
       </c>
       <c r="R3" t="n">
-        <v>5.67</v>
+        <v>6.22</v>
       </c>
       <c r="S3" t="n">
         <v>1.33</v>
@@ -1854,19 +1854,19 @@
         <v>0.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>18.22</v>
+        <v>19</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.22</v>
+        <v>12.89</v>
       </c>
       <c r="AB3" t="n">
-        <v>6</v>
+        <v>6.11</v>
       </c>
       <c r="AC3" t="n">
         <v>23.56</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AE3" t="n">
         <v>2.56</v>
@@ -2010,13 +2010,13 @@
         <v>2.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CA3" t="n">
         <v>3.37</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CC3" t="n">
         <v>3.22</v>
@@ -2085,22 +2085,22 @@
         <v>1.56</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC3" t="n">
         <v>1.96</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
@@ -2142,7 +2142,7 @@
         <v>14.71</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.119999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="DS3" t="n">
         <v>0.17</v>
@@ -2160,19 +2160,19 @@
         <v>0.24</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.41</v>
+        <v>14.82</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.470000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.94</v>
+        <v>5</v>
       </c>
       <c r="EA3" t="n">
         <v>23.12</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="EC3" t="n">
         <v>2.82</v>
@@ -2230,10 +2230,10 @@
         <v>16</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.88</v>
+        <v>14.75</v>
       </c>
       <c r="R4" t="n">
-        <v>6.5</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -2251,25 +2251,25 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>51.75</v>
+        <v>51.38</v>
       </c>
       <c r="Y4" t="n">
         <v>0.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.88</v>
+        <v>18.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.5</v>
+        <v>13.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.38</v>
+        <v>4.5</v>
       </c>
       <c r="AC4" t="n">
         <v>28.62</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AE4" t="n">
         <v>3.25</v>
@@ -2542,10 +2542,10 @@
         <v>17.06</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.94</v>
+        <v>12.88</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.380000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="DS4" t="n">
         <v>0.12</v>
@@ -2557,25 +2557,25 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.18</v>
+        <v>47</v>
       </c>
       <c r="DW4" t="n">
         <v>0.19</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.5</v>
+        <v>16.62</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.88</v>
+        <v>11.93</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.63</v>
+        <v>4.69</v>
       </c>
       <c r="EA4" t="n">
         <v>26.37</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="EC4" t="n">
         <v>3.12</v>
@@ -3036,10 +3036,10 @@
         <v>14.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.75</v>
+        <v>14.5</v>
       </c>
       <c r="R6" t="n">
-        <v>9.119999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="S6" t="n">
         <v>0.88</v>
@@ -3057,25 +3057,25 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50.62</v>
+        <v>51.25</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.62</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.12</v>
+        <v>4.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>22.62</v>
+        <v>22.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -3344,10 +3344,10 @@
         <v>16.06</v>
       </c>
       <c r="DQ6" t="n">
-        <v>15.06</v>
+        <v>14.94</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.64</v>
+        <v>11</v>
       </c>
       <c r="DS6" t="n">
         <v>0.23</v>
@@ -3359,25 +3359,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.76</v>
+        <v>45.06</v>
       </c>
       <c r="DW6" t="n">
         <v>0.12</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.59</v>
+        <v>11.77</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.59</v>
+        <v>7.71</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="EA6" t="n">
-        <v>23.41</v>
+        <v>23.35</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="EC6" t="n">
         <v>2.17</v>
@@ -3435,10 +3435,10 @@
         <v>17</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.38</v>
+        <v>17.25</v>
       </c>
       <c r="R7" t="n">
-        <v>6.38</v>
+        <v>7.5</v>
       </c>
       <c r="S7" t="n">
         <v>0.88</v>
@@ -3456,25 +3456,25 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>55</v>
+        <v>55.88</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>14.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="AB7" t="n">
         <v>5.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>20</v>
+        <v>19.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE7" t="n">
         <v>2.62</v>
@@ -3618,13 +3618,13 @@
         <v>1.83</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CA7" t="n">
         <v>3.39</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CC7" t="n">
         <v>2.42</v>
@@ -3690,25 +3690,25 @@
         <v>1.84</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="DB7" t="n">
         <v>1.32</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
@@ -3747,10 +3747,10 @@
         <v>14.75</v>
       </c>
       <c r="DQ7" t="n">
-        <v>16.81</v>
+        <v>16.75</v>
       </c>
       <c r="DR7" t="n">
-        <v>8</v>
+        <v>8.56</v>
       </c>
       <c r="DS7" t="n">
         <v>0.12</v>
@@ -3762,22 +3762,22 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.56</v>
+        <v>54</v>
       </c>
       <c r="DW7" t="n">
         <v>0.25</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.31</v>
+        <v>13.43</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.5</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DZ7" t="n">
         <v>4.81</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.94</v>
+        <v>19.88</v>
       </c>
       <c r="EB7" t="n">
         <v>1.56</v>
@@ -3841,7 +3841,7 @@
         <v>13</v>
       </c>
       <c r="R8" t="n">
-        <v>5.88</v>
+        <v>7.38</v>
       </c>
       <c r="S8" t="n">
         <v>1.5</v>
@@ -3859,16 +3859,16 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>52.62</v>
+        <v>53.12</v>
       </c>
       <c r="Y8" t="n">
         <v>0.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.25</v>
+        <v>15.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AB8" t="n">
         <v>5.25</v>
@@ -3877,7 +3877,7 @@
         <v>24.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE8" t="n">
         <v>3.62</v>
@@ -4153,7 +4153,7 @@
         <v>14.12</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.89</v>
+        <v>7.59</v>
       </c>
       <c r="DS8" t="n">
         <v>0.06</v>
@@ -4165,16 +4165,16 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.35</v>
+        <v>51.58</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.47</v>
+        <v>14.71</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.65</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DZ8" t="n">
         <v>4.82</v>
@@ -4183,7 +4183,7 @@
         <v>23.71</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="EC8" t="n">
         <v>3.35</v>
@@ -4241,10 +4241,10 @@
         <v>14.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.33</v>
+        <v>14.22</v>
       </c>
       <c r="R9" t="n">
-        <v>6.11</v>
+        <v>7.22</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -4262,25 +4262,25 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>50.11</v>
+        <v>50.22</v>
       </c>
       <c r="Y9" t="n">
         <v>0.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.67</v>
+        <v>14.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.11</v>
+        <v>10.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.56</v>
+        <v>4.33</v>
       </c>
       <c r="AC9" t="n">
         <v>24.22</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE9" t="n">
         <v>2.11</v>
@@ -4553,10 +4553,10 @@
         <v>14.32</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.69</v>
+        <v>15.62</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.75</v>
+        <v>7.37</v>
       </c>
       <c r="DS9" t="n">
         <v>0.18</v>
@@ -4568,25 +4568,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.75</v>
+        <v>51.81</v>
       </c>
       <c r="DW9" t="n">
         <v>0.18</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.12</v>
+        <v>15.19</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.25</v>
+        <v>10.44</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.88</v>
+        <v>4.75</v>
       </c>
       <c r="EA9" t="n">
         <v>22.37</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="EC9" t="n">
         <v>2.25</v>
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0.11</v>
@@ -5095,136 +5095,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="AH11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>82.88</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO11" t="n">
         <v>2</v>
       </c>
-      <c r="AI11" t="n">
-        <v>75.86</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>39.29</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>2.29</v>
-      </c>
       <c r="AP11" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15.29</v>
+        <v>15.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>16.57</v>
+        <v>16.88</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.57</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AU11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>46.62</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BL11" t="n">
         <v>1</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>45.86</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.9399999999999999</v>
       </c>
       <c r="BM11" t="n">
         <v>1.06</v>
       </c>
       <c r="BN11" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP11" t="n">
         <v>4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.25</v>
+        <v>5.59</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU11" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BV11" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW11" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY11" t="n">
         <v>2.52</v>
@@ -5239,64 +5239,64 @@
         <v>3.18</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="CE11" t="n">
         <v>1.43</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CG11" t="n">
         <v>2.63</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.85</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO11" t="n">
         <v>1.34</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="CR11" t="n">
         <v>1.44</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CU11" t="n">
         <v>1.35</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW11" t="n">
         <v>1.87</v>
@@ -5317,52 +5317,52 @@
         <v>1.37</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="DE11" t="n">
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.38</v>
+        <v>2.71</v>
       </c>
       <c r="DH11" t="n">
-        <v>86.94</v>
+        <v>89.59</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.25</v>
+        <v>4.53</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DM11" t="n">
-        <v>46.94</v>
+        <v>48.71</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.94</v>
+        <v>14.12</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.37</v>
+        <v>16.53</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.31</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.69</v>
+        <v>48.88</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.18</v>
+        <v>12.17</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.88</v>
+        <v>7.94</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.31</v>
+        <v>4.23</v>
       </c>
       <c r="EA11" t="n">
-        <v>22.06</v>
+        <v>22.18</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="EC11" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="12">
@@ -5405,94 +5405,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F12" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="G12" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="H12" t="n">
-        <v>86.62</v>
+        <v>90.56</v>
       </c>
       <c r="I12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="K12" t="n">
-        <v>6.62</v>
+        <v>6.56</v>
       </c>
       <c r="L12" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="M12" t="n">
-        <v>56.12</v>
+        <v>58.67</v>
       </c>
       <c r="N12" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O12" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="P12" t="n">
-        <v>16.12</v>
+        <v>16.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.12</v>
+        <v>14.44</v>
       </c>
       <c r="R12" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="S12" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51.88</v>
+        <v>51.44</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.38</v>
+        <v>13.67</v>
       </c>
       <c r="AA12" t="n">
-        <v>10</v>
+        <v>9.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>21.12</v>
+        <v>21.56</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5576,67 +5576,67 @@
         <v>2.75</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.380000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK12" t="n">
         <v>0.88</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.94</v>
+        <v>5.29</v>
       </c>
       <c r="BR12" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT12" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU12" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BV12" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX12" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CB12" t="n">
         <v>3.27</v>
@@ -5651,10 +5651,10 @@
         <v>1.42</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CH12" t="n">
         <v>1.34</v>
@@ -5666,13 +5666,13 @@
         <v>1.85</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN12" t="n">
         <v>1.89</v>
@@ -5684,22 +5684,22 @@
         <v>2.13</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="CR12" t="n">
         <v>1.44</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW12" t="n">
         <v>1.9</v>
@@ -5723,82 +5723,82 @@
         <v>2.19</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="DH12" t="n">
-        <v>80.44</v>
+        <v>82.88</v>
       </c>
       <c r="DI12" t="n">
         <v>0.18</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.56</v>
+        <v>5.59</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM12" t="n">
-        <v>50</v>
+        <v>51.71</v>
       </c>
       <c r="DN12" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.75</v>
+        <v>15</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.62</v>
+        <v>14.76</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.25</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.88</v>
+        <v>48.82</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.88</v>
+        <v>12.59</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.31</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.81</v>
+        <v>21.06</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="13">
@@ -5937,7 +5937,7 @@
         <v>18.11</v>
       </c>
       <c r="AS13" t="n">
-        <v>11.78</v>
+        <v>12.89</v>
       </c>
       <c r="AT13" t="n">
         <v>1.33</v>
@@ -5955,25 +5955,25 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>46</v>
+        <v>45.44</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.22</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.220000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="BB13" t="n">
-        <v>7</v>
+        <v>7.11</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="BD13" t="n">
         <v>21.78</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="BF13" t="n">
         <v>2.33</v>
@@ -6042,7 +6042,7 @@
         <v>3.27</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CC13" t="n">
         <v>4.31</v>
@@ -6111,13 +6111,13 @@
         <v>1.5</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.51</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="DB13" t="n">
         <v>1.37</v>
@@ -6168,7 +6168,7 @@
         <v>16.7</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.77</v>
+        <v>10.35</v>
       </c>
       <c r="DS13" t="n">
         <v>0.11</v>
@@ -6180,25 +6180,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45.06</v>
+        <v>44.76</v>
       </c>
       <c r="DW13" t="n">
         <v>0.3</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.29</v>
+        <v>11.41</v>
       </c>
       <c r="DY13" t="n">
-        <v>8</v>
+        <v>8.06</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="EA13" t="n">
         <v>21.7</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="EC13" t="n">
         <v>2.29</v>
@@ -6337,10 +6337,10 @@
         <v>12.25</v>
       </c>
       <c r="AR14" t="n">
-        <v>18.12</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.880000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AT14" t="n">
         <v>1.88</v>
@@ -6358,19 +6358,19 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>49.38</v>
+        <v>48.88</v>
       </c>
       <c r="AZ14" t="n">
         <v>0.25</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>10.12</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.38</v>
+        <v>6.62</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="BD14" t="n">
         <v>19.62</v>
@@ -6564,10 +6564,10 @@
         <v>13.75</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.25</v>
+        <v>17.19</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.94</v>
+        <v>9.75</v>
       </c>
       <c r="DS14" t="n">
         <v>0.18</v>
@@ -6579,19 +6579,19 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51</v>
+        <v>50.75</v>
       </c>
       <c r="DW14" t="n">
         <v>0.32</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.31</v>
+        <v>13.37</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.880000000000001</v>
+        <v>9</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.44</v>
+        <v>4.38</v>
       </c>
       <c r="EA14" t="n">
         <v>22.18</v>
@@ -6739,7 +6739,7 @@
         <v>15.25</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.25</v>
+        <v>9.75</v>
       </c>
       <c r="AT15" t="n">
         <v>1.75</v>
@@ -6763,10 +6763,10 @@
         <v>0.12</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.88</v>
+        <v>11.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.88</v>
+        <v>7.5</v>
       </c>
       <c r="BC15" t="n">
         <v>4</v>
@@ -6775,7 +6775,7 @@
         <v>21.88</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BF15" t="n">
         <v>2.38</v>
@@ -6844,7 +6844,7 @@
         <v>3.12</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CC15" t="n">
         <v>3.67</v>
@@ -6904,18 +6904,18 @@
         <v>1.38</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX15" t="inlineStr"/>
       <c r="CY15" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CZ15" t="inlineStr"/>
       <c r="DA15" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DB15" t="n">
         <v>1.34</v>
@@ -6924,7 +6924,7 @@
         <v>2.09</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
         <v>15.32</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.18</v>
+        <v>9.93</v>
       </c>
       <c r="DS15" t="n">
         <v>0.12</v>
@@ -6984,10 +6984,10 @@
         <v>0.25</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.38</v>
+        <v>10.69</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.56</v>
+        <v>6.88</v>
       </c>
       <c r="DZ15" t="n">
         <v>3.81</v>
@@ -6996,7 +6996,7 @@
         <v>20.31</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="EC15" t="n">
         <v>2.63</v>
@@ -7054,10 +7054,10 @@
         <v>15.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.88</v>
+        <v>13.62</v>
       </c>
       <c r="R16" t="n">
-        <v>8.119999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>0.88</v>
@@ -7075,7 +7075,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>53.62</v>
+        <v>54.38</v>
       </c>
       <c r="Y16" t="n">
         <v>0.12</v>
@@ -7237,7 +7237,7 @@
         <v>2.39</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="CA16" t="n">
         <v>3.18</v>
@@ -7312,13 +7312,13 @@
         <v>1.55</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.4</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="DB16" t="n">
         <v>1.34</v>
@@ -7366,10 +7366,10 @@
         <v>15.5</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.69</v>
+        <v>12.56</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.06</v>
+        <v>8.56</v>
       </c>
       <c r="DS16" t="n">
         <v>0.18</v>
@@ -7381,7 +7381,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.12</v>
+        <v>51.5</v>
       </c>
       <c r="DW16" t="n">
         <v>0.25</v>
@@ -7541,7 +7541,7 @@
         <v>11.11</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.56</v>
+        <v>8.33</v>
       </c>
       <c r="AT17" t="n">
         <v>1.11</v>
@@ -7559,19 +7559,19 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>45.33</v>
+        <v>44.56</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.22</v>
+        <v>11.33</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.44</v>
+        <v>7.67</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.78</v>
+        <v>3.67</v>
       </c>
       <c r="BD17" t="n">
         <v>21.44</v>
@@ -7646,13 +7646,13 @@
         <v>3.16</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CC17" t="n">
         <v>2.86</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CE17" t="n">
         <v>1.41</v>
@@ -7712,25 +7712,25 @@
         <v>1.91</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DB17" t="n">
         <v>1.36</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="DE17" t="n">
         <v>0.06</v>
@@ -7772,7 +7772,7 @@
         <v>11.53</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.95</v>
+        <v>8.35</v>
       </c>
       <c r="DS17" t="n">
         <v>0.12</v>
@@ -7784,19 +7784,19 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>46.77</v>
+        <v>46.36</v>
       </c>
       <c r="DW17" t="n">
         <v>0.53</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.18</v>
+        <v>12.23</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.06</v>
+        <v>8.18</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.12</v>
+        <v>4.06</v>
       </c>
       <c r="EA17" t="n">
         <v>21.52</v>
@@ -7941,10 +7941,10 @@
         <v>11.38</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.62</v>
+        <v>14.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.119999999999999</v>
+        <v>10.75</v>
       </c>
       <c r="AT18" t="n">
         <v>1</v>
@@ -7962,16 +7962,16 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>48.62</v>
+        <v>48.5</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.25</v>
+        <v>12.38</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.75</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BC18" t="n">
         <v>3.5</v>
@@ -7980,7 +7980,7 @@
         <v>20</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="BF18" t="n">
         <v>2.12</v>
@@ -8172,10 +8172,10 @@
         <v>13.07</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.56</v>
+        <v>15.5</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.869999999999999</v>
+        <v>10.68</v>
       </c>
       <c r="DS18" t="n">
         <v>0.12</v>
@@ -8187,16 +8187,16 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.06</v>
+        <v>47</v>
       </c>
       <c r="DW18" t="n">
         <v>0.12</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.32</v>
+        <v>11.38</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.18</v>
+        <v>7.25</v>
       </c>
       <c r="DZ18" t="n">
         <v>4.12</v>
@@ -8344,10 +8344,10 @@
         <v>15.11</v>
       </c>
       <c r="AR19" t="n">
-        <v>17.22</v>
+        <v>16.78</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.67</v>
+        <v>8.44</v>
       </c>
       <c r="AT19" t="n">
         <v>0.89</v>
@@ -8365,19 +8365,19 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>53.67</v>
+        <v>54</v>
       </c>
       <c r="AZ19" t="n">
         <v>0.11</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.22</v>
+        <v>12.44</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.56</v>
+        <v>7.89</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.67</v>
+        <v>4.56</v>
       </c>
       <c r="BD19" t="n">
         <v>22.56</v>
@@ -8575,10 +8575,10 @@
         <v>14.75</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.31</v>
+        <v>15.07</v>
       </c>
       <c r="DR19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8590,19 +8590,19 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.32</v>
+        <v>55.5</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.69</v>
+        <v>12.81</v>
       </c>
       <c r="DY19" t="n">
-        <v>8</v>
+        <v>8.19</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.69</v>
+        <v>4.63</v>
       </c>
       <c r="EA19" t="n">
         <v>21.38</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0.12</v>
@@ -2275,52 +2275,52 @@
         <v>3.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AI4" t="n">
-        <v>72.5</v>
+        <v>72.56</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AL4" t="n">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="AM4" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AN4" t="n">
-        <v>47.62</v>
+        <v>47.44</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18.12</v>
+        <v>18</v>
       </c>
       <c r="AR4" t="n">
-        <v>11</v>
+        <v>11.44</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.25</v>
+        <v>9</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>42.62</v>
+        <v>42.11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BA4" t="n">
-        <v>15.12</v>
+        <v>14.67</v>
       </c>
       <c r="BB4" t="n">
-        <v>10.25</v>
+        <v>9.56</v>
       </c>
       <c r="BC4" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BP4" t="n">
         <v>4.88</v>
       </c>
-      <c r="BD4" t="n">
-        <v>24.12</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>5.06</v>
-      </c>
       <c r="BQ4" t="n">
-        <v>4.31</v>
+        <v>4.41</v>
       </c>
       <c r="BR4" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT4" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BV4" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY4" t="n">
         <v>2.5</v>
@@ -2416,46 +2416,46 @@
         <v>2.57</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CH4" t="n">
         <v>1.25</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CK4" t="n">
         <v>1.34</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CO4" t="n">
         <v>1.28</v>
@@ -2467,85 +2467,85 @@
         <v>3.61</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CV4" t="n">
         <v>1.86</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX4" t="n">
         <v>1.49</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.55</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="DH4" t="n">
-        <v>76.94</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.38</v>
+        <v>3.53</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.44</v>
+        <v>6.36</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="DM4" t="n">
-        <v>56.44</v>
+        <v>55.82</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO4" t="n">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="DP4" t="n">
         <v>17.06</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.88</v>
+        <v>13</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.18</v>
+        <v>8.59</v>
       </c>
       <c r="DS4" t="n">
         <v>0.12</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47</v>
+        <v>46.47</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.62</v>
+        <v>16.29</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.93</v>
+        <v>11.47</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.69</v>
+        <v>4.82</v>
       </c>
       <c r="EA4" t="n">
-        <v>26.37</v>
+        <v>24.76</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.12</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0.11</v>
@@ -2678,139 +2678,139 @@
         <v>3.22</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>80.43000000000001</v>
+        <v>80.38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.57</v>
+        <v>5.62</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AN5" t="n">
-        <v>49.14</v>
+        <v>49.88</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16.43</v>
+        <v>16.5</v>
       </c>
       <c r="AR5" t="n">
         <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.29</v>
+        <v>5.38</v>
       </c>
       <c r="AT5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>54</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BL5" t="n">
         <v>0.29</v>
       </c>
-      <c r="AU5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>52.29</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>13.57</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>27.14</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0.31</v>
-      </c>
       <c r="BM5" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.06</v>
+        <v>3.88</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT5" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BU5" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BV5" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY5" t="n">
         <v>2.02</v>
@@ -2822,37 +2822,37 @@
         <v>3.04</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="CD5" t="n">
         <v>2.68</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CG5" t="n">
         <v>2.53</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="CM5" t="n">
         <v>2.49</v>
@@ -2861,25 +2861,25 @@
         <v>1.9</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV5" t="n">
         <v>1.95</v>
@@ -2891,97 +2891,97 @@
         <v>1.51</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="DB5" t="n">
         <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DD5" t="n">
         <v>3.7</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.19</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.81</v>
+        <v>3.71</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.87</v>
+        <v>4.94</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DM5" t="n">
-        <v>57.06</v>
+        <v>56.94</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.69</v>
+        <v>15.76</v>
       </c>
       <c r="DQ5" t="n">
         <v>15.06</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.56</v>
+        <v>5.18</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.69</v>
+        <v>56.29</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.56</v>
+        <v>14.59</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.56</v>
+        <v>9.59</v>
       </c>
       <c r="DZ5" t="n">
         <v>5</v>
       </c>
       <c r="EA5" t="n">
-        <v>25.25</v>
+        <v>23.7</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="EC5" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="6">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4289,136 +4289,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AI9" t="n">
-        <v>85.29000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AL9" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN9" t="n">
-        <v>55.43</v>
+        <v>56.88</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.86</v>
+        <v>14.75</v>
       </c>
       <c r="AR9" t="n">
-        <v>17.43</v>
+        <v>17.25</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.57</v>
+        <v>6.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AU9" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>53.86</v>
+        <v>53.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA9" t="n">
-        <v>15.71</v>
+        <v>14.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.43</v>
+        <v>9.25</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.29</v>
+        <v>5.25</v>
       </c>
       <c r="BD9" t="n">
-        <v>20</v>
+        <v>17.38</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.44</v>
+        <v>10.29</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="BO9" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.56</v>
+        <v>4.29</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.31</v>
+        <v>5.47</v>
       </c>
       <c r="BR9" t="n">
-        <v>100</v>
+        <v>94.12</v>
       </c>
       <c r="BS9" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU9" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV9" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY9" t="n">
         <v>2.05</v>
@@ -4433,16 +4433,16 @@
         <v>3.37</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="CD9" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="CE9" t="n">
         <v>1.41</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CG9" t="n">
         <v>2.73</v>
@@ -4451,37 +4451,37 @@
         <v>1.35</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL9" t="n">
         <v>1.73</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CO9" t="n">
         <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CR9" t="n">
         <v>1.41</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CT9" t="n">
         <v>2.89</v>
@@ -4490,106 +4490,106 @@
         <v>1.37</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX9" t="n">
         <v>1.5</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.54</v>
       </c>
       <c r="DA9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DC9" t="n">
         <v>2.07</v>
       </c>
-      <c r="DB9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>2.08</v>
-      </c>
       <c r="DD9" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="DH9" t="n">
-        <v>89.5</v>
+        <v>90.3</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.88</v>
+        <v>5.77</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DM9" t="n">
-        <v>60</v>
+        <v>60.42</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.32</v>
+        <v>14.71</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.62</v>
+        <v>15.65</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.37</v>
+        <v>6.88</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.81</v>
+        <v>51.76</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.19</v>
+        <v>14.65</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.44</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.37</v>
+        <v>21</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="10">
@@ -4599,94 +4599,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="G10" t="n">
-        <v>3.88</v>
+        <v>3.44</v>
       </c>
       <c r="H10" t="n">
-        <v>79.62</v>
+        <v>76.89</v>
       </c>
       <c r="I10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="K10" t="n">
-        <v>6.25</v>
+        <v>5.67</v>
       </c>
       <c r="L10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M10" t="n">
-        <v>55.88</v>
+        <v>51.78</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="O10" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="P10" t="n">
-        <v>13</v>
+        <v>12.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.25</v>
+        <v>15.44</v>
       </c>
       <c r="R10" t="n">
-        <v>6.62</v>
+        <v>5.78</v>
       </c>
       <c r="S10" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="T10" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="U10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>58.5</v>
+        <v>55.78</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>15.88</v>
+        <v>14.78</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.62</v>
+        <v>11.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.62</v>
+        <v>18.22</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="AE10" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AF10" t="n">
         <v>0.25</v>
@@ -4770,70 +4770,70 @@
         <v>2.88</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.25</v>
+        <v>10.06</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.19</v>
+        <v>4.29</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.38</v>
+        <v>5.12</v>
       </c>
       <c r="BR10" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS10" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BU10" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BV10" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CC10" t="n">
         <v>2.55</v>
@@ -4845,10 +4845,10 @@
         <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CH10" t="n">
         <v>1.35</v>
@@ -4860,16 +4860,16 @@
         <v>1.87</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CN10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CO10" t="n">
         <v>1.35</v>
@@ -4878,16 +4878,16 @@
         <v>2.1</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="CR10" t="n">
         <v>1.44</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CU10" t="n">
         <v>1.35</v>
@@ -4902,13 +4902,13 @@
         <v>1.51</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="DA10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB10" t="n">
         <v>1.37</v>
@@ -4917,49 +4917,49 @@
         <v>2.18</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="DH10" t="n">
-        <v>81.94</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.38</v>
+        <v>5.12</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DM10" t="n">
-        <v>54.56</v>
+        <v>52.47</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.94</v>
+        <v>13.71</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.88</v>
+        <v>15</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.81</v>
+        <v>7.3</v>
       </c>
       <c r="DS10" t="n">
         <v>0.18</v>
@@ -4971,28 +4971,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>53.81</v>
+        <v>52.65</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.88</v>
+        <v>13.42</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.93</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DZ10" t="n">
         <v>3.94</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.69</v>
+        <v>18.47</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="11">
@@ -6211,94 +6211,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G14" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="H14" t="n">
-        <v>76.12</v>
+        <v>78.33</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="K14" t="n">
-        <v>6.5</v>
+        <v>6.22</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="M14" t="n">
-        <v>52.5</v>
+        <v>52.78</v>
       </c>
       <c r="N14" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="P14" t="n">
-        <v>15.25</v>
+        <v>15.22</v>
       </c>
       <c r="Q14" t="n">
-        <v>16.38</v>
+        <v>17.11</v>
       </c>
       <c r="R14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S14" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T14" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="U14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>52.62</v>
+        <v>52.22</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.62</v>
+        <v>15.22</v>
       </c>
       <c r="AA14" t="n">
-        <v>11.38</v>
+        <v>10.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.25</v>
+        <v>4.89</v>
       </c>
       <c r="AC14" t="n">
-        <v>24.75</v>
+        <v>21.89</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="AF14" t="n">
         <v>0.25</v>
@@ -6382,70 +6382,70 @@
         <v>3</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.5</v>
+        <v>11.29</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BM14" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.69</v>
+        <v>4.41</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.62</v>
+        <v>6.71</v>
       </c>
       <c r="BR14" t="n">
-        <v>100</v>
+        <v>94.12</v>
       </c>
       <c r="BS14" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU14" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV14" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CC14" t="n">
         <v>3.6</v>
@@ -6469,25 +6469,25 @@
         <v>2</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK14" t="n">
         <v>1.25</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO14" t="n">
         <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CQ14" t="n">
         <v>3.2</v>
@@ -6505,10 +6505,10 @@
         <v>1.4</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
@@ -6522,52 +6522,52 @@
         <v>1.31</v>
       </c>
       <c r="DC14" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="DH14" t="n">
-        <v>74.37</v>
+        <v>75.64</v>
       </c>
       <c r="DI14" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="DM14" t="n">
-        <v>45.12</v>
+        <v>45.71</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.75</v>
+        <v>13.82</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.19</v>
+        <v>17.53</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.75</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0.18</v>
@@ -6579,28 +6579,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.75</v>
+        <v>50.65</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.37</v>
+        <v>12.82</v>
       </c>
       <c r="DY14" t="n">
-        <v>9</v>
+        <v>8.58</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.38</v>
+        <v>4.24</v>
       </c>
       <c r="EA14" t="n">
-        <v>22.18</v>
+        <v>20.82</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="15">
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>8</v>
@@ -6622,82 +6622,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="H15" t="n">
-        <v>70.12</v>
+        <v>71.11</v>
       </c>
       <c r="I15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J15" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="K15" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="L15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M15" t="n">
-        <v>37</v>
+        <v>37.56</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="P15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.38</v>
+        <v>15.67</v>
       </c>
       <c r="R15" t="n">
-        <v>10.12</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T15" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>47.5</v>
+        <v>48.11</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.880000000000001</v>
+        <v>10.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="AC15" t="n">
-        <v>18.75</v>
+        <v>16.56</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6781,70 +6781,70 @@
         <v>2.38</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.38</v>
+        <v>10.47</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.56</v>
+        <v>4.71</v>
       </c>
       <c r="BQ15" t="n">
         <v>4.94</v>
       </c>
       <c r="BR15" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS15" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU15" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV15" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX15" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CA15" t="n">
         <v>3.12</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CC15" t="n">
         <v>3.67</v>
@@ -6853,13 +6853,13 @@
         <v>4.18</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CH15" t="n">
         <v>1.28</v>
@@ -6868,138 +6868,142 @@
         <v>1.8</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CO15" t="n">
         <v>1.23</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CU15" t="n">
         <v>1.38</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CX15" t="inlineStr"/>
+        <v>1.87</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>1.47</v>
+      </c>
       <c r="CY15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CZ15" t="inlineStr"/>
+        <v>1.7</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>2.52</v>
+      </c>
       <c r="DA15" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="DB15" t="n">
         <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DH15" t="n">
-        <v>67.5</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="DI15" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DM15" t="n">
-        <v>40.75</v>
+        <v>40.83</v>
       </c>
       <c r="DN15" t="n">
         <v>0.88</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.81</v>
+        <v>14.59</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.32</v>
+        <v>15.47</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.93</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.62</v>
+        <v>47.94</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.69</v>
+        <v>10.88</v>
       </c>
       <c r="DY15" t="n">
         <v>6.88</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.81</v>
+        <v>4</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.31</v>
+        <v>19.06</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="16">
@@ -7009,13 +7013,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0.12</v>
@@ -7102,136 +7106,136 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="AI16" t="n">
-        <v>88.38</v>
+        <v>86.67</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="AL16" t="n">
-        <v>4</v>
+        <v>4.44</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN16" t="n">
-        <v>49.75</v>
+        <v>48.67</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15.88</v>
+        <v>16</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.5</v>
+        <v>11.44</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>48.62</v>
+        <v>48.44</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.38</v>
+        <v>11.11</v>
       </c>
       <c r="BB16" t="n">
-        <v>8</v>
+        <v>7.89</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.12</v>
+        <v>16.89</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.44</v>
+        <v>9.59</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BO16" t="n">
         <v>1.12</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.25</v>
+        <v>4.41</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.19</v>
+        <v>4.24</v>
       </c>
       <c r="BR16" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS16" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BT16" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU16" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV16" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BY16" t="n">
         <v>2.39</v>
@@ -7246,76 +7250,76 @@
         <v>3.29</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.11</v>
+        <v>3.03</v>
       </c>
       <c r="CE16" t="n">
         <v>1.41</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CG16" t="n">
         <v>2.7</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.81</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CO16" t="n">
         <v>1.31</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.47</v>
+        <v>3.51</v>
       </c>
       <c r="CR16" t="n">
         <v>1.42</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CU16" t="n">
         <v>1.37</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CW16" t="n">
         <v>1.84</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY16" t="n">
         <v>1.82</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="DA16" t="n">
         <v>2</v>
@@ -7324,10 +7328,10 @@
         <v>1.34</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="DE16" t="n">
         <v>0.06</v>
@@ -7336,73 +7340,73 @@
         <v>2.06</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="DH16" t="n">
-        <v>85</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="DI16" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.38</v>
+        <v>4.59</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="DM16" t="n">
-        <v>51.06</v>
+        <v>50.42</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="DP16" t="n">
-        <v>15.5</v>
+        <v>15.59</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.56</v>
+        <v>12.47</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.56</v>
+        <v>8</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.5</v>
+        <v>51.24</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.94</v>
+        <v>12.71</v>
       </c>
       <c r="DY16" t="n">
-        <v>8</v>
+        <v>7.94</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.94</v>
+        <v>4.76</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.87</v>
+        <v>19.59</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="17">
@@ -7815,94 +7819,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F18" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="G18" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>78</v>
+        <v>78.33</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="K18" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="L18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M18" t="n">
-        <v>47.38</v>
+        <v>49.78</v>
       </c>
       <c r="N18" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="O18" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="P18" t="n">
-        <v>14.75</v>
+        <v>14.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>16.5</v>
+        <v>16.78</v>
       </c>
       <c r="R18" t="n">
-        <v>10.62</v>
+        <v>9.33</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="T18" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="U18" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="V18" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>45.5</v>
+        <v>47.33</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>10.38</v>
+        <v>10.56</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.62</v>
+        <v>5.78</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.75</v>
+        <v>4.78</v>
       </c>
       <c r="AC18" t="n">
-        <v>19.38</v>
+        <v>17.11</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.75</v>
+        <v>3.11</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7986,70 +7990,70 @@
         <v>2.12</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.880000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.62</v>
+        <v>5.65</v>
       </c>
       <c r="BR18" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BT18" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BU18" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BV18" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BX18" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY18" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="BZ18" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="CC18" t="n">
         <v>4.61</v>
@@ -8058,19 +8062,19 @@
         <v>5.07</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CH18" t="n">
         <v>1.4</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.78</v>
@@ -8082,7 +8086,7 @@
         <v>1.73</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CN18" t="n">
         <v>2.2</v>
@@ -8091,25 +8095,25 @@
         <v>1.28</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CR18" t="n">
         <v>1.39</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CT18" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CU18" t="n">
         <v>1.4</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW18" t="n">
         <v>1.85</v>
@@ -8124,91 +8128,91 @@
         <v>2.58</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="DE18" t="n">
         <v>0.12</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DH18" t="n">
-        <v>79.75</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="DI18" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DM18" t="n">
-        <v>48.88</v>
+        <v>50.06</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="DP18" t="n">
-        <v>13.07</v>
+        <v>13</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.5</v>
+        <v>15.71</v>
       </c>
       <c r="DR18" t="n">
-        <v>10.68</v>
+        <v>10</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47</v>
+        <v>47.88</v>
       </c>
       <c r="DW18" t="n">
         <v>0.12</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.38</v>
+        <v>11.42</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.12</v>
+        <v>4.18</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.69</v>
+        <v>18.47</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -2311,10 +2311,10 @@
         <v>18</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.44</v>
+        <v>11.11</v>
       </c>
       <c r="AS4" t="n">
-        <v>9</v>
+        <v>10.33</v>
       </c>
       <c r="AT4" t="n">
         <v>1.56</v>
@@ -2332,25 +2332,25 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>42.11</v>
+        <v>41.78</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.11</v>
       </c>
       <c r="BA4" t="n">
-        <v>14.67</v>
+        <v>15</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.56</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.11</v>
+        <v>5.22</v>
       </c>
       <c r="BD4" t="n">
-        <v>21.33</v>
+        <v>23.78</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="BF4" t="n">
         <v>3.22</v>
@@ -2542,10 +2542,10 @@
         <v>17.06</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13</v>
+        <v>12.82</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.59</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DS4" t="n">
         <v>0.12</v>
@@ -2557,25 +2557,25 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.47</v>
+        <v>46.3</v>
       </c>
       <c r="DW4" t="n">
         <v>0.24</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.29</v>
+        <v>16.47</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.47</v>
+        <v>11.59</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.82</v>
+        <v>4.88</v>
       </c>
       <c r="EA4" t="n">
-        <v>24.76</v>
+        <v>26.06</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="EC4" t="n">
         <v>3.23</v>
@@ -4325,7 +4325,7 @@
         <v>17.25</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.5</v>
+        <v>7.38</v>
       </c>
       <c r="AT9" t="n">
         <v>1.62</v>
@@ -4343,25 +4343,25 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>53.5</v>
+        <v>53.62</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.12</v>
       </c>
       <c r="BA9" t="n">
-        <v>14.5</v>
+        <v>15.12</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.25</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BC9" t="n">
         <v>5.25</v>
       </c>
       <c r="BD9" t="n">
-        <v>17.38</v>
+        <v>21.25</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="BF9" t="n">
         <v>2.62</v>
@@ -4556,7 +4556,7 @@
         <v>15.65</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.88</v>
+        <v>7.3</v>
       </c>
       <c r="DS9" t="n">
         <v>0.17</v>
@@ -4568,25 +4568,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.76</v>
+        <v>51.82</v>
       </c>
       <c r="DW9" t="n">
         <v>0.17</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.65</v>
+        <v>14.94</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.880000000000001</v>
+        <v>10.18</v>
       </c>
       <c r="DZ9" t="n">
         <v>4.76</v>
       </c>
       <c r="EA9" t="n">
-        <v>21</v>
+        <v>22.82</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="EC9" t="n">
         <v>2.35</v>
@@ -6256,10 +6256,10 @@
         <v>15.22</v>
       </c>
       <c r="Q14" t="n">
-        <v>17.11</v>
+        <v>17</v>
       </c>
       <c r="R14" t="n">
-        <v>7</v>
+        <v>7.44</v>
       </c>
       <c r="S14" t="n">
         <v>1.22</v>
@@ -6277,25 +6277,25 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>52.22</v>
+        <v>52.11</v>
       </c>
       <c r="Y14" t="n">
         <v>0.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.22</v>
+        <v>15.56</v>
       </c>
       <c r="AA14" t="n">
-        <v>10.33</v>
+        <v>10.78</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.89</v>
+        <v>4.78</v>
       </c>
       <c r="AC14" t="n">
-        <v>21.89</v>
+        <v>24.44</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE14" t="n">
         <v>2.67</v>
@@ -6564,10 +6564,10 @@
         <v>13.82</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.53</v>
+        <v>17.47</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.119999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="DS14" t="n">
         <v>0.18</v>
@@ -6579,22 +6579,22 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.65</v>
+        <v>50.59</v>
       </c>
       <c r="DW14" t="n">
         <v>0.29</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.82</v>
+        <v>13</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.58</v>
+        <v>8.82</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.24</v>
+        <v>4.18</v>
       </c>
       <c r="EA14" t="n">
-        <v>20.82</v>
+        <v>22.17</v>
       </c>
       <c r="EB14" t="n">
         <v>1.44</v>
@@ -6655,10 +6655,10 @@
         <v>15</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.67</v>
+        <v>15.56</v>
       </c>
       <c r="R15" t="n">
-        <v>8.890000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="S15" t="n">
         <v>1.11</v>
@@ -6676,25 +6676,25 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>48.11</v>
+        <v>47.11</v>
       </c>
       <c r="Y15" t="n">
         <v>0.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.33</v>
+        <v>10.56</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.33</v>
+        <v>6.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.56</v>
+        <v>19</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AE15" t="n">
         <v>2.67</v>
@@ -6967,10 +6967,10 @@
         <v>14.59</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.47</v>
+        <v>15.41</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.289999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="DS15" t="n">
         <v>0.11</v>
@@ -6982,25 +6982,25 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.94</v>
+        <v>47.41</v>
       </c>
       <c r="DW15" t="n">
         <v>0.23</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.88</v>
+        <v>11</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.88</v>
+        <v>6.94</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.06</v>
+        <v>20.36</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="EC15" t="n">
         <v>2.53</v>
@@ -7142,7 +7142,7 @@
         <v>11.44</v>
       </c>
       <c r="AS16" t="n">
-        <v>7</v>
+        <v>7.56</v>
       </c>
       <c r="AT16" t="n">
         <v>0.67</v>
@@ -7160,25 +7160,25 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>48.44</v>
+        <v>49.44</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.33</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.11</v>
+        <v>11.44</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.89</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BC16" t="n">
         <v>3.22</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.89</v>
+        <v>20</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BF16" t="n">
         <v>2.89</v>
@@ -7373,7 +7373,7 @@
         <v>12.47</v>
       </c>
       <c r="DR16" t="n">
-        <v>8</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS16" t="n">
         <v>0.17</v>
@@ -7385,25 +7385,25 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.24</v>
+        <v>51.76</v>
       </c>
       <c r="DW16" t="n">
         <v>0.23</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.71</v>
+        <v>12.88</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.94</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DZ16" t="n">
         <v>4.76</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.59</v>
+        <v>21.23</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="EC16" t="n">
         <v>3.12</v>
@@ -7864,10 +7864,10 @@
         <v>14.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>16.78</v>
+        <v>16.56</v>
       </c>
       <c r="R18" t="n">
-        <v>9.33</v>
+        <v>10.22</v>
       </c>
       <c r="S18" t="n">
         <v>1.56</v>
@@ -7885,25 +7885,25 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>47.33</v>
+        <v>47.67</v>
       </c>
       <c r="Y18" t="n">
         <v>0.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>10.56</v>
+        <v>11</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.78</v>
+        <v>6.22</v>
       </c>
       <c r="AB18" t="n">
         <v>4.78</v>
       </c>
       <c r="AC18" t="n">
-        <v>17.11</v>
+        <v>20.56</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE18" t="n">
         <v>3.11</v>
@@ -8176,10 +8176,10 @@
         <v>13</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.71</v>
+        <v>15.59</v>
       </c>
       <c r="DR18" t="n">
-        <v>10</v>
+        <v>10.47</v>
       </c>
       <c r="DS18" t="n">
         <v>0.17</v>
@@ -8191,25 +8191,25 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.88</v>
+        <v>48.06</v>
       </c>
       <c r="DW18" t="n">
         <v>0.12</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.42</v>
+        <v>11.65</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.24</v>
+        <v>7.47</v>
       </c>
       <c r="DZ18" t="n">
         <v>4.18</v>
       </c>
       <c r="EA18" t="n">
-        <v>18.47</v>
+        <v>20.3</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="EC18" t="n">
         <v>2.64</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
@@ -1394,46 +1394,46 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="H2" t="n">
-        <v>82.75</v>
+        <v>82.78</v>
       </c>
       <c r="I2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="K2" t="n">
-        <v>5.88</v>
+        <v>5.67</v>
       </c>
       <c r="L2" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="M2" t="n">
-        <v>57.12</v>
+        <v>55.33</v>
       </c>
       <c r="N2" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="O2" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="P2" t="n">
-        <v>13.25</v>
+        <v>12.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.62</v>
+        <v>12.78</v>
       </c>
       <c r="R2" t="n">
-        <v>6</v>
+        <v>5.22</v>
       </c>
       <c r="S2" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="T2" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1448,25 +1448,25 @@
         <v>52</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.25</v>
+        <v>15.67</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.38</v>
+        <v>10.11</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.62</v>
+        <v>23.44</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AF2" t="n">
         <v>0.22</v>
@@ -1550,70 +1550,70 @@
         <v>2.78</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.710000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.24</v>
+        <v>4.17</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.47</v>
+        <v>5.28</v>
       </c>
       <c r="BR2" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS2" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT2" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU2" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV2" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX2" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CA2" t="n">
         <v>3.24</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CC2" t="n">
         <v>3.01</v>
@@ -1625,10 +1625,10 @@
         <v>1.45</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CH2" t="n">
         <v>1.33</v>
@@ -1640,16 +1640,16 @@
         <v>1.88</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL2" t="n">
         <v>1.8</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CO2" t="n">
         <v>1.35</v>
@@ -1658,7 +1658,7 @@
         <v>2.11</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="CR2" t="n">
         <v>1.46</v>
@@ -1682,13 +1682,13 @@
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.51</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DB2" t="n">
         <v>1.4</v>
@@ -1697,49 +1697,49 @@
         <v>2.26</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.16</v>
+        <v>4.14</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF2" t="n">
         <v>2</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="DH2" t="n">
-        <v>81.23999999999999</v>
+        <v>81.33</v>
       </c>
       <c r="DI2" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.53</v>
+        <v>5.44</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="DM2" t="n">
-        <v>53</v>
+        <v>52.33</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.82</v>
+        <v>13.56</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.47</v>
+        <v>13.5</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.23</v>
+        <v>5.83</v>
       </c>
       <c r="DS2" t="n">
         <v>0.06</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.82</v>
+        <v>50.89</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.88</v>
+        <v>14.67</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.59</v>
+        <v>9.5</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.3</v>
+        <v>5.17</v>
       </c>
       <c r="EA2" t="n">
-        <v>23</v>
+        <v>22.94</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="3">
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
@@ -3402,49 +3402,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="G7" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>84.88</v>
+        <v>86.33</v>
       </c>
       <c r="I7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J7" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="K7" t="n">
-        <v>4.12</v>
+        <v>4.78</v>
       </c>
       <c r="L7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M7" t="n">
-        <v>57.62</v>
+        <v>60.44</v>
       </c>
       <c r="N7" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="P7" t="n">
-        <v>17</v>
+        <v>16.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.25</v>
+        <v>16.67</v>
       </c>
       <c r="R7" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="T7" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3456,28 +3456,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>55.88</v>
+        <v>55.78</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.25</v>
+        <v>14.56</v>
       </c>
       <c r="AA7" t="n">
-        <v>9</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.25</v>
+        <v>5.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>19.88</v>
+        <v>19.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3561,49 +3561,49 @@
         <v>5.12</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.19</v>
+        <v>9.59</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.31</v>
+        <v>4.35</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.75</v>
+        <v>5.12</v>
       </c>
       <c r="BR7" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS7" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT7" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BU7" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3612,16 +3612,16 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="CB7" t="n">
         <v>3.47</v>
@@ -3636,10 +3636,10 @@
         <v>1.39</v>
       </c>
       <c r="CF7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="CG7" t="n">
         <v>2.8</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>2.81</v>
       </c>
       <c r="CH7" t="n">
         <v>1.38</v>
@@ -3651,16 +3651,16 @@
         <v>1.8</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CO7" t="n">
         <v>1.28</v>
@@ -3675,31 +3675,31 @@
         <v>1.4</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CU7" t="n">
         <v>1.39</v>
       </c>
       <c r="CV7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX7" t="n">
         <v>1.49</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="DB7" t="n">
         <v>1.32</v>
@@ -3708,49 +3708,49 @@
         <v>2.04</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="DH7" t="n">
-        <v>82.06</v>
+        <v>83</v>
       </c>
       <c r="DI7" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ7" t="n">
-        <v>4.19</v>
+        <v>4.06</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.94</v>
+        <v>4.3</v>
       </c>
       <c r="DL7" t="n">
         <v>0.06</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.75</v>
+        <v>54.53</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.75</v>
+        <v>14.41</v>
       </c>
       <c r="DQ7" t="n">
-        <v>16.75</v>
+        <v>16.47</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.56</v>
+        <v>8.23</v>
       </c>
       <c r="DS7" t="n">
         <v>0.12</v>
@@ -3762,28 +3762,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54</v>
+        <v>54.06</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.43</v>
+        <v>13.65</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.619999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.81</v>
+        <v>4.88</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.88</v>
+        <v>19.77</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.87</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="8">
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5901,136 +5901,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AI13" t="n">
-        <v>75.44</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="AM13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BK13" t="n">
         <v>0.33</v>
       </c>
-      <c r="AN13" t="n">
-        <v>38.89</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>18.11</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU13" t="n">
+      <c r="BL13" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BM13" t="n">
         <v>0.67</v>
       </c>
-      <c r="AV13" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>45.44</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>21.78</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.71</v>
-      </c>
       <c r="BN13" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.59</v>
+        <v>5.89</v>
       </c>
       <c r="BR13" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BS13" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT13" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU13" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX13" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>3.06</v>
@@ -6039,22 +6039,22 @@
         <v>3.33</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CB13" t="n">
         <v>3.48</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.31</v>
+        <v>4.32</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.02</v>
+        <v>5.05</v>
       </c>
       <c r="CE13" t="n">
         <v>1.43</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CG13" t="n">
         <v>2.65</v>
@@ -6069,16 +6069,16 @@
         <v>1.9</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CO13" t="n">
         <v>1.35</v>
@@ -6087,13 +6087,13 @@
         <v>2.1</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CR13" t="n">
         <v>1.43</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CT13" t="n">
         <v>2.84</v>
@@ -6102,7 +6102,7 @@
         <v>1.36</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW13" t="n">
         <v>1.97</v>
@@ -6114,10 +6114,10 @@
         <v>1.79</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DB13" t="n">
         <v>1.37</v>
@@ -6126,49 +6126,49 @@
         <v>2.18</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="DH13" t="n">
-        <v>76.41</v>
+        <v>75.89</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.47</v>
+        <v>3.61</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM13" t="n">
-        <v>44.94</v>
+        <v>44.61</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.12</v>
+        <v>14.94</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.7</v>
+        <v>16.39</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.35</v>
+        <v>10.5</v>
       </c>
       <c r="DS13" t="n">
         <v>0.11</v>
@@ -6180,28 +6180,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.76</v>
+        <v>44.78</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.41</v>
+        <v>11.22</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.06</v>
+        <v>7.83</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.7</v>
+        <v>21.39</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="14">
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
         <v>0.14</v>
@@ -8315,49 +8315,49 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="AI19" t="n">
-        <v>85</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.11</v>
+        <v>4.7</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AN19" t="n">
-        <v>52.44</v>
+        <v>52.4</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15.11</v>
+        <v>15</v>
       </c>
       <c r="AR19" t="n">
-        <v>16.78</v>
+        <v>16.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.44</v>
+        <v>7.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8369,82 +8369,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>54</v>
+        <v>53.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.44</v>
+        <v>12.1</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.89</v>
+        <v>7.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.56</v>
+        <v>4.3</v>
       </c>
       <c r="BD19" t="n">
-        <v>22.56</v>
+        <v>22.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.12</v>
+        <v>10.76</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.56</v>
+        <v>5.35</v>
       </c>
       <c r="BR19" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU19" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV19" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY19" t="n">
         <v>2.15</v>
@@ -8459,40 +8459,40 @@
         <v>3.35</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.37</v>
+        <v>2.51</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="CE19" t="n">
         <v>1.41</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CH19" t="n">
         <v>1.36</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CO19" t="n">
         <v>1.3</v>
@@ -8507,7 +8507,7 @@
         <v>1.42</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CT19" t="n">
         <v>2.87</v>
@@ -8525,64 +8525,64 @@
         <v>1.54</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.42</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="DB19" t="n">
         <v>1.35</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="DE19" t="n">
         <v>0.06</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="DH19" t="n">
-        <v>84.19</v>
+        <v>84</v>
       </c>
       <c r="DI19" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.63</v>
+        <v>5.35</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM19" t="n">
-        <v>56.06</v>
+        <v>55.82</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.75</v>
+        <v>14.71</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.07</v>
+        <v>14.82</v>
       </c>
       <c r="DR19" t="n">
-        <v>8</v>
+        <v>7.47</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8594,28 +8594,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.5</v>
+        <v>55.06</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.81</v>
+        <v>12.59</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.19</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.63</v>
+        <v>4.47</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.38</v>
+        <v>21.41</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="G3" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="H3" t="n">
-        <v>92</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="K3" t="n">
-        <v>8.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>71.11</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.89</v>
+        <v>15</v>
       </c>
       <c r="R3" t="n">
-        <v>6.22</v>
+        <v>5.5</v>
       </c>
       <c r="S3" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>56.78</v>
+        <v>57.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.89</v>
+        <v>12.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.11</v>
+        <v>6.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>23.56</v>
+        <v>23</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AF3" t="n">
         <v>0.12</v>
@@ -1953,70 +1953,70 @@
         <v>3.12</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.59</v>
+        <v>11.39</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.76</v>
+        <v>5.61</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>94.12</v>
+        <v>88.89</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU3" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX3" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CC3" t="n">
         <v>3.22</v>
@@ -2025,10 +2025,10 @@
         <v>3.7</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CG3" t="n">
         <v>2.85</v>
@@ -2049,19 +2049,19 @@
         <v>1.8</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2085,97 +2085,97 @@
         <v>1.56</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="DB3" t="n">
         <v>1.3</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.29</v>
+        <v>3.22</v>
       </c>
       <c r="DH3" t="n">
-        <v>83.59</v>
+        <v>83</v>
       </c>
       <c r="DI3" t="n">
         <v>0.17</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.65</v>
+        <v>6.56</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM3" t="n">
-        <v>57.7</v>
+        <v>57.89</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.18</v>
+        <v>14.39</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.71</v>
+        <v>14.78</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.41</v>
+        <v>7.89</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>49.88</v>
+        <v>50.66</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.82</v>
+        <v>14.89</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.83</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="EA3" t="n">
-        <v>23.12</v>
+        <v>22.83</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0.11</v>
@@ -2678,139 +2678,139 @@
         <v>3.22</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AI5" t="n">
-        <v>80.38</v>
+        <v>77.67</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.62</v>
+        <v>5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.38</v>
+        <v>0.22</v>
       </c>
       <c r="AN5" t="n">
-        <v>49.88</v>
+        <v>46.78</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AP5" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16.5</v>
+        <v>16.33</v>
       </c>
       <c r="AR5" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.38</v>
+        <v>4.67</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>54</v>
+        <v>53.44</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.75</v>
+        <v>12.67</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.25</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="BD5" t="n">
-        <v>23.62</v>
+        <v>23.22</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="BF5" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.529999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.71</v>
+        <v>3.44</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.88</v>
+        <v>3.61</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT5" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BV5" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BY5" t="n">
         <v>2.02</v>
@@ -2819,25 +2819,25 @@
         <v>1.98</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="CE5" t="n">
         <v>1.33</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CH5" t="n">
         <v>1.28</v>
@@ -2846,10 +2846,10 @@
         <v>1.78</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CL5" t="n">
         <v>1.72</v>
@@ -2861,22 +2861,22 @@
         <v>1.9</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CR5" t="n">
         <v>1.42</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CU5" t="n">
         <v>1.37</v>
@@ -2888,16 +2888,16 @@
         <v>1.89</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="DB5" t="n">
         <v>1.34</v>
@@ -2906,82 +2906,82 @@
         <v>2.1</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.70999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="DK5" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>55</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>55.89</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>14</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="DZ5" t="n">
         <v>4.94</v>
       </c>
-      <c r="DL5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>56.94</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="DP5" t="n">
-        <v>15.76</v>
-      </c>
-      <c r="DQ5" t="n">
-        <v>15.06</v>
-      </c>
-      <c r="DR5" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="DS5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DT5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV5" t="n">
-        <v>56.29</v>
-      </c>
-      <c r="DW5" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="DX5" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="DY5" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="DZ5" t="n">
-        <v>5</v>
-      </c>
       <c r="EA5" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="EC5" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="H6" t="n">
-        <v>95</v>
+        <v>91.22</v>
       </c>
       <c r="I6" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="K6" t="n">
-        <v>5.62</v>
+        <v>5.22</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>60.5</v>
+        <v>57.11</v>
       </c>
       <c r="N6" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="P6" t="n">
-        <v>14.88</v>
+        <v>14.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.5</v>
+        <v>13.89</v>
       </c>
       <c r="R6" t="n">
-        <v>9.880000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="S6" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="U6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>51.25</v>
+        <v>50</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>12.22</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.75</v>
+        <v>8.33</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.25</v>
+        <v>3.89</v>
       </c>
       <c r="AC6" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3165,64 +3165,64 @@
         <v>2</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.82</v>
+        <v>10.44</v>
       </c>
       <c r="BI6" t="n">
         <v>2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.41</v>
+        <v>6.11</v>
       </c>
       <c r="BR6" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS6" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.21</v>
+        <v>3.09</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CB6" t="n">
         <v>3.52</v>
@@ -3234,19 +3234,19 @@
         <v>4.92</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="CG6" t="n">
         <v>2.62</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.72</v>
@@ -3255,28 +3255,28 @@
         <v>1.19</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO6" t="n">
         <v>1.22</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CR6" t="n">
         <v>1.41</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CT6" t="n">
         <v>2.92</v>
@@ -3288,15 +3288,15 @@
         <v>1.97</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX6" t="inlineStr"/>
       <c r="CY6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CZ6" t="inlineStr"/>
       <c r="DA6" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DB6" t="n">
         <v>1.32</v>
@@ -3311,76 +3311,76 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="DH6" t="n">
-        <v>84.3</v>
+        <v>83</v>
       </c>
       <c r="DI6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="DL6" t="n">
         <v>0.11</v>
       </c>
-      <c r="DJ6" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>0.12</v>
-      </c>
       <c r="DM6" t="n">
-        <v>51.47</v>
+        <v>50.28</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="DO6" t="n">
         <v>1.94</v>
       </c>
       <c r="DP6" t="n">
-        <v>16.06</v>
+        <v>15.84</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.94</v>
+        <v>14.61</v>
       </c>
       <c r="DR6" t="n">
-        <v>11</v>
+        <v>10.34</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.06</v>
+        <v>44.78</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.77</v>
+        <v>11.44</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.71</v>
+        <v>7.56</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.06</v>
+        <v>3.89</v>
       </c>
       <c r="EA6" t="n">
-        <v>23.35</v>
+        <v>23.06</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="7">
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
@@ -3805,49 +3805,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="G8" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="H8" t="n">
-        <v>92.38</v>
+        <v>96.44</v>
       </c>
       <c r="I8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="K8" t="n">
-        <v>6.12</v>
+        <v>6.44</v>
       </c>
       <c r="L8" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="M8" t="n">
-        <v>66.25</v>
+        <v>68.11</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="P8" t="n">
-        <v>14.88</v>
+        <v>15.22</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>13.22</v>
       </c>
       <c r="R8" t="n">
-        <v>7.38</v>
+        <v>6.44</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3859,28 +3859,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>53.12</v>
+        <v>53.44</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.75</v>
+        <v>15.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.5</v>
+        <v>10.22</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.25</v>
+        <v>5.56</v>
       </c>
       <c r="AC8" t="n">
-        <v>24.75</v>
+        <v>25.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="AF8" t="n">
         <v>0.11</v>
@@ -3964,70 +3964,70 @@
         <v>3.11</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.76</v>
+        <v>10.17</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.29</v>
+        <v>4.56</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.47</v>
+        <v>5.61</v>
       </c>
       <c r="BR8" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BS8" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT8" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BU8" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV8" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX8" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="CC8" t="n">
         <v>2.42</v>
@@ -4039,7 +4039,7 @@
         <v>1.42</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CG8" t="n">
         <v>2.68</v>
@@ -4048,7 +4048,7 @@
         <v>1.34</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.83</v>
@@ -4057,37 +4057,37 @@
         <v>1.31</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CO8" t="n">
         <v>1.32</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CR8" t="n">
         <v>1.43</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CU8" t="n">
         <v>1.36</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW8" t="n">
         <v>1.9</v>
@@ -4096,7 +4096,7 @@
         <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.48</v>
@@ -4105,55 +4105,55 @@
         <v>2.09</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="DE8" t="n">
         <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.76</v>
+        <v>3.84</v>
       </c>
       <c r="DH8" t="n">
-        <v>87.23999999999999</v>
+        <v>89.56</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.94</v>
+        <v>6.11</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="DM8" t="n">
-        <v>58.76</v>
+        <v>60.11</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.12</v>
+        <v>14.33</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.12</v>
+        <v>14.16</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.59</v>
+        <v>7.11</v>
       </c>
       <c r="DS8" t="n">
         <v>0.06</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.58</v>
+        <v>51.83</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.71</v>
+        <v>14.78</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.880000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.82</v>
+        <v>5</v>
       </c>
       <c r="EA8" t="n">
-        <v>23.71</v>
+        <v>24.23</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="9">
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -4208,82 +4208,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="H9" t="n">
-        <v>92.78</v>
+        <v>93.3</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="K9" t="n">
-        <v>6.56</v>
+        <v>6.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="M9" t="n">
-        <v>63.56</v>
+        <v>63.2</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O9" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>14.67</v>
+        <v>14.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.22</v>
+        <v>14.8</v>
       </c>
       <c r="R9" t="n">
-        <v>7.22</v>
+        <v>6.4</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="U9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>50.22</v>
+        <v>50.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.78</v>
+        <v>14.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.44</v>
+        <v>10.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>24.22</v>
+        <v>24.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4367,70 +4367,70 @@
         <v>2.62</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.29</v>
+        <v>10.06</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="BO9" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.47</v>
+        <v>5.28</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS9" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT9" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU9" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV9" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="CC9" t="n">
         <v>2.86</v>
@@ -4451,7 +4451,7 @@
         <v>1.35</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.8</v>
@@ -4463,7 +4463,7 @@
         <v>1.73</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CN9" t="n">
         <v>2.09</v>
@@ -4475,37 +4475,37 @@
         <v>2.02</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CR9" t="n">
         <v>1.41</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CU9" t="n">
         <v>1.37</v>
       </c>
       <c r="CV9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX9" t="n">
         <v>1.5</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.54</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DB9" t="n">
         <v>1.33</v>
@@ -4514,82 +4514,82 @@
         <v>2.07</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="DH9" t="n">
-        <v>90.3</v>
+        <v>90.72</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.77</v>
+        <v>5.61</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM9" t="n">
-        <v>60.42</v>
+        <v>60.39</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.71</v>
+        <v>14.72</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.65</v>
+        <v>15.89</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.3</v>
+        <v>6.84</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.82</v>
+        <v>51.83</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.94</v>
+        <v>14.61</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.18</v>
+        <v>10</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.76</v>
+        <v>4.61</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.82</v>
+        <v>23.11</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="10">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0.11</v>
@@ -4689,139 +4689,139 @@
         <v>2.89</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AI10" t="n">
-        <v>84.25</v>
+        <v>81.11</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN10" t="n">
-        <v>53.25</v>
+        <v>50.67</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.88</v>
+        <v>14.78</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS10" t="n">
-        <v>9</v>
+        <v>7.89</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>49.12</v>
+        <v>47.67</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.88</v>
+        <v>10.56</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.25</v>
+        <v>6.44</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.62</v>
+        <v>4.11</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.75</v>
+        <v>18.78</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.06</v>
+        <v>9.94</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BO10" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.29</v>
+        <v>4.33</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS10" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BT10" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BU10" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BY10" t="n">
         <v>2.06</v>
@@ -4833,13 +4833,13 @@
         <v>3.2</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CE10" t="n">
         <v>1.42</v>
@@ -4851,25 +4851,25 @@
         <v>2.67</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CO10" t="n">
         <v>1.35</v>
@@ -4878,7 +4878,7 @@
         <v>2.1</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="CR10" t="n">
         <v>1.44</v>
@@ -4893,58 +4893,58 @@
         <v>1.35</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX10" t="n">
         <v>1.51</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.5</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="DH10" t="n">
-        <v>80.34999999999999</v>
+        <v>79</v>
       </c>
       <c r="DI10" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="DM10" t="n">
-        <v>52.47</v>
+        <v>51.22</v>
       </c>
       <c r="DN10" t="n">
         <v>1</v>
@@ -4953,43 +4953,43 @@
         <v>2.06</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.71</v>
+        <v>13.72</v>
       </c>
       <c r="DQ10" t="n">
-        <v>15</v>
+        <v>15.22</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.3</v>
+        <v>6.84</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>52.65</v>
+        <v>51.72</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.42</v>
+        <v>12.67</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.470000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.94</v>
+        <v>3.72</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.47</v>
+        <v>18.5</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="EC10" t="n">
         <v>2.89</v>
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0.11</v>
@@ -5095,49 +5095,49 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AI11" t="n">
-        <v>82.88</v>
+        <v>82.44</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>4.88</v>
+        <v>4.56</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>44</v>
+        <v>43.44</v>
       </c>
       <c r="AO11" t="n">
         <v>2</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15.5</v>
+        <v>15.67</v>
       </c>
       <c r="AR11" t="n">
-        <v>16.88</v>
+        <v>17.11</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.119999999999999</v>
+        <v>7.11</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5149,82 +5149,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>46.62</v>
+        <v>46.78</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.75</v>
+        <v>10.56</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.12</v>
+        <v>7.11</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="BD11" t="n">
-        <v>22.5</v>
+        <v>21.89</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.38</v>
+        <v>4.11</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.29</v>
+        <v>3.17</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.59</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.29</v>
+        <v>3.17</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BL11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BM11" t="n">
         <v>1</v>
       </c>
-      <c r="BM11" t="n">
-        <v>1.06</v>
-      </c>
       <c r="BN11" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BP11" t="n">
         <v>4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.59</v>
+        <v>5.39</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU11" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BV11" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX11" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
         <v>2.52</v>
@@ -5233,28 +5233,28 @@
         <v>2.82</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.31</v>
+        <v>3.64</v>
       </c>
       <c r="CE11" t="n">
         <v>1.43</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CG11" t="n">
         <v>2.63</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI11" t="n">
         <v>1.87</v>
@@ -5269,100 +5269,100 @@
         <v>1.75</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CO11" t="n">
         <v>1.34</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CR11" t="n">
         <v>1.44</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CX11" t="n">
         <v>1.51</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.49</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="DE11" t="n">
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="DH11" t="n">
-        <v>89.59</v>
+        <v>89</v>
       </c>
       <c r="DI11" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.53</v>
+        <v>4.44</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM11" t="n">
-        <v>48.71</v>
+        <v>48.16</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.12</v>
+        <v>14.28</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.53</v>
+        <v>16.67</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.109999999999999</v>
+        <v>7.61</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.88</v>
+        <v>48.84</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.17</v>
+        <v>12</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.94</v>
+        <v>7.89</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.23</v>
+        <v>4.11</v>
       </c>
       <c r="EA11" t="n">
-        <v>22.18</v>
+        <v>21.89</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="EC11" t="n">
-        <v>3.24</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="12">
@@ -5405,94 +5405,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F12" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="G12" t="n">
-        <v>3.33</v>
+        <v>2.9</v>
       </c>
       <c r="H12" t="n">
-        <v>90.56</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J12" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="K12" t="n">
-        <v>6.56</v>
+        <v>6.8</v>
       </c>
       <c r="L12" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="M12" t="n">
-        <v>58.67</v>
+        <v>58.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O12" t="n">
-        <v>3.11</v>
+        <v>2.7</v>
       </c>
       <c r="P12" t="n">
-        <v>16.44</v>
+        <v>16.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.44</v>
+        <v>14.7</v>
       </c>
       <c r="R12" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="T12" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="U12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51.44</v>
+        <v>51.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.67</v>
+        <v>13.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.44</v>
+        <v>9</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>21.56</v>
+        <v>21.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5576,67 +5576,67 @@
         <v>2.75</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.710000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.29</v>
+        <v>4.94</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT12" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU12" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV12" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX12" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CB12" t="n">
         <v>3.27</v>
@@ -5651,10 +5651,10 @@
         <v>1.42</v>
       </c>
       <c r="CF12" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CH12" t="n">
         <v>1.34</v>
@@ -5666,10 +5666,10 @@
         <v>1.85</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM12" t="n">
         <v>2.49</v>
@@ -5684,7 +5684,7 @@
         <v>2.13</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="CR12" t="n">
         <v>1.44</v>
@@ -5693,7 +5693,7 @@
         <v>3.17</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CU12" t="n">
         <v>1.36</v>
@@ -5705,16 +5705,16 @@
         <v>1.9</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="DB12" t="n">
         <v>1.37</v>
@@ -5729,43 +5729,43 @@
         <v>0.17</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="DH12" t="n">
-        <v>82.88</v>
+        <v>81.56</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.59</v>
+        <v>5.78</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.53</v>
+        <v>0.45</v>
       </c>
       <c r="DM12" t="n">
-        <v>51.71</v>
+        <v>52.11</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="DP12" t="n">
-        <v>15</v>
+        <v>15.17</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.76</v>
+        <v>14.89</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.289999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DS12" t="n">
         <v>0.11</v>
@@ -5777,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.82</v>
+        <v>48.95</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.59</v>
+        <v>12.39</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.109999999999999</v>
+        <v>7.94</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.06</v>
+        <v>21.28</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="13">
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0.22</v>
@@ -6301,139 +6301,139 @@
         <v>2.67</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AI14" t="n">
-        <v>72.62</v>
+        <v>76.11</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="AL14" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AM14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ14" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN14" t="n">
-        <v>37.75</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>48.88</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>19.62</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.53</v>
-      </c>
       <c r="BK14" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BM14" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.71</v>
+        <v>6.39</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS14" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT14" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU14" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV14" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY14" t="n">
         <v>2.76</v>
@@ -6442,16 +6442,16 @@
         <v>2.93</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.18</v>
+        <v>4.09</v>
       </c>
       <c r="CE14" t="n">
         <v>1.38</v>
@@ -6460,10 +6460,10 @@
         <v>2.82</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI14" t="n">
         <v>2</v>
@@ -6478,10 +6478,10 @@
         <v>1.61</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CO14" t="n">
         <v>1.28</v>
@@ -6490,7 +6490,7 @@
         <v>1.93</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CR14" t="n">
         <v>1.39</v>
@@ -6525,82 +6525,82 @@
         <v>1.99</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="DH14" t="n">
-        <v>75.64</v>
+        <v>77.22</v>
       </c>
       <c r="DI14" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.29</v>
+        <v>3.22</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.7</v>
+        <v>4.56</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="DM14" t="n">
-        <v>45.71</v>
+        <v>47.17</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.82</v>
+        <v>13.5</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.47</v>
+        <v>17.28</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.35</v>
+        <v>8.77</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.59</v>
+        <v>51.11</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX14" t="n">
-        <v>13</v>
+        <v>13.12</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.82</v>
+        <v>8.84</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.18</v>
+        <v>4.28</v>
       </c>
       <c r="EA14" t="n">
-        <v>22.17</v>
+        <v>22.44</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="15">
@@ -7819,13 +7819,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>0.22</v>
@@ -7912,49 +7912,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AI18" t="n">
-        <v>81.5</v>
+        <v>83.22</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AL18" t="n">
-        <v>4</v>
+        <v>4.44</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AN18" t="n">
-        <v>50.38</v>
+        <v>50.67</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP18" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.38</v>
+        <v>11.33</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.5</v>
+        <v>15.67</v>
       </c>
       <c r="AS18" t="n">
-        <v>10.75</v>
+        <v>9.44</v>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7966,82 +7966,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.38</v>
+        <v>12</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.880000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BD18" t="n">
-        <v>20</v>
+        <v>20.44</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.76</v>
+        <v>10.17</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.65</v>
+        <v>5.78</v>
       </c>
       <c r="BR18" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS18" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BT18" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BU18" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV18" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW18" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX18" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BY18" t="n">
         <v>3.21</v>
@@ -8050,40 +8050,40 @@
         <v>3.53</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.61</v>
+        <v>4.68</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.07</v>
+        <v>5.18</v>
       </c>
       <c r="CE18" t="n">
         <v>1.38</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CG18" t="n">
         <v>2.87</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CK18" t="n">
         <v>1.32</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CM18" t="n">
         <v>2.96</v>
@@ -8095,10 +8095,10 @@
         <v>1.28</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CR18" t="n">
         <v>1.39</v>
@@ -8107,7 +8107,7 @@
         <v>2.98</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CU18" t="n">
         <v>1.4</v>
@@ -8116,7 +8116,7 @@
         <v>1.98</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX18" t="n">
         <v>1.48</v>
@@ -8131,88 +8131,88 @@
         <v>2.23</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC18" t="n">
         <v>2.02</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="DG18" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DH18" t="n">
-        <v>79.81999999999999</v>
+        <v>80.78</v>
       </c>
       <c r="DI18" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.77</v>
+        <v>4</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="DM18" t="n">
-        <v>50.06</v>
+        <v>50.22</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="DP18" t="n">
-        <v>13</v>
+        <v>12.88</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.59</v>
+        <v>16.11</v>
       </c>
       <c r="DR18" t="n">
-        <v>10.47</v>
+        <v>9.83</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.06</v>
+        <v>47.84</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.65</v>
+        <v>11.5</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.47</v>
+        <v>7.44</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.18</v>
+        <v>4.06</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1827,10 +1827,10 @@
         <v>14.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="R3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
         <v>1.2</v>
@@ -1848,25 +1848,25 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>57.5</v>
+        <v>57.6</v>
       </c>
       <c r="Y3" t="n">
         <v>0.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>18.7</v>
+        <v>19.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="AC3" t="n">
         <v>23</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AE3" t="n">
         <v>2.6</v>
@@ -2139,10 +2139,10 @@
         <v>14.39</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.78</v>
+        <v>14.61</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.89</v>
+        <v>8.17</v>
       </c>
       <c r="DS3" t="n">
         <v>0.16</v>
@@ -2154,25 +2154,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50.66</v>
+        <v>50.72</v>
       </c>
       <c r="DW3" t="n">
         <v>0.28</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.89</v>
+        <v>15.11</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.779999999999999</v>
+        <v>10.06</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="EA3" t="n">
         <v>22.83</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="EC3" t="n">
         <v>2.83</v>
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F4" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="H4" t="n">
-        <v>81.38</v>
+        <v>82.33</v>
       </c>
       <c r="I4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="K4" t="n">
-        <v>6.88</v>
+        <v>6.78</v>
       </c>
       <c r="L4" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>65.25</v>
+        <v>63.89</v>
       </c>
       <c r="N4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="P4" t="n">
-        <v>16</v>
+        <v>15.56</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.75</v>
+        <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>8.119999999999999</v>
+        <v>7.11</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="U4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>51.38</v>
+        <v>51</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.12</v>
+        <v>16.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.62</v>
+        <v>12.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>28.62</v>
+        <v>27</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="AF4" t="n">
         <v>0.33</v>
@@ -2356,67 +2356,67 @@
         <v>3.22</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.06</v>
+        <v>10.33</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.88</v>
+        <v>5.06</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.41</v>
+        <v>4.56</v>
       </c>
       <c r="BR4" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS4" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT4" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU4" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV4" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX4" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>2.5</v>
       </c>
-      <c r="BZ4" t="n">
-        <v>2.57</v>
-      </c>
       <c r="CA4" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CB4" t="n">
         <v>3.21</v>
@@ -2431,16 +2431,16 @@
         <v>1.37</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CG4" t="n">
         <v>2.46</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.77</v>
@@ -2449,13 +2449,13 @@
         <v>1.34</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CO4" t="n">
         <v>1.28</v>
@@ -2500,85 +2500,85 @@
         <v>1.4</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="DG4" t="n">
         <v>3</v>
       </c>
       <c r="DH4" t="n">
-        <v>76.70999999999999</v>
+        <v>77.44</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.36</v>
+        <v>6.34</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DM4" t="n">
-        <v>55.82</v>
+        <v>55.66</v>
       </c>
       <c r="DN4" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="DP4" t="n">
-        <v>17.06</v>
+        <v>16.78</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.82</v>
+        <v>12.56</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.289999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.3</v>
+        <v>46.39</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.47</v>
+        <v>15.84</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.59</v>
+        <v>11.06</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.88</v>
+        <v>4.77</v>
       </c>
       <c r="EA4" t="n">
-        <v>26.06</v>
+        <v>25.39</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="5">
@@ -2714,10 +2714,10 @@
         <v>16.33</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.56</v>
+        <v>15.44</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.67</v>
+        <v>5.56</v>
       </c>
       <c r="AT5" t="n">
         <v>0.44</v>
@@ -2735,25 +2735,25 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>53.44</v>
+        <v>53.89</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.11</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.67</v>
+        <v>13.44</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.220000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.44</v>
+        <v>4.78</v>
       </c>
       <c r="BD5" t="n">
         <v>23.22</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="BF5" t="n">
         <v>2.89</v>
@@ -2762,7 +2762,7 @@
         <v>2.44</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.56</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="BI5" t="n">
         <v>2.44</v>
@@ -2945,10 +2945,10 @@
         <v>15.72</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.34</v>
+        <v>15.28</v>
       </c>
       <c r="DR5" t="n">
-        <v>4.84</v>
+        <v>5.28</v>
       </c>
       <c r="DS5" t="n">
         <v>0.11</v>
@@ -2960,25 +2960,25 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.89</v>
+        <v>56.11</v>
       </c>
       <c r="DW5" t="n">
         <v>0.28</v>
       </c>
       <c r="DX5" t="n">
-        <v>14</v>
+        <v>14.38</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.06</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.94</v>
+        <v>5.11</v>
       </c>
       <c r="EA5" t="n">
         <v>23.5</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="EC5" t="n">
         <v>3.06</v>
@@ -3390,13 +3390,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3483,127 +3483,127 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="AH7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>79.22</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>48.11</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP7" t="n">
         <v>2</v>
       </c>
-      <c r="AI7" t="n">
-        <v>79.25</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>47.88</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>12.5</v>
+        <v>12.56</v>
       </c>
       <c r="AR7" t="n">
-        <v>16.25</v>
+        <v>17.22</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.619999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AU7" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>52.12</v>
+        <v>52.67</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BA7" t="n">
-        <v>12.62</v>
+        <v>12.78</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.25</v>
+        <v>8.33</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.88</v>
+        <v>19.67</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.12</v>
+        <v>4.67</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.59</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.35</v>
+        <v>4.44</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.12</v>
+        <v>5.06</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS7" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT7" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BU7" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3612,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
         <v>1.81</v>
@@ -3621,31 +3621,31 @@
         <v>1.91</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CH7" t="n">
         <v>1.38</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.8</v>
@@ -3654,7 +3654,7 @@
         <v>1.38</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM7" t="n">
         <v>2.72</v>
@@ -3666,28 +3666,28 @@
         <v>1.28</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CU7" t="n">
         <v>1.39</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX7" t="n">
         <v>1.49</v>
@@ -3702,88 +3702,88 @@
         <v>2.08</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DH7" t="n">
-        <v>83</v>
+        <v>82.78</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ7" t="n">
-        <v>4.06</v>
+        <v>3.89</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.3</v>
+        <v>4.39</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="DM7" t="n">
-        <v>54.53</v>
+        <v>54.28</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.41</v>
+        <v>14.34</v>
       </c>
       <c r="DQ7" t="n">
-        <v>16.47</v>
+        <v>16.94</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.23</v>
+        <v>7.72</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.06</v>
+        <v>54.22</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.65</v>
+        <v>13.67</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.76</v>
+        <v>8.77</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.77</v>
+        <v>19.67</v>
       </c>
       <c r="EB7" t="n">
         <v>1.59</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.76</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="8">
@@ -4241,10 +4241,10 @@
         <v>14.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="R9" t="n">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -4262,25 +4262,25 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>50.4</v>
+        <v>51.3</v>
       </c>
       <c r="Y9" t="n">
         <v>0.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AC9" t="n">
         <v>24.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -4553,10 +4553,10 @@
         <v>14.72</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.89</v>
+        <v>15.83</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.84</v>
+        <v>7.22</v>
       </c>
       <c r="DS9" t="n">
         <v>0.16</v>
@@ -4568,25 +4568,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.83</v>
+        <v>52.33</v>
       </c>
       <c r="DW9" t="n">
         <v>0.22</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.61</v>
+        <v>14.78</v>
       </c>
       <c r="DY9" t="n">
-        <v>10</v>
+        <v>10.06</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.61</v>
+        <v>4.72</v>
       </c>
       <c r="EA9" t="n">
         <v>23.11</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="EC9" t="n">
         <v>2.28</v>
@@ -4725,10 +4725,10 @@
         <v>14.78</v>
       </c>
       <c r="AR10" t="n">
-        <v>15</v>
+        <v>14.89</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.89</v>
+        <v>9.44</v>
       </c>
       <c r="AT10" t="n">
         <v>0.89</v>
@@ -4746,25 +4746,25 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>47.67</v>
+        <v>47.56</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.33</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.56</v>
+        <v>10.89</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.44</v>
+        <v>6.67</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.11</v>
+        <v>4.22</v>
       </c>
       <c r="BD10" t="n">
         <v>18.78</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BF10" t="n">
         <v>2.89</v>
@@ -4956,10 +4956,10 @@
         <v>13.72</v>
       </c>
       <c r="DQ10" t="n">
-        <v>15.22</v>
+        <v>15.16</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.84</v>
+        <v>7.61</v>
       </c>
       <c r="DS10" t="n">
         <v>0.16</v>
@@ -4971,25 +4971,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.72</v>
+        <v>51.67</v>
       </c>
       <c r="DW10" t="n">
         <v>0.22</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.67</v>
+        <v>12.84</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.94</v>
+        <v>9.06</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.72</v>
+        <v>3.77</v>
       </c>
       <c r="EA10" t="n">
         <v>18.5</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="EC10" t="n">
         <v>2.89</v>
@@ -5128,10 +5128,10 @@
         <v>15.67</v>
       </c>
       <c r="AR11" t="n">
-        <v>17.11</v>
+        <v>17</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.11</v>
+        <v>8.33</v>
       </c>
       <c r="AT11" t="n">
         <v>1.56</v>
@@ -5149,7 +5149,7 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>46.78</v>
+        <v>45.78</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.44</v>
@@ -5359,10 +5359,10 @@
         <v>14.28</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.67</v>
+        <v>16.61</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.61</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.84</v>
+        <v>48.34</v>
       </c>
       <c r="DW11" t="n">
         <v>0.28</v>
@@ -5432,7 +5432,7 @@
         <v>2.4</v>
       </c>
       <c r="K12" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="L12" t="n">
         <v>0.5</v>
@@ -5453,7 +5453,7 @@
         <v>14.7</v>
       </c>
       <c r="R12" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="S12" t="n">
         <v>1.6</v>
@@ -5471,19 +5471,19 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51.4</v>
+        <v>51</v>
       </c>
       <c r="Y12" t="n">
         <v>0.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AC12" t="n">
         <v>21.9</v>
@@ -5579,7 +5579,7 @@
         <v>3</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.67</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BI12" t="n">
         <v>3</v>
@@ -5744,7 +5744,7 @@
         <v>2.84</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.78</v>
+        <v>5.83</v>
       </c>
       <c r="DL12" t="n">
         <v>0.45</v>
@@ -5765,7 +5765,7 @@
         <v>14.89</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.720000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="DS12" t="n">
         <v>0.11</v>
@@ -5777,19 +5777,19 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.95</v>
+        <v>48.72</v>
       </c>
       <c r="DW12" t="n">
         <v>0.22</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.39</v>
+        <v>12.56</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.94</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.44</v>
+        <v>4.28</v>
       </c>
       <c r="EA12" t="n">
         <v>21.28</v>
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6703,136 +6703,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="AI15" t="n">
-        <v>64.88</v>
+        <v>68.33</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.62</v>
+        <v>5.11</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AN15" t="n">
-        <v>44.5</v>
+        <v>47.67</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14.12</v>
+        <v>13.33</v>
       </c>
       <c r="AR15" t="n">
-        <v>15.25</v>
+        <v>15</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.75</v>
+        <v>8.56</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AU15" t="n">
         <v>1</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>47.75</v>
+        <v>48.22</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA15" t="n">
-        <v>11.5</v>
+        <v>11.11</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.5</v>
+        <v>7.11</v>
       </c>
       <c r="BC15" t="n">
         <v>4</v>
       </c>
       <c r="BD15" t="n">
-        <v>21.88</v>
+        <v>22.56</v>
       </c>
       <c r="BE15" t="n">
         <v>1.32</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.47</v>
+        <v>10.72</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.71</v>
+        <v>4.89</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.94</v>
+        <v>5.06</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS15" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU15" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV15" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX15" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY15" t="n">
         <v>2.5</v>
@@ -6841,25 +6841,25 @@
         <v>2.94</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="CE15" t="n">
         <v>1.33</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH15" t="n">
         <v>1.28</v>
@@ -6868,28 +6868,28 @@
         <v>1.8</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CL15" t="n">
         <v>1.65</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP15" t="n">
         <v>1.92</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
@@ -6904,7 +6904,7 @@
         <v>1.38</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW15" t="n">
         <v>1.87</v>
@@ -6928,49 +6928,49 @@
         <v>2.1</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="DH15" t="n">
-        <v>68.18000000000001</v>
+        <v>69.72</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.18</v>
+        <v>4.44</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.53</v>
+        <v>0.66</v>
       </c>
       <c r="DM15" t="n">
-        <v>40.83</v>
+        <v>42.62</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.59</v>
+        <v>14.16</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.41</v>
+        <v>15.28</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.59</v>
+        <v>9</v>
       </c>
       <c r="DS15" t="n">
         <v>0.11</v>
@@ -6982,28 +6982,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.41</v>
+        <v>47.66</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX15" t="n">
-        <v>11</v>
+        <v>10.84</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.94</v>
+        <v>6.78</v>
       </c>
       <c r="DZ15" t="n">
         <v>4.06</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.36</v>
+        <v>20.78</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="16">
@@ -7013,94 +7013,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F16" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="G16" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>81.62</v>
+        <v>79.22</v>
       </c>
       <c r="I16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J16" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="K16" t="n">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="L16" t="n">
-        <v>0.62</v>
+        <v>0.44</v>
       </c>
       <c r="M16" t="n">
-        <v>52.38</v>
+        <v>49.56</v>
       </c>
       <c r="N16" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="O16" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>15.12</v>
+        <v>14.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.62</v>
+        <v>13.78</v>
       </c>
       <c r="R16" t="n">
-        <v>9.119999999999999</v>
+        <v>8</v>
       </c>
       <c r="S16" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="U16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>54.38</v>
+        <v>52.67</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>14.5</v>
+        <v>13.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>8</v>
+        <v>7.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.5</v>
+        <v>5.89</v>
       </c>
       <c r="AC16" t="n">
-        <v>22.62</v>
+        <v>21.67</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AE16" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7184,70 +7184,70 @@
         <v>2.89</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.59</v>
+        <v>9.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.41</v>
+        <v>4.11</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.24</v>
+        <v>3.94</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS16" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT16" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV16" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CC16" t="n">
         <v>2.88</v>
@@ -7259,19 +7259,19 @@
         <v>1.41</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CH16" t="n">
         <v>1.35</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK16" t="n">
         <v>1.36</v>
@@ -7280,133 +7280,133 @@
         <v>1.83</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CN16" t="n">
         <v>1.84</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="CR16" t="n">
         <v>1.42</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV16" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW16" t="n">
         <v>1.84</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY16" t="n">
         <v>1.82</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DA16" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.76</v>
+        <v>3.79</v>
       </c>
       <c r="DE16" t="n">
         <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="DH16" t="n">
-        <v>84.29000000000001</v>
+        <v>82.94</v>
       </c>
       <c r="DI16" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.41</v>
+        <v>3.28</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.59</v>
+        <v>0.5</v>
       </c>
       <c r="DM16" t="n">
-        <v>50.42</v>
+        <v>49.12</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="DP16" t="n">
-        <v>15.59</v>
+        <v>15.16</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.47</v>
+        <v>12.61</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.289999999999999</v>
+        <v>7.78</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.76</v>
+        <v>51.06</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.88</v>
+        <v>12.38</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.119999999999999</v>
+        <v>7.83</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.76</v>
+        <v>4.56</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.23</v>
+        <v>20.84</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -7416,13 +7416,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7506,139 +7506,139 @@
         <v>2.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AH17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF17" t="n">
         <v>3</v>
       </c>
-      <c r="AI17" t="n">
-        <v>86.11</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>55.78</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>44.56</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>21.44</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>3.11</v>
-      </c>
       <c r="BG17" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.94</v>
+        <v>9.83</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.53</v>
+        <v>4.22</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.88</v>
+        <v>4.56</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS17" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BT17" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BU17" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV17" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX17" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BY17" t="n">
         <v>1.78</v>
@@ -7650,28 +7650,28 @@
         <v>3.16</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="CE17" t="n">
         <v>1.41</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CH17" t="n">
         <v>1.35</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.84</v>
@@ -7683,28 +7683,28 @@
         <v>1.81</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CO17" t="n">
         <v>1.33</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="CR17" t="n">
         <v>1.43</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CU17" t="n">
         <v>1.37</v>
@@ -7716,100 +7716,100 @@
         <v>1.91</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB17" t="n">
         <v>1.36</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.86</v>
+        <v>3.89</v>
       </c>
       <c r="DE17" t="n">
         <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="DH17" t="n">
-        <v>84.12</v>
+        <v>84.5</v>
       </c>
       <c r="DI17" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="DK17" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="DM17" t="n">
-        <v>55</v>
+        <v>55.05</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="DO17" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.18</v>
+        <v>12.11</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.53</v>
+        <v>11.39</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.35</v>
+        <v>7.84</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>46.36</v>
+        <v>47.17</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.23</v>
+        <v>12.61</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.18</v>
+        <v>8.44</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.06</v>
+        <v>4.17</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.52</v>
+        <v>21.61</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="18">
@@ -8222,61 +8222,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F19" t="n">
-        <v>0.86</v>
+        <v>1.38</v>
       </c>
       <c r="G19" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H19" t="n">
-        <v>83.14</v>
+        <v>81.5</v>
       </c>
       <c r="I19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J19" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="K19" t="n">
-        <v>6.29</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M19" t="n">
-        <v>60.71</v>
+        <v>58.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O19" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="P19" t="n">
-        <v>14.29</v>
+        <v>15.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.86</v>
+        <v>12.88</v>
       </c>
       <c r="R19" t="n">
-        <v>7.43</v>
+        <v>6.38</v>
       </c>
       <c r="S19" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="T19" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8288,28 +8288,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>57.43</v>
+        <v>55.62</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.29</v>
+        <v>12.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.57</v>
+        <v>8</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.71</v>
+        <v>4.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>19.86</v>
+        <v>19.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8393,70 +8393,70 @@
         <v>3.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.76</v>
+        <v>10.72</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.41</v>
+        <v>5.44</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.35</v>
+        <v>5.28</v>
       </c>
       <c r="BR19" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS19" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT19" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU19" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV19" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CC19" t="n">
         <v>2.51</v>
@@ -8468,10 +8468,10 @@
         <v>1.41</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CH19" t="n">
         <v>1.36</v>
@@ -8486,7 +8486,7 @@
         <v>1.39</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM19" t="n">
         <v>2.71</v>
@@ -8498,25 +8498,25 @@
         <v>1.3</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="CR19" t="n">
         <v>1.42</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CU19" t="n">
         <v>1.37</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW19" t="n">
         <v>1.86</v>
@@ -8537,52 +8537,52 @@
         <v>1.35</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.77</v>
+        <v>3.79</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="DH19" t="n">
-        <v>84</v>
+        <v>83.22</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.35</v>
+        <v>5.28</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM19" t="n">
-        <v>55.82</v>
+        <v>55.11</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.71</v>
+        <v>15.05</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.82</v>
+        <v>14.72</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.47</v>
+        <v>7</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8594,28 +8594,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>55.06</v>
+        <v>54.39</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.59</v>
+        <v>12.39</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.119999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.41</v>
+        <v>21.22</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,139 +1469,139 @@
         <v>2.44</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG2" t="n">
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AI2" t="n">
-        <v>79.89</v>
+        <v>77.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.22</v>
+        <v>4.9</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AN2" t="n">
-        <v>49.33</v>
+        <v>48.1</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.33</v>
+        <v>14.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>14.22</v>
+        <v>14.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.44</v>
+        <v>5.7</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>49.78</v>
+        <v>48.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.67</v>
+        <v>13.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.890000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.78</v>
+        <v>4.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>22.44</v>
+        <v>22.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BG2" t="n">
         <v>2.89</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.44</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI2" t="n">
         <v>2.89</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.28</v>
+        <v>5.26</v>
       </c>
       <c r="BR2" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT2" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU2" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV2" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX2" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY2" t="n">
         <v>2.03</v>
@@ -1610,19 +1610,19 @@
         <v>2.03</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF2" t="n">
         <v>3.09</v>
@@ -1646,31 +1646,31 @@
         <v>1.8</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP2" t="n">
         <v>2.11</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CR2" t="n">
         <v>1.46</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV2" t="n">
         <v>1.88</v>
@@ -1691,13 +1691,13 @@
         <v>2.11</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="DE2" t="n">
         <v>0.11</v>
@@ -1706,73 +1706,73 @@
         <v>2</v>
       </c>
       <c r="DG2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>80.11</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DJ2" t="n">
         <v>3</v>
       </c>
-      <c r="DH2" t="n">
-        <v>81.33</v>
-      </c>
-      <c r="DI2" t="n">
+      <c r="DK2" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>51.52</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="DS2" t="n">
         <v>0.11</v>
       </c>
-      <c r="DJ2" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>52.33</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>13.56</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.06</v>
-      </c>
       <c r="DT2" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.89</v>
+        <v>50</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.67</v>
+        <v>14.37</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.5</v>
+        <v>9.16</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.17</v>
+        <v>5.21</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.94</v>
+        <v>22.95</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="3">
@@ -2230,10 +2230,10 @@
         <v>15.56</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>13.89</v>
       </c>
       <c r="R4" t="n">
-        <v>7.11</v>
+        <v>8.44</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>51</v>
+        <v>50.89</v>
       </c>
       <c r="Y4" t="n">
         <v>0.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.67</v>
+        <v>17.78</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.33</v>
+        <v>13.44</v>
       </c>
       <c r="AB4" t="n">
         <v>4.33</v>
@@ -2269,7 +2269,7 @@
         <v>27</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AE4" t="n">
         <v>3.33</v>
@@ -2542,10 +2542,10 @@
         <v>16.78</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.56</v>
+        <v>12.5</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.720000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DS4" t="n">
         <v>0.11</v>
@@ -2557,16 +2557,16 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.39</v>
+        <v>46.34</v>
       </c>
       <c r="DW4" t="n">
         <v>0.22</v>
       </c>
       <c r="DX4" t="n">
-        <v>15.84</v>
+        <v>16.39</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.06</v>
+        <v>11.61</v>
       </c>
       <c r="DZ4" t="n">
         <v>4.77</v>
@@ -2575,7 +2575,7 @@
         <v>25.39</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="EC4" t="n">
         <v>3.28</v>
@@ -3543,19 +3543,19 @@
         <v>0.44</v>
       </c>
       <c r="BA7" t="n">
-        <v>12.78</v>
+        <v>11.89</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.33</v>
+        <v>7.56</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.44</v>
+        <v>4.33</v>
       </c>
       <c r="BD7" t="n">
         <v>19.67</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BF7" t="n">
         <v>4.67</v>
@@ -3768,19 +3768,19 @@
         <v>0.22</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.67</v>
+        <v>13.23</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.77</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.89</v>
+        <v>4.83</v>
       </c>
       <c r="EA7" t="n">
         <v>19.67</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="EC7" t="n">
         <v>3.62</v>
@@ -5808,10 +5808,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
@@ -5820,82 +5820,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.88</v>
+        <v>2.56</v>
       </c>
       <c r="G13" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="H13" t="n">
-        <v>77.5</v>
+        <v>79.22</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.88</v>
+        <v>3.44</v>
       </c>
       <c r="K13" t="n">
-        <v>3.62</v>
+        <v>4.11</v>
       </c>
       <c r="L13" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>51.75</v>
+        <v>52</v>
       </c>
       <c r="N13" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="P13" t="n">
-        <v>16.75</v>
+        <v>16.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.12</v>
+        <v>15.22</v>
       </c>
       <c r="R13" t="n">
-        <v>7.5</v>
+        <v>6.56</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="U13" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="V13" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>44</v>
+        <v>46.44</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.62</v>
+        <v>14.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.119999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.5</v>
+        <v>4.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>21.62</v>
+        <v>22.44</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.25</v>
+        <v>2.89</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5979,67 +5979,67 @@
         <v>2.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.94</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.89</v>
+        <v>5.84</v>
       </c>
       <c r="BR13" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BS13" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU13" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.33</v>
+        <v>3.55</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="CB13" t="n">
         <v>3.48</v>
@@ -6063,13 +6063,13 @@
         <v>1.34</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL13" t="n">
         <v>1.87</v>
@@ -6084,19 +6084,19 @@
         <v>1.35</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ13" t="n">
         <v>3.79</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CU13" t="n">
         <v>1.36</v>
@@ -6123,85 +6123,85 @@
         <v>1.37</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="DH13" t="n">
-        <v>75.89</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.61</v>
+        <v>3.84</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM13" t="n">
-        <v>44.61</v>
+        <v>45.11</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.94</v>
+        <v>14.79</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.39</v>
+        <v>16.37</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.5</v>
+        <v>9.9</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.78</v>
+        <v>45.89</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.22</v>
+        <v>11.68</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.83</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.39</v>
+        <v>3.58</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.39</v>
+        <v>21.79</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="14">
@@ -6736,10 +6736,10 @@
         <v>13.33</v>
       </c>
       <c r="AR15" t="n">
-        <v>15</v>
+        <v>14.89</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.56</v>
+        <v>9.67</v>
       </c>
       <c r="AT15" t="n">
         <v>1.78</v>
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>48.22</v>
+        <v>48.33</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.11</v>
@@ -6766,10 +6766,10 @@
         <v>11.11</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.11</v>
+        <v>7.22</v>
       </c>
       <c r="BC15" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BD15" t="n">
         <v>22.56</v>
@@ -6967,10 +6967,10 @@
         <v>14.16</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.28</v>
+        <v>15.22</v>
       </c>
       <c r="DR15" t="n">
-        <v>9</v>
+        <v>9.56</v>
       </c>
       <c r="DS15" t="n">
         <v>0.11</v>
@@ -6982,7 +6982,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.66</v>
+        <v>47.72</v>
       </c>
       <c r="DW15" t="n">
         <v>0.22</v>
@@ -6991,10 +6991,10 @@
         <v>10.84</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.78</v>
+        <v>6.83</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="EA15" t="n">
         <v>20.78</v>
@@ -7058,10 +7058,10 @@
         <v>14.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.78</v>
+        <v>13.67</v>
       </c>
       <c r="R16" t="n">
-        <v>8</v>
+        <v>9.33</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -7079,7 +7079,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>52.67</v>
+        <v>53.44</v>
       </c>
       <c r="Y16" t="n">
         <v>0.11</v>
@@ -7187,7 +7187,7 @@
         <v>2.33</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.5</v>
+        <v>9.56</v>
       </c>
       <c r="BI16" t="n">
         <v>2.33</v>
@@ -7370,10 +7370,10 @@
         <v>15.16</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.61</v>
+        <v>12.56</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.78</v>
+        <v>8.44</v>
       </c>
       <c r="DS16" t="n">
         <v>0.16</v>
@@ -7385,7 +7385,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.06</v>
+        <v>51.44</v>
       </c>
       <c r="DW16" t="n">
         <v>0.22</v>
@@ -7524,7 +7524,7 @@
         <v>3.6</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
@@ -7542,10 +7542,10 @@
         <v>12.7</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="AT17" t="n">
         <v>1.1</v>
@@ -7563,25 +7563,25 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>46.2</v>
+        <v>45.5</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BC17" t="n">
         <v>3.9</v>
       </c>
       <c r="BD17" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="BF17" t="n">
         <v>3</v>
@@ -7590,7 +7590,7 @@
         <v>2.39</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.83</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI17" t="n">
         <v>2.39</v>
@@ -7755,7 +7755,7 @@
         <v>3.33</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.94</v>
+        <v>5</v>
       </c>
       <c r="DL17" t="n">
         <v>0.05</v>
@@ -7773,10 +7773,10 @@
         <v>12.11</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.39</v>
+        <v>11.33</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.84</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DS17" t="n">
         <v>0.17</v>
@@ -7788,25 +7788,25 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.17</v>
+        <v>46.78</v>
       </c>
       <c r="DW17" t="n">
         <v>0.5</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.61</v>
+        <v>12.67</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.44</v>
+        <v>8.5</v>
       </c>
       <c r="DZ17" t="n">
         <v>4.17</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.61</v>
+        <v>21.55</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="EC17" t="n">
         <v>2.61</v>
@@ -8234,7 +8234,7 @@
         <v>0.12</v>
       </c>
       <c r="F19" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="G19" t="n">
         <v>2.88</v>
@@ -8246,7 +8246,7 @@
         <v>0.12</v>
       </c>
       <c r="J19" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
@@ -8309,7 +8309,7 @@
         <v>1.56</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8546,7 +8546,7 @@
         <v>0.05</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="DG19" t="n">
         <v>2.72</v>
@@ -8558,7 +8558,7 @@
         <v>0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="DK19" t="n">
         <v>5.28</v>
@@ -8615,7 +8615,7 @@
         <v>1.49</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1670,7 +1670,7 @@
         <v>2.73</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CV2" t="n">
         <v>1.88</v>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,139 +1872,139 @@
         <v>2.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AI3" t="n">
-        <v>74.12</v>
+        <v>75.67</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN3" t="n">
-        <v>42.62</v>
+        <v>43.56</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.38</v>
+        <v>14.67</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.5</v>
+        <v>15.56</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.88</v>
+        <v>9.56</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>42.12</v>
+        <v>42.89</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.12</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.38</v>
+        <v>5.78</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="BD3" t="n">
-        <v>22.62</v>
+        <v>22</v>
       </c>
       <c r="BE3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BO3" t="n">
         <v>1.21</v>
       </c>
-      <c r="BF3" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>11.39</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>1.28</v>
-      </c>
       <c r="BP3" t="n">
-        <v>5.67</v>
+        <v>5.68</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.61</v>
+        <v>5.58</v>
       </c>
       <c r="BR3" t="n">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU3" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV3" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX3" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BY3" t="n">
         <v>2.07</v>
@@ -2013,22 +2013,22 @@
         <v>2.23</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="CE3" t="n">
         <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CG3" t="n">
         <v>2.85</v>
@@ -2055,19 +2055,19 @@
         <v>2.09</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP3" t="n">
         <v>1.92</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CT3" t="n">
         <v>3.03</v>
@@ -2091,7 +2091,7 @@
         <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DB3" t="n">
         <v>1.3</v>
@@ -2100,49 +2100,49 @@
         <v>1.97</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="DE3" t="n">
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="DH3" t="n">
-        <v>83</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.56</v>
+        <v>6.42</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="DM3" t="n">
-        <v>57.89</v>
+        <v>57.53</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.39</v>
+        <v>14.53</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.61</v>
+        <v>15.11</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.17</v>
+        <v>7.69</v>
       </c>
       <c r="DS3" t="n">
         <v>0.16</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50.72</v>
+        <v>50.63</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.11</v>
+        <v>14.42</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.06</v>
+        <v>9.58</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.06</v>
+        <v>4.84</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.83</v>
+        <v>22.53</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0.11</v>
@@ -2275,139 +2275,139 @@
         <v>3.33</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AI4" t="n">
-        <v>72.56</v>
+        <v>71.8</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.89</v>
+        <v>5.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AN4" t="n">
-        <v>47.44</v>
+        <v>46.8</v>
       </c>
       <c r="AO4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BO4" t="n">
         <v>1.11</v>
       </c>
-      <c r="AP4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>41.78</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>23.78</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BP4" t="n">
-        <v>5.06</v>
+        <v>4.95</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="BR4" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BT4" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU4" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV4" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX4" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY4" t="n">
         <v>2.45</v>
@@ -2416,22 +2416,22 @@
         <v>2.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CG4" t="n">
         <v>2.46</v>
@@ -2443,25 +2443,25 @@
         <v>1.72</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CN4" t="n">
         <v>1.88</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CQ4" t="n">
         <v>3.61</v>
@@ -2479,106 +2479,106 @@
         <v>1.34</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW4" t="n">
         <v>1.97</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.55</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB4" t="n">
         <v>1.4</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="DG4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="DH4" t="n">
-        <v>77.44</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.34</v>
+        <v>6.26</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM4" t="n">
-        <v>55.66</v>
+        <v>54.9</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="DP4" t="n">
-        <v>16.78</v>
+        <v>16.95</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.5</v>
+        <v>12.53</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.380000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.34</v>
+        <v>46.63</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.39</v>
+        <v>16</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.61</v>
+        <v>11.37</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.77</v>
+        <v>4.63</v>
       </c>
       <c r="EA4" t="n">
-        <v>25.39</v>
+        <v>25.47</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="5">
@@ -2588,61 +2588,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H5" t="n">
-        <v>94.22</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4.11</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="L5" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>63.22</v>
+        <v>61.7</v>
       </c>
       <c r="N5" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="P5" t="n">
-        <v>15.11</v>
+        <v>14.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.11</v>
+        <v>15.4</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58.33</v>
+        <v>58.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.33</v>
+        <v>15.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.890000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.44</v>
+        <v>5.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>23.78</v>
+        <v>23.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="AF5" t="n">
         <v>0.33</v>
@@ -2759,67 +2759,67 @@
         <v>2.89</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.609999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BM5" t="n">
         <v>0.89</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BU5" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV5" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CB5" t="n">
         <v>3.48</v>
@@ -2831,13 +2831,13 @@
         <v>2.58</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CH5" t="n">
         <v>1.28</v>
@@ -2846,13 +2846,13 @@
         <v>1.78</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CM5" t="n">
         <v>2.49</v>
@@ -2864,10 +2864,10 @@
         <v>1.24</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="CR5" t="n">
         <v>1.42</v>
@@ -2882,106 +2882,106 @@
         <v>1.37</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX5" t="n">
         <v>1.54</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DH5" t="n">
-        <v>85.94</v>
+        <v>86.05</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.61</v>
+        <v>3.53</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.66</v>
+        <v>4.84</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.28</v>
+        <v>0.37</v>
       </c>
       <c r="DM5" t="n">
-        <v>55</v>
+        <v>54.63</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.72</v>
+        <v>15.52</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.28</v>
+        <v>15.42</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.28</v>
+        <v>4.95</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.11</v>
+        <v>56.37</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.38</v>
+        <v>14.31</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.279999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DZ5" t="n">
         <v>5.11</v>
       </c>
       <c r="EA5" t="n">
-        <v>23.5</v>
+        <v>23.31</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="EC5" t="n">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AI6" t="n">
-        <v>74.78</v>
+        <v>75.2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="AN6" t="n">
-        <v>43.44</v>
+        <v>42</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>17.11</v>
+        <v>16.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.33</v>
+        <v>15.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>12</v>
+        <v>10.7</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AU6" t="n">
         <v>1</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>39.56</v>
+        <v>40.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.67</v>
+        <v>10.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.78</v>
+        <v>6.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.89</v>
+        <v>3.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>24.11</v>
+        <v>24.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.44</v>
+        <v>10.32</v>
       </c>
       <c r="BI6" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.11</v>
+        <v>5.74</v>
       </c>
       <c r="BR6" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT6" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BU6" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BY6" t="n">
         <v>2.73</v>
@@ -3222,46 +3222,46 @@
         <v>3.09</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.65</v>
+        <v>4.44</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.92</v>
+        <v>4.71</v>
       </c>
       <c r="CE6" t="n">
         <v>1.32</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI6" t="n">
         <v>1.81</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CL6" t="n">
         <v>1.54</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO6" t="n">
         <v>1.22</v>
@@ -3270,7 +3270,7 @@
         <v>1.88</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CR6" t="n">
         <v>1.41</v>
@@ -3288,7 +3288,7 @@
         <v>1.97</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX6" t="inlineStr"/>
       <c r="CY6" t="n">
@@ -3311,76 +3311,76 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="DH6" t="n">
-        <v>83</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.66</v>
+        <v>4.63</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="DM6" t="n">
-        <v>50.28</v>
+        <v>49.16</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.84</v>
+        <v>15.74</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.61</v>
+        <v>14.68</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.34</v>
+        <v>9.74</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.78</v>
+        <v>44.89</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.44</v>
+        <v>11.1</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.56</v>
+        <v>7.37</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.89</v>
+        <v>3.74</v>
       </c>
       <c r="EA6" t="n">
-        <v>23.06</v>
+        <v>23.16</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="7">
@@ -3390,13 +3390,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3483,127 +3483,127 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AI7" t="n">
-        <v>79.22</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>5.22</v>
+        <v>5</v>
       </c>
       <c r="AL7" t="n">
         <v>4</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>48.11</v>
+        <v>51.1</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AP7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.56</v>
+        <v>13.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>17.22</v>
+        <v>17</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>52.67</v>
+        <v>53.9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.89</v>
+        <v>12.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.56</v>
+        <v>7.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.67</v>
+        <v>19.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.609999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BL7" t="n">
         <v>0.89</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.44</v>
+        <v>4.47</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.06</v>
+        <v>4.84</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BT7" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BU7" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3612,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY7" t="n">
         <v>1.81</v>
@@ -3624,19 +3624,19 @@
         <v>3.37</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="CE7" t="n">
         <v>1.4</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CG7" t="n">
         <v>2.78</v>
@@ -3645,7 +3645,7 @@
         <v>1.38</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.8</v>
@@ -3654,7 +3654,7 @@
         <v>1.38</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM7" t="n">
         <v>2.72</v>
@@ -3666,10 +3666,10 @@
         <v>1.28</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
@@ -3681,7 +3681,7 @@
         <v>2.93</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV7" t="n">
         <v>1.98</v>
@@ -3714,43 +3714,43 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="DH7" t="n">
-        <v>82.78</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DM7" t="n">
-        <v>54.28</v>
+        <v>55.52</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.34</v>
+        <v>14.53</v>
       </c>
       <c r="DQ7" t="n">
-        <v>16.94</v>
+        <v>16.84</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.72</v>
+        <v>7.63</v>
       </c>
       <c r="DS7" t="n">
         <v>0.11</v>
@@ -3762,28 +3762,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.22</v>
+        <v>54.79</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.23</v>
+        <v>13.32</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.390000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.83</v>
+        <v>4.79</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.67</v>
+        <v>19.63</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="8">
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3883,139 +3883,139 @@
         <v>3.67</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AI8" t="n">
-        <v>82.67</v>
+        <v>83.2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.78</v>
+        <v>5.6</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AN8" t="n">
-        <v>52.11</v>
+        <v>51.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.44</v>
+        <v>13.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.11</v>
+        <v>15.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.78</v>
+        <v>6.9</v>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>50.22</v>
+        <v>50.2</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.78</v>
+        <v>13</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.33</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>22.78</v>
+        <v>23.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.17</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.56</v>
+        <v>4.42</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.61</v>
+        <v>5.47</v>
       </c>
       <c r="BR8" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BS8" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT8" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BU8" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BV8" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX8" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BY8" t="n">
         <v>1.95</v>
@@ -4027,19 +4027,19 @@
         <v>3.24</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="CE8" t="n">
         <v>1.42</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CG8" t="n">
         <v>2.68</v>
@@ -4051,7 +4051,7 @@
         <v>1.87</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK8" t="n">
         <v>1.31</v>
@@ -4060,7 +4060,7 @@
         <v>1.71</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CN8" t="n">
         <v>1.99</v>
@@ -4072,7 +4072,7 @@
         <v>2.04</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="CR8" t="n">
         <v>1.43</v>
@@ -4096,13 +4096,13 @@
         <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.48</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DB8" t="n">
         <v>1.35</v>
@@ -4111,82 +4111,82 @@
         <v>2.13</v>
       </c>
       <c r="DD8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="DG8" t="n">
         <v>3.79</v>
       </c>
-      <c r="DE8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>3.84</v>
-      </c>
       <c r="DH8" t="n">
-        <v>89.56</v>
+        <v>89.47</v>
       </c>
       <c r="DI8" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.11</v>
+        <v>6</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM8" t="n">
-        <v>60.11</v>
+        <v>59.53</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.33</v>
+        <v>14.31</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.16</v>
+        <v>14.37</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.11</v>
+        <v>6.68</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.83</v>
+        <v>51.73</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.78</v>
+        <v>14.32</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.77</v>
+        <v>9.42</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="EA8" t="n">
-        <v>24.23</v>
+        <v>24.48</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="9">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4292,133 +4292,133 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AI9" t="n">
-        <v>87.5</v>
+        <v>86.89</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.88</v>
+        <v>4.56</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN9" t="n">
-        <v>56.88</v>
+        <v>54.67</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.75</v>
+        <v>14.67</v>
       </c>
       <c r="AR9" t="n">
-        <v>17.25</v>
+        <v>16.67</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.38</v>
+        <v>6.44</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>53.62</v>
+        <v>52</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA9" t="n">
-        <v>15.12</v>
+        <v>14.44</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.880000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="BD9" t="n">
-        <v>21.25</v>
+        <v>21.44</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.06</v>
+        <v>10.05</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.28</v>
+        <v>4.37</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.28</v>
+        <v>5.21</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT9" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BU9" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV9" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY9" t="n">
         <v>2.01</v>
@@ -4427,55 +4427,55 @@
         <v>2.03</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CB9" t="n">
         <v>3.4</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.86</v>
+        <v>3.02</v>
       </c>
       <c r="CD9" t="n">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="CE9" t="n">
         <v>1.41</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH9" t="n">
         <v>1.35</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK9" t="n">
         <v>1.38</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CO9" t="n">
         <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="CR9" t="n">
         <v>1.41</v>
@@ -4490,73 +4490,73 @@
         <v>1.37</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX9" t="n">
         <v>1.5</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="DB9" t="n">
         <v>1.33</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DG9" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DH9" t="n">
-        <v>90.72</v>
+        <v>90.26000000000001</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.61</v>
+        <v>5.42</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM9" t="n">
-        <v>60.39</v>
+        <v>59.16</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.72</v>
+        <v>14.69</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.83</v>
+        <v>15.63</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.22</v>
+        <v>6.79</v>
       </c>
       <c r="DS9" t="n">
         <v>0.16</v>
@@ -4568,28 +4568,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52.33</v>
+        <v>51.63</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.78</v>
+        <v>14.47</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.06</v>
+        <v>9.84</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.72</v>
+        <v>4.63</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.11</v>
+        <v>23.1</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="10">
@@ -4599,94 +4599,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F10" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="n">
-        <v>76.89</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>5.67</v>
+        <v>5.4</v>
       </c>
       <c r="L10" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="M10" t="n">
-        <v>51.78</v>
+        <v>52.4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="P10" t="n">
-        <v>12.67</v>
+        <v>12.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.44</v>
+        <v>15.2</v>
       </c>
       <c r="R10" t="n">
-        <v>5.78</v>
+        <v>5.1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>55.78</v>
+        <v>56.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.78</v>
+        <v>14.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.44</v>
+        <v>10.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.22</v>
+        <v>17.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AF10" t="n">
         <v>0.22</v>
@@ -4770,64 +4770,64 @@
         <v>2.89</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.94</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.33</v>
+        <v>4.26</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT10" t="n">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
       <c r="BU10" t="n">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CA10" t="n">
         <v>3.2</v>
@@ -4845,28 +4845,28 @@
         <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI10" t="n">
         <v>1.88</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CK10" t="n">
         <v>1.42</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CN10" t="n">
         <v>2</v>
@@ -4878,7 +4878,7 @@
         <v>2.1</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="CR10" t="n">
         <v>1.44</v>
@@ -4893,7 +4893,7 @@
         <v>1.35</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW10" t="n">
         <v>1.9</v>
@@ -4902,13 +4902,13 @@
         <v>1.51</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DB10" t="n">
         <v>1.36</v>
@@ -4923,43 +4923,43 @@
         <v>0.16</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="DH10" t="n">
-        <v>79</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="DK10" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="DM10" t="n">
-        <v>51.22</v>
+        <v>51.58</v>
       </c>
       <c r="DN10" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.72</v>
+        <v>13.79</v>
       </c>
       <c r="DQ10" t="n">
-        <v>15.16</v>
+        <v>15.05</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.61</v>
+        <v>7.16</v>
       </c>
       <c r="DS10" t="n">
         <v>0.16</v>
@@ -4971,28 +4971,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.67</v>
+        <v>52.11</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.84</v>
+        <v>12.68</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.06</v>
+        <v>8.84</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.77</v>
+        <v>3.84</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.5</v>
+        <v>18.26</v>
       </c>
       <c r="EB10" t="n">
         <v>1.44</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -5002,61 +5002,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F11" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="H11" t="n">
-        <v>95.56</v>
+        <v>96</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="K11" t="n">
-        <v>4.67</v>
+        <v>4.9</v>
       </c>
       <c r="L11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M11" t="n">
-        <v>52.89</v>
+        <v>54</v>
       </c>
       <c r="N11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="P11" t="n">
-        <v>12.89</v>
+        <v>13.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>16.22</v>
+        <v>16.5</v>
       </c>
       <c r="R11" t="n">
-        <v>8.109999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="S11" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5068,28 +5068,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>50.89</v>
+        <v>50.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.44</v>
+        <v>12.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.67</v>
+        <v>8.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.78</v>
+        <v>4.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.89</v>
+        <v>23.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5173,70 +5173,70 @@
         <v>4.11</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.390000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM11" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BP11" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.39</v>
+        <v>5.37</v>
       </c>
       <c r="BR11" t="n">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BT11" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU11" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV11" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CC11" t="n">
         <v>3.35</v>
@@ -5251,16 +5251,16 @@
         <v>3.03</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CH11" t="n">
         <v>1.34</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK11" t="n">
         <v>1.32</v>
@@ -5269,37 +5269,37 @@
         <v>1.75</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CO11" t="n">
         <v>1.34</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CU11" t="n">
         <v>1.36</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX11" t="n">
         <v>1.51</v>
@@ -5317,52 +5317,52 @@
         <v>1.36</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="DH11" t="n">
-        <v>89</v>
+        <v>89.58</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.44</v>
+        <v>4.58</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM11" t="n">
-        <v>48.16</v>
+        <v>49</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.28</v>
+        <v>14.74</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.61</v>
+        <v>16.74</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.220000000000001</v>
+        <v>7.74</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.34</v>
+        <v>48.47</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX11" t="n">
-        <v>12</v>
+        <v>11.69</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.89</v>
+        <v>7.63</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.89</v>
+        <v>22.84</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="EC11" t="n">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="12">
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0.3</v>
@@ -5498,136 +5498,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AI12" t="n">
-        <v>74.25</v>
+        <v>74.56</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>43.88</v>
+        <v>43.78</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.38</v>
+        <v>13.22</v>
       </c>
       <c r="AR12" t="n">
-        <v>15.12</v>
+        <v>15.11</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.75</v>
+        <v>9.44</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>45.88</v>
+        <v>45.22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.38</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.62</v>
+        <v>6.44</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.75</v>
+        <v>4.56</v>
       </c>
       <c r="BD12" t="n">
-        <v>20.5</v>
+        <v>20.33</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BG12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.720000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="BI12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BP12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.94</v>
+        <v>4.89</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT12" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU12" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BV12" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY12" t="n">
         <v>2.42</v>
@@ -5642,34 +5642,34 @@
         <v>3.27</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.16</v>
+        <v>3.24</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="CE12" t="n">
         <v>1.42</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CH12" t="n">
         <v>1.34</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.85</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CM12" t="n">
         <v>2.49</v>
@@ -5678,7 +5678,7 @@
         <v>1.89</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP12" t="n">
         <v>2.13</v>
@@ -5690,7 +5690,7 @@
         <v>1.44</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CT12" t="n">
         <v>2.79</v>
@@ -5711,10 +5711,10 @@
         <v>1.8</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DB12" t="n">
         <v>1.37</v>
@@ -5726,79 +5726,79 @@
         <v>3.94</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DH12" t="n">
-        <v>81.56</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.83</v>
+        <v>5.73</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DM12" t="n">
-        <v>52.11</v>
+        <v>51.63</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.17</v>
+        <v>15</v>
       </c>
       <c r="DQ12" t="n">
         <v>14.89</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.94</v>
+        <v>8.42</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.72</v>
+        <v>48.26</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.56</v>
+        <v>12.32</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.279999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.28</v>
+        <v>4.21</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.28</v>
+        <v>21.16</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="13">
@@ -6036,13 +6036,13 @@
         <v>3.25</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="CA13" t="n">
         <v>3.3</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="CC13" t="n">
         <v>4.32</v>
@@ -6093,10 +6093,10 @@
         <v>1.42</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CU13" t="n">
         <v>1.36</v>
@@ -6126,7 +6126,7 @@
         <v>2.17</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
@@ -6211,94 +6211,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="H14" t="n">
-        <v>78.33</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>6.22</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="M14" t="n">
-        <v>52.78</v>
+        <v>51.7</v>
       </c>
       <c r="N14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>15.22</v>
+        <v>15</v>
       </c>
       <c r="Q14" t="n">
-        <v>17</v>
+        <v>17.7</v>
       </c>
       <c r="R14" t="n">
-        <v>7.44</v>
+        <v>6.6</v>
       </c>
       <c r="S14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T14" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="U14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>52.11</v>
+        <v>51.7</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.56</v>
+        <v>14.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>10.78</v>
+        <v>10.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.78</v>
+        <v>4.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>24.44</v>
+        <v>24.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AF14" t="n">
         <v>0.22</v>
@@ -6382,70 +6382,70 @@
         <v>2.89</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.89</v>
+        <v>10.79</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.33</v>
+        <v>4.26</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.39</v>
+        <v>6.37</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BT14" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU14" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV14" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CC14" t="n">
         <v>3.53</v>
@@ -6457,117 +6457,121 @@
         <v>1.38</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI14" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO14" t="n">
         <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CR14" t="n">
         <v>1.39</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CT14" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CU14" t="n">
         <v>1.4</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="CX14" t="inlineStr"/>
+        <v>1.81</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>1.45</v>
+      </c>
       <c r="CY14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CZ14" t="inlineStr"/>
+        <v>1.63</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>2.58</v>
+      </c>
       <c r="DA14" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DB14" t="n">
         <v>1.31</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DH14" t="n">
-        <v>77.22</v>
+        <v>76.37</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="DM14" t="n">
-        <v>47.17</v>
+        <v>46.9</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.5</v>
+        <v>13.47</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.28</v>
+        <v>17.63</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.77</v>
+        <v>8.26</v>
       </c>
       <c r="DS14" t="n">
         <v>0.16</v>
@@ -6579,28 +6583,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.11</v>
+        <v>50.95</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.12</v>
+        <v>12.79</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.84</v>
+        <v>8.68</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.28</v>
+        <v>4.11</v>
       </c>
       <c r="EA14" t="n">
-        <v>22.44</v>
+        <v>22.47</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="15">
@@ -6610,10 +6614,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>9</v>
@@ -6622,82 +6626,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="G15" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="H15" t="n">
-        <v>71.11</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="L15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M15" t="n">
-        <v>37.56</v>
+        <v>37.3</v>
       </c>
       <c r="N15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="R15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="S15" t="n">
         <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P15" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="R15" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.11</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>47.11</v>
+        <v>46.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.56</v>
+        <v>10.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.44</v>
+        <v>6.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="AC15" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6781,67 +6785,67 @@
         <v>2.22</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.72</v>
+        <v>10.47</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BP15" t="n">
         <v>4.89</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.06</v>
+        <v>4.84</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BT15" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU15" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV15" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX15" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CB15" t="n">
         <v>3.4</v>
@@ -6853,19 +6857,19 @@
         <v>4.17</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.73</v>
@@ -6883,19 +6887,19 @@
         <v>1.99</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CT15" t="n">
         <v>2.92</v>
@@ -6934,76 +6938,76 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="DH15" t="n">
-        <v>69.72</v>
+        <v>70.05</v>
       </c>
       <c r="DI15" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.44</v>
+        <v>4.32</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="DM15" t="n">
-        <v>42.62</v>
+        <v>42.21</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.16</v>
+        <v>14.31</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.22</v>
+        <v>15.42</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.56</v>
+        <v>9</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.72</v>
+        <v>47.37</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.84</v>
+        <v>10.63</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.83</v>
+        <v>6.68</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.78</v>
+        <v>20.74</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="16">
@@ -7416,10 +7420,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -7428,13 +7432,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="H17" t="n">
-        <v>81.88</v>
+        <v>80.78</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -7443,67 +7447,67 @@
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="L17" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="M17" t="n">
-        <v>54.12</v>
+        <v>52.78</v>
       </c>
       <c r="N17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P17" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.5</v>
       </c>
-      <c r="O17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P17" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>12</v>
-      </c>
-      <c r="R17" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>48.38</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>21.62</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AE17" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AF17" t="n">
         <v>0.1</v>
@@ -7587,70 +7591,70 @@
         <v>3</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.890000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.22</v>
+        <v>4.11</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BT17" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BU17" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV17" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX17" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CC17" t="n">
         <v>2.89</v>
@@ -7662,13 +7666,13 @@
         <v>1.41</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI17" t="n">
         <v>1.9</v>
@@ -7680,10 +7684,10 @@
         <v>1.4</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CN17" t="n">
         <v>2.04</v>
@@ -7692,10 +7696,10 @@
         <v>1.33</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="CR17" t="n">
         <v>1.43</v>
@@ -7719,13 +7723,13 @@
         <v>1.52</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.43</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="DB17" t="n">
         <v>1.36</v>
@@ -7737,79 +7741,79 @@
         <v>3.89</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="DH17" t="n">
-        <v>84.5</v>
+        <v>83.84</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="DK17" t="n">
-        <v>5</v>
+        <v>4.79</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DM17" t="n">
-        <v>55.05</v>
+        <v>54.37</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.11</v>
+        <v>12.32</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.33</v>
+        <v>11.58</v>
       </c>
       <c r="DR17" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>46.95</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="DY17" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="DS17" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DT17" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV17" t="n">
-        <v>46.78</v>
-      </c>
-      <c r="DW17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DX17" t="n">
-        <v>12.67</v>
-      </c>
-      <c r="DY17" t="n">
-        <v>8.5</v>
-      </c>
       <c r="DZ17" t="n">
-        <v>4.17</v>
+        <v>4.26</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.55</v>
+        <v>21.26</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="18">
@@ -7819,94 +7823,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="F18" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="H18" t="n">
-        <v>78.33</v>
+        <v>77.5</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>49.78</v>
+        <v>49</v>
       </c>
       <c r="N18" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="P18" t="n">
-        <v>14.44</v>
+        <v>14.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>16.56</v>
+        <v>16.9</v>
       </c>
       <c r="R18" t="n">
-        <v>10.22</v>
+        <v>9.1</v>
       </c>
       <c r="S18" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="U18" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>47.67</v>
+        <v>48.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.22</v>
+        <v>6.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.78</v>
+        <v>5</v>
       </c>
       <c r="AC18" t="n">
-        <v>20.56</v>
+        <v>20.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE18" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7990,70 +7994,70 @@
         <v>2.22</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.17</v>
+        <v>10.05</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BP18" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>84.20999999999999</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BZ18" t="n">
         <v>3.44</v>
       </c>
-      <c r="BQ18" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>83.33</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>55.56</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>27.78</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>27.78</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>38.89</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>3.53</v>
-      </c>
       <c r="CA18" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CC18" t="n">
         <v>4.68</v>
@@ -8065,7 +8069,7 @@
         <v>1.38</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CG18" t="n">
         <v>2.87</v>
@@ -8074,31 +8078,31 @@
         <v>1.39</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CL18" t="n">
         <v>1.72</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CO18" t="n">
         <v>1.28</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="CR18" t="n">
         <v>1.39</v>
@@ -8107,7 +8111,7 @@
         <v>2.98</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CU18" t="n">
         <v>1.4</v>
@@ -8128,10 +8132,10 @@
         <v>2.58</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC18" t="n">
         <v>2.02</v>
@@ -8140,46 +8144,46 @@
         <v>3.48</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DF18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DG18" t="n">
         <v>1.89</v>
       </c>
-      <c r="DG18" t="n">
-        <v>2.05</v>
-      </c>
       <c r="DH18" t="n">
-        <v>80.78</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="DK18" t="n">
         <v>4</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="DM18" t="n">
-        <v>50.22</v>
+        <v>49.79</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.88</v>
+        <v>12.89</v>
       </c>
       <c r="DQ18" t="n">
-        <v>16.11</v>
+        <v>16.32</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.83</v>
+        <v>9.26</v>
       </c>
       <c r="DS18" t="n">
         <v>0.16</v>
@@ -8191,28 +8195,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.84</v>
+        <v>48.11</v>
       </c>
       <c r="DW18" t="n">
         <v>0.11</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.5</v>
+        <v>11.63</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.44</v>
+        <v>7.42</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.06</v>
+        <v>4.21</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.5</v>
+        <v>20.68</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="19">
@@ -8270,7 +8274,7 @@
         <v>12.88</v>
       </c>
       <c r="R19" t="n">
-        <v>6.38</v>
+        <v>7</v>
       </c>
       <c r="S19" t="n">
         <v>1.62</v>
@@ -8288,25 +8292,25 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>55.62</v>
+        <v>54.88</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.75</v>
+        <v>13.62</v>
       </c>
       <c r="AA19" t="n">
-        <v>8</v>
+        <v>8.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.75</v>
+        <v>4.88</v>
       </c>
       <c r="AC19" t="n">
         <v>19.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AE19" t="n">
         <v>2.38</v>
@@ -8582,7 +8586,7 @@
         <v>14.72</v>
       </c>
       <c r="DR19" t="n">
-        <v>7</v>
+        <v>7.28</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8594,25 +8598,25 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.39</v>
+        <v>54.06</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.39</v>
+        <v>12.78</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.89</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="EA19" t="n">
         <v>21.22</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="EC19" t="n">
         <v>2.95</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1505,10 +1505,10 @@
         <v>14.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
         <v>1.4</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.1</v>
@@ -1535,16 +1535,16 @@
         <v>13.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BD2" t="n">
         <v>22.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="BF2" t="n">
         <v>2.7</v>
@@ -1736,10 +1736,10 @@
         <v>13.58</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.63</v>
+        <v>13.53</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.47</v>
+        <v>5.95</v>
       </c>
       <c r="DS2" t="n">
         <v>0.11</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50</v>
+        <v>50.16</v>
       </c>
       <c r="DW2" t="n">
         <v>0.21</v>
@@ -1760,16 +1760,16 @@
         <v>14.37</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.16</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.21</v>
+        <v>5.16</v>
       </c>
       <c r="EA2" t="n">
         <v>22.95</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="EC2" t="n">
         <v>2.58</v>
@@ -2633,10 +2633,10 @@
         <v>14.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -2654,25 +2654,25 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58.6</v>
+        <v>58</v>
       </c>
       <c r="Y5" t="n">
         <v>0.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AC5" t="n">
         <v>23.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AE5" t="n">
         <v>2.9</v>
@@ -2945,10 +2945,10 @@
         <v>15.52</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.42</v>
+        <v>15.21</v>
       </c>
       <c r="DR5" t="n">
-        <v>4.95</v>
+        <v>5.58</v>
       </c>
       <c r="DS5" t="n">
         <v>0.1</v>
@@ -2960,25 +2960,25 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.37</v>
+        <v>56.05</v>
       </c>
       <c r="DW5" t="n">
         <v>0.32</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.31</v>
+        <v>14.58</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.210000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.11</v>
+        <v>5.16</v>
       </c>
       <c r="EA5" t="n">
         <v>23.31</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="EC5" t="n">
         <v>2.9</v>
@@ -4325,7 +4325,7 @@
         <v>16.67</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.44</v>
+        <v>7.56</v>
       </c>
       <c r="AT9" t="n">
         <v>1.56</v>
@@ -4343,7 +4343,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>52</v>
+        <v>52.67</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.11</v>
@@ -4556,7 +4556,7 @@
         <v>15.63</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.79</v>
+        <v>7.32</v>
       </c>
       <c r="DS9" t="n">
         <v>0.16</v>
@@ -4568,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.63</v>
+        <v>51.95</v>
       </c>
       <c r="DW9" t="n">
         <v>0.21</v>
@@ -4644,10 +4644,10 @@
         <v>12.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="R10" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -4665,16 +4665,16 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>56.2</v>
+        <v>55.8</v>
       </c>
       <c r="Y10" t="n">
         <v>0.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="AB10" t="n">
         <v>3.5</v>
@@ -4683,7 +4683,7 @@
         <v>17.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AE10" t="n">
         <v>3.1</v>
@@ -4956,10 +4956,10 @@
         <v>13.79</v>
       </c>
       <c r="DQ10" t="n">
-        <v>15.05</v>
+        <v>15</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.16</v>
+        <v>7.63</v>
       </c>
       <c r="DS10" t="n">
         <v>0.16</v>
@@ -4971,16 +4971,16 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>52.11</v>
+        <v>51.9</v>
       </c>
       <c r="DW10" t="n">
         <v>0.21</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.68</v>
+        <v>12.84</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.84</v>
+        <v>9</v>
       </c>
       <c r="DZ10" t="n">
         <v>3.84</v>
@@ -4989,7 +4989,7 @@
         <v>18.26</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="EC10" t="n">
         <v>3</v>
@@ -5534,7 +5534,7 @@
         <v>15.11</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.44</v>
+        <v>10.11</v>
       </c>
       <c r="AT12" t="n">
         <v>1.67</v>
@@ -5552,16 +5552,16 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>45.22</v>
+        <v>45.67</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.33</v>
       </c>
       <c r="BA12" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.44</v>
+        <v>6.56</v>
       </c>
       <c r="BC12" t="n">
         <v>4.56</v>
@@ -5570,7 +5570,7 @@
         <v>20.33</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BF12" t="n">
         <v>2.67</v>
@@ -5765,7 +5765,7 @@
         <v>14.89</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.42</v>
+        <v>8.74</v>
       </c>
       <c r="DS12" t="n">
         <v>0.1</v>
@@ -5777,16 +5777,16 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.26</v>
+        <v>48.48</v>
       </c>
       <c r="DW12" t="n">
         <v>0.21</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.32</v>
+        <v>12.37</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.1</v>
+        <v>8.16</v>
       </c>
       <c r="DZ12" t="n">
         <v>4.21</v>
@@ -5853,10 +5853,10 @@
         <v>16.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.22</v>
+        <v>15.11</v>
       </c>
       <c r="R13" t="n">
-        <v>6.56</v>
+        <v>7.44</v>
       </c>
       <c r="S13" t="n">
         <v>1.44</v>
@@ -5874,19 +5874,19 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>46.44</v>
+        <v>46.11</v>
       </c>
       <c r="Y13" t="n">
         <v>0.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.33</v>
+        <v>14.44</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.56</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.78</v>
+        <v>4.67</v>
       </c>
       <c r="AC13" t="n">
         <v>22.44</v>
@@ -6165,10 +6165,10 @@
         <v>14.79</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.37</v>
+        <v>16.32</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.9</v>
+        <v>10.31</v>
       </c>
       <c r="DS13" t="n">
         <v>0.16</v>
@@ -6180,19 +6180,19 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45.89</v>
+        <v>45.74</v>
       </c>
       <c r="DW13" t="n">
         <v>0.26</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.68</v>
+        <v>11.73</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.109999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.58</v>
+        <v>3.53</v>
       </c>
       <c r="EA13" t="n">
         <v>21.79</v>
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0.11</v>
@@ -7107,139 +7107,139 @@
         <v>3.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>86.67</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>48.67</v>
+        <v>50.1</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>16</v>
+        <v>15.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.44</v>
+        <v>12</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.56</v>
+        <v>6.7</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>49.44</v>
+        <v>49.8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.44</v>
+        <v>10.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.220000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.56</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.11</v>
+        <v>4.16</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU16" t="n">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
       <c r="BV16" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BY16" t="n">
         <v>2.37</v>
@@ -7251,22 +7251,22 @@
         <v>3.17</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.03</v>
+        <v>3.12</v>
       </c>
       <c r="CE16" t="n">
         <v>1.41</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CH16" t="n">
         <v>1.35</v>
@@ -7284,28 +7284,28 @@
         <v>1.83</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO16" t="n">
         <v>1.32</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="CR16" t="n">
         <v>1.42</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CU16" t="n">
         <v>1.36</v>
@@ -7314,19 +7314,19 @@
         <v>1.99</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX16" t="n">
         <v>1.53</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.43</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DB16" t="n">
         <v>1.35</v>
@@ -7335,49 +7335,49 @@
         <v>2.13</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DF16" t="n">
         <v>2</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="DH16" t="n">
-        <v>82.94</v>
+        <v>87.05</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.56</v>
+        <v>4.48</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM16" t="n">
-        <v>49.12</v>
+        <v>49.84</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="DP16" t="n">
-        <v>15.16</v>
+        <v>14.89</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.56</v>
+        <v>12.79</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.44</v>
+        <v>7.95</v>
       </c>
       <c r="DS16" t="n">
         <v>0.16</v>
@@ -7389,28 +7389,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.44</v>
+        <v>51.52</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.38</v>
+        <v>11.95</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.83</v>
+        <v>7.47</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.84</v>
+        <v>20.9</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="EC16" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="17">
@@ -8226,61 +8226,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F19" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="G19" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="H19" t="n">
-        <v>81.5</v>
+        <v>85.56</v>
       </c>
       <c r="I19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J19" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="L19" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="M19" t="n">
-        <v>58.5</v>
+        <v>57</v>
       </c>
       <c r="N19" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O19" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="P19" t="n">
-        <v>15.12</v>
+        <v>15</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.88</v>
+        <v>12.56</v>
       </c>
       <c r="R19" t="n">
-        <v>7</v>
+        <v>6.11</v>
       </c>
       <c r="S19" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="T19" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8292,28 +8292,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>54.88</v>
+        <v>54</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.62</v>
+        <v>13.11</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.75</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="AC19" t="n">
-        <v>19.62</v>
+        <v>19.89</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,70 +8397,70 @@
         <v>3.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.72</v>
+        <v>10.58</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.44</v>
+        <v>5.42</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.28</v>
+        <v>5.16</v>
       </c>
       <c r="BR19" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS19" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT19" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU19" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BV19" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CC19" t="n">
         <v>2.51</v>
@@ -8475,7 +8475,7 @@
         <v>2.98</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CH19" t="n">
         <v>1.36</v>
@@ -8505,13 +8505,13 @@
         <v>2.03</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CT19" t="n">
         <v>2.85</v>
@@ -8523,7 +8523,7 @@
         <v>1.97</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CX19" t="n">
         <v>1.54</v>
@@ -8535,7 +8535,7 @@
         <v>2.42</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DB19" t="n">
         <v>1.35</v>
@@ -8544,49 +8544,49 @@
         <v>2.14</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="DE19" t="n">
         <v>0.05</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="DH19" t="n">
-        <v>83.22</v>
+        <v>85.05</v>
       </c>
       <c r="DI19" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.28</v>
+        <v>5.26</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="DM19" t="n">
-        <v>55.11</v>
+        <v>54.58</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="DP19" t="n">
-        <v>15.05</v>
+        <v>15</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.72</v>
+        <v>14.48</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.28</v>
+        <v>6.84</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8598,28 +8598,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.06</v>
+        <v>53.68</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.78</v>
+        <v>12.58</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.220000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.22</v>
+        <v>21.26</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="H3" t="n">
-        <v>90.09999999999999</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="K3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="M3" t="n">
-        <v>70.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="P3" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.7</v>
+        <v>14.64</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>5.73</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>57.6</v>
+        <v>58.18</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>19.1</v>
+        <v>19.09</v>
       </c>
       <c r="AA3" t="n">
         <v>13</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.1</v>
+        <v>6.09</v>
       </c>
       <c r="AC3" t="n">
-        <v>23</v>
+        <v>22.64</v>
       </c>
       <c r="AD3" t="n">
         <v>2.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AF3" t="n">
         <v>0.11</v>
@@ -1953,70 +1953,70 @@
         <v>2.89</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.37</v>
+        <v>11.3</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.68</v>
+        <v>5.7</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.58</v>
+        <v>5.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS3" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT3" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BU3" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV3" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY3" t="n">
         <v>2.07</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CC3" t="n">
         <v>3.13</v>
@@ -2028,10 +2028,10 @@
         <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CH3" t="n">
         <v>1.39</v>
@@ -2046,7 +2046,7 @@
         <v>1.38</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CM3" t="n">
         <v>2.74</v>
@@ -2058,25 +2058,25 @@
         <v>1.28</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CU3" t="n">
         <v>1.41</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CW3" t="n">
         <v>1.78</v>
@@ -2091,91 +2091,91 @@
         <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DB3" t="n">
         <v>1.3</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="DE3" t="n">
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="DH3" t="n">
-        <v>83.26000000000001</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.42</v>
+        <v>6.55</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DM3" t="n">
-        <v>57.53</v>
+        <v>58.1</v>
       </c>
       <c r="DN3" t="n">
         <v>1.05</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.53</v>
+        <v>14.85</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.11</v>
+        <v>15.05</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.69</v>
+        <v>7.45</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50.63</v>
+        <v>51.3</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.42</v>
+        <v>14.65</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.58</v>
+        <v>9.75</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.84</v>
+        <v>4.9</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.53</v>
+        <v>22.35</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="H6" t="n">
-        <v>91.22</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="K6" t="n">
-        <v>5.22</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>57.11</v>
+        <v>57</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>14.56</v>
+        <v>14.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.89</v>
+        <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>8.67</v>
+        <v>7.7</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T6" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="U6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.22</v>
+        <v>11.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.33</v>
+        <v>7.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>2.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.32</v>
+        <v>10</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BP6" t="n">
         <v>4.05</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.74</v>
+        <v>5.45</v>
       </c>
       <c r="BR6" t="n">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS6" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BT6" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BU6" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.09</v>
+        <v>3.03</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CC6" t="n">
         <v>4.44</v>
@@ -3237,7 +3237,7 @@
         <v>1.32</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="CG6" t="n">
         <v>2.63</v>
@@ -3249,46 +3249,46 @@
         <v>1.81</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="CR6" t="n">
         <v>1.41</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="CU6" t="n">
         <v>1.38</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CX6" t="inlineStr"/>
       <c r="CY6" t="n">
@@ -3299,88 +3299,88 @@
         <v>2.16</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="DH6" t="n">
-        <v>82.79000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.63</v>
+        <v>4.45</v>
       </c>
       <c r="DL6" t="n">
         <v>0.05</v>
       </c>
       <c r="DM6" t="n">
-        <v>49.16</v>
+        <v>49.5</v>
       </c>
       <c r="DN6" t="n">
         <v>1.05</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.74</v>
+        <v>15.85</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.68</v>
+        <v>14.7</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.74</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.89</v>
+        <v>45.25</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.1</v>
+        <v>10.95</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.37</v>
+        <v>7.2</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="EA6" t="n">
-        <v>23.16</v>
+        <v>23</v>
       </c>
       <c r="EB6" t="n">
         <v>1.32</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="7">
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.1</v>
@@ -5095,49 +5095,49 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AI11" t="n">
-        <v>82.44</v>
+        <v>87.2</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>4.56</v>
+        <v>4.3</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>43.44</v>
+        <v>44.1</v>
       </c>
       <c r="AO11" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15.67</v>
+        <v>15.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.33</v>
+        <v>7.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5149,82 +5149,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>45.78</v>
+        <v>46</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.56</v>
+        <v>10.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.11</v>
+        <v>6.7</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>21.89</v>
+        <v>21.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.11</v>
+        <v>3.9</v>
       </c>
       <c r="BG11" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.470000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.37</v>
+        <v>5.1</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.73999999999999</v>
+        <v>90</v>
       </c>
       <c r="BS11" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV11" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW11" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX11" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY11" t="n">
         <v>2.53</v>
@@ -5236,19 +5236,19 @@
         <v>3.11</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CG11" t="n">
         <v>2.65</v>
@@ -5257,112 +5257,112 @@
         <v>1.34</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK11" t="n">
         <v>1.32</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO11" t="n">
         <v>1.34</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.63</v>
+        <v>3.68</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CU11" t="n">
         <v>1.36</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CX11" t="n">
         <v>1.51</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.49</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="DE11" t="n">
         <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="DH11" t="n">
-        <v>89.58</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.58</v>
+        <v>4.5</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DM11" t="n">
-        <v>49</v>
+        <v>49.05</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.74</v>
+        <v>14.65</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.74</v>
+        <v>16.95</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.74</v>
+        <v>7.3</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.47</v>
+        <v>48.45</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.69</v>
+        <v>11.4</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.63</v>
+        <v>7.4</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="EA11" t="n">
-        <v>22.84</v>
+        <v>22.7</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="EC11" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="12">
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0.3</v>
@@ -5498,136 +5498,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>74.56</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.44</v>
+        <v>4.1</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>43.78</v>
+        <v>41.4</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.22</v>
+        <v>13.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>15.11</v>
+        <v>15.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.11</v>
+        <v>10.3</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>45.67</v>
+        <v>44.7</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.11</v>
+        <v>10.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.56</v>
+        <v>6</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.56</v>
+        <v>4.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>20.33</v>
+        <v>20.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="BG12" t="n">
         <v>3.05</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.58</v>
+        <v>9.6</v>
       </c>
       <c r="BI12" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.89</v>
+        <v>4.85</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS12" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT12" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU12" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BV12" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX12" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY12" t="n">
         <v>2.42</v>
@@ -5639,13 +5639,13 @@
         <v>3.13</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CC12" t="n">
         <v>3.24</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CE12" t="n">
         <v>1.42</v>
@@ -5660,7 +5660,7 @@
         <v>1.34</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.85</v>
@@ -5672,10 +5672,10 @@
         <v>1.76</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO12" t="n">
         <v>1.33</v>
@@ -5690,7 +5690,7 @@
         <v>1.44</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CT12" t="n">
         <v>2.79</v>
@@ -5720,52 +5720,52 @@
         <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="DH12" t="n">
-        <v>81.31999999999999</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.73</v>
+        <v>5.5</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM12" t="n">
-        <v>51.63</v>
+        <v>50.05</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="DP12" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.89</v>
+        <v>15.25</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.74</v>
+        <v>8.9</v>
       </c>
       <c r="DS12" t="n">
         <v>0.1</v>
@@ -5777,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.48</v>
+        <v>47.85</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.37</v>
+        <v>11.95</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.16</v>
+        <v>7.8</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.21</v>
+        <v>4.15</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.16</v>
+        <v>21.15</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -7143,10 +7143,10 @@
         <v>15.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="AT16" t="n">
         <v>0.9</v>
@@ -7164,16 +7164,16 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>49.8</v>
+        <v>50.6</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.3</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC16" t="n">
         <v>3.2</v>
@@ -7182,7 +7182,7 @@
         <v>20.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="BF16" t="n">
         <v>2.8</v>
@@ -7374,10 +7374,10 @@
         <v>14.89</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.79</v>
+        <v>12.63</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.95</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DS16" t="n">
         <v>0.16</v>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.52</v>
+        <v>51.95</v>
       </c>
       <c r="DW16" t="n">
         <v>0.21</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.95</v>
+        <v>12.31</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.47</v>
+        <v>7.84</v>
       </c>
       <c r="DZ16" t="n">
         <v>4.47</v>
@@ -7407,7 +7407,7 @@
         <v>20.9</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="EC16" t="n">
         <v>2.95</v>
@@ -8274,7 +8274,7 @@
         <v>12.56</v>
       </c>
       <c r="R19" t="n">
-        <v>6.11</v>
+        <v>6.89</v>
       </c>
       <c r="S19" t="n">
         <v>1.56</v>
@@ -8292,25 +8292,25 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>54</v>
+        <v>53.11</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.11</v>
+        <v>13.44</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.109999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="AB19" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="AC19" t="n">
         <v>19.89</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="n">
         <v>2.22</v>
@@ -8586,7 +8586,7 @@
         <v>14.48</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.84</v>
+        <v>7.21</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8598,25 +8598,25 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>53.68</v>
+        <v>53.26</v>
       </c>
       <c r="DW19" t="n">
         <v>0.05</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.58</v>
+        <v>12.73</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.95</v>
+        <v>8.16</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.63</v>
+        <v>4.58</v>
       </c>
       <c r="EA19" t="n">
         <v>21.26</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="EC19" t="n">
         <v>2.84</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
@@ -1391,49 +1391,49 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G2" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="H2" t="n">
-        <v>82.78</v>
+        <v>82.7</v>
       </c>
       <c r="I2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>5.67</v>
+        <v>5.7</v>
       </c>
       <c r="L2" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="M2" t="n">
-        <v>55.33</v>
+        <v>54.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="P2" t="n">
-        <v>12.78</v>
+        <v>12.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.78</v>
+        <v>13.3</v>
       </c>
       <c r="R2" t="n">
-        <v>5.22</v>
+        <v>4.6</v>
       </c>
       <c r="S2" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.67</v>
+        <v>15.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.11</v>
+        <v>10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.56</v>
+        <v>5.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.44</v>
+        <v>23.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AF2" t="n">
         <v>0.2</v>
@@ -1550,70 +1550,70 @@
         <v>2.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.470000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="BO2" t="n">
         <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.16</v>
+        <v>4.25</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.26</v>
+        <v>5.25</v>
       </c>
       <c r="BR2" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS2" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT2" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU2" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV2" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX2" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CC2" t="n">
         <v>2.88</v>
@@ -1628,7 +1628,7 @@
         <v>3.09</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CH2" t="n">
         <v>1.33</v>
@@ -1643,13 +1643,13 @@
         <v>1.38</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CO2" t="n">
         <v>1.34</v>
@@ -1676,103 +1676,103 @@
         <v>1.88</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.51</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DB2" t="n">
         <v>1.39</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF2" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DG2" t="n">
         <v>2.9</v>
       </c>
       <c r="DH2" t="n">
-        <v>80.11</v>
+        <v>80.2</v>
       </c>
       <c r="DI2" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.26</v>
+        <v>5.3</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.52</v>
+        <v>51.25</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.58</v>
+        <v>13.5</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.53</v>
+        <v>13.75</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.95</v>
+        <v>5.6</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.16</v>
+        <v>50.35</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.37</v>
+        <v>14.25</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.210000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.16</v>
+        <v>5.05</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="G4" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="H4" t="n">
-        <v>82.33</v>
+        <v>82.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>6.78</v>
+        <v>6.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="M4" t="n">
-        <v>63.89</v>
+        <v>62.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="O4" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>15.56</v>
+        <v>15.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.89</v>
+        <v>14.6</v>
       </c>
       <c r="R4" t="n">
-        <v>8.44</v>
+        <v>7.5</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50.89</v>
+        <v>51.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.78</v>
+        <v>17.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.44</v>
+        <v>12.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>27</v>
+        <v>27.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="AF4" t="n">
         <v>0.3</v>
@@ -2356,70 +2356,70 @@
         <v>3.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.26</v>
+        <v>10.25</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BP4" t="n">
         <v>4.95</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.63</v>
+        <v>4.65</v>
       </c>
       <c r="BR4" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS4" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT4" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU4" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX4" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CC4" t="n">
         <v>3.22</v>
@@ -2431,10 +2431,10 @@
         <v>1.38</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CH4" t="n">
         <v>1.26</v>
@@ -2443,28 +2443,28 @@
         <v>1.72</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CK4" t="n">
         <v>1.35</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CN4" t="n">
         <v>1.88</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.61</v>
+        <v>3.65</v>
       </c>
       <c r="CR4" t="n">
         <v>1.47</v>
@@ -2473,28 +2473,28 @@
         <v>3.28</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW4" t="n">
         <v>1.97</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="DB4" t="n">
         <v>1.4</v>
@@ -2503,49 +2503,49 @@
         <v>2.29</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="DH4" t="n">
-        <v>76.79000000000001</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.26</v>
+        <v>6.2</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="DM4" t="n">
-        <v>54.9</v>
+        <v>54.8</v>
       </c>
       <c r="DN4" t="n">
         <v>0.95</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="DP4" t="n">
-        <v>16.95</v>
+        <v>16.75</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.53</v>
+        <v>12.95</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.84</v>
+        <v>8.35</v>
       </c>
       <c r="DS4" t="n">
         <v>0.1</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.63</v>
+        <v>47.05</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX4" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.37</v>
+        <v>11.2</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="EA4" t="n">
-        <v>25.47</v>
+        <v>25.7</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0.2</v>
@@ -2678,139 +2678,139 @@
         <v>2.9</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
-        <v>77.67</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.11</v>
+        <v>3.6</v>
       </c>
       <c r="AL5" t="n">
         <v>5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.78</v>
+        <v>47.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16.33</v>
+        <v>16.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.44</v>
+        <v>15.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.56</v>
+        <v>4.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>53.89</v>
+        <v>53</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.44</v>
+        <v>13.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.67</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.78</v>
+        <v>4.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>23.22</v>
+        <v>23.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.68</v>
+        <v>8.75</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT5" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BU5" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV5" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BY5" t="n">
         <v>1.99</v>
@@ -2819,25 +2819,25 @@
         <v>1.96</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CH5" t="n">
         <v>1.28</v>
@@ -2846,109 +2846,109 @@
         <v>1.78</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL5" t="n">
         <v>1.74</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="CR5" t="n">
         <v>1.42</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CU5" t="n">
         <v>1.37</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CX5" t="n">
         <v>1.54</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB5" t="n">
         <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.73</v>
+        <v>3.77</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="DH5" t="n">
-        <v>86.05</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="DI5" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.53</v>
+        <v>3.75</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM5" t="n">
-        <v>54.63</v>
+        <v>54.6</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.52</v>
+        <v>15.8</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.21</v>
+        <v>15.3</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.58</v>
+        <v>5.25</v>
       </c>
       <c r="DS5" t="n">
         <v>0.1</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.05</v>
+        <v>55.5</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.58</v>
+        <v>14.4</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.16</v>
+        <v>5.2</v>
       </c>
       <c r="EA5" t="n">
-        <v>23.31</v>
+        <v>23.45</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3219,7 +3219,7 @@
         <v>2.7</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CA6" t="n">
         <v>3.37</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
@@ -3402,49 +3402,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="H7" t="n">
-        <v>86.33</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="L7" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>60.44</v>
+        <v>59.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="P7" t="n">
-        <v>16.11</v>
+        <v>15.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.67</v>
+        <v>16.6</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="S7" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3456,28 +3456,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>55.78</v>
+        <v>55.7</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.56</v>
+        <v>13.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.220000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>19.67</v>
+        <v>20.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3561,49 +3561,49 @@
         <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.42</v>
+        <v>9.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.47</v>
+        <v>4.55</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS7" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT7" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BU7" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3612,19 +3612,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="CC7" t="n">
         <v>2.41</v>
@@ -3636,10 +3636,10 @@
         <v>1.4</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CH7" t="n">
         <v>1.38</v>
@@ -3654,7 +3654,7 @@
         <v>1.38</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM7" t="n">
         <v>2.72</v>
@@ -3669,7 +3669,7 @@
         <v>1.96</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
@@ -3693,7 +3693,7 @@
         <v>1.49</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.52</v>
@@ -3705,85 +3705,85 @@
         <v>1.33</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DH7" t="n">
-        <v>84.09999999999999</v>
+        <v>83.75</v>
       </c>
       <c r="DI7" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DM7" t="n">
-        <v>55.52</v>
+        <v>55.45</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.53</v>
+        <v>14.35</v>
       </c>
       <c r="DQ7" t="n">
-        <v>16.84</v>
+        <v>16.8</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.63</v>
+        <v>7.2</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.79</v>
+        <v>54.8</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.32</v>
+        <v>12.95</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.529999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.63</v>
+        <v>20</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="8">
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
@@ -3805,49 +3805,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="G8" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="H8" t="n">
-        <v>96.44</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>6.44</v>
+        <v>6.1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="M8" t="n">
-        <v>68.11</v>
+        <v>68.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="O8" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>15.22</v>
+        <v>15.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.22</v>
+        <v>13.4</v>
       </c>
       <c r="R8" t="n">
-        <v>6.44</v>
+        <v>5.7</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3859,28 +3859,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>53.44</v>
+        <v>53.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.78</v>
+        <v>15.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.22</v>
+        <v>9.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.56</v>
+        <v>5.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>25.67</v>
+        <v>25.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="AF8" t="n">
         <v>0.1</v>
@@ -3964,70 +3964,70 @@
         <v>3.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.890000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.42</v>
+        <v>4.25</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.47</v>
+        <v>5.35</v>
       </c>
       <c r="BR8" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BS8" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT8" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BU8" t="n">
-        <v>10.53</v>
+        <v>15</v>
       </c>
       <c r="BV8" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX8" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CA8" t="n">
         <v>3.24</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="CC8" t="n">
         <v>2.44</v>
@@ -4039,7 +4039,7 @@
         <v>1.42</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CG8" t="n">
         <v>2.68</v>
@@ -4051,19 +4051,19 @@
         <v>1.87</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK8" t="n">
         <v>1.31</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CO8" t="n">
         <v>1.32</v>
@@ -4072,7 +4072,7 @@
         <v>2.04</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="CR8" t="n">
         <v>1.43</v>
@@ -4087,10 +4087,10 @@
         <v>1.36</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CX8" t="n">
         <v>1.51</v>
@@ -4117,43 +4117,43 @@
         <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="DH8" t="n">
-        <v>89.47</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="DK8" t="n">
-        <v>6</v>
+        <v>5.85</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DM8" t="n">
-        <v>59.53</v>
+        <v>60.05</v>
       </c>
       <c r="DN8" t="n">
         <v>0.9</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.31</v>
+        <v>14.55</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.37</v>
+        <v>14.4</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.68</v>
+        <v>6.3</v>
       </c>
       <c r="DS8" t="n">
         <v>0.05</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.73</v>
+        <v>51.85</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.32</v>
+        <v>14.25</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.42</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="EA8" t="n">
-        <v>24.48</v>
+        <v>24.45</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
@@ -4208,82 +4208,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="G9" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>93.3</v>
+        <v>94.64</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.6</v>
+        <v>3.09</v>
       </c>
       <c r="K9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="M9" t="n">
-        <v>63.2</v>
+        <v>62.36</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.7</v>
+        <v>14.91</v>
       </c>
       <c r="R9" t="n">
-        <v>7.1</v>
+        <v>6.36</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>51.3</v>
+        <v>50.91</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.5</v>
+        <v>14.09</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.2</v>
+        <v>9.82</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="AC9" t="n">
-        <v>24.6</v>
+        <v>23.64</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4367,61 +4367,61 @@
         <v>2.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="BH9" t="n">
         <v>10.05</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="BO9" t="n">
         <v>0.95</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT9" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BU9" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV9" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="BZ9" t="n">
         <v>2.03</v>
@@ -4460,7 +4460,7 @@
         <v>1.38</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM9" t="n">
         <v>2.75</v>
@@ -4469,13 +4469,13 @@
         <v>2.08</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="CR9" t="n">
         <v>1.41</v>
@@ -4490,7 +4490,7 @@
         <v>1.37</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW9" t="n">
         <v>1.86</v>
@@ -4508,88 +4508,88 @@
         <v>2.08</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC9" t="n">
         <v>2.08</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="DG9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DJ9" t="n">
         <v>2.95</v>
       </c>
-      <c r="DH9" t="n">
-        <v>90.26000000000001</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>2.69</v>
-      </c>
       <c r="DK9" t="n">
-        <v>5.42</v>
+        <v>5.35</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM9" t="n">
-        <v>59.16</v>
+        <v>58.9</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.69</v>
+        <v>14.85</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.63</v>
+        <v>15.7</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.32</v>
+        <v>6.9</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.95</v>
+        <v>51.7</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.47</v>
+        <v>14.25</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.84</v>
+        <v>9.65</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.1</v>
+        <v>22.65</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0.1</v>
@@ -4689,139 +4689,139 @@
         <v>3.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>81.11</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>50.67</v>
+        <v>50.9</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.78</v>
+        <v>14.9</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.89</v>
+        <v>15.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.44</v>
+        <v>8.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>47.56</v>
+        <v>48.1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.89</v>
+        <v>11.3</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.67</v>
+        <v>6.9</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.78</v>
+        <v>19.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.789999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BO10" t="n">
         <v>1</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="BQ10" t="n">
         <v>4.95</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS10" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BT10" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BU10" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV10" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY10" t="n">
         <v>2.04</v>
@@ -4830,25 +4830,25 @@
         <v>2.16</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CB10" t="n">
         <v>3.3</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="CE10" t="n">
         <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CH10" t="n">
         <v>1.35</v>
@@ -4863,7 +4863,7 @@
         <v>1.42</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM10" t="n">
         <v>2.62</v>
@@ -4875,10 +4875,10 @@
         <v>1.35</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="CR10" t="n">
         <v>1.44</v>
@@ -4917,82 +4917,82 @@
         <v>2.17</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="DH10" t="n">
-        <v>80.31999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="DI10" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.89</v>
+        <v>4.95</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM10" t="n">
-        <v>51.58</v>
+        <v>51.65</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.79</v>
+        <v>13.9</v>
       </c>
       <c r="DQ10" t="n">
-        <v>15</v>
+        <v>15.45</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.63</v>
+        <v>7.2</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.9</v>
+        <v>51.95</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.84</v>
+        <v>12.95</v>
       </c>
       <c r="DY10" t="n">
         <v>9</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.26</v>
+        <v>18.75</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="EC10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="11">
@@ -5242,7 +5242,7 @@
         <v>3.32</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="CE11" t="n">
         <v>1.42</v>
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>0.2</v>
@@ -6301,139 +6301,139 @@
         <v>2.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>76.11</v>
+        <v>74</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.56</v>
+        <v>41.6</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.78</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>17.56</v>
+        <v>17.1</v>
       </c>
       <c r="AS14" t="n">
-        <v>10.11</v>
+        <v>9</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>50.11</v>
+        <v>49.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.67</v>
+        <v>10.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.89</v>
+        <v>6.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>20.44</v>
+        <v>20.2</v>
       </c>
       <c r="BE14" t="n">
         <v>1.24</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.79</v>
+        <v>10.8</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM14" t="n">
         <v>0.95</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.26</v>
+        <v>4.35</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.37</v>
+        <v>6.3</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS14" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT14" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU14" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV14" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY14" t="n">
         <v>2.75</v>
@@ -6442,40 +6442,40 @@
         <v>2.9</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.53</v>
+        <v>3.66</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.09</v>
+        <v>4.25</v>
       </c>
       <c r="CE14" t="n">
         <v>1.38</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CH14" t="n">
         <v>1.39</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CM14" t="n">
         <v>2.74</v>
@@ -6490,7 +6490,7 @@
         <v>1.96</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CR14" t="n">
         <v>1.39</v>
@@ -6514,97 +6514,97 @@
         <v>1.45</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.58</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DB14" t="n">
         <v>1.31</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="DH14" t="n">
-        <v>76.37</v>
+        <v>75.3</v>
       </c>
       <c r="DI14" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.53</v>
+        <v>4.6</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.9</v>
+        <v>46.65</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.47</v>
+        <v>13.5</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.63</v>
+        <v>17.4</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.26</v>
+        <v>7.8</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.95</v>
+        <v>50.65</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.79</v>
+        <v>12.6</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.68</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.11</v>
+        <v>4.15</v>
       </c>
       <c r="EA14" t="n">
-        <v>22.47</v>
+        <v>22.25</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="15">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6707,136 +6707,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="AI15" t="n">
-        <v>68.33</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.11</v>
+        <v>4.7</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AN15" t="n">
-        <v>47.67</v>
+        <v>47</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13.33</v>
+        <v>13.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.89</v>
+        <v>15.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.67</v>
+        <v>8.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>48.33</v>
+        <v>48.1</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA15" t="n">
-        <v>11.11</v>
+        <v>10.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.22</v>
+        <v>6.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>22.56</v>
+        <v>21.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.47</v>
+        <v>10.15</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.89</v>
+        <v>4.7</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.84</v>
+        <v>4.75</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS15" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT15" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BU15" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BV15" t="n">
-        <v>10.53</v>
+        <v>15</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX15" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BY15" t="n">
         <v>2.59</v>
@@ -6845,25 +6845,25 @@
         <v>3.03</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.68</v>
+        <v>3.77</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.17</v>
+        <v>4.22</v>
       </c>
       <c r="CE15" t="n">
         <v>1.34</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CH15" t="n">
         <v>1.29</v>
@@ -6872,19 +6872,19 @@
         <v>1.81</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK15" t="n">
         <v>1.29</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CO15" t="n">
         <v>1.25</v>
@@ -6893,7 +6893,7 @@
         <v>1.93</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
@@ -6902,7 +6902,7 @@
         <v>3.06</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CU15" t="n">
         <v>1.38</v>
@@ -6911,7 +6911,7 @@
         <v>1.96</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CX15" t="n">
         <v>1.47</v>
@@ -6932,49 +6932,49 @@
         <v>2.1</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="DH15" t="n">
-        <v>70.05</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.32</v>
+        <v>4.15</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="DM15" t="n">
-        <v>42.21</v>
+        <v>42.15</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.31</v>
+        <v>14.3</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.42</v>
+        <v>15.7</v>
       </c>
       <c r="DR15" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="DS15" t="n">
         <v>0.1</v>
@@ -6986,28 +6986,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.37</v>
+        <v>47.3</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.63</v>
+        <v>10.35</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.68</v>
+        <v>6.4</v>
       </c>
       <c r="DZ15" t="n">
         <v>3.95</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.74</v>
+        <v>20.4</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="16">
@@ -7017,94 +7017,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F16" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H16" t="n">
-        <v>79.22</v>
+        <v>80.8</v>
       </c>
       <c r="I16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>4.67</v>
+        <v>4.9</v>
       </c>
       <c r="L16" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="M16" t="n">
-        <v>49.56</v>
+        <v>49.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="P16" t="n">
-        <v>14.33</v>
+        <v>13.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.67</v>
+        <v>13.6</v>
       </c>
       <c r="R16" t="n">
-        <v>9.33</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>53.44</v>
+        <v>54.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.33</v>
+        <v>12.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.44</v>
+        <v>7.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.89</v>
+        <v>5.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>21.67</v>
+        <v>22.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AE16" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="AF16" t="n">
         <v>0.1</v>
@@ -7188,70 +7188,70 @@
         <v>2.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.470000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS16" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT16" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV16" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="CA16" t="n">
         <v>3.17</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CC16" t="n">
         <v>2.94</v>
@@ -7263,10 +7263,10 @@
         <v>1.41</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CH16" t="n">
         <v>1.35</v>
@@ -7284,28 +7284,28 @@
         <v>1.83</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CR16" t="n">
         <v>1.42</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CU16" t="n">
         <v>1.36</v>
@@ -7320,7 +7320,7 @@
         <v>1.53</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.43</v>
@@ -7332,85 +7332,85 @@
         <v>1.35</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="DE16" t="n">
         <v>0.1</v>
       </c>
       <c r="DF16" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="DH16" t="n">
-        <v>87.05</v>
+        <v>87.45</v>
       </c>
       <c r="DI16" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.48</v>
+        <v>4.6</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="DM16" t="n">
-        <v>49.84</v>
+        <v>49.9</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.89</v>
+        <v>14.6</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.63</v>
+        <v>12.65</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.210000000000001</v>
+        <v>7.75</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.95</v>
+        <v>52.4</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.31</v>
+        <v>12.15</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.84</v>
+        <v>7.65</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.9</v>
+        <v>21.15</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7510,139 +7510,139 @@
         <v>2.22</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AI17" t="n">
-        <v>86.59999999999999</v>
+        <v>87.36</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AN17" t="n">
-        <v>55.8</v>
+        <v>55.82</v>
       </c>
       <c r="AO17" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.7</v>
+        <v>12.64</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.8</v>
+        <v>11.09</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.9</v>
+        <v>7.09</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>45.5</v>
+        <v>45.55</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="BA17" t="n">
-        <v>12.2</v>
+        <v>11.91</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.300000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="BD17" t="n">
-        <v>21.5</v>
+        <v>21.91</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="BF17" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.630000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS17" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BT17" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU17" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV17" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX17" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BY17" t="n">
         <v>1.86</v>
@@ -7651,22 +7651,22 @@
         <v>2.12</v>
       </c>
       <c r="CA17" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="CD17" t="n">
         <v>3.15</v>
-      </c>
-      <c r="CB17" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="CC17" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="CD17" t="n">
-        <v>3.11</v>
       </c>
       <c r="CE17" t="n">
         <v>1.41</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CG17" t="n">
         <v>2.69</v>
@@ -7684,10 +7684,10 @@
         <v>1.4</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CN17" t="n">
         <v>2.04</v>
@@ -7696,19 +7696,19 @@
         <v>1.33</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="CR17" t="n">
         <v>1.43</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CU17" t="n">
         <v>1.37</v>
@@ -7720,16 +7720,16 @@
         <v>1.91</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DB17" t="n">
         <v>1.36</v>
@@ -7744,76 +7744,76 @@
         <v>0.05</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DH17" t="n">
-        <v>83.84</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="DI17" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="DM17" t="n">
-        <v>54.37</v>
+        <v>54.45</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.32</v>
+        <v>12.3</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.58</v>
+        <v>11.7</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.63</v>
+        <v>7.2</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>46.95</v>
+        <v>46.9</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.37</v>
+        <v>12.2</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.109999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.26</v>
+        <v>4.1</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.26</v>
+        <v>21.5</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="18">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
         <v>0.3</v>
@@ -7916,49 +7916,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AI18" t="n">
-        <v>83.22</v>
+        <v>84.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AN18" t="n">
-        <v>50.67</v>
+        <v>51</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.33</v>
+        <v>11.3</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.67</v>
+        <v>15.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.44</v>
+        <v>8.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7970,82 +7970,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>48</v>
+        <v>47.1</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>12</v>
+        <v>11.3</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.67</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="BD18" t="n">
-        <v>20.44</v>
+        <v>20.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="BH18" t="n">
         <v>10.05</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.42</v>
+        <v>5.4</v>
       </c>
       <c r="BR18" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS18" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BT18" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BU18" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV18" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW18" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX18" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY18" t="n">
         <v>3.13</v>
@@ -8054,16 +8054,16 @@
         <v>3.44</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.68</v>
+        <v>4.56</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.18</v>
+        <v>5.06</v>
       </c>
       <c r="CE18" t="n">
         <v>1.38</v>
@@ -8087,10 +8087,10 @@
         <v>1.33</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CN18" t="n">
         <v>2.19</v>
@@ -8120,7 +8120,7 @@
         <v>1.98</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX18" t="n">
         <v>1.48</v>
@@ -8132,10 +8132,10 @@
         <v>2.58</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC18" t="n">
         <v>2.02</v>
@@ -8144,79 +8144,79 @@
         <v>3.48</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DH18" t="n">
-        <v>80.20999999999999</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="DI18" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="DK18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>50</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="DZ18" t="n">
         <v>4</v>
       </c>
-      <c r="DL18" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="DM18" t="n">
-        <v>49.79</v>
-      </c>
-      <c r="DN18" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="DO18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="DP18" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="DQ18" t="n">
-        <v>16.32</v>
-      </c>
-      <c r="DR18" t="n">
-        <v>9.26</v>
-      </c>
-      <c r="DS18" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DT18" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV18" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="DW18" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DX18" t="n">
-        <v>11.63</v>
-      </c>
-      <c r="DY18" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="DZ18" t="n">
-        <v>4.21</v>
-      </c>
       <c r="EA18" t="n">
-        <v>20.68</v>
+        <v>20.6</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -2681,7 +2681,7 @@
         <v>0.3</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="n">
         <v>2</v>
@@ -2693,7 +2693,7 @@
         <v>0.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AL5" t="n">
         <v>5</v>
@@ -2738,7 +2738,7 @@
         <v>53</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="BA5" t="n">
         <v>13.2</v>
@@ -2912,7 +2912,7 @@
         <v>0.25</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="DG5" t="n">
         <v>1.95</v>
@@ -2924,7 +2924,7 @@
         <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="DK5" t="n">
         <v>4.85</v>
@@ -2963,7 +2963,7 @@
         <v>55.5</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="DX5" t="n">
         <v>14.4</v>
@@ -3036,10 +3036,10 @@
         <v>14.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="R6" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="S6" t="n">
         <v>0.9</v>
@@ -3063,19 +3063,19 @@
         <v>0.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.8</v>
+        <v>12.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -3344,10 +3344,10 @@
         <v>15.85</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.7</v>
+        <v>14.65</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DS6" t="n">
         <v>0.2</v>
@@ -3365,16 +3365,16 @@
         <v>0.2</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.95</v>
+        <v>11.15</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="EA6" t="n">
-        <v>23</v>
+        <v>22.95</v>
       </c>
       <c r="EB6" t="n">
         <v>1.32</v>
@@ -5128,10 +5128,10 @@
         <v>15.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="AT11" t="n">
         <v>1.4</v>
@@ -5155,10 +5155,10 @@
         <v>0.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="BC11" t="n">
         <v>3.4</v>
@@ -5359,10 +5359,10 @@
         <v>14.65</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.95</v>
+        <v>16.9</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.3</v>
+        <v>7.65</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5380,10 +5380,10 @@
         <v>0.25</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.4</v>
+        <v>11.45</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.4</v>
+        <v>7.45</v>
       </c>
       <c r="DZ11" t="n">
         <v>4</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -2233,7 +2233,7 @@
         <v>14.6</v>
       </c>
       <c r="R4" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>51.3</v>
+        <v>50.5</v>
       </c>
       <c r="Y4" t="n">
         <v>0.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="AB4" t="n">
         <v>4.3</v>
@@ -2269,7 +2269,7 @@
         <v>27.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AE4" t="n">
         <v>3.3</v>
@@ -2545,7 +2545,7 @@
         <v>12.95</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.35</v>
+        <v>8.6</v>
       </c>
       <c r="DS4" t="n">
         <v>0.1</v>
@@ -2557,16 +2557,16 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.05</v>
+        <v>46.65</v>
       </c>
       <c r="DW4" t="n">
         <v>0.2</v>
       </c>
       <c r="DX4" t="n">
-        <v>15.8</v>
+        <v>15.85</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.2</v>
+        <v>11.25</v>
       </c>
       <c r="DZ4" t="n">
         <v>4.6</v>
@@ -2575,7 +2575,7 @@
         <v>25.7</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="EC4" t="n">
         <v>3.3</v>
@@ -2714,10 +2714,10 @@
         <v>16.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AT5" t="n">
         <v>0.5</v>
@@ -2735,16 +2735,16 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>53</v>
+        <v>53.8</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC5" t="n">
         <v>4.9</v>
@@ -2753,7 +2753,7 @@
         <v>23.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BF5" t="n">
         <v>3.1</v>
@@ -2945,10 +2945,10 @@
         <v>15.8</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.3</v>
+        <v>15.15</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.25</v>
+        <v>5.65</v>
       </c>
       <c r="DS5" t="n">
         <v>0.1</v>
@@ -2960,16 +2960,16 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.5</v>
+        <v>55.9</v>
       </c>
       <c r="DW5" t="n">
         <v>0.4</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.4</v>
+        <v>14.55</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="DZ5" t="n">
         <v>5.2</v>
@@ -2978,7 +2978,7 @@
         <v>23.45</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="EC5" t="n">
         <v>3</v>
@@ -3435,10 +3435,10 @@
         <v>15.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.6</v>
+        <v>16.3</v>
       </c>
       <c r="R7" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="S7" t="n">
         <v>0.8</v>
@@ -3456,16 +3456,16 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>55.7</v>
+        <v>55.9</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="AB7" t="n">
         <v>5.2</v>
@@ -3474,7 +3474,7 @@
         <v>20.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AE7" t="n">
         <v>2.7</v>
@@ -3747,10 +3747,10 @@
         <v>14.35</v>
       </c>
       <c r="DQ7" t="n">
-        <v>16.8</v>
+        <v>16.65</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="DS7" t="n">
         <v>0.1</v>
@@ -3762,16 +3762,16 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.8</v>
+        <v>54.9</v>
       </c>
       <c r="DW7" t="n">
         <v>0.2</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.95</v>
+        <v>13.4</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="DZ7" t="n">
         <v>4.75</v>
@@ -3780,7 +3780,7 @@
         <v>20</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="EC7" t="n">
         <v>3.6</v>
@@ -3838,10 +3838,10 @@
         <v>15.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="R8" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="S8" t="n">
         <v>1.5</v>
@@ -3859,25 +3859,25 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>53.5</v>
+        <v>54</v>
       </c>
       <c r="Y8" t="n">
         <v>0.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.5</v>
+        <v>16.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AC8" t="n">
         <v>25.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AE8" t="n">
         <v>3.7</v>
@@ -4150,10 +4150,10 @@
         <v>14.55</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.4</v>
+        <v>14.35</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="DS8" t="n">
         <v>0.05</v>
@@ -4165,25 +4165,25 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.85</v>
+        <v>52.1</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.25</v>
+        <v>14.55</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="EA8" t="n">
         <v>24.45</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="EC8" t="n">
         <v>3.4</v>
@@ -6337,10 +6337,10 @@
         <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="AS14" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT14" t="n">
         <v>1.6</v>
@@ -6358,25 +6358,25 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
       <c r="AZ14" t="n">
         <v>0.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC14" t="n">
         <v>3.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BF14" t="n">
         <v>2.9</v>
@@ -6568,10 +6568,10 @@
         <v>13.5</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.4</v>
+        <v>17.35</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0.2</v>
@@ -6583,22 +6583,22 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.65</v>
+        <v>50.55</v>
       </c>
       <c r="DW14" t="n">
         <v>0.25</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.449999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ14" t="n">
         <v>4.15</v>
       </c>
       <c r="EA14" t="n">
-        <v>22.25</v>
+        <v>22.3</v>
       </c>
       <c r="EB14" t="n">
         <v>1.42</v>
@@ -6740,10 +6740,10 @@
         <v>13.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.6</v>
+        <v>10.1</v>
       </c>
       <c r="AT15" t="n">
         <v>1.8</v>
@@ -6761,16 +6761,16 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.1</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="BC15" t="n">
         <v>3.9</v>
@@ -6779,7 +6779,7 @@
         <v>21.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="BF15" t="n">
         <v>2.5</v>
@@ -6971,10 +6971,10 @@
         <v>14.3</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.5</v>
+        <v>9.25</v>
       </c>
       <c r="DS15" t="n">
         <v>0.1</v>
@@ -6986,16 +6986,16 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.3</v>
+        <v>47.05</v>
       </c>
       <c r="DW15" t="n">
         <v>0.2</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.35</v>
+        <v>10.6</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.4</v>
+        <v>6.65</v>
       </c>
       <c r="DZ15" t="n">
         <v>3.95</v>
@@ -7004,7 +7004,7 @@
         <v>20.4</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="EC15" t="n">
         <v>2.65</v>
@@ -7062,10 +7062,10 @@
         <v>13.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="R16" t="n">
-        <v>8.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="S16" t="n">
         <v>0.9</v>
@@ -7083,7 +7083,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>54.2</v>
+        <v>53.7</v>
       </c>
       <c r="Y16" t="n">
         <v>0.1</v>
@@ -7374,10 +7374,10 @@
         <v>14.6</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.65</v>
+        <v>12.55</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.75</v>
+        <v>8.15</v>
       </c>
       <c r="DS16" t="n">
         <v>0.15</v>
@@ -7389,7 +7389,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>52.4</v>
+        <v>52.15</v>
       </c>
       <c r="DW16" t="n">
         <v>0.2</v>
@@ -7949,10 +7949,10 @@
         <v>11.3</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT18" t="n">
         <v>1</v>
@@ -7970,16 +7970,16 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>47.1</v>
+        <v>47.6</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="BC18" t="n">
         <v>3</v>
@@ -7988,7 +7988,7 @@
         <v>20.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BF18" t="n">
         <v>2.1</v>
@@ -8180,10 +8180,10 @@
         <v>12.8</v>
       </c>
       <c r="DQ18" t="n">
-        <v>16.15</v>
+        <v>15.95</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.75</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DS18" t="n">
         <v>0.15</v>
@@ -8195,16 +8195,16 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.65</v>
+        <v>47.9</v>
       </c>
       <c r="DW18" t="n">
         <v>0.1</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="DZ18" t="n">
         <v>4</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,139 +1469,139 @@
         <v>2.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AI2" t="n">
-        <v>77.7</v>
+        <v>78.73</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.9</v>
+        <v>4.73</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AN2" t="n">
-        <v>48.1</v>
+        <v>48.09</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.3</v>
+        <v>14.73</v>
       </c>
       <c r="AR2" t="n">
-        <v>14.2</v>
+        <v>13.91</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>5.91</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>48.5</v>
+        <v>47.91</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.2</v>
+        <v>12.91</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.4</v>
+        <v>8.18</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.8</v>
+        <v>4.73</v>
       </c>
       <c r="BD2" t="n">
-        <v>22.5</v>
+        <v>22.09</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.550000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.25</v>
+        <v>5.14</v>
       </c>
       <c r="BR2" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT2" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU2" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BV2" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW2" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX2" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY2" t="n">
         <v>2.04</v>
@@ -1616,10 +1616,10 @@
         <v>3.3</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="CE2" t="n">
         <v>1.44</v>
@@ -1628,7 +1628,7 @@
         <v>3.09</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CH2" t="n">
         <v>1.33</v>
@@ -1640,13 +1640,13 @@
         <v>1.88</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CN2" t="n">
         <v>2.04</v>
@@ -1688,7 +1688,7 @@
         <v>2.51</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DB2" t="n">
         <v>1.39</v>
@@ -1700,79 +1700,79 @@
         <v>4.11</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="DG2" t="n">
         <v>2.9</v>
       </c>
       <c r="DH2" t="n">
-        <v>80.2</v>
+        <v>80.62</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.3</v>
+        <v>5.19</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.25</v>
+        <v>51.09</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.5</v>
+        <v>13.76</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.75</v>
+        <v>13.62</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.6</v>
+        <v>5.29</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.35</v>
+        <v>49.95</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.25</v>
+        <v>14.05</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.85</v>
+        <v>22.62</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="3">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0.1</v>
@@ -2275,52 +2275,52 @@
         <v>3.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>71.8</v>
+        <v>74.36</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.8</v>
+        <v>5.73</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.8</v>
+        <v>49.09</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18.2</v>
+        <v>17.64</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.3</v>
+        <v>11.64</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>42.8</v>
+        <v>43.55</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA4" t="n">
-        <v>14.4</v>
+        <v>14.18</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.5</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.9</v>
+        <v>4.73</v>
       </c>
       <c r="BD4" t="n">
-        <v>24.1</v>
+        <v>24.27</v>
       </c>
       <c r="BE4" t="n">
         <v>1.58</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.25</v>
+        <v>10.14</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="BO4" t="n">
         <v>1.05</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.95</v>
+        <v>4.67</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.65</v>
+        <v>4.38</v>
       </c>
       <c r="BR4" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV4" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW4" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX4" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY4" t="n">
         <v>2.55</v>
@@ -2416,22 +2416,22 @@
         <v>2.59</v>
       </c>
       <c r="CA4" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="CC4" t="n">
         <v>3.16</v>
       </c>
-      <c r="CB4" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>3.22</v>
-      </c>
       <c r="CD4" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CG4" t="n">
         <v>2.45</v>
@@ -2440,16 +2440,16 @@
         <v>1.26</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM4" t="n">
         <v>2.47</v>
@@ -2461,19 +2461,19 @@
         <v>1.3</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS4" t="n">
         <v>3.28</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CU4" t="n">
         <v>1.33</v>
@@ -2488,64 +2488,64 @@
         <v>1.5</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="DG4" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="DH4" t="n">
-        <v>77.15000000000001</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.55</v>
+        <v>3.43</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.2</v>
+        <v>6.14</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="DM4" t="n">
-        <v>54.8</v>
+        <v>55.62</v>
       </c>
       <c r="DN4" t="n">
         <v>0.95</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="DP4" t="n">
-        <v>16.75</v>
+        <v>16.53</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.95</v>
+        <v>13.05</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.6</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS4" t="n">
         <v>0.1</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.65</v>
+        <v>46.86</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX4" t="n">
-        <v>15.85</v>
+        <v>15.67</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.25</v>
+        <v>11.14</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.6</v>
+        <v>4.53</v>
       </c>
       <c r="EA4" t="n">
-        <v>25.7</v>
+        <v>25.71</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="5">
@@ -2588,61 +2588,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="H5" t="n">
-        <v>93.59999999999999</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="K5" t="n">
-        <v>4.7</v>
+        <v>4.73</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="M5" t="n">
-        <v>61.7</v>
+        <v>61.45</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="P5" t="n">
-        <v>14.8</v>
+        <v>14.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>15.91</v>
       </c>
       <c r="R5" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58</v>
+        <v>57.55</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.6</v>
+        <v>15.36</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.5</v>
+        <v>5.27</v>
       </c>
       <c r="AC5" t="n">
-        <v>23.4</v>
+        <v>23.27</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="AF5" t="n">
         <v>0.3</v>
@@ -2759,67 +2759,67 @@
         <v>3.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.75</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BM5" t="n">
         <v>0.9</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.65</v>
+        <v>3.43</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BU5" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV5" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CB5" t="n">
         <v>3.46</v>
@@ -2834,10 +2834,10 @@
         <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CH5" t="n">
         <v>1.28</v>
@@ -2849,22 +2849,22 @@
         <v>1.76</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CN5" t="n">
         <v>1.89</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ5" t="n">
         <v>3.36</v>
@@ -2882,7 +2882,7 @@
         <v>1.37</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW5" t="n">
         <v>1.91</v>
@@ -2891,13 +2891,13 @@
         <v>1.54</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.4</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB5" t="n">
         <v>1.35</v>
@@ -2909,46 +2909,46 @@
         <v>3.77</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="DH5" t="n">
-        <v>86.09999999999999</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="DI5" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="DM5" t="n">
-        <v>54.6</v>
+        <v>54.81</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.8</v>
+        <v>15.43</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.15</v>
+        <v>15.62</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.65</v>
+        <v>5.33</v>
       </c>
       <c r="DS5" t="n">
         <v>0.1</v>
@@ -2960,22 +2960,22 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.9</v>
+        <v>55.76</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.55</v>
+        <v>14.47</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.35</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.2</v>
+        <v>5.09</v>
       </c>
       <c r="EA5" t="n">
-        <v>23.45</v>
+        <v>23.38</v>
       </c>
       <c r="EB5" t="n">
         <v>1.61</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" t="n">
-        <v>75.2</v>
+        <v>75.09</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>42</v>
+        <v>41.55</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AQ6" t="n">
-        <v>16.8</v>
+        <v>17.09</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.4</v>
+        <v>15.64</v>
       </c>
       <c r="AS6" t="n">
-        <v>10.7</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AU6" t="n">
         <v>1</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>40.3</v>
+        <v>40.55</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.1</v>
+        <v>10.18</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.5</v>
+        <v>6.73</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BD6" t="n">
-        <v>24.2</v>
+        <v>24.18</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="BH6" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.05</v>
+        <v>3.81</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.45</v>
+        <v>5.14</v>
       </c>
       <c r="BR6" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BS6" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BT6" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BV6" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BY6" t="n">
         <v>2.7</v>
@@ -3228,16 +3228,16 @@
         <v>3.48</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.44</v>
+        <v>4.47</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.71</v>
+        <v>4.8</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CG6" t="n">
         <v>2.63</v>
@@ -3246,37 +3246,37 @@
         <v>1.31</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CO6" t="n">
         <v>1.24</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CT6" t="n">
         <v>2.89</v>
@@ -3285,10 +3285,10 @@
         <v>1.38</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX6" t="inlineStr"/>
       <c r="CY6" t="n">
@@ -3302,85 +3302,85 @@
         <v>1.33</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="DH6" t="n">
-        <v>85.40000000000001</v>
+        <v>84.86</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.45</v>
+        <v>4.52</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>49.5</v>
+        <v>48.91</v>
       </c>
       <c r="DN6" t="n">
         <v>1.05</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.85</v>
+        <v>16.05</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.65</v>
+        <v>14.81</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.550000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.25</v>
+        <v>45.15</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.15</v>
+        <v>11.14</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.5</v>
+        <v>7.57</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.65</v>
+        <v>3.57</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.95</v>
+        <v>23</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="7">
@@ -3390,13 +3390,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3483,127 +3483,127 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.8</v>
+        <v>2.36</v>
       </c>
       <c r="AI7" t="n">
-        <v>82.09999999999999</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>5</v>
+        <v>4.82</v>
       </c>
       <c r="AL7" t="n">
-        <v>4</v>
+        <v>4.73</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN7" t="n">
-        <v>51.1</v>
+        <v>55.55</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.1</v>
+        <v>13.55</v>
       </c>
       <c r="AR7" t="n">
-        <v>17</v>
+        <v>16.36</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.36</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AU7" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>53.9</v>
+        <v>54.82</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BA7" t="n">
-        <v>12.2</v>
+        <v>12.55</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.3</v>
+        <v>4.55</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.6</v>
+        <v>19.64</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.5</v>
+        <v>4.36</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.5</v>
+        <v>9.76</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.55</v>
+        <v>4.57</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.85</v>
+        <v>5.1</v>
       </c>
       <c r="BR7" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BU7" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3612,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY7" t="n">
         <v>1.8</v>
@@ -3621,25 +3621,25 @@
         <v>1.88</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CB7" t="n">
         <v>3.48</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="CE7" t="n">
         <v>1.4</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CH7" t="n">
         <v>1.38</v>
@@ -3687,7 +3687,7 @@
         <v>1.98</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX7" t="n">
         <v>1.49</v>
@@ -3705,7 +3705,7 @@
         <v>1.33</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DD7" t="n">
         <v>3.56</v>
@@ -3714,76 +3714,76 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="DH7" t="n">
-        <v>83.75</v>
+        <v>85.28</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.4</v>
+        <v>4.76</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DM7" t="n">
-        <v>55.45</v>
+        <v>57.57</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="DO7" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.35</v>
+        <v>14.53</v>
       </c>
       <c r="DQ7" t="n">
-        <v>16.65</v>
+        <v>16.33</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.7</v>
+        <v>7.28</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.9</v>
+        <v>55.33</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.4</v>
+        <v>13.53</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.65</v>
+        <v>8.67</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.75</v>
+        <v>4.86</v>
       </c>
       <c r="EA7" t="n">
         <v>20</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="8">
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3883,139 +3883,139 @@
         <v>3.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="AI8" t="n">
-        <v>83.2</v>
+        <v>83.36</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.6</v>
+        <v>5.36</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="AN8" t="n">
-        <v>51.8</v>
+        <v>50.73</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.5</v>
+        <v>13.18</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.4</v>
+        <v>15.73</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.9</v>
+        <v>6.18</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>50.2</v>
+        <v>49.91</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>13</v>
+        <v>12.36</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.3</v>
+        <v>4.18</v>
       </c>
       <c r="BD8" t="n">
-        <v>23.4</v>
+        <v>23</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.6</v>
+        <v>9.52</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.35</v>
+        <v>5.05</v>
       </c>
       <c r="BR8" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BS8" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BT8" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BU8" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV8" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW8" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX8" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BY8" t="n">
         <v>1.93</v>
@@ -4027,13 +4027,13 @@
         <v>3.24</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.61</v>
+        <v>2.84</v>
       </c>
       <c r="CE8" t="n">
         <v>1.42</v>
@@ -4042,28 +4042,28 @@
         <v>2.97</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CH8" t="n">
         <v>1.34</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.85</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CN8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CO8" t="n">
         <v>1.32</v>
@@ -4072,7 +4072,7 @@
         <v>2.04</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CR8" t="n">
         <v>1.43</v>
@@ -4093,16 +4093,16 @@
         <v>1.91</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="DB8" t="n">
         <v>1.35</v>
@@ -4117,43 +4117,43 @@
         <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.75</v>
+        <v>3.52</v>
       </c>
       <c r="DH8" t="n">
-        <v>90.65000000000001</v>
+        <v>90.38</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.85</v>
+        <v>5.71</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="DM8" t="n">
-        <v>60.05</v>
+        <v>59.1</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.55</v>
+        <v>14.33</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.35</v>
+        <v>14.57</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.6</v>
+        <v>6.24</v>
       </c>
       <c r="DS8" t="n">
         <v>0.05</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>52.1</v>
+        <v>51.86</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.55</v>
+        <v>14.14</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.550000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="EA8" t="n">
-        <v>24.45</v>
+        <v>24.19</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="9">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4286,139 +4286,139 @@
         <v>2.55</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>86.89</v>
+        <v>87.7</v>
       </c>
       <c r="AJ9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>54</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BK9" t="n">
         <v>0.33</v>
       </c>
-      <c r="AK9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>54.67</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>52.67</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>14.44</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>21.44</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.3</v>
-      </c>
       <c r="BL9" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BO9" t="n">
         <v>0.95</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.35</v>
+        <v>4.1</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BR9" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT9" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BU9" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV9" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY9" t="n">
         <v>2.04</v>
@@ -4427,16 +4427,16 @@
         <v>2.03</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.11</v>
+        <v>3.03</v>
       </c>
       <c r="CE9" t="n">
         <v>1.41</v>
@@ -4445,10 +4445,10 @@
         <v>2.94</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI9" t="n">
         <v>1.9</v>
@@ -4460,22 +4460,22 @@
         <v>1.38</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO9" t="n">
         <v>1.31</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="CR9" t="n">
         <v>1.41</v>
@@ -4493,103 +4493,103 @@
         <v>1.97</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CX9" t="n">
         <v>1.5</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.51</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB9" t="n">
         <v>1.34</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="DE9" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.85</v>
+        <v>2.67</v>
       </c>
       <c r="DH9" t="n">
-        <v>91.15000000000001</v>
+        <v>91.34</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.35</v>
+        <v>5.29</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="DM9" t="n">
-        <v>58.9</v>
+        <v>58.38</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.85</v>
+        <v>14.67</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.7</v>
+        <v>15.86</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.9</v>
+        <v>6.52</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.7</v>
+        <v>51.57</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.25</v>
+        <v>14.05</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.65</v>
+        <v>9.57</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.6</v>
+        <v>4.47</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.65</v>
+        <v>23.34</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="10">
@@ -4599,94 +4599,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="G10" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="H10" t="n">
-        <v>79.59999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="K10" t="n">
-        <v>5.4</v>
+        <v>5.18</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="M10" t="n">
-        <v>52.4</v>
+        <v>52.64</v>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="O10" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="P10" t="n">
-        <v>12.9</v>
+        <v>13.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.1</v>
+        <v>15.64</v>
       </c>
       <c r="R10" t="n">
-        <v>6</v>
+        <v>5.36</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>55.8</v>
+        <v>55.91</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.6</v>
+        <v>14.27</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.1</v>
+        <v>10.64</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.8</v>
+        <v>18.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AF10" t="n">
         <v>0.2</v>
@@ -4770,70 +4770,70 @@
         <v>3</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN10" t="n">
         <v>1.1</v>
       </c>
       <c r="BO10" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.95</v>
+        <v>4.67</v>
       </c>
       <c r="BR10" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BT10" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BU10" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV10" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CC10" t="n">
         <v>2.61</v>
@@ -4845,16 +4845,16 @@
         <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CH10" t="n">
         <v>1.35</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.87</v>
@@ -4863,7 +4863,7 @@
         <v>1.42</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CM10" t="n">
         <v>2.62</v>
@@ -4878,7 +4878,7 @@
         <v>2.11</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="CR10" t="n">
         <v>1.44</v>
@@ -4893,10 +4893,10 @@
         <v>1.35</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CX10" t="n">
         <v>1.51</v>
@@ -4911,7 +4911,7 @@
         <v>2.02</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC10" t="n">
         <v>2.17</v>
@@ -4920,79 +4920,79 @@
         <v>3.89</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="DH10" t="n">
-        <v>83.09999999999999</v>
+        <v>83.48</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.95</v>
+        <v>4.86</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DM10" t="n">
-        <v>51.65</v>
+        <v>51.81</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DO10" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.9</v>
+        <v>14.05</v>
       </c>
       <c r="DQ10" t="n">
-        <v>15.45</v>
+        <v>15.72</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.2</v>
+        <v>6.81</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.95</v>
+        <v>52.19</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.95</v>
+        <v>12.86</v>
       </c>
       <c r="DY10" t="n">
-        <v>9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.75</v>
+        <v>18.9</v>
       </c>
       <c r="EB10" t="n">
         <v>1.46</v>
       </c>
       <c r="EC10" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="11">
@@ -5002,61 +5002,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="H11" t="n">
-        <v>96</v>
+        <v>93.91</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9</v>
+        <v>4.73</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="M11" t="n">
-        <v>54</v>
+        <v>52.82</v>
       </c>
       <c r="N11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="O11" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="P11" t="n">
-        <v>13.9</v>
+        <v>13.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>16.5</v>
+        <v>16.18</v>
       </c>
       <c r="R11" t="n">
-        <v>7.2</v>
+        <v>6.45</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5068,28 +5068,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>50.9</v>
+        <v>50.73</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.7</v>
+        <v>12.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="AC11" t="n">
-        <v>23.7</v>
+        <v>23.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5173,70 +5173,70 @@
         <v>3.9</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM11" t="n">
         <v>0.9</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BO11" t="n">
         <v>1.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.1</v>
+        <v>4.81</v>
       </c>
       <c r="BR11" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS11" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU11" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV11" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW11" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX11" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY11" t="n">
         <v>2.53</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CC11" t="n">
         <v>3.32</v>
@@ -5245,16 +5245,16 @@
         <v>3.57</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF11" t="n">
         <v>3.05</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CI11" t="n">
         <v>1.87</v>
@@ -5263,13 +5263,13 @@
         <v>1.85</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CN11" t="n">
         <v>1.94</v>
@@ -5278,10 +5278,10 @@
         <v>1.34</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="CR11" t="n">
         <v>1.44</v>
@@ -5290,13 +5290,13 @@
         <v>3.17</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW11" t="n">
         <v>1.89</v>
@@ -5308,61 +5308,61 @@
         <v>1.8</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB11" t="n">
         <v>1.37</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="DE11" t="n">
         <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="DH11" t="n">
-        <v>91.59999999999999</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="DM11" t="n">
-        <v>49.05</v>
+        <v>48.67</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.65</v>
+        <v>14.62</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.9</v>
+        <v>16.71</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.65</v>
+        <v>7.24</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.45</v>
+        <v>48.48</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.45</v>
+        <v>11.38</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.45</v>
+        <v>7.43</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="EA11" t="n">
-        <v>22.7</v>
+        <v>22.48</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="EC11" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="12">
@@ -5405,67 +5405,67 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="G12" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="H12" t="n">
-        <v>87.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J12" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="K12" t="n">
-        <v>6.9</v>
+        <v>6.45</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="M12" t="n">
-        <v>58.7</v>
+        <v>56.09</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O12" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="P12" t="n">
-        <v>16.6</v>
+        <v>16.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.7</v>
+        <v>14.82</v>
       </c>
       <c r="R12" t="n">
-        <v>7.5</v>
+        <v>6.73</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -5474,25 +5474,25 @@
         <v>51</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.5</v>
+        <v>12.73</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.6</v>
+        <v>8.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AC12" t="n">
-        <v>21.9</v>
+        <v>22.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5579,67 +5579,67 @@
         <v>3.05</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.6</v>
+        <v>9.43</v>
       </c>
       <c r="BI12" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK12" t="n">
         <v>0.9</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.05</v>
+        <v>3.81</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.85</v>
+        <v>4.57</v>
       </c>
       <c r="BR12" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT12" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU12" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BV12" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW12" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX12" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="CA12" t="n">
         <v>3.13</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CC12" t="n">
         <v>3.24</v>
@@ -5648,13 +5648,13 @@
         <v>3.49</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF12" t="n">
         <v>3</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CH12" t="n">
         <v>1.34</v>
@@ -5669,7 +5669,7 @@
         <v>1.36</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM12" t="n">
         <v>2.5</v>
@@ -5684,7 +5684,7 @@
         <v>2.13</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="CR12" t="n">
         <v>1.44</v>
@@ -5699,7 +5699,7 @@
         <v>1.36</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW12" t="n">
         <v>1.9</v>
@@ -5720,85 +5720,85 @@
         <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="DH12" t="n">
-        <v>81.65000000000001</v>
+        <v>80.67</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DM12" t="n">
-        <v>50.05</v>
+        <v>49.09</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15.25</v>
+        <v>15.29</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.9</v>
+        <v>8.43</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.85</v>
+        <v>48</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.95</v>
+        <v>11.62</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.8</v>
+        <v>7.43</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.15</v>
+        <v>4.19</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.15</v>
+        <v>21.71</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="13">
@@ -6614,10 +6614,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
@@ -6626,82 +6626,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="H15" t="n">
-        <v>71.59999999999999</v>
+        <v>73.09</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6</v>
+        <v>3.27</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M15" t="n">
-        <v>37.3</v>
+        <v>37.55</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="P15" t="n">
-        <v>15.2</v>
+        <v>14.73</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.9</v>
+        <v>16.27</v>
       </c>
       <c r="R15" t="n">
-        <v>8.4</v>
+        <v>7.55</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>46.5</v>
+        <v>47.55</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.2</v>
+        <v>10.09</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.2</v>
+        <v>6.09</v>
       </c>
       <c r="AB15" t="n">
         <v>4</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.1</v>
+        <v>19.27</v>
       </c>
       <c r="AD15" t="n">
         <v>1.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6785,70 +6785,70 @@
         <v>2.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.15</v>
+        <v>9.81</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.7</v>
+        <v>4.48</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="BR15" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS15" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BU15" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BV15" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW15" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX15" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.59</v>
+        <v>2.67</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.03</v>
+        <v>3.15</v>
       </c>
       <c r="CA15" t="n">
         <v>3.15</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CC15" t="n">
         <v>3.77</v>
@@ -6857,10 +6857,10 @@
         <v>4.22</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CG15" t="n">
         <v>2.56</v>
@@ -6869,31 +6869,31 @@
         <v>1.29</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CN15" t="n">
         <v>2</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
@@ -6908,106 +6908,106 @@
         <v>1.38</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW15" t="n">
         <v>1.88</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DH15" t="n">
-        <v>70.84999999999999</v>
+        <v>71.67</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DM15" t="n">
-        <v>42.15</v>
+        <v>42.05</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.6</v>
+        <v>15.81</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.25</v>
+        <v>8.76</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.05</v>
+        <v>47.57</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.6</v>
+        <v>10.52</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.65</v>
+        <v>6.57</v>
       </c>
       <c r="DZ15" t="n">
         <v>3.95</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.4</v>
+        <v>20.43</v>
       </c>
       <c r="EB15" t="n">
         <v>1.2</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="16">
@@ -7823,94 +7823,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="H18" t="n">
-        <v>77.5</v>
+        <v>75</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>49</v>
+        <v>46.27</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="P18" t="n">
-        <v>14.3</v>
+        <v>13.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>16.9</v>
+        <v>17.18</v>
       </c>
       <c r="R18" t="n">
-        <v>9.1</v>
+        <v>8.18</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>48.2</v>
+        <v>47.09</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>11.3</v>
+        <v>10.82</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.3</v>
+        <v>5.91</v>
       </c>
       <c r="AB18" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>20.9</v>
+        <v>19.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7994,70 +7994,70 @@
         <v>2.1</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.05</v>
+        <v>10.29</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.4</v>
+        <v>5.62</v>
       </c>
       <c r="BR18" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BT18" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BU18" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV18" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW18" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX18" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BY18" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="BZ18" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CC18" t="n">
         <v>4.56</v>
@@ -8069,10 +8069,10 @@
         <v>1.38</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CH18" t="n">
         <v>1.39</v>
@@ -8090,7 +8090,7 @@
         <v>1.73</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CN18" t="n">
         <v>2.19</v>
@@ -8102,7 +8102,7 @@
         <v>1.94</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CR18" t="n">
         <v>1.39</v>
@@ -8144,79 +8144,79 @@
         <v>3.48</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DH18" t="n">
-        <v>80.84999999999999</v>
+        <v>79.38</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.05</v>
+        <v>-0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM18" t="n">
-        <v>50</v>
+        <v>48.52</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.8</v>
+        <v>12.62</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.95</v>
+        <v>16.14</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.050000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.9</v>
+        <v>47.33</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.4</v>
+        <v>11.14</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.4</v>
+        <v>7.14</v>
       </c>
       <c r="DZ18" t="n">
         <v>4</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.6</v>
+        <v>20.1</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1505,10 +1505,10 @@
         <v>14.73</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.91</v>
+        <v>13.82</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.91</v>
+        <v>6.55</v>
       </c>
       <c r="AT2" t="n">
         <v>1.55</v>
@@ -1526,16 +1526,16 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>47.91</v>
+        <v>48.18</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.18</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.91</v>
+        <v>13.09</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.18</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BC2" t="n">
         <v>4.73</v>
@@ -1544,7 +1544,7 @@
         <v>22.09</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="BF2" t="n">
         <v>2.64</v>
@@ -1736,10 +1736,10 @@
         <v>13.76</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.62</v>
+        <v>13.57</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.29</v>
+        <v>5.62</v>
       </c>
       <c r="DS2" t="n">
         <v>0.09</v>
@@ -1751,16 +1751,16 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.95</v>
+        <v>50.09</v>
       </c>
       <c r="DW2" t="n">
         <v>0.33</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.05</v>
+        <v>14.14</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.050000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DZ2" t="n">
         <v>5</v>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,139 +1872,139 @@
         <v>2.55</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AP3" t="n">
         <v>2</v>
       </c>
-      <c r="AI3" t="n">
-        <v>75.67</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AQ3" t="n">
-        <v>14.67</v>
+        <v>15.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.56</v>
+        <v>15.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.56</v>
+        <v>8.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>42.89</v>
+        <v>43.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.220000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="BD3" t="n">
         <v>22</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.7</v>
+        <v>5.38</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.5</v>
+        <v>5.19</v>
       </c>
       <c r="BR3" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU3" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV3" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX3" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY3" t="n">
         <v>2.07</v>
@@ -2016,70 +2016,70 @@
         <v>3.32</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.58</v>
+        <v>3.44</v>
       </c>
       <c r="CE3" t="n">
         <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CH3" t="n">
         <v>1.39</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CL3" t="n">
         <v>1.79</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CQ3" t="n">
         <v>3.22</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CU3" t="n">
         <v>1.41</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX3" t="n">
         <v>1.56</v>
@@ -2097,85 +2097,85 @@
         <v>1.3</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="DE3" t="n">
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="DH3" t="n">
-        <v>85.84999999999999</v>
+        <v>85.38</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.55</v>
+        <v>6.43</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="DM3" t="n">
-        <v>58.1</v>
+        <v>57.1</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.85</v>
+        <v>15.05</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.05</v>
+        <v>14.86</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.45</v>
+        <v>7.05</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.3</v>
+        <v>51.33</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.65</v>
+        <v>14.57</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.75</v>
+        <v>9.52</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.9</v>
+        <v>5.05</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.35</v>
+        <v>22.34</v>
       </c>
       <c r="EB3" t="n">
         <v>1.68</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="4">
@@ -3120,7 +3120,7 @@
         <v>15.64</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.640000000000001</v>
+        <v>10.55</v>
       </c>
       <c r="AT6" t="n">
         <v>1.18</v>
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>40.55</v>
+        <v>40.18</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.18</v>
@@ -3165,7 +3165,7 @@
         <v>1.9</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.949999999999999</v>
+        <v>10</v>
       </c>
       <c r="BI6" t="n">
         <v>1.9</v>
@@ -3347,7 +3347,7 @@
         <v>14.81</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.050000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DS6" t="n">
         <v>0.19</v>
@@ -3359,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.15</v>
+        <v>44.95</v>
       </c>
       <c r="DW6" t="n">
         <v>0.19</v>
@@ -4626,7 +4626,7 @@
         <v>3.36</v>
       </c>
       <c r="K10" t="n">
-        <v>5.18</v>
+        <v>5.27</v>
       </c>
       <c r="L10" t="n">
         <v>0.18</v>
@@ -4647,7 +4647,7 @@
         <v>15.64</v>
       </c>
       <c r="R10" t="n">
-        <v>5.36</v>
+        <v>6.09</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -4665,25 +4665,25 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>55.91</v>
+        <v>56.27</v>
       </c>
       <c r="Y10" t="n">
         <v>0.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.27</v>
+        <v>14.73</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.64</v>
+        <v>11</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.64</v>
+        <v>3.73</v>
       </c>
       <c r="AC10" t="n">
         <v>18.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="n">
         <v>3.18</v>
@@ -4773,7 +4773,7 @@
         <v>2.05</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.76</v>
+        <v>9.81</v>
       </c>
       <c r="BI10" t="n">
         <v>2.05</v>
@@ -4938,7 +4938,7 @@
         <v>3.43</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.86</v>
+        <v>4.9</v>
       </c>
       <c r="DL10" t="n">
         <v>0.33</v>
@@ -4959,7 +4959,7 @@
         <v>15.72</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.81</v>
+        <v>7.19</v>
       </c>
       <c r="DS10" t="n">
         <v>0.14</v>
@@ -4971,25 +4971,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>52.19</v>
+        <v>52.38</v>
       </c>
       <c r="DW10" t="n">
         <v>0.19</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.86</v>
+        <v>13.1</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.859999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="EA10" t="n">
         <v>18.9</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="EC10" t="n">
         <v>3.09</v>
@@ -6211,94 +6211,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="H14" t="n">
-        <v>76.59999999999999</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>5.73</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
       <c r="M14" t="n">
-        <v>51.7</v>
+        <v>49.64</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>14.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>17.7</v>
+        <v>17.91</v>
       </c>
       <c r="R14" t="n">
-        <v>6.6</v>
+        <v>5.91</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>51.7</v>
+        <v>51.36</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.7</v>
+        <v>13.82</v>
       </c>
       <c r="AA14" t="n">
-        <v>10.3</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>24.3</v>
+        <v>23.64</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AF14" t="n">
         <v>0.2</v>
@@ -6382,70 +6382,70 @@
         <v>2.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.8</v>
+        <v>10.62</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM14" t="n">
         <v>0.95</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.35</v>
+        <v>4.1</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.3</v>
+        <v>5.95</v>
       </c>
       <c r="BR14" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BU14" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV14" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CC14" t="n">
         <v>3.66</v>
@@ -6457,7 +6457,7 @@
         <v>1.38</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CG14" t="n">
         <v>2.78</v>
@@ -6466,28 +6466,28 @@
         <v>1.39</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK14" t="n">
         <v>1.27</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CO14" t="n">
         <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CQ14" t="n">
         <v>3.22</v>
@@ -6496,19 +6496,19 @@
         <v>1.39</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CU14" t="n">
         <v>1.4</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX14" t="n">
         <v>1.45</v>
@@ -6529,82 +6529,82 @@
         <v>2</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="DH14" t="n">
-        <v>75.3</v>
+        <v>76.19</v>
       </c>
       <c r="DI14" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.6</v>
+        <v>4.53</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.65</v>
+        <v>45.81</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.5</v>
+        <v>13.28</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.35</v>
+        <v>17.48</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.76</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.55</v>
+        <v>50.43</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.7</v>
+        <v>12.33</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.550000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="EA14" t="n">
-        <v>22.3</v>
+        <v>22.05</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="15">
@@ -6659,10 +6659,10 @@
         <v>14.73</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.27</v>
+        <v>16.18</v>
       </c>
       <c r="R15" t="n">
-        <v>7.55</v>
+        <v>8.73</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -6680,19 +6680,19 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>47.55</v>
+        <v>47.27</v>
       </c>
       <c r="Y15" t="n">
         <v>0.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.09</v>
+        <v>10.18</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.09</v>
+        <v>6.27</v>
       </c>
       <c r="AB15" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="AC15" t="n">
         <v>19.27</v>
@@ -6971,10 +6971,10 @@
         <v>14.1</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.81</v>
+        <v>15.76</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.76</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DS15" t="n">
         <v>0.09</v>
@@ -6986,19 +6986,19 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.57</v>
+        <v>47.43</v>
       </c>
       <c r="DW15" t="n">
         <v>0.19</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.52</v>
+        <v>10.57</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.57</v>
+        <v>6.67</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="EA15" t="n">
         <v>20.43</v>
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
@@ -7432,82 +7432,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="G17" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>80.78</v>
+        <v>82.5</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K17" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="L17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M17" t="n">
-        <v>52.78</v>
+        <v>54.1</v>
       </c>
       <c r="N17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="P17" t="n">
-        <v>11.89</v>
+        <v>12.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.44</v>
+        <v>12.6</v>
       </c>
       <c r="R17" t="n">
-        <v>7.33</v>
+        <v>6.5</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="U17" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="V17" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>48.56</v>
+        <v>49.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.56</v>
+        <v>12.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.89</v>
+        <v>7.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.67</v>
+        <v>4.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AF17" t="n">
         <v>0.09</v>
@@ -7591,70 +7591,70 @@
         <v>2.82</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.699999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.2</v>
+        <v>4.29</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.5</v>
+        <v>4.38</v>
       </c>
       <c r="BR17" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BT17" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU17" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BV17" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW17" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX17" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CC17" t="n">
         <v>2.95</v>
@@ -7663,22 +7663,22 @@
         <v>3.15</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF17" t="n">
         <v>2.98</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CH17" t="n">
         <v>1.34</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK17" t="n">
         <v>1.4</v>
@@ -7687,10 +7687,10 @@
         <v>1.82</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CO17" t="n">
         <v>1.33</v>
@@ -7699,7 +7699,7 @@
         <v>2.07</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CR17" t="n">
         <v>1.43</v>
@@ -7711,31 +7711,31 @@
         <v>2.82</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV17" t="n">
         <v>1.94</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB17" t="n">
         <v>1.36</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DD17" t="n">
         <v>3.89</v>
@@ -7744,76 +7744,76 @@
         <v>0.05</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="DH17" t="n">
-        <v>84.40000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM17" t="n">
-        <v>54.45</v>
+        <v>55</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.3</v>
+        <v>12.48</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.7</v>
+        <v>11.81</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.2</v>
+        <v>6.81</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>46.9</v>
+        <v>47.62</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.2</v>
+        <v>12.29</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.1</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.1</v>
+        <v>4.24</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.5</v>
+        <v>21.57</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="18">
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
         <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>0.11</v>
@@ -8319,46 +8319,46 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AI19" t="n">
-        <v>84.59999999999999</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN19" t="n">
-        <v>52.4</v>
+        <v>50.73</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15</v>
+        <v>14.73</v>
       </c>
       <c r="AR19" t="n">
-        <v>16.2</v>
+        <v>16.45</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.5</v>
+        <v>6.73</v>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AU19" t="n">
         <v>1</v>
@@ -8373,82 +8373,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>53.4</v>
+        <v>52</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.1</v>
+        <v>11.82</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.8</v>
+        <v>7.64</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.3</v>
+        <v>4.18</v>
       </c>
       <c r="BD19" t="n">
-        <v>22.5</v>
+        <v>21.64</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.58</v>
+        <v>10.45</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.42</v>
+        <v>5.45</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.16</v>
+        <v>5</v>
       </c>
       <c r="BR19" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS19" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT19" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU19" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BV19" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY19" t="n">
         <v>2.17</v>
@@ -8457,34 +8457,34 @@
         <v>2.33</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF19" t="n">
         <v>2.98</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CH19" t="n">
         <v>1.36</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK19" t="n">
         <v>1.39</v>
@@ -8493,7 +8493,7 @@
         <v>1.86</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CN19" t="n">
         <v>2.05</v>
@@ -8502,7 +8502,7 @@
         <v>1.3</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ19" t="n">
         <v>3.59</v>
@@ -8511,13 +8511,13 @@
         <v>1.43</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV19" t="n">
         <v>1.97</v>
@@ -8526,16 +8526,16 @@
         <v>1.87</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY19" t="n">
         <v>1.74</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DB19" t="n">
         <v>1.35</v>
@@ -8544,49 +8544,49 @@
         <v>2.14</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="DE19" t="n">
         <v>0.05</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="DH19" t="n">
-        <v>85.05</v>
+        <v>84.05</v>
       </c>
       <c r="DI19" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.26</v>
+        <v>5.15</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM19" t="n">
-        <v>54.58</v>
+        <v>53.55</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="DP19" t="n">
-        <v>15</v>
+        <v>14.85</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.48</v>
+        <v>14.7</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.21</v>
+        <v>6.8</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8598,28 +8598,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>53.26</v>
+        <v>52.5</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.73</v>
+        <v>12.55</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.16</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.58</v>
+        <v>4.5</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.26</v>
+        <v>20.85</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -2311,10 +2311,10 @@
         <v>17.64</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.64</v>
+        <v>11.55</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.27</v>
+        <v>9.18</v>
       </c>
       <c r="AT4" t="n">
         <v>1.45</v>
@@ -2332,16 +2332,16 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>43.55</v>
+        <v>44</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.09</v>
       </c>
       <c r="BA4" t="n">
-        <v>14.18</v>
+        <v>14.36</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.449999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BC4" t="n">
         <v>4.73</v>
@@ -2350,7 +2350,7 @@
         <v>24.27</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BF4" t="n">
         <v>3.09</v>
@@ -2359,7 +2359,7 @@
         <v>2.52</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.14</v>
+        <v>10.19</v>
       </c>
       <c r="BI4" t="n">
         <v>2.52</v>
@@ -2542,10 +2542,10 @@
         <v>16.53</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13.05</v>
+        <v>13</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.140000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS4" t="n">
         <v>0.1</v>
@@ -2557,16 +2557,16 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.86</v>
+        <v>47.1</v>
       </c>
       <c r="DW4" t="n">
         <v>0.19</v>
       </c>
       <c r="DX4" t="n">
-        <v>15.67</v>
+        <v>15.76</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.14</v>
+        <v>11.24</v>
       </c>
       <c r="DZ4" t="n">
         <v>4.53</v>
@@ -2575,7 +2575,7 @@
         <v>25.71</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="EC4" t="n">
         <v>3.19</v>
@@ -2633,10 +2633,10 @@
         <v>14.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.91</v>
+        <v>15.55</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>5.45</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -2654,25 +2654,25 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>57.55</v>
+        <v>58.73</v>
       </c>
       <c r="Y5" t="n">
         <v>0.45</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.36</v>
+        <v>15.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.09</v>
+        <v>10.18</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.27</v>
+        <v>5.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>23.27</v>
+        <v>23.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AE5" t="n">
         <v>2.91</v>
@@ -2762,7 +2762,7 @@
         <v>2.33</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.710000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="BI5" t="n">
         <v>2.33</v>
@@ -2945,10 +2945,10 @@
         <v>15.43</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.62</v>
+        <v>15.43</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.33</v>
+        <v>5.57</v>
       </c>
       <c r="DS5" t="n">
         <v>0.1</v>
@@ -2960,25 +2960,25 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.76</v>
+        <v>56.38</v>
       </c>
       <c r="DW5" t="n">
         <v>0.38</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.47</v>
+        <v>14.57</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.380000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.09</v>
+        <v>5.14</v>
       </c>
       <c r="EA5" t="n">
-        <v>23.38</v>
+        <v>23.43</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="EC5" t="n">
         <v>3</v>
@@ -3516,10 +3516,10 @@
         <v>13.55</v>
       </c>
       <c r="AR7" t="n">
-        <v>16.36</v>
+        <v>16.27</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.36</v>
+        <v>7.73</v>
       </c>
       <c r="AT7" t="n">
         <v>1.27</v>
@@ -3537,19 +3537,19 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>54.82</v>
+        <v>56.36</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.36</v>
       </c>
       <c r="BA7" t="n">
-        <v>12.55</v>
+        <v>12.64</v>
       </c>
       <c r="BB7" t="n">
-        <v>8</v>
+        <v>8.18</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.55</v>
+        <v>4.45</v>
       </c>
       <c r="BD7" t="n">
         <v>19.64</v>
@@ -3747,10 +3747,10 @@
         <v>14.53</v>
       </c>
       <c r="DQ7" t="n">
-        <v>16.33</v>
+        <v>16.28</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.28</v>
+        <v>7.48</v>
       </c>
       <c r="DS7" t="n">
         <v>0.09</v>
@@ -3762,19 +3762,19 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>55.33</v>
+        <v>56.14</v>
       </c>
       <c r="DW7" t="n">
         <v>0.19</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.53</v>
+        <v>13.57</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.67</v>
+        <v>8.76</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.86</v>
+        <v>4.81</v>
       </c>
       <c r="EA7" t="n">
         <v>20</v>
@@ -3901,7 +3901,7 @@
         <v>3.09</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.36</v>
+        <v>5.45</v>
       </c>
       <c r="AM8" t="n">
         <v>0.45</v>
@@ -3919,10 +3919,10 @@
         <v>13.18</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.73</v>
+        <v>15.64</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.18</v>
+        <v>7.36</v>
       </c>
       <c r="AT8" t="n">
         <v>1</v>
@@ -3940,7 +3940,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>49.91</v>
+        <v>48.73</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -3967,7 +3967,7 @@
         <v>2.14</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.52</v>
+        <v>9.57</v>
       </c>
       <c r="BI8" t="n">
         <v>2.14</v>
@@ -4132,7 +4132,7 @@
         <v>3.43</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.71</v>
+        <v>5.76</v>
       </c>
       <c r="DL8" t="n">
         <v>0.57</v>
@@ -4150,10 +4150,10 @@
         <v>14.33</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.57</v>
+        <v>14.53</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.24</v>
+        <v>6.86</v>
       </c>
       <c r="DS8" t="n">
         <v>0.05</v>
@@ -4165,7 +4165,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.86</v>
+        <v>51.24</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
@@ -4304,7 +4304,7 @@
         <v>2.9</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
@@ -4325,7 +4325,7 @@
         <v>16.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="AT9" t="n">
         <v>1.6</v>
@@ -4343,25 +4343,25 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>52.3</v>
+        <v>52.7</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.1</v>
       </c>
       <c r="BA9" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BD9" t="n">
         <v>23</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BF9" t="n">
         <v>2.8</v>
@@ -4370,7 +4370,7 @@
         <v>2.29</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.859999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="BI9" t="n">
         <v>2.29</v>
@@ -4535,7 +4535,7 @@
         <v>3</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.29</v>
+        <v>5.33</v>
       </c>
       <c r="DL9" t="n">
         <v>0.38</v>
@@ -4556,7 +4556,7 @@
         <v>15.86</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.52</v>
+        <v>6.81</v>
       </c>
       <c r="DS9" t="n">
         <v>0.14</v>
@@ -4568,25 +4568,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.57</v>
+        <v>51.76</v>
       </c>
       <c r="DW9" t="n">
         <v>0.19</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.05</v>
+        <v>13.9</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.57</v>
+        <v>9.48</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.47</v>
+        <v>4.43</v>
       </c>
       <c r="EA9" t="n">
         <v>23.34</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="EC9" t="n">
         <v>2.67</v>
@@ -5029,7 +5029,7 @@
         <v>2.91</v>
       </c>
       <c r="K11" t="n">
-        <v>4.73</v>
+        <v>4.82</v>
       </c>
       <c r="L11" t="n">
         <v>0.09</v>
@@ -5047,10 +5047,10 @@
         <v>13.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>16.18</v>
+        <v>16.09</v>
       </c>
       <c r="R11" t="n">
-        <v>6.45</v>
+        <v>7.55</v>
       </c>
       <c r="S11" t="n">
         <v>2.09</v>
@@ -5068,16 +5068,16 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>50.73</v>
+        <v>50.27</v>
       </c>
       <c r="Y11" t="n">
         <v>0.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.45</v>
+        <v>12.36</v>
       </c>
       <c r="AA11" t="n">
-        <v>8</v>
+        <v>7.91</v>
       </c>
       <c r="AB11" t="n">
         <v>4.45</v>
@@ -5176,7 +5176,7 @@
         <v>2.86</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.140000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="BI11" t="n">
         <v>2.86</v>
@@ -5341,7 +5341,7 @@
         <v>3.57</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.43</v>
+        <v>4.48</v>
       </c>
       <c r="DL11" t="n">
         <v>0.19</v>
@@ -5359,10 +5359,10 @@
         <v>14.62</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.71</v>
+        <v>16.67</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.24</v>
+        <v>7.81</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,16 +5374,16 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.48</v>
+        <v>48.24</v>
       </c>
       <c r="DW11" t="n">
         <v>0.24</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.38</v>
+        <v>11.33</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.43</v>
+        <v>7.38</v>
       </c>
       <c r="DZ11" t="n">
         <v>3.95</v>
@@ -5450,10 +5450,10 @@
         <v>16.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.82</v>
+        <v>14.45</v>
       </c>
       <c r="R12" t="n">
-        <v>6.73</v>
+        <v>7.82</v>
       </c>
       <c r="S12" t="n">
         <v>1.55</v>
@@ -5471,25 +5471,25 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51</v>
+        <v>50.64</v>
       </c>
       <c r="Y12" t="n">
         <v>0.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.73</v>
+        <v>12.64</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.73</v>
+        <v>8.91</v>
       </c>
       <c r="AB12" t="n">
-        <v>4</v>
+        <v>3.73</v>
       </c>
       <c r="AC12" t="n">
-        <v>22.91</v>
+        <v>22.73</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
         <v>2.09</v>
@@ -5579,7 +5579,7 @@
         <v>3.05</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.43</v>
+        <v>9.48</v>
       </c>
       <c r="BI12" t="n">
         <v>3.05</v>
@@ -5762,10 +5762,10 @@
         <v>15</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15.29</v>
+        <v>15.09</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.43</v>
+        <v>9</v>
       </c>
       <c r="DS12" t="n">
         <v>0.14</v>
@@ -5777,25 +5777,25 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48</v>
+        <v>47.81</v>
       </c>
       <c r="DW12" t="n">
         <v>0.19</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.62</v>
+        <v>11.57</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.43</v>
+        <v>7.52</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.71</v>
+        <v>21.62</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="EC12" t="n">
         <v>2.52</v>
@@ -5808,10 +5808,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
@@ -5820,82 +5820,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="G13" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="H13" t="n">
-        <v>79.22</v>
+        <v>79.3</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>4.11</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="M13" t="n">
-        <v>52</v>
+        <v>53.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="P13" t="n">
-        <v>16.22</v>
+        <v>15.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.11</v>
+        <v>15.3</v>
       </c>
       <c r="R13" t="n">
-        <v>7.44</v>
+        <v>6.6</v>
       </c>
       <c r="S13" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="T13" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="U13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>46.11</v>
+        <v>46.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.44</v>
+        <v>14.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.779999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.44</v>
+        <v>23</v>
       </c>
       <c r="AD13" t="n">
         <v>1.61</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5979,70 +5979,70 @@
         <v>2.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.949999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.84</v>
+        <v>5.8</v>
       </c>
       <c r="BR13" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BS13" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT13" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU13" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX13" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CC13" t="n">
         <v>4.32</v>
@@ -6054,10 +6054,10 @@
         <v>1.43</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CH13" t="n">
         <v>1.34</v>
@@ -6069,55 +6069,55 @@
         <v>1.89</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL13" t="n">
         <v>1.87</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP13" t="n">
         <v>2.09</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="CR13" t="n">
         <v>1.42</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CU13" t="n">
         <v>1.36</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY13" t="n">
         <v>1.79</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB13" t="n">
         <v>1.37</v>
@@ -6126,7 +6126,7 @@
         <v>2.17</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
@@ -6135,10 +6135,10 @@
         <v>2.05</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="DH13" t="n">
-        <v>76.79000000000001</v>
+        <v>76.95</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
@@ -6147,61 +6147,61 @@
         <v>3</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="DM13" t="n">
-        <v>45.11</v>
+        <v>46</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.79</v>
+        <v>14.65</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.32</v>
+        <v>16.35</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.31</v>
+        <v>9.75</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45.74</v>
+        <v>45.85</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.73</v>
+        <v>11.9</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.210000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.79</v>
+        <v>22.1</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="14">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0.1</v>
@@ -7107,139 +7107,139 @@
         <v>2.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AH16" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AI16" t="n">
-        <v>94.09999999999999</v>
+        <v>93.27</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.3</v>
+        <v>4.09</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AN16" t="n">
-        <v>50.1</v>
+        <v>49.45</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15.4</v>
+        <v>15.36</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.7</v>
+        <v>11.91</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.2</v>
+        <v>6.45</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>50.6</v>
+        <v>50.73</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.4</v>
+        <v>11.36</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.91</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BD16" t="n">
-        <v>20.2</v>
+        <v>20.55</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.8</v>
+        <v>3.09</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.5</v>
+        <v>9.43</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.2</v>
+        <v>4.14</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BR16" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU16" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV16" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BY16" t="n">
         <v>2.33</v>
@@ -7248,22 +7248,22 @@
         <v>2.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="CE16" t="n">
         <v>1.41</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CG16" t="n">
         <v>2.69</v>
@@ -7314,19 +7314,19 @@
         <v>1.99</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX16" t="n">
         <v>1.53</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.43</v>
       </c>
       <c r="DA16" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB16" t="n">
         <v>1.35</v>
@@ -7335,82 +7335,82 @@
         <v>2.12</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DH16" t="n">
-        <v>87.45</v>
+        <v>87.33</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.05</v>
+        <v>3.19</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.6</v>
+        <v>4.48</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM16" t="n">
-        <v>49.9</v>
+        <v>49.57</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.6</v>
+        <v>14.62</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.55</v>
+        <v>12.62</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.15</v>
+        <v>7.71</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>52.15</v>
+        <v>52.14</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.15</v>
+        <v>12.09</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.65</v>
+        <v>7.52</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.15</v>
+        <v>21.29</v>
       </c>
       <c r="EB16" t="n">
         <v>1.44</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="17">
@@ -7465,10 +7465,10 @@
         <v>12.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="R17" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="S17" t="n">
         <v>1.2</v>
@@ -7486,25 +7486,25 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>49.9</v>
+        <v>49.6</v>
       </c>
       <c r="Y17" t="n">
         <v>0.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.7</v>
+        <v>13.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AC17" t="n">
         <v>21.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="n">
         <v>2.2</v>
@@ -7777,10 +7777,10 @@
         <v>12.48</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.81</v>
+        <v>11.76</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.81</v>
+        <v>7.14</v>
       </c>
       <c r="DS17" t="n">
         <v>0.24</v>
@@ -7792,25 +7792,25 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.62</v>
+        <v>47.48</v>
       </c>
       <c r="DW17" t="n">
         <v>0.53</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.29</v>
+        <v>12.52</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.050000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.24</v>
+        <v>4.29</v>
       </c>
       <c r="EA17" t="n">
         <v>21.57</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="EC17" t="n">
         <v>2.52</v>
@@ -7868,10 +7868,10 @@
         <v>13.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>17.18</v>
+        <v>17</v>
       </c>
       <c r="R18" t="n">
-        <v>8.18</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="S18" t="n">
         <v>1.36</v>
@@ -7889,19 +7889,19 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>47.09</v>
+        <v>45.55</v>
       </c>
       <c r="Y18" t="n">
         <v>0.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>10.82</v>
+        <v>10.91</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.91</v>
+        <v>6.09</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.91</v>
+        <v>4.82</v>
       </c>
       <c r="AC18" t="n">
         <v>19.91</v>
@@ -8180,10 +8180,10 @@
         <v>12.62</v>
       </c>
       <c r="DQ18" t="n">
-        <v>16.14</v>
+        <v>16.05</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.57</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DS18" t="n">
         <v>0.14</v>
@@ -8195,19 +8195,19 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.33</v>
+        <v>46.53</v>
       </c>
       <c r="DW18" t="n">
         <v>0.14</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.14</v>
+        <v>11.19</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.14</v>
+        <v>7.24</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="EA18" t="n">
         <v>20.1</v>
@@ -8352,10 +8352,10 @@
         <v>14.73</v>
       </c>
       <c r="AR19" t="n">
-        <v>16.45</v>
+        <v>16.09</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.73</v>
+        <v>7.82</v>
       </c>
       <c r="AT19" t="n">
         <v>1.18</v>
@@ -8373,19 +8373,19 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>52</v>
+        <v>52.27</v>
       </c>
       <c r="AZ19" t="n">
         <v>0.18</v>
       </c>
       <c r="BA19" t="n">
-        <v>11.82</v>
+        <v>11.91</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.64</v>
+        <v>7.82</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.18</v>
+        <v>4.09</v>
       </c>
       <c r="BD19" t="n">
         <v>21.64</v>
@@ -8583,10 +8583,10 @@
         <v>14.85</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8598,19 +8598,19 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.5</v>
+        <v>52.65</v>
       </c>
       <c r="DW19" t="n">
         <v>0.1</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.55</v>
+        <v>12.6</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.050000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="EA19" t="n">
         <v>20.85</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
@@ -1391,49 +1391,49 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H2" t="n">
-        <v>82.7</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="K2" t="n">
-        <v>5.7</v>
+        <v>5.82</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="M2" t="n">
-        <v>54.4</v>
+        <v>54.82</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="P2" t="n">
-        <v>12.7</v>
+        <v>12.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.3</v>
+        <v>13.09</v>
       </c>
       <c r="R2" t="n">
-        <v>4.6</v>
+        <v>4.09</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>52.2</v>
+        <v>51.91</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.3</v>
+        <v>14.64</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.3</v>
+        <v>5.09</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.2</v>
+        <v>22.64</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AF2" t="n">
         <v>0.18</v>
@@ -1550,70 +1550,70 @@
         <v>2.64</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.24</v>
+        <v>9.32</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="BQ2" t="n">
         <v>5.14</v>
       </c>
       <c r="BR2" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS2" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT2" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU2" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BV2" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX2" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="CC2" t="n">
         <v>2.79</v>
@@ -1625,28 +1625,28 @@
         <v>1.44</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CH2" t="n">
         <v>1.33</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.88</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CN2" t="n">
         <v>2.04</v>
@@ -1655,22 +1655,22 @@
         <v>1.34</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV2" t="n">
         <v>1.88</v>
@@ -1694,10 +1694,10 @@
         <v>1.39</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.11</v>
+        <v>4.07</v>
       </c>
       <c r="DE2" t="n">
         <v>0.09</v>
@@ -1706,10 +1706,10 @@
         <v>1.86</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="DH2" t="n">
-        <v>80.62</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>0.09</v>
@@ -1718,28 +1718,28 @@
         <v>3.14</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.19</v>
+        <v>5.28</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.09</v>
+        <v>51.46</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.76</v>
+        <v>13.46</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.57</v>
+        <v>13.46</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.62</v>
+        <v>5.32</v>
       </c>
       <c r="DS2" t="n">
         <v>0.09</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.09</v>
+        <v>50.04</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.14</v>
+        <v>13.87</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.140000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.62</v>
+        <v>22.36</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G3" t="n">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="H3" t="n">
-        <v>94.18000000000001</v>
+        <v>91.83</v>
       </c>
       <c r="I3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="J3" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="K3" t="n">
-        <v>8.27</v>
+        <v>7.83</v>
       </c>
       <c r="L3" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="M3" t="n">
-        <v>70</v>
+        <v>66.83</v>
       </c>
       <c r="N3" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>4.09</v>
+        <v>3.83</v>
       </c>
       <c r="P3" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="Q3" t="n">
         <v>15</v>
       </c>
-      <c r="Q3" t="n">
-        <v>14.64</v>
-      </c>
       <c r="R3" t="n">
-        <v>5.73</v>
+        <v>5.17</v>
       </c>
       <c r="S3" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="V3" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>58.18</v>
+        <v>57.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>19.09</v>
+        <v>18.33</v>
       </c>
       <c r="AA3" t="n">
-        <v>13</v>
+        <v>12.17</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.09</v>
+        <v>6.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>22.64</v>
+        <v>22.58</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AF3" t="n">
         <v>0.1</v>
@@ -1908,10 +1908,10 @@
         <v>15.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="AT3" t="n">
         <v>1.3</v>
@@ -1935,88 +1935,88 @@
         <v>0.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
         <v>22</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BF3" t="n">
         <v>2.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.1</v>
+        <v>11.05</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.19</v>
+        <v>5.14</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS3" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT3" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU3" t="n">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
       <c r="BV3" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BX3" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CC3" t="n">
         <v>3.04</v>
@@ -2028,10 +2028,10 @@
         <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CH3" t="n">
         <v>1.39</v>
@@ -2052,7 +2052,7 @@
         <v>2.75</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CO3" t="n">
         <v>1.27</v>
@@ -2091,91 +2091,91 @@
         <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DB3" t="n">
         <v>1.3</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DD3" t="n">
         <v>3.39</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="DH3" t="n">
-        <v>85.38</v>
+        <v>84.5</v>
       </c>
       <c r="DI3" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.43</v>
+        <v>6.27</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM3" t="n">
-        <v>57.1</v>
+        <v>55.95</v>
       </c>
       <c r="DN3" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.05</v>
+        <v>15.45</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.86</v>
+        <v>15</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.05</v>
+        <v>6.96</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.33</v>
+        <v>51.18</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.57</v>
+        <v>14.63</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.52</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.05</v>
+        <v>5.18</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.34</v>
+        <v>22.32</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="H4" t="n">
-        <v>82.5</v>
+        <v>81.55</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="K4" t="n">
-        <v>6.6</v>
+        <v>6.18</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="M4" t="n">
-        <v>62.8</v>
+        <v>60.73</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>15.3</v>
+        <v>15.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.6</v>
+        <v>14.82</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>7.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50.5</v>
+        <v>50.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.3</v>
+        <v>16.18</v>
       </c>
       <c r="AA4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.3</v>
+        <v>4.18</v>
       </c>
       <c r="AC4" t="n">
-        <v>27.3</v>
+        <v>27</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AF4" t="n">
         <v>0.27</v>
@@ -2356,64 +2356,64 @@
         <v>3.09</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.19</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.67</v>
+        <v>4.55</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.38</v>
+        <v>4.32</v>
       </c>
       <c r="BR4" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS4" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU4" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV4" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX4" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY4" t="n">
         <v>2.55</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="CA4" t="n">
         <v>3.14</v>
@@ -2431,7 +2431,7 @@
         <v>1.39</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CG4" t="n">
         <v>2.45</v>
@@ -2443,28 +2443,28 @@
         <v>1.73</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK4" t="n">
         <v>1.36</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CN4" t="n">
         <v>1.88</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.68</v>
+        <v>3.73</v>
       </c>
       <c r="CR4" t="n">
         <v>1.48</v>
@@ -2473,7 +2473,7 @@
         <v>3.28</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CU4" t="n">
         <v>1.33</v>
@@ -2488,97 +2488,97 @@
         <v>1.5</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DB4" t="n">
         <v>1.41</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.22</v>
+        <v>4.25</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="DH4" t="n">
-        <v>78.23999999999999</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.14</v>
+        <v>5.95</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DM4" t="n">
-        <v>55.62</v>
+        <v>54.91</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="DP4" t="n">
-        <v>16.53</v>
+        <v>16.69</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13</v>
+        <v>13.19</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.619999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.1</v>
+        <v>47.04</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX4" t="n">
-        <v>15.76</v>
+        <v>15.27</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.24</v>
+        <v>10.82</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.53</v>
+        <v>4.45</v>
       </c>
       <c r="EA4" t="n">
-        <v>25.71</v>
+        <v>25.64</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.19</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="5">
@@ -3793,61 +3793,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="H8" t="n">
-        <v>98.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="K8" t="n">
-        <v>6.1</v>
+        <v>5.91</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="M8" t="n">
-        <v>68.3</v>
+        <v>65.55</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="O8" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="P8" t="n">
-        <v>15.6</v>
+        <v>15.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.3</v>
+        <v>13.18</v>
       </c>
       <c r="R8" t="n">
-        <v>6.3</v>
+        <v>5.64</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3859,28 +3859,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>54</v>
+        <v>52.82</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>16.1</v>
+        <v>15.36</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.4</v>
+        <v>9.82</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>25.5</v>
+        <v>26.36</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="AF8" t="n">
         <v>0.09</v>
@@ -3964,70 +3964,70 @@
         <v>3.09</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.57</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BP8" t="n">
         <v>4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="BR8" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BU8" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV8" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX8" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CC8" t="n">
         <v>2.63</v>
@@ -4039,10 +4039,10 @@
         <v>1.42</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CH8" t="n">
         <v>1.34</v>
@@ -4057,7 +4057,7 @@
         <v>1.32</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CM8" t="n">
         <v>2.62</v>
@@ -4069,19 +4069,19 @@
         <v>1.32</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="CR8" t="n">
         <v>1.43</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CU8" t="n">
         <v>1.36</v>
@@ -4093,52 +4093,52 @@
         <v>1.91</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY8" t="n">
         <v>1.74</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="DH8" t="n">
-        <v>90.38</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.76</v>
+        <v>5.68</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DM8" t="n">
-        <v>59.1</v>
+        <v>58.14</v>
       </c>
       <c r="DN8" t="n">
         <v>0.91</v>
@@ -4147,46 +4147,46 @@
         <v>1.95</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.33</v>
+        <v>14.5</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.53</v>
+        <v>14.41</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.86</v>
+        <v>6.5</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.24</v>
+        <v>50.78</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>14.14</v>
+        <v>13.86</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.24</v>
+        <v>9</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.9</v>
+        <v>4.86</v>
       </c>
       <c r="EA8" t="n">
-        <v>24.19</v>
+        <v>24.68</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="9">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4286,139 +4286,139 @@
         <v>2.55</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AI9" t="n">
-        <v>87.7</v>
+        <v>86.73</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.6</v>
+        <v>4.73</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>54</v>
+        <v>53.91</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AU9" t="n">
         <v>1</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0.9</v>
-      </c>
       <c r="AV9" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>52.7</v>
+        <v>52.64</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA9" t="n">
-        <v>13.7</v>
+        <v>13.18</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.1</v>
+        <v>8.82</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.6</v>
+        <v>4.36</v>
       </c>
       <c r="BD9" t="n">
-        <v>23</v>
+        <v>22.55</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.9</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.9</v>
+        <v>4.86</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT9" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BU9" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BV9" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BX9" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>2.04</v>
@@ -4430,13 +4430,13 @@
         <v>3.14</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CE9" t="n">
         <v>1.41</v>
@@ -4445,10 +4445,10 @@
         <v>2.94</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI9" t="n">
         <v>1.9</v>
@@ -4463,7 +4463,7 @@
         <v>1.76</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CN9" t="n">
         <v>2.07</v>
@@ -4475,7 +4475,7 @@
         <v>2.05</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CR9" t="n">
         <v>1.41</v>
@@ -4493,7 +4493,7 @@
         <v>1.97</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX9" t="n">
         <v>1.5</v>
@@ -4505,7 +4505,7 @@
         <v>2.51</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DB9" t="n">
         <v>1.34</v>
@@ -4514,82 +4514,82 @@
         <v>2.1</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="DH9" t="n">
-        <v>91.34</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="DI9" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.33</v>
+        <v>5.36</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM9" t="n">
-        <v>58.38</v>
+        <v>58.14</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.67</v>
+        <v>14.78</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.86</v>
+        <v>16.36</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.81</v>
+        <v>6.45</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.76</v>
+        <v>51.78</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.9</v>
+        <v>13.64</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.48</v>
+        <v>9.32</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.43</v>
+        <v>4.32</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.34</v>
+        <v>23.1</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0.09</v>
@@ -4689,139 +4689,139 @@
         <v>3.18</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AH10" t="n">
         <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>86.59999999999999</v>
+        <v>86.55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.5</v>
+        <v>4.36</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AN10" t="n">
-        <v>50.9</v>
+        <v>51.09</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.9</v>
+        <v>14.82</v>
       </c>
       <c r="AR10" t="n">
-        <v>15.8</v>
+        <v>16.55</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.4</v>
+        <v>7.55</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>48.1</v>
+        <v>48.64</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.3</v>
+        <v>10.82</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.9</v>
+        <v>6.73</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.4</v>
+        <v>4.09</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.7</v>
+        <v>19.91</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="BF10" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.81</v>
+        <v>9.59</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BP10" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.67</v>
+        <v>4.59</v>
       </c>
       <c r="BR10" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS10" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BT10" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BU10" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV10" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BY10" t="n">
         <v>2.01</v>
@@ -4830,34 +4830,34 @@
         <v>2.11</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CE10" t="n">
         <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CK10" t="n">
         <v>1.42</v>
@@ -4866,7 +4866,7 @@
         <v>1.83</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CN10" t="n">
         <v>2</v>
@@ -4875,19 +4875,19 @@
         <v>1.35</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.71</v>
+        <v>3.76</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CS10" t="n">
         <v>3.2</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CU10" t="n">
         <v>1.35</v>
@@ -4896,7 +4896,7 @@
         <v>1.92</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CX10" t="n">
         <v>1.51</v>
@@ -4905,94 +4905,94 @@
         <v>1.8</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB10" t="n">
         <v>1.37</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.89</v>
+        <v>3.93</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DH10" t="n">
-        <v>83.48</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="DI10" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.43</v>
+        <v>3.32</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.9</v>
+        <v>4.82</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM10" t="n">
-        <v>51.81</v>
+        <v>51.86</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.05</v>
+        <v>14.04</v>
       </c>
       <c r="DQ10" t="n">
-        <v>15.72</v>
+        <v>16.1</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.19</v>
+        <v>6.82</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>52.38</v>
+        <v>52.46</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.1</v>
+        <v>12.78</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.050000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.05</v>
+        <v>3.91</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.9</v>
+        <v>19.05</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="EC10" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0.09</v>
@@ -5095,136 +5095,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AI11" t="n">
-        <v>87.2</v>
+        <v>85.45</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK11" t="n">
-        <v>4.3</v>
+        <v>3.91</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN11" t="n">
-        <v>44.1</v>
+        <v>43.91</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15.4</v>
+        <v>15.09</v>
       </c>
       <c r="AR11" t="n">
-        <v>17.3</v>
+        <v>17.36</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.1</v>
+        <v>7.27</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AU11" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>46</v>
+        <v>47.18</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.8</v>
+        <v>7.55</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BD11" t="n">
-        <v>21.7</v>
+        <v>20.55</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="BG11" t="n">
         <v>2.86</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.19</v>
+        <v>9.09</v>
       </c>
       <c r="BI11" t="n">
         <v>2.86</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BP11" t="n">
         <v>3.86</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.81</v>
+        <v>4.73</v>
       </c>
       <c r="BR11" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS11" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU11" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV11" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX11" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
         <v>2.53</v>
@@ -5239,16 +5239,16 @@
         <v>3.2</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="CE11" t="n">
         <v>1.43</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CG11" t="n">
         <v>2.63</v>
@@ -5257,10 +5257,10 @@
         <v>1.33</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK11" t="n">
         <v>1.33</v>
@@ -5281,16 +5281,16 @@
         <v>2.14</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="CR11" t="n">
         <v>1.44</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CU11" t="n">
         <v>1.35</v>
@@ -5308,10 +5308,10 @@
         <v>1.8</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DB11" t="n">
         <v>1.37</v>
@@ -5320,82 +5320,82 @@
         <v>2.21</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF11" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="DH11" t="n">
-        <v>90.70999999999999</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="DI11" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.57</v>
+        <v>3.41</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.48</v>
+        <v>4.41</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM11" t="n">
-        <v>48.67</v>
+        <v>48.36</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.62</v>
+        <v>14.5</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.67</v>
+        <v>16.72</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.81</v>
+        <v>7.41</v>
       </c>
       <c r="DS11" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.24</v>
+        <v>48.72</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.33</v>
+        <v>11.68</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.38</v>
+        <v>7.73</v>
       </c>
       <c r="DZ11" t="n">
         <v>3.95</v>
       </c>
       <c r="EA11" t="n">
-        <v>22.48</v>
+        <v>21.86</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="EC11" t="n">
-        <v>3.29</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="12">
@@ -5856,7 +5856,7 @@
         <v>15.3</v>
       </c>
       <c r="R13" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="S13" t="n">
         <v>1.6</v>
@@ -5874,16 +5874,16 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>46.3</v>
+        <v>46.9</v>
       </c>
       <c r="Y13" t="n">
         <v>0.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="AB13" t="n">
         <v>4.5</v>
@@ -5892,7 +5892,7 @@
         <v>23</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AE13" t="n">
         <v>2.9</v>
@@ -6168,7 +6168,7 @@
         <v>16.35</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.75</v>
+        <v>10.15</v>
       </c>
       <c r="DS13" t="n">
         <v>0.15</v>
@@ -6180,16 +6180,16 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45.85</v>
+        <v>46.15</v>
       </c>
       <c r="DW13" t="n">
         <v>0.25</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.9</v>
+        <v>12.05</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ13" t="n">
         <v>3.5</v>
@@ -6198,7 +6198,7 @@
         <v>22.1</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC13" t="n">
         <v>2.65</v>
@@ -6238,7 +6238,7 @@
         <v>2.91</v>
       </c>
       <c r="K14" t="n">
-        <v>5.73</v>
+        <v>5.82</v>
       </c>
       <c r="L14" t="n">
         <v>0.73</v>
@@ -6256,10 +6256,10 @@
         <v>14.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>17.91</v>
+        <v>17.82</v>
       </c>
       <c r="R14" t="n">
-        <v>5.91</v>
+        <v>6.82</v>
       </c>
       <c r="S14" t="n">
         <v>1.18</v>
@@ -6283,10 +6283,10 @@
         <v>0.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.82</v>
+        <v>14</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.449999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AB14" t="n">
         <v>4.36</v>
@@ -6295,7 +6295,7 @@
         <v>23.64</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE14" t="n">
         <v>2.55</v>
@@ -6385,7 +6385,7 @@
         <v>2.43</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.62</v>
+        <v>10.67</v>
       </c>
       <c r="BI14" t="n">
         <v>2.43</v>
@@ -6550,7 +6550,7 @@
         <v>3.1</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.53</v>
+        <v>4.57</v>
       </c>
       <c r="DL14" t="n">
         <v>0.57</v>
@@ -6568,10 +6568,10 @@
         <v>13.28</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.48</v>
+        <v>17.43</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.76</v>
+        <v>8.24</v>
       </c>
       <c r="DS14" t="n">
         <v>0.19</v>
@@ -6589,10 +6589,10 @@
         <v>0.24</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.33</v>
+        <v>12.43</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.19</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DZ14" t="n">
         <v>4.14</v>
@@ -6601,7 +6601,7 @@
         <v>22.05</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC14" t="n">
         <v>2.72</v>
@@ -7143,10 +7143,10 @@
         <v>15.36</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.91</v>
+        <v>11.73</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.45</v>
+        <v>8.09</v>
       </c>
       <c r="AT16" t="n">
         <v>0.82</v>
@@ -7164,25 +7164,25 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>50.73</v>
+        <v>50.18</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.27</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.36</v>
+        <v>11.64</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.91</v>
+        <v>8.09</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BD16" t="n">
         <v>20.55</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="BF16" t="n">
         <v>3.09</v>
@@ -7374,10 +7374,10 @@
         <v>14.62</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.62</v>
+        <v>12.53</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.71</v>
+        <v>8.57</v>
       </c>
       <c r="DS16" t="n">
         <v>0.19</v>
@@ -7389,25 +7389,25 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>52.14</v>
+        <v>51.86</v>
       </c>
       <c r="DW16" t="n">
         <v>0.19</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.09</v>
+        <v>12.24</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.52</v>
+        <v>7.62</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="EA16" t="n">
         <v>21.29</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="EC16" t="n">
         <v>2.95</v>
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
         <v>0.27</v>
@@ -7916,136 +7916,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>85.36</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>50.82</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>47.91</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BN18" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>51</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1.43</v>
-      </c>
       <c r="BO18" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.62</v>
+        <v>5.59</v>
       </c>
       <c r="BR18" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS18" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT18" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BU18" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BV18" t="n">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
       <c r="BW18" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX18" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BY18" t="n">
         <v>3.18</v>
@@ -8054,16 +8054,16 @@
         <v>3.45</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.56</v>
+        <v>4.64</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.06</v>
+        <v>5.22</v>
       </c>
       <c r="CE18" t="n">
         <v>1.38</v>
@@ -8078,10 +8078,10 @@
         <v>1.39</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CK18" t="n">
         <v>1.33</v>
@@ -8093,22 +8093,22 @@
         <v>2.93</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CO18" t="n">
         <v>1.28</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CR18" t="n">
         <v>1.39</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CT18" t="n">
         <v>2.98</v>
@@ -8120,19 +8120,19 @@
         <v>1.98</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX18" t="n">
         <v>1.48</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.58</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DB18" t="n">
         <v>1.31</v>
@@ -8147,43 +8147,43 @@
         <v>0.14</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="DH18" t="n">
-        <v>79.38</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="DK18" t="n">
         <v>3.91</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="DM18" t="n">
-        <v>48.52</v>
+        <v>48.54</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.62</v>
+        <v>12.28</v>
       </c>
       <c r="DQ18" t="n">
-        <v>16.05</v>
+        <v>16.28</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.289999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="DS18" t="n">
         <v>0.14</v>
@@ -8195,28 +8195,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.53</v>
+        <v>46.73</v>
       </c>
       <c r="DW18" t="n">
         <v>0.14</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.19</v>
+        <v>10.78</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.24</v>
+        <v>6.91</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.1</v>
+        <v>20.45</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -2010,7 +2010,7 @@
         <v>2.1</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CA3" t="n">
         <v>3.31</v>
@@ -2064,16 +2064,16 @@
         <v>3.22</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV3" t="n">
         <v>2.08</v>
@@ -2197,7 +2197,7 @@
         <v>0.09</v>
       </c>
       <c r="F4" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="G4" t="n">
         <v>3.09</v>
@@ -2209,7 +2209,7 @@
         <v>0.27</v>
       </c>
       <c r="J4" t="n">
-        <v>3.82</v>
+        <v>3.73</v>
       </c>
       <c r="K4" t="n">
         <v>6.18</v>
@@ -2272,7 +2272,7 @@
         <v>1.75</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.45</v>
+        <v>3.36</v>
       </c>
       <c r="AF4" t="n">
         <v>0.27</v>
@@ -2509,7 +2509,7 @@
         <v>0.18</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="DG4" t="n">
         <v>2.72</v>
@@ -2521,7 +2521,7 @@
         <v>0.14</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="DK4" t="n">
         <v>5.95</v>
@@ -2578,7 +2578,7 @@
         <v>1.67</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0.18</v>
@@ -2678,139 +2678,139 @@
         <v>2.91</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AI5" t="n">
-        <v>78.59999999999999</v>
+        <v>79.45</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AL5" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN5" t="n">
-        <v>47.5</v>
+        <v>47.09</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16.8</v>
+        <v>16.64</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.3</v>
+        <v>15.64</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.7</v>
+        <v>5.09</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AU5" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>53.8</v>
+        <v>52.91</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.5</v>
+        <v>13.18</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.6</v>
+        <v>8.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="BD5" t="n">
-        <v>23.5</v>
+        <v>24.55</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.76</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.43</v>
+        <v>3.36</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.48</v>
+        <v>3.41</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT5" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BU5" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV5" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BY5" t="n">
         <v>1.96</v>
@@ -2822,82 +2822,82 @@
         <v>3.05</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CI5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CL5" t="n">
         <v>1.78</v>
       </c>
-      <c r="CJ5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>1.76</v>
-      </c>
       <c r="CM5" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CO5" t="n">
         <v>1.26</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="CR5" t="n">
         <v>1.42</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CU5" t="n">
         <v>1.37</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CW5" t="n">
         <v>1.91</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DB5" t="n">
         <v>1.35</v>
@@ -2906,79 +2906,79 @@
         <v>2.12</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="DH5" t="n">
-        <v>86.56999999999999</v>
+        <v>86.64</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.86</v>
+        <v>4.64</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM5" t="n">
-        <v>54.81</v>
+        <v>54.27</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.43</v>
+        <v>15.41</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.43</v>
+        <v>15.6</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.57</v>
+        <v>5.27</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.38</v>
+        <v>55.82</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.57</v>
+        <v>14.36</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.43</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DZ5" t="n">
         <v>5.14</v>
       </c>
       <c r="EA5" t="n">
-        <v>23.43</v>
+        <v>23.96</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="EC5" t="n">
         <v>3</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="H6" t="n">
-        <v>95.59999999999999</v>
+        <v>93.45</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>57</v>
+        <v>54.64</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="P6" t="n">
-        <v>14.9</v>
+        <v>14.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.9</v>
+        <v>14.55</v>
       </c>
       <c r="R6" t="n">
-        <v>8.4</v>
+        <v>7.55</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50.2</v>
+        <v>50.18</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="AD6" t="n">
         <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>2.45</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BH6" t="n">
-        <v>10</v>
+        <v>9.73</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN6" t="n">
         <v>1.14</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="BR6" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT6" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BU6" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BV6" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CC6" t="n">
         <v>4.47</v>
@@ -3237,28 +3237,28 @@
         <v>1.33</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CH6" t="n">
         <v>1.31</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.75</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN6" t="n">
         <v>1.92</v>
@@ -3267,22 +3267,22 @@
         <v>1.24</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="CR6" t="n">
         <v>1.42</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV6" t="n">
         <v>1.95</v>
@@ -3290,97 +3290,101 @@
       <c r="CW6" t="n">
         <v>1.89</v>
       </c>
-      <c r="CX6" t="inlineStr"/>
+      <c r="CX6" t="n">
+        <v>1.5</v>
+      </c>
       <c r="CY6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CZ6" t="inlineStr"/>
+        <v>1.69</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>2.43</v>
+      </c>
       <c r="DA6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.64</v>
+        <v>3.69</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="DH6" t="n">
-        <v>84.86</v>
+        <v>84.27</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.52</v>
+        <v>4.41</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>48.91</v>
+        <v>48.1</v>
       </c>
       <c r="DN6" t="n">
         <v>1.05</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="DP6" t="n">
-        <v>16.05</v>
+        <v>15.87</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.81</v>
+        <v>15.1</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.529999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.95</v>
+        <v>45.18</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.14</v>
+        <v>11.09</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.57</v>
+        <v>7.36</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.57</v>
+        <v>3.72</v>
       </c>
       <c r="EA6" t="n">
-        <v>23</v>
+        <v>23.09</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="7">
@@ -3390,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
@@ -3402,49 +3406,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="H7" t="n">
-        <v>85.40000000000001</v>
+        <v>86.09</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8</v>
+        <v>4.73</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M7" t="n">
-        <v>59.8</v>
+        <v>58.36</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="P7" t="n">
-        <v>15.6</v>
+        <v>15.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.3</v>
+        <v>16.45</v>
       </c>
       <c r="R7" t="n">
-        <v>7.2</v>
+        <v>6.45</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3456,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>55.9</v>
+        <v>55.91</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.6</v>
+        <v>13.82</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.4</v>
+        <v>8.91</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.2</v>
+        <v>4.91</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.4</v>
+        <v>20.27</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3561,49 +3565,49 @@
         <v>4.36</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.76</v>
+        <v>9.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.57</v>
+        <v>4.45</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS7" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT7" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BU7" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3612,19 +3616,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="CC7" t="n">
         <v>2.37</v>
@@ -3636,49 +3640,49 @@
         <v>1.4</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CH7" t="n">
         <v>1.38</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CU7" t="n">
         <v>1.38</v>
@@ -3690,67 +3694,67 @@
         <v>1.85</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="DB7" t="n">
         <v>1.33</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="DH7" t="n">
-        <v>85.28</v>
+        <v>85.64</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.76</v>
+        <v>4.73</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM7" t="n">
-        <v>57.57</v>
+        <v>56.96</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="DO7" t="n">
         <v>2.09</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.53</v>
+        <v>14.46</v>
       </c>
       <c r="DQ7" t="n">
-        <v>16.28</v>
+        <v>16.36</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.48</v>
+        <v>7.09</v>
       </c>
       <c r="DS7" t="n">
         <v>0.09</v>
@@ -3765,25 +3769,25 @@
         <v>56.14</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.57</v>
+        <v>13.23</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.76</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.81</v>
+        <v>4.68</v>
       </c>
       <c r="EA7" t="n">
-        <v>20</v>
+        <v>19.95</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="8">
@@ -4436,7 +4440,7 @@
         <v>2.98</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CE9" t="n">
         <v>1.41</v>
@@ -5405,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0.27</v>
@@ -5498,136 +5502,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AI12" t="n">
-        <v>75.90000000000001</v>
+        <v>77.36</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>41.4</v>
+        <v>41.73</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AP12" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.2</v>
+        <v>13.64</v>
       </c>
       <c r="AR12" t="n">
-        <v>15.8</v>
+        <v>15.73</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.3</v>
+        <v>9.27</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>44.7</v>
+        <v>45.18</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.4</v>
+        <v>10.27</v>
       </c>
       <c r="BB12" t="n">
-        <v>6</v>
+        <v>5.82</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="BD12" t="n">
-        <v>20.4</v>
+        <v>21.18</v>
       </c>
       <c r="BE12" t="n">
         <v>1.26</v>
       </c>
       <c r="BF12" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BG12" t="n">
         <v>3</v>
       </c>
-      <c r="BG12" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BH12" t="n">
-        <v>9.48</v>
+        <v>9.23</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BL12" t="n">
         <v>0.86</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.57</v>
+        <v>4.45</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS12" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BU12" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BV12" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX12" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY12" t="n">
         <v>2.47</v>
@@ -5636,22 +5640,22 @@
         <v>2.89</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.24</v>
+        <v>3.19</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.49</v>
+        <v>3.44</v>
       </c>
       <c r="CE12" t="n">
         <v>1.43</v>
       </c>
       <c r="CF12" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CG12" t="n">
         <v>2.62</v>
@@ -5666,10 +5670,10 @@
         <v>1.85</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM12" t="n">
         <v>2.5</v>
@@ -5681,10 +5685,10 @@
         <v>1.33</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
       <c r="CR12" t="n">
         <v>1.44</v>
@@ -5693,16 +5697,16 @@
         <v>3.17</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV12" t="n">
         <v>1.92</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CX12" t="n">
         <v>1.51</v>
@@ -5714,7 +5718,7 @@
         <v>2.49</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB12" t="n">
         <v>1.37</v>
@@ -5723,82 +5727,82 @@
         <v>2.2</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="DE12" t="n">
         <v>0.14</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="DH12" t="n">
-        <v>80.67</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.33</v>
+        <v>5.18</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM12" t="n">
-        <v>49.09</v>
+        <v>48.91</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="DP12" t="n">
-        <v>15</v>
+        <v>15.14</v>
       </c>
       <c r="DQ12" t="n">
         <v>15.09</v>
       </c>
       <c r="DR12" t="n">
-        <v>9</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.81</v>
+        <v>47.91</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.57</v>
+        <v>11.46</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.52</v>
+        <v>7.37</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.62</v>
+        <v>21.96</v>
       </c>
       <c r="EB12" t="n">
         <v>1.36</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -5808,10 +5812,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
@@ -5820,82 +5824,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="H13" t="n">
-        <v>79.3</v>
+        <v>80.55</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>4.64</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="M13" t="n">
-        <v>53.1</v>
+        <v>53.45</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O13" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="P13" t="n">
-        <v>15.8</v>
+        <v>15.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.3</v>
+        <v>14.82</v>
       </c>
       <c r="R13" t="n">
-        <v>7.4</v>
+        <v>6.64</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>46.9</v>
+        <v>46.64</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.8</v>
+        <v>14.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.3</v>
+        <v>10.18</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.5</v>
+        <v>4.27</v>
       </c>
       <c r="AC13" t="n">
-        <v>23</v>
+        <v>22.45</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5979,70 +5983,70 @@
         <v>2.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.85</v>
+        <v>10.14</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.9</v>
+        <v>3.67</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.8</v>
+        <v>5.48</v>
       </c>
       <c r="BR13" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV13" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW13" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.22</v>
+        <v>3.29</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.56</v>
+        <v>3.64</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CC13" t="n">
         <v>4.32</v>
@@ -6057,7 +6061,7 @@
         <v>2.99</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CH13" t="n">
         <v>1.34</v>
@@ -6072,31 +6076,31 @@
         <v>1.41</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CN13" t="n">
         <v>2.01</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CU13" t="n">
         <v>1.36</v>
@@ -6114,7 +6118,7 @@
         <v>1.79</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DA13" t="n">
         <v>2.01</v>
@@ -6135,73 +6139,73 @@
         <v>2.05</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="DH13" t="n">
-        <v>76.95</v>
+        <v>77.72</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.95</v>
+        <v>4.14</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="DM13" t="n">
-        <v>46</v>
+        <v>46.52</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.65</v>
+        <v>14.67</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.35</v>
+        <v>16.05</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.15</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46.15</v>
+        <v>46.05</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.05</v>
+        <v>12</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.550000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.1</v>
+        <v>21.85</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="14">
@@ -6211,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
         <v>0.18</v>
@@ -6301,139 +6305,139 @@
         <v>2.55</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AI14" t="n">
-        <v>74</v>
+        <v>73.73</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.6</v>
+        <v>42.45</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>11.55</v>
       </c>
       <c r="AR14" t="n">
-        <v>17</v>
+        <v>16.91</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.800000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>49.4</v>
+        <v>49.55</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.7</v>
+        <v>10.91</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.8</v>
+        <v>6.64</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.9</v>
+        <v>4.27</v>
       </c>
       <c r="BD14" t="n">
-        <v>20.3</v>
+        <v>20.45</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.43</v>
+        <v>2.64</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.67</v>
+        <v>10.64</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.43</v>
+        <v>2.64</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="BM14" t="n">
         <v>0.95</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.95</v>
+        <v>5.91</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS14" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT14" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BU14" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BV14" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BX14" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY14" t="n">
         <v>2.74</v>
@@ -6448,10 +6452,10 @@
         <v>3.49</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="CE14" t="n">
         <v>1.38</v>
@@ -6472,22 +6476,22 @@
         <v>1.75</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO14" t="n">
         <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CQ14" t="n">
         <v>3.22</v>
@@ -6517,94 +6521,94 @@
         <v>1.64</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DB14" t="n">
         <v>1.31</v>
       </c>
       <c r="DC14" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="DH14" t="n">
-        <v>76.19</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.57</v>
+        <v>4.69</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="DM14" t="n">
-        <v>45.81</v>
+        <v>46.04</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DO14" t="n">
         <v>2.09</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.28</v>
+        <v>13</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.43</v>
+        <v>17.36</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.24</v>
+        <v>7.82</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.43</v>
+        <v>50.46</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.43</v>
+        <v>12.46</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.289999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.14</v>
+        <v>4.32</v>
       </c>
       <c r="EA14" t="n">
-        <v>22.05</v>
+        <v>22.04</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="15">
@@ -6614,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6707,136 +6711,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>69.81999999999999</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>46.18</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP15" t="n">
         <v>2</v>
       </c>
-      <c r="AH15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>47</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>13.4</v>
+        <v>13.18</v>
       </c>
       <c r="AR15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="AS15" t="n">
-        <v>10.1</v>
+        <v>9.09</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>47.6</v>
+        <v>48.18</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA15" t="n">
-        <v>11</v>
+        <v>10.73</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.1</v>
+        <v>6.91</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="BD15" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.81</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.48</v>
+        <v>4.36</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.67</v>
+        <v>4.55</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BV15" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX15" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
         <v>2.67</v>
@@ -6845,22 +6849,22 @@
         <v>3.15</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CB15" t="n">
         <v>3.4</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="CE15" t="n">
         <v>1.35</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CG15" t="n">
         <v>2.56</v>
@@ -6869,10 +6873,10 @@
         <v>1.29</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK15" t="n">
         <v>1.3</v>
@@ -6881,7 +6885,7 @@
         <v>1.66</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CN15" t="n">
         <v>2</v>
@@ -6890,10 +6894,10 @@
         <v>1.26</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
@@ -6929,7 +6933,7 @@
         <v>1.35</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DD15" t="n">
         <v>3.73</v>
@@ -6938,43 +6942,43 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="DG15" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DH15" t="n">
-        <v>71.67</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DM15" t="n">
-        <v>42.05</v>
+        <v>41.86</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.1</v>
+        <v>13.96</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.76</v>
+        <v>16.09</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.380000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="DS15" t="n">
         <v>0.09</v>
@@ -6986,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.43</v>
+        <v>47.72</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.57</v>
+        <v>10.46</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.67</v>
+        <v>6.59</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.91</v>
+        <v>3.86</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.43</v>
+        <v>20.64</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="16">
@@ -7017,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="H16" t="n">
-        <v>80.8</v>
+        <v>79.09</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="K16" t="n">
-        <v>4.9</v>
+        <v>4.73</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="M16" t="n">
-        <v>49.7</v>
+        <v>48.64</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="O16" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="P16" t="n">
-        <v>13.8</v>
+        <v>13.82</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.4</v>
+        <v>12.82</v>
       </c>
       <c r="R16" t="n">
-        <v>9.1</v>
+        <v>8.18</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>53.7</v>
+        <v>53.27</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.8</v>
+        <v>5.91</v>
       </c>
       <c r="AC16" t="n">
-        <v>22.1</v>
+        <v>22.27</v>
       </c>
       <c r="AD16" t="n">
         <v>1.58</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AF16" t="n">
         <v>0.09</v>
@@ -7188,70 +7192,70 @@
         <v>3.09</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.43</v>
+        <v>2.64</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.43</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.43</v>
+        <v>2.64</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.14</v>
+        <v>4.18</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="BR16" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS16" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU16" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BV16" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BX16" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CC16" t="n">
         <v>2.89</v>
@@ -7266,7 +7270,7 @@
         <v>2.9</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CH16" t="n">
         <v>1.35</v>
@@ -7275,28 +7279,28 @@
         <v>1.91</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM16" t="n">
         <v>2.43</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CO16" t="n">
         <v>1.31</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CR16" t="n">
         <v>1.42</v>
@@ -7317,100 +7321,100 @@
         <v>1.84</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY16" t="n">
         <v>1.81</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DH16" t="n">
-        <v>87.33</v>
+        <v>86.18000000000001</v>
       </c>
       <c r="DI16" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.48</v>
+        <v>4.41</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="DM16" t="n">
-        <v>49.57</v>
+        <v>49.04</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.62</v>
+        <v>14.59</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.53</v>
+        <v>12.28</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.57</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.86</v>
+        <v>51.72</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.24</v>
+        <v>12.32</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.62</v>
+        <v>7.59</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.62</v>
+        <v>4.73</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.29</v>
+        <v>21.41</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="17">
@@ -7420,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7510,139 +7514,139 @@
         <v>2.2</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AI17" t="n">
-        <v>87.36</v>
+        <v>87.75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.73</v>
+        <v>3.42</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.18</v>
+        <v>5.42</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="AN17" t="n">
-        <v>55.82</v>
+        <v>56.33</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.64</v>
+        <v>12.17</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.09</v>
+        <v>11.67</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.09</v>
+        <v>6.42</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>45.55</v>
+        <v>46.42</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.91</v>
+        <v>11.83</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.27</v>
+        <v>8.17</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="BD17" t="n">
-        <v>21.91</v>
+        <v>22.17</v>
       </c>
       <c r="BE17" t="n">
         <v>1.41</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.619999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.29</v>
+        <v>4.05</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.38</v>
+        <v>4.14</v>
       </c>
       <c r="BR17" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="BS17" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BT17" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU17" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV17" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX17" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BY17" t="n">
         <v>1.91</v>
@@ -7651,25 +7655,25 @@
         <v>2.15</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CH17" t="n">
         <v>1.34</v>
@@ -7687,7 +7691,7 @@
         <v>1.82</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CN17" t="n">
         <v>2.03</v>
@@ -7696,7 +7700,7 @@
         <v>1.33</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CQ17" t="n">
         <v>3.64</v>
@@ -7705,7 +7709,7 @@
         <v>1.43</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CT17" t="n">
         <v>2.82</v>
@@ -7729,7 +7733,7 @@
         <v>2.46</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DB17" t="n">
         <v>1.36</v>
@@ -7738,82 +7742,82 @@
         <v>2.17</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="DH17" t="n">
-        <v>85.05</v>
+        <v>85.36</v>
       </c>
       <c r="DI17" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.33</v>
+        <v>3.18</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.81</v>
+        <v>4.96</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="DM17" t="n">
-        <v>55</v>
+        <v>55.32</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.48</v>
+        <v>12.23</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.76</v>
+        <v>12.05</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.14</v>
+        <v>6.77</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.48</v>
+        <v>47.87</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.52</v>
+        <v>12.45</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.24</v>
+        <v>8.18</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.57</v>
+        <v>21.73</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="18">
@@ -8226,94 +8230,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.56</v>
       </c>
-      <c r="G19" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="H19" t="n">
-        <v>85.56</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="K19" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="M19" t="n">
-        <v>57</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="P19" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>12.56</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>53.11</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>13.44</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>19.89</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AE19" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8397,70 +8401,70 @@
         <v>3.36</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.45</v>
+        <v>10.14</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.45</v>
+        <v>5.29</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="BR19" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS19" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU19" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BV19" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CC19" t="n">
         <v>2.56</v>
@@ -8481,7 +8485,7 @@
         <v>1.36</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.82</v>
@@ -8493,10 +8497,10 @@
         <v>1.86</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CO19" t="n">
         <v>1.3</v>
@@ -8505,25 +8509,25 @@
         <v>2.04</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CR19" t="n">
         <v>1.43</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CT19" t="n">
         <v>2.84</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV19" t="n">
         <v>1.97</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX19" t="n">
         <v>1.53</v>
@@ -8544,49 +8548,49 @@
         <v>2.14</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="DE19" t="n">
         <v>0.05</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="DH19" t="n">
-        <v>84.05</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM19" t="n">
-        <v>53.55</v>
+        <v>52.81</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.85</v>
+        <v>15</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.5</v>
+        <v>14.43</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8598,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.65</v>
+        <v>52.33</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.6</v>
+        <v>12.38</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.15</v>
+        <v>7.91</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.85</v>
+        <v>20.62</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1424,10 +1424,10 @@
         <v>12.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.09</v>
+        <v>13</v>
       </c>
       <c r="R2" t="n">
-        <v>4.09</v>
+        <v>4.36</v>
       </c>
       <c r="S2" t="n">
         <v>0.73</v>
@@ -1445,25 +1445,25 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>51.91</v>
+        <v>52.27</v>
       </c>
       <c r="Y2" t="n">
         <v>0.45</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.64</v>
+        <v>15.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.550000000000001</v>
+        <v>10</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.09</v>
+        <v>5.73</v>
       </c>
       <c r="AC2" t="n">
         <v>22.64</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AE2" t="n">
         <v>2.36</v>
@@ -1736,10 +1736,10 @@
         <v>13.46</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.46</v>
+        <v>13.41</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.32</v>
+        <v>5.45</v>
       </c>
       <c r="DS2" t="n">
         <v>0.09</v>
@@ -1751,25 +1751,25 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.04</v>
+        <v>50.22</v>
       </c>
       <c r="DW2" t="n">
         <v>0.32</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.87</v>
+        <v>14.41</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.960000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.91</v>
+        <v>5.23</v>
       </c>
       <c r="EA2" t="n">
         <v>22.36</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="EC2" t="n">
         <v>2.5</v>
@@ -2230,10 +2230,10 @@
         <v>15.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.82</v>
+        <v>14.73</v>
       </c>
       <c r="R4" t="n">
-        <v>7.18</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="S4" t="n">
         <v>0.91</v>
@@ -2251,25 +2251,25 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50.09</v>
+        <v>49.64</v>
       </c>
       <c r="Y4" t="n">
         <v>0.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.18</v>
+        <v>16.09</v>
       </c>
       <c r="AA4" t="n">
         <v>12</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.18</v>
+        <v>4.09</v>
       </c>
       <c r="AC4" t="n">
         <v>27</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE4" t="n">
         <v>3.36</v>
@@ -2542,10 +2542,10 @@
         <v>16.69</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13.19</v>
+        <v>13.14</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.18</v>
+        <v>8.91</v>
       </c>
       <c r="DS4" t="n">
         <v>0.09</v>
@@ -2557,25 +2557,25 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.04</v>
+        <v>46.82</v>
       </c>
       <c r="DW4" t="n">
         <v>0.18</v>
       </c>
       <c r="DX4" t="n">
-        <v>15.27</v>
+        <v>15.22</v>
       </c>
       <c r="DY4" t="n">
         <v>10.82</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.45</v>
+        <v>4.41</v>
       </c>
       <c r="EA4" t="n">
         <v>25.64</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="EC4" t="n">
         <v>3.22</v>
@@ -2714,10 +2714,10 @@
         <v>16.64</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.64</v>
+        <v>15.45</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.09</v>
+        <v>5.91</v>
       </c>
       <c r="AT5" t="n">
         <v>0.45</v>
@@ -2735,16 +2735,16 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>52.91</v>
+        <v>52.73</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.27</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.18</v>
+        <v>13.36</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.27</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BC5" t="n">
         <v>4.91</v>
@@ -2753,7 +2753,7 @@
         <v>24.55</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="BF5" t="n">
         <v>3.09</v>
@@ -2945,10 +2945,10 @@
         <v>15.41</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.27</v>
+        <v>5.68</v>
       </c>
       <c r="DS5" t="n">
         <v>0.09</v>
@@ -2960,16 +2960,16 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.82</v>
+        <v>55.73</v>
       </c>
       <c r="DW5" t="n">
         <v>0.36</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.36</v>
+        <v>14.46</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.220000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="DZ5" t="n">
         <v>5.14</v>
@@ -3036,10 +3036,10 @@
         <v>14.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.55</v>
+        <v>14.64</v>
       </c>
       <c r="R6" t="n">
-        <v>7.55</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S6" t="n">
         <v>0.82</v>
@@ -3057,25 +3057,25 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50.18</v>
+        <v>49.64</v>
       </c>
       <c r="Y6" t="n">
         <v>0.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>12</v>
+        <v>11.82</v>
       </c>
       <c r="AA6" t="n">
-        <v>8</v>
+        <v>7.91</v>
       </c>
       <c r="AB6" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="AC6" t="n">
-        <v>22</v>
+        <v>22.09</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE6" t="n">
         <v>2.18</v>
@@ -3348,10 +3348,10 @@
         <v>15.87</v>
       </c>
       <c r="DQ6" t="n">
-        <v>15.1</v>
+        <v>15.14</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.050000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DS6" t="n">
         <v>0.18</v>
@@ -3363,25 +3363,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.18</v>
+        <v>44.91</v>
       </c>
       <c r="DW6" t="n">
         <v>0.18</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.09</v>
+        <v>11</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.36</v>
+        <v>7.32</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="EA6" t="n">
-        <v>23.09</v>
+        <v>23.14</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="EC6" t="n">
         <v>2.32</v>
@@ -3439,10 +3439,10 @@
         <v>15.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.45</v>
+        <v>16.36</v>
       </c>
       <c r="R7" t="n">
-        <v>6.45</v>
+        <v>7.18</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -3460,25 +3460,25 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>55.91</v>
+        <v>56.09</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.82</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.91</v>
+        <v>9.09</v>
       </c>
       <c r="AB7" t="n">
         <v>4.91</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.27</v>
+        <v>20.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE7" t="n">
         <v>2.73</v>
@@ -3751,10 +3751,10 @@
         <v>14.46</v>
       </c>
       <c r="DQ7" t="n">
-        <v>16.36</v>
+        <v>16.31</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.09</v>
+        <v>7.45</v>
       </c>
       <c r="DS7" t="n">
         <v>0.09</v>
@@ -3766,25 +3766,25 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>56.14</v>
+        <v>56.22</v>
       </c>
       <c r="DW7" t="n">
         <v>0.18</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.23</v>
+        <v>13.32</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.539999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DZ7" t="n">
         <v>4.68</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.95</v>
+        <v>20</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="EC7" t="n">
         <v>3.55</v>
@@ -3845,7 +3845,7 @@
         <v>13.18</v>
       </c>
       <c r="R8" t="n">
-        <v>5.64</v>
+        <v>6.91</v>
       </c>
       <c r="S8" t="n">
         <v>1.55</v>
@@ -3863,16 +3863,16 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>52.82</v>
+        <v>52.91</v>
       </c>
       <c r="Y8" t="n">
         <v>0.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.36</v>
+        <v>15.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.82</v>
+        <v>9.91</v>
       </c>
       <c r="AB8" t="n">
         <v>5.55</v>
@@ -4157,7 +4157,7 @@
         <v>14.41</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.5</v>
+        <v>7.14</v>
       </c>
       <c r="DS8" t="n">
         <v>0.04</v>
@@ -4169,16 +4169,16 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.78</v>
+        <v>50.82</v>
       </c>
       <c r="DW8" t="n">
         <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.86</v>
+        <v>13.9</v>
       </c>
       <c r="DY8" t="n">
-        <v>9</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DZ8" t="n">
         <v>4.86</v>
@@ -4729,10 +4729,10 @@
         <v>14.82</v>
       </c>
       <c r="AR10" t="n">
-        <v>16.55</v>
+        <v>16.36</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.55</v>
+        <v>7.91</v>
       </c>
       <c r="AT10" t="n">
         <v>0.91</v>
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>48.64</v>
+        <v>49.09</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.27</v>
@@ -4759,16 +4759,16 @@
         <v>10.82</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.73</v>
+        <v>6.82</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.91</v>
+        <v>19.82</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BF10" t="n">
         <v>2.82</v>
@@ -4960,10 +4960,10 @@
         <v>14.04</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.82</v>
+        <v>7</v>
       </c>
       <c r="DS10" t="n">
         <v>0.13</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>52.46</v>
+        <v>52.68</v>
       </c>
       <c r="DW10" t="n">
         <v>0.18</v>
@@ -4984,13 +4984,13 @@
         <v>12.78</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.859999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.91</v>
+        <v>3.86</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.05</v>
+        <v>19</v>
       </c>
       <c r="EB10" t="n">
         <v>1.45</v>
@@ -5132,10 +5132,10 @@
         <v>15.09</v>
       </c>
       <c r="AR11" t="n">
-        <v>17.36</v>
+        <v>17.27</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.27</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AT11" t="n">
         <v>1.36</v>
@@ -5153,25 +5153,25 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.18</v>
+        <v>47.09</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.36</v>
       </c>
       <c r="BA11" t="n">
-        <v>11</v>
+        <v>11.09</v>
       </c>
       <c r="BB11" t="n">
         <v>7.55</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BD11" t="n">
         <v>20.55</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BF11" t="n">
         <v>3.55</v>
@@ -5363,10 +5363,10 @@
         <v>14.5</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.72</v>
+        <v>16.68</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.41</v>
+        <v>7.95</v>
       </c>
       <c r="DS11" t="n">
         <v>0.04</v>
@@ -5378,25 +5378,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.72</v>
+        <v>48.68</v>
       </c>
       <c r="DW11" t="n">
         <v>0.22</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.68</v>
+        <v>11.72</v>
       </c>
       <c r="DY11" t="n">
         <v>7.73</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="EA11" t="n">
         <v>21.86</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC11" t="n">
         <v>3.14</v>
@@ -5535,10 +5535,10 @@
         <v>13.64</v>
       </c>
       <c r="AR12" t="n">
-        <v>15.73</v>
+        <v>15.55</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.27</v>
+        <v>9.73</v>
       </c>
       <c r="AT12" t="n">
         <v>1.64</v>
@@ -5556,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>45.18</v>
+        <v>45.73</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.27</v>
@@ -5565,13 +5565,13 @@
         <v>10.27</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.82</v>
+        <v>5.91</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.45</v>
+        <v>4.36</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.18</v>
+        <v>21</v>
       </c>
       <c r="BE12" t="n">
         <v>1.26</v>
@@ -5766,10 +5766,10 @@
         <v>15.14</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15.09</v>
+        <v>15</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.539999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DS12" t="n">
         <v>0.13</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.91</v>
+        <v>48.18</v>
       </c>
       <c r="DW12" t="n">
         <v>0.18</v>
@@ -5790,13 +5790,13 @@
         <v>11.46</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.37</v>
+        <v>7.41</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.96</v>
+        <v>21.86</v>
       </c>
       <c r="EB12" t="n">
         <v>1.36</v>
@@ -6341,10 +6341,10 @@
         <v>11.55</v>
       </c>
       <c r="AR14" t="n">
-        <v>16.91</v>
+        <v>16.73</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.82</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AT14" t="n">
         <v>1.82</v>
@@ -6362,25 +6362,25 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>49.55</v>
+        <v>49.18</v>
       </c>
       <c r="AZ14" t="n">
         <v>0.18</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.91</v>
+        <v>11.36</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.64</v>
+        <v>7</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.27</v>
+        <v>4.36</v>
       </c>
       <c r="BD14" t="n">
-        <v>20.45</v>
+        <v>20.55</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BF14" t="n">
         <v>2.73</v>
@@ -6572,10 +6572,10 @@
         <v>13</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.36</v>
+        <v>17.28</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.82</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS14" t="n">
         <v>0.18</v>
@@ -6587,25 +6587,25 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.46</v>
+        <v>50.27</v>
       </c>
       <c r="DW14" t="n">
         <v>0.22</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.46</v>
+        <v>12.68</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.140000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.32</v>
+        <v>4.36</v>
       </c>
       <c r="EA14" t="n">
-        <v>22.04</v>
+        <v>22.1</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="EC14" t="n">
         <v>2.64</v>
@@ -6744,10 +6744,10 @@
         <v>13.18</v>
       </c>
       <c r="AR15" t="n">
-        <v>16</v>
+        <v>15.55</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.09</v>
+        <v>9.73</v>
       </c>
       <c r="AT15" t="n">
         <v>1.82</v>
@@ -6765,25 +6765,25 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>48.18</v>
+        <v>48.36</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.09</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.73</v>
+        <v>10.82</v>
       </c>
       <c r="BB15" t="n">
         <v>6.91</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.82</v>
+        <v>3.91</v>
       </c>
       <c r="BD15" t="n">
-        <v>22</v>
+        <v>21.91</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BF15" t="n">
         <v>2.73</v>
@@ -6975,10 +6975,10 @@
         <v>13.96</v>
       </c>
       <c r="DQ15" t="n">
-        <v>16.09</v>
+        <v>15.86</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.91</v>
+        <v>9.23</v>
       </c>
       <c r="DS15" t="n">
         <v>0.09</v>
@@ -6990,25 +6990,25 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.72</v>
+        <v>47.82</v>
       </c>
       <c r="DW15" t="n">
         <v>0.18</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.46</v>
+        <v>10.5</v>
       </c>
       <c r="DY15" t="n">
         <v>6.59</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.86</v>
+        <v>3.91</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.64</v>
+        <v>20.59</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="EC15" t="n">
         <v>2.82</v>
@@ -7069,7 +7069,7 @@
         <v>12.82</v>
       </c>
       <c r="R16" t="n">
-        <v>8.18</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>1.09</v>
@@ -7087,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>53.27</v>
+        <v>53.64</v>
       </c>
       <c r="Y16" t="n">
         <v>0.09</v>
@@ -7096,13 +7096,13 @@
         <v>13</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.09</v>
+        <v>7.18</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.91</v>
+        <v>5.82</v>
       </c>
       <c r="AC16" t="n">
-        <v>22.27</v>
+        <v>22.09</v>
       </c>
       <c r="AD16" t="n">
         <v>1.58</v>
@@ -7381,7 +7381,7 @@
         <v>12.28</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.130000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="DS16" t="n">
         <v>0.18</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.72</v>
+        <v>51.91</v>
       </c>
       <c r="DW16" t="n">
         <v>0.18</v>
@@ -7402,13 +7402,13 @@
         <v>12.32</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.59</v>
+        <v>7.63</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.73</v>
+        <v>4.69</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.41</v>
+        <v>21.32</v>
       </c>
       <c r="EB16" t="n">
         <v>1.46</v>
@@ -7953,10 +7953,10 @@
         <v>10.73</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.55</v>
+        <v>15.27</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.09</v>
+        <v>9.09</v>
       </c>
       <c r="AT18" t="n">
         <v>1.27</v>
@@ -7974,25 +7974,25 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>47.91</v>
+        <v>47.55</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.64</v>
+        <v>11.18</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.73</v>
+        <v>8.18</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="BD18" t="n">
         <v>21</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BF18" t="n">
         <v>2.27</v>
@@ -8184,10 +8184,10 @@
         <v>12.28</v>
       </c>
       <c r="DQ18" t="n">
-        <v>16.28</v>
+        <v>16.14</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.82</v>
+        <v>9.32</v>
       </c>
       <c r="DS18" t="n">
         <v>0.14</v>
@@ -8199,25 +8199,25 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.73</v>
+        <v>46.55</v>
       </c>
       <c r="DW18" t="n">
         <v>0.14</v>
       </c>
       <c r="DX18" t="n">
-        <v>10.78</v>
+        <v>11.04</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.91</v>
+        <v>7.13</v>
       </c>
       <c r="DZ18" t="n">
-        <v>3.86</v>
+        <v>3.91</v>
       </c>
       <c r="EA18" t="n">
         <v>20.45</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="EC18" t="n">
         <v>2.54</v>
@@ -8275,10 +8275,10 @@
         <v>15.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="R19" t="n">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="S19" t="n">
         <v>1.6</v>
@@ -8296,16 +8296,16 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>52.4</v>
+        <v>52.2</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AB19" t="n">
         <v>4.9</v>
@@ -8314,7 +8314,7 @@
         <v>19.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE19" t="n">
         <v>2.4</v>
@@ -8587,10 +8587,10 @@
         <v>15</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.43</v>
+        <v>14.33</v>
       </c>
       <c r="DR19" t="n">
-        <v>7</v>
+        <v>7.43</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8602,16 +8602,16 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.33</v>
+        <v>52.24</v>
       </c>
       <c r="DW19" t="n">
         <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.38</v>
+        <v>12.33</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.91</v>
+        <v>7.86</v>
       </c>
       <c r="DZ19" t="n">
         <v>4.48</v>

--- a/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,139 +1469,139 @@
         <v>2.36</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>78.73</v>
+        <v>79.83</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.73</v>
+        <v>4.67</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AN2" t="n">
-        <v>48.09</v>
+        <v>48.83</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.73</v>
+        <v>14.75</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.82</v>
+        <v>13.75</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.55</v>
+        <v>5.92</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>48.18</v>
+        <v>48.75</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.09</v>
+        <v>12.58</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.359999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="BD2" t="n">
-        <v>22.09</v>
+        <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.32</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.14</v>
+        <v>5.09</v>
       </c>
       <c r="BR2" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>77.27</v>
+        <v>73.91</v>
       </c>
       <c r="BT2" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BU2" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV2" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX2" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY2" t="n">
         <v>1.99</v>
@@ -1610,22 +1610,22 @@
         <v>2</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CB2" t="n">
         <v>3.34</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="CE2" t="n">
         <v>1.44</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CG2" t="n">
         <v>2.65</v>
@@ -1646,7 +1646,7 @@
         <v>1.81</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CN2" t="n">
         <v>2.04</v>
@@ -1655,10 +1655,10 @@
         <v>1.34</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CR2" t="n">
         <v>1.45</v>
@@ -1694,52 +1694,52 @@
         <v>1.39</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.07</v>
+        <v>4.05</v>
       </c>
       <c r="DE2" t="n">
         <v>0.09</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="DH2" t="n">
-        <v>80.95999999999999</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.28</v>
+        <v>5.22</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.46</v>
+        <v>51.69</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.46</v>
+        <v>13.52</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.41</v>
+        <v>13.39</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.45</v>
+        <v>5.17</v>
       </c>
       <c r="DS2" t="n">
         <v>0.09</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50.22</v>
+        <v>50.43</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.41</v>
+        <v>14.09</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.18</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.23</v>
+        <v>5.13</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.36</v>
+        <v>22.83</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0.08</v>
@@ -1872,139 +1872,139 @@
         <v>2.42</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.7</v>
+        <v>2.09</v>
       </c>
       <c r="AI3" t="n">
-        <v>75.7</v>
+        <v>77.45</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.4</v>
+        <v>4.64</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>42.9</v>
+        <v>44.55</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AP3" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15.1</v>
+        <v>14.45</v>
       </c>
       <c r="AR3" t="n">
-        <v>15</v>
+        <v>15.18</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.1</v>
+        <v>8.18</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>43.8</v>
+        <v>44.64</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.2</v>
+        <v>10.27</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.2</v>
+        <v>6.45</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="BD3" t="n">
-        <v>22</v>
+        <v>22.27</v>
       </c>
       <c r="BE3" t="n">
         <v>1.24</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.05</v>
+        <v>10.96</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.36</v>
+        <v>5.26</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.14</v>
+        <v>5.17</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS3" t="n">
-        <v>86.36</v>
+        <v>82.61</v>
       </c>
       <c r="BT3" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BU3" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV3" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW3" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY3" t="n">
         <v>2.1</v>
@@ -2019,16 +2019,16 @@
         <v>3.48</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="CE3" t="n">
         <v>1.38</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CG3" t="n">
         <v>2.84</v>
@@ -2061,7 +2061,7 @@
         <v>1.92</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CR3" t="n">
         <v>1.39</v>
@@ -2091,7 +2091,7 @@
         <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DB3" t="n">
         <v>1.3</v>
@@ -2103,79 +2103,79 @@
         <v>3.39</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="DG3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>84.95</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>56.17</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DO3" t="n">
         <v>2.91</v>
       </c>
-      <c r="DH3" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="DI3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DJ3" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="DK3" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="DL3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DM3" t="n">
-        <v>55.95</v>
-      </c>
-      <c r="DN3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="DO3" t="n">
-        <v>3</v>
-      </c>
       <c r="DP3" t="n">
-        <v>15.45</v>
+        <v>15.13</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15</v>
+        <v>15.09</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.96</v>
+        <v>6.61</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.18</v>
+        <v>51.26</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.63</v>
+        <v>14.48</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.460000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.18</v>
+        <v>5.05</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.32</v>
+        <v>22.43</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0.09</v>
@@ -2275,52 +2275,52 @@
         <v>3.36</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="AI4" t="n">
-        <v>74.36</v>
+        <v>73.67</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.73</v>
+        <v>5.67</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AN4" t="n">
-        <v>49.09</v>
+        <v>48.25</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17.64</v>
+        <v>17.58</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.55</v>
+        <v>11.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.18</v>
+        <v>8.33</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>44</v>
+        <v>44.33</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="BA4" t="n">
-        <v>14.36</v>
+        <v>14</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.640000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.73</v>
+        <v>4.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>24.27</v>
+        <v>24.08</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.949999999999999</v>
+        <v>10.09</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.32</v>
+        <v>4.39</v>
       </c>
       <c r="BR4" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BT4" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BU4" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV4" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX4" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY4" t="n">
         <v>2.55</v>
@@ -2416,22 +2416,22 @@
         <v>2.63</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="CE4" t="n">
         <v>1.39</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CG4" t="n">
         <v>2.45</v>
@@ -2446,7 +2446,7 @@
         <v>1.81</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL4" t="n">
         <v>1.81</v>
@@ -2464,7 +2464,7 @@
         <v>2.09</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="CR4" t="n">
         <v>1.48</v>
@@ -2473,7 +2473,7 @@
         <v>3.28</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CU4" t="n">
         <v>1.33</v>
@@ -2503,49 +2503,49 @@
         <v>2.31</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="DH4" t="n">
-        <v>77.95999999999999</v>
+        <v>77.44</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.95</v>
+        <v>5.91</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DM4" t="n">
-        <v>54.91</v>
+        <v>54.22</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="DP4" t="n">
-        <v>16.69</v>
+        <v>16.7</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13.14</v>
+        <v>13.04</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.91</v>
+        <v>8.48</v>
       </c>
       <c r="DS4" t="n">
         <v>0.09</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.82</v>
+        <v>46.87</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DX4" t="n">
-        <v>15.22</v>
+        <v>15</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.82</v>
+        <v>10.7</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.41</v>
+        <v>4.3</v>
       </c>
       <c r="EA4" t="n">
-        <v>25.64</v>
+        <v>25.48</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="5">
@@ -2588,61 +2588,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F5" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="G5" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>93.81999999999999</v>
+        <v>94</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="K5" t="n">
-        <v>4.73</v>
+        <v>4.83</v>
       </c>
       <c r="L5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>61.45</v>
+        <v>61.67</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="P5" t="n">
-        <v>14.18</v>
+        <v>14.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.55</v>
+        <v>15.08</v>
       </c>
       <c r="R5" t="n">
-        <v>5.45</v>
+        <v>4.92</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="T5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58.73</v>
+        <v>58.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.55</v>
+        <v>15.08</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.18</v>
+        <v>10.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.36</v>
+        <v>5</v>
       </c>
       <c r="AC5" t="n">
-        <v>23.36</v>
+        <v>23</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AF5" t="n">
         <v>0.27</v>
@@ -2759,70 +2759,70 @@
         <v>3.09</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.550000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="BM5" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.41</v>
+        <v>3.52</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BU5" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV5" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="CC5" t="n">
         <v>2.24</v>
@@ -2834,10 +2834,10 @@
         <v>1.36</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CH5" t="n">
         <v>1.29</v>
@@ -2846,16 +2846,16 @@
         <v>1.79</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CK5" t="n">
         <v>1.37</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CN5" t="n">
         <v>1.88</v>
@@ -2867,7 +2867,7 @@
         <v>1.97</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="CR5" t="n">
         <v>1.42</v>
@@ -2882,7 +2882,7 @@
         <v>1.37</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW5" t="n">
         <v>1.91</v>
@@ -2891,13 +2891,13 @@
         <v>1.55</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB5" t="n">
         <v>1.35</v>
@@ -2906,49 +2906,49 @@
         <v>2.12</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="DE5" t="n">
         <v>0.22</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="DH5" t="n">
-        <v>86.64</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="DI5" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.64</v>
+        <v>4.7</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM5" t="n">
-        <v>54.27</v>
+        <v>54.7</v>
       </c>
       <c r="DN5" t="n">
         <v>1.09</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.41</v>
+        <v>15.48</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.5</v>
+        <v>15.26</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.68</v>
+        <v>5.39</v>
       </c>
       <c r="DS5" t="n">
         <v>0.09</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.73</v>
+        <v>55.61</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.46</v>
+        <v>14.26</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.32</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.14</v>
+        <v>4.96</v>
       </c>
       <c r="EA5" t="n">
-        <v>23.96</v>
+        <v>23.74</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="EC5" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="AI6" t="n">
-        <v>75.09</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.27</v>
+        <v>4.42</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>41.55</v>
+        <v>41.67</v>
       </c>
       <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>24.17</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BN6" t="n">
         <v>1.09</v>
       </c>
-      <c r="AP6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>17.09</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>15.64</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>40.18</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>24.18</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>9.73</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BO6" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5</v>
+        <v>5.13</v>
       </c>
       <c r="BR6" t="n">
-        <v>81.81999999999999</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BT6" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BU6" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BV6" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BY6" t="n">
         <v>2.68</v>
@@ -3222,22 +3222,22 @@
         <v>3.02</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CB6" t="n">
         <v>3.47</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.47</v>
+        <v>4.41</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.8</v>
+        <v>4.79</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CG6" t="n">
         <v>2.62</v>
@@ -3246,31 +3246,31 @@
         <v>1.31</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CL6" t="n">
         <v>1.59</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CN6" t="n">
         <v>1.92</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="CR6" t="n">
         <v>1.42</v>
@@ -3285,10 +3285,10 @@
         <v>1.37</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX6" t="n">
         <v>1.5</v>
@@ -3315,49 +3315,49 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="DH6" t="n">
-        <v>84.27</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="DI6" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.41</v>
+        <v>4.48</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>48.1</v>
+        <v>47.87</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="DP6" t="n">
-        <v>15.87</v>
+        <v>15.96</v>
       </c>
       <c r="DQ6" t="n">
-        <v>15.14</v>
+        <v>15.13</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.550000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
@@ -3366,25 +3366,25 @@
         <v>44.91</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX6" t="n">
-        <v>11</v>
+        <v>10.87</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.32</v>
+        <v>7.3</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.68</v>
+        <v>3.57</v>
       </c>
       <c r="EA6" t="n">
-        <v>23.14</v>
+        <v>23.18</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,127 +3487,127 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AI7" t="n">
-        <v>85.18000000000001</v>
+        <v>82.42</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AN7" t="n">
-        <v>55.55</v>
+        <v>52.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.55</v>
+        <v>13.42</v>
       </c>
       <c r="AR7" t="n">
-        <v>16.27</v>
+        <v>16.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.73</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>56.36</v>
+        <v>55.83</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BA7" t="n">
-        <v>12.64</v>
+        <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.18</v>
+        <v>7.67</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.64</v>
+        <v>19.25</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.36</v>
+        <v>4.25</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.5</v>
+        <v>9.43</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.45</v>
+        <v>4.39</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT7" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU7" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY7" t="n">
         <v>1.89</v>
@@ -3625,28 +3625,28 @@
         <v>2.02</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI7" t="n">
         <v>1.92</v>
@@ -3655,34 +3655,34 @@
         <v>1.81</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CO7" t="n">
         <v>1.29</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CU7" t="n">
         <v>1.38</v>
@@ -3694,67 +3694,67 @@
         <v>1.85</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="DB7" t="n">
         <v>1.33</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="DH7" t="n">
-        <v>85.64</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="DI7" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.73</v>
+        <v>4.65</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="DM7" t="n">
-        <v>56.96</v>
+        <v>55.3</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.46</v>
+        <v>14.35</v>
       </c>
       <c r="DQ7" t="n">
-        <v>16.31</v>
+        <v>16.43</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.45</v>
+        <v>7.09</v>
       </c>
       <c r="DS7" t="n">
         <v>0.09</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>56.22</v>
+        <v>55.95</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.32</v>
+        <v>12.96</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.630000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.68</v>
+        <v>4.61</v>
       </c>
       <c r="EA7" t="n">
-        <v>20</v>
+        <v>19.78</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>0.09</v>
@@ -3887,139 +3887,139 @@
         <v>3.64</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="AI8" t="n">
-        <v>83.36</v>
+        <v>81.67</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.45</v>
+        <v>5.33</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AN8" t="n">
-        <v>50.73</v>
+        <v>50.17</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.18</v>
+        <v>13.42</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.64</v>
+        <v>15.25</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.36</v>
+        <v>6.67</v>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>48.73</v>
+        <v>48.5</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.36</v>
+        <v>12.25</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.18</v>
+        <v>7.92</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="BD8" t="n">
-        <v>23</v>
+        <v>22.58</v>
       </c>
       <c r="BE8" t="n">
         <v>1.44</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.449999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BP8" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.95</v>
+        <v>5.09</v>
       </c>
       <c r="BR8" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS8" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BU8" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BV8" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX8" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BY8" t="n">
         <v>1.94</v>
@@ -4028,25 +4028,25 @@
         <v>2.02</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF8" t="n">
         <v>2.99</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CH8" t="n">
         <v>1.34</v>
@@ -4058,13 +4058,13 @@
         <v>1.85</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CN8" t="n">
         <v>1.99</v>
@@ -4073,10 +4073,10 @@
         <v>1.32</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="CR8" t="n">
         <v>1.43</v>
@@ -4085,13 +4085,13 @@
         <v>3.16</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CU8" t="n">
         <v>1.36</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CW8" t="n">
         <v>1.91</v>
@@ -4100,64 +4100,64 @@
         <v>1.51</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB8" t="n">
         <v>1.36</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="DH8" t="n">
-        <v>89.68000000000001</v>
+        <v>88.52</v>
       </c>
       <c r="DI8" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.68</v>
+        <v>5.61</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DM8" t="n">
-        <v>58.14</v>
+        <v>57.53</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.5</v>
+        <v>14.57</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.41</v>
+        <v>14.26</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.14</v>
+        <v>6.78</v>
       </c>
       <c r="DS8" t="n">
         <v>0.04</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.82</v>
+        <v>50.61</v>
       </c>
       <c r="DW8" t="n">
         <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.9</v>
+        <v>13.78</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.039999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.86</v>
+        <v>4.91</v>
       </c>
       <c r="EA8" t="n">
-        <v>24.68</v>
+        <v>24.39</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="EC8" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="H9" t="n">
-        <v>94.64</v>
+        <v>93.75</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="K9" t="n">
         <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="M9" t="n">
-        <v>62.36</v>
+        <v>61.83</v>
       </c>
       <c r="N9" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>14.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.91</v>
+        <v>15.42</v>
       </c>
       <c r="R9" t="n">
-        <v>6.36</v>
+        <v>5.75</v>
       </c>
       <c r="S9" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="T9" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="U9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>50.91</v>
+        <v>51.25</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.09</v>
+        <v>13.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.82</v>
+        <v>9.67</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.27</v>
+        <v>4.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>23.64</v>
+        <v>23.58</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AF9" t="n">
         <v>0.09</v>
@@ -4371,70 +4371,70 @@
         <v>2.64</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.859999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="BO9" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.45</v>
+        <v>91.3</v>
       </c>
       <c r="BS9" t="n">
-        <v>77.27</v>
+        <v>73.91</v>
       </c>
       <c r="BT9" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BU9" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV9" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CC9" t="n">
         <v>2.98</v>
@@ -4446,7 +4446,7 @@
         <v>1.41</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CG9" t="n">
         <v>2.71</v>
@@ -4458,13 +4458,13 @@
         <v>1.9</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK9" t="n">
         <v>1.38</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CM9" t="n">
         <v>2.73</v>
@@ -4479,7 +4479,7 @@
         <v>2.05</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="CR9" t="n">
         <v>1.41</v>
@@ -4494,10 +4494,10 @@
         <v>1.37</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CX9" t="n">
         <v>1.5</v>
@@ -4524,76 +4524,76 @@
         <v>0.04</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="DH9" t="n">
-        <v>90.68000000000001</v>
+        <v>90.39</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.36</v>
+        <v>5.39</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DM9" t="n">
-        <v>58.14</v>
+        <v>58.04</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.78</v>
+        <v>14.74</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.36</v>
+        <v>16.57</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.45</v>
+        <v>6.13</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.78</v>
+        <v>51.91</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.64</v>
+        <v>13.48</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.32</v>
+        <v>9.26</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.32</v>
+        <v>4.21</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.1</v>
+        <v>23.09</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F10" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>80.64</v>
+        <v>81.33</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J10" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="K10" t="n">
-        <v>5.27</v>
+        <v>5.33</v>
       </c>
       <c r="L10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M10" t="n">
-        <v>52.64</v>
+        <v>52</v>
       </c>
       <c r="N10" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>13.27</v>
+        <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.64</v>
+        <v>16</v>
       </c>
       <c r="R10" t="n">
-        <v>6.09</v>
+        <v>5.5</v>
       </c>
       <c r="S10" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
-        <v>0.91</v>
-      </c>
       <c r="U10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>56.27</v>
+        <v>56.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.73</v>
+        <v>14.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>11</v>
+        <v>10.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.73</v>
+        <v>3.92</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.18</v>
+        <v>18.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="AF10" t="n">
         <v>0.18</v>
@@ -4777,22 +4777,22 @@
         <v>2</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.59</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI10" t="n">
         <v>2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN10" t="n">
         <v>1.09</v>
@@ -4801,43 +4801,43 @@
         <v>0.91</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.59</v>
+        <v>4.74</v>
       </c>
       <c r="BR10" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS10" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BT10" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BU10" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV10" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CC10" t="n">
         <v>2.63</v>
@@ -4849,10 +4849,10 @@
         <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CH10" t="n">
         <v>1.34</v>
@@ -4864,16 +4864,16 @@
         <v>1.88</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL10" t="n">
         <v>1.83</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CN10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CO10" t="n">
         <v>1.35</v>
@@ -4882,22 +4882,22 @@
         <v>2.13</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CR10" t="n">
         <v>1.45</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CU10" t="n">
         <v>1.35</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CW10" t="n">
         <v>1.92</v>
@@ -4906,13 +4906,13 @@
         <v>1.51</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="DB10" t="n">
         <v>1.37</v>
@@ -4921,49 +4921,49 @@
         <v>2.19</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.93</v>
+        <v>3.96</v>
       </c>
       <c r="DE10" t="n">
         <v>0.13</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="DH10" t="n">
-        <v>83.59999999999999</v>
+        <v>83.83</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.82</v>
+        <v>4.87</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM10" t="n">
-        <v>51.86</v>
+        <v>51.56</v>
       </c>
       <c r="DN10" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.04</v>
+        <v>13.87</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16</v>
+        <v>16.17</v>
       </c>
       <c r="DR10" t="n">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="DS10" t="n">
         <v>0.13</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>52.68</v>
+        <v>52.74</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.78</v>
+        <v>12.65</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.91</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.86</v>
+        <v>3.96</v>
       </c>
       <c r="EA10" t="n">
         <v>19</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="EC10" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F11" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G11" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="H11" t="n">
-        <v>93.91</v>
+        <v>91.92</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J11" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="K11" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="M11" t="n">
-        <v>52.82</v>
+        <v>52</v>
       </c>
       <c r="N11" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="O11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="P11" t="n">
-        <v>13.91</v>
+        <v>14.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>16.09</v>
+        <v>15.92</v>
       </c>
       <c r="R11" t="n">
-        <v>7.55</v>
+        <v>6.83</v>
       </c>
       <c r="S11" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="T11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>50.27</v>
+        <v>50.25</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.36</v>
+        <v>12.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.91</v>
+        <v>8</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>23.18</v>
+        <v>23.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5177,70 +5177,70 @@
         <v>3.55</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.09</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
       <c r="BR11" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS11" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU11" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV11" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CC11" t="n">
         <v>3.34</v>
@@ -5252,7 +5252,7 @@
         <v>1.43</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CG11" t="n">
         <v>2.63</v>
@@ -5267,25 +5267,25 @@
         <v>1.86</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="CR11" t="n">
         <v>1.44</v>
@@ -5306,16 +5306,16 @@
         <v>1.89</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="DA11" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="DB11" t="n">
         <v>1.37</v>
@@ -5330,76 +5330,76 @@
         <v>0.04</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="DH11" t="n">
-        <v>89.68000000000001</v>
+        <v>88.83</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DM11" t="n">
-        <v>48.36</v>
+        <v>48.13</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.5</v>
+        <v>14.65</v>
       </c>
       <c r="DQ11" t="n">
-        <v>16.68</v>
+        <v>16.57</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.95</v>
+        <v>7.56</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.68</v>
+        <v>48.74</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.72</v>
+        <v>11.74</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.73</v>
+        <v>7.78</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.86</v>
+        <v>21.92</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="EC11" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F12" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="G12" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="H12" t="n">
-        <v>85</v>
+        <v>83.67</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J12" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>6.45</v>
+        <v>6.58</v>
       </c>
       <c r="L12" t="n">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="M12" t="n">
-        <v>56.09</v>
+        <v>55.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>16.64</v>
+        <v>16.17</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.45</v>
+        <v>15.17</v>
       </c>
       <c r="R12" t="n">
-        <v>7.82</v>
+        <v>7.08</v>
       </c>
       <c r="S12" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="T12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="U12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>50.64</v>
+        <v>50.75</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.64</v>
+        <v>12.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.91</v>
+        <v>8.83</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>22.73</v>
+        <v>23.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,70 +5580,70 @@
         <v>2.91</v>
       </c>
       <c r="BG12" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.23</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.73</v>
+        <v>3.87</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.45</v>
+        <v>4.52</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS12" t="n">
-        <v>81.81999999999999</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BU12" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV12" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX12" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BY12" t="n">
         <v>2.47</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CA12" t="n">
         <v>3.12</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CC12" t="n">
         <v>3.19</v>
@@ -5655,28 +5655,28 @@
         <v>1.43</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.85</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN12" t="n">
         <v>1.9</v>
@@ -5688,7 +5688,7 @@
         <v>2.14</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="CR12" t="n">
         <v>1.44</v>
@@ -5697,7 +5697,7 @@
         <v>3.17</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CU12" t="n">
         <v>1.35</v>
@@ -5721,55 +5721,55 @@
         <v>2.01</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="DH12" t="n">
-        <v>81.18000000000001</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.18</v>
+        <v>5.3</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.32</v>
+        <v>0.43</v>
       </c>
       <c r="DM12" t="n">
         <v>48.91</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.14</v>
+        <v>14.96</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15</v>
+        <v>15.35</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.779999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="DS12" t="n">
         <v>0.13</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.18</v>
+        <v>48.35</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.46</v>
+        <v>11.34</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.41</v>
+        <v>7.43</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.05</v>
+        <v>3.91</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.86</v>
+        <v>22.17</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AI13" t="n">
-        <v>74.59999999999999</v>
+        <v>77.09</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.6</v>
+        <v>4.09</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="AN13" t="n">
-        <v>38.9</v>
+        <v>41</v>
       </c>
       <c r="AO13" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>17.4</v>
+        <v>17.36</v>
       </c>
       <c r="AS13" t="n">
-        <v>12.9</v>
+        <v>11.64</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>45.4</v>
+        <v>46.91</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.300000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.8</v>
+        <v>7.45</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="BD13" t="n">
-        <v>21.2</v>
+        <v>21.36</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.14</v>
+        <v>10.18</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.67</v>
+        <v>3.45</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.48</v>
+        <v>5.18</v>
       </c>
       <c r="BR13" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BS13" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BU13" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV13" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX13" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY13" t="n">
         <v>3.29</v>
@@ -6043,16 +6043,16 @@
         <v>3.64</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CB13" t="n">
         <v>3.46</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.32</v>
+        <v>4.24</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.05</v>
+        <v>4.93</v>
       </c>
       <c r="CE13" t="n">
         <v>1.43</v>
@@ -6070,142 +6070,142 @@
         <v>1.82</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK13" t="n">
         <v>1.41</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CM13" t="n">
         <v>2.63</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CU13" t="n">
         <v>1.36</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.48</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="DH13" t="n">
-        <v>77.72</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="DI13" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.14</v>
+        <v>4.36</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="DM13" t="n">
-        <v>46.52</v>
+        <v>47.22</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.67</v>
+        <v>14.86</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.05</v>
+        <v>16.09</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.619999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46.05</v>
+        <v>46.78</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX13" t="n">
-        <v>12</v>
+        <v>12.27</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.57</v>
+        <v>8.82</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.43</v>
+        <v>3.46</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.85</v>
+        <v>21.9</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F14" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="H14" t="n">
-        <v>78.18000000000001</v>
+        <v>79</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="K14" t="n">
-        <v>5.82</v>
+        <v>5.58</v>
       </c>
       <c r="L14" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="M14" t="n">
-        <v>49.64</v>
+        <v>49.92</v>
       </c>
       <c r="N14" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="O14" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="P14" t="n">
-        <v>14.45</v>
+        <v>14.17</v>
       </c>
       <c r="Q14" t="n">
-        <v>17.82</v>
+        <v>17.58</v>
       </c>
       <c r="R14" t="n">
-        <v>6.82</v>
+        <v>6.17</v>
       </c>
       <c r="S14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T14" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>51.36</v>
+        <v>50.83</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>14</v>
+        <v>13.42</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.640000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="AC14" t="n">
-        <v>23.64</v>
+        <v>23.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AF14" t="n">
         <v>0.18</v>
@@ -6386,67 +6386,67 @@
         <v>2.73</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.64</v>
+        <v>10.48</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.91</v>
+        <v>5.83</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS14" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BU14" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV14" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX14" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.95</v>
+        <v>3.06</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CB14" t="n">
         <v>3.49</v>
@@ -6470,22 +6470,22 @@
         <v>1.39</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK14" t="n">
         <v>1.28</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CO14" t="n">
         <v>1.28</v>
@@ -6494,7 +6494,7 @@
         <v>1.94</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CR14" t="n">
         <v>1.39</v>
@@ -6503,13 +6503,13 @@
         <v>2.96</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CU14" t="n">
         <v>1.4</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CW14" t="n">
         <v>1.8</v>
@@ -6530,22 +6530,22 @@
         <v>1.31</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DH14" t="n">
-        <v>75.95999999999999</v>
+        <v>76.48</v>
       </c>
       <c r="DI14" t="n">
         <v>0.04</v>
@@ -6554,61 +6554,61 @@
         <v>3</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.69</v>
+        <v>4.61</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.04</v>
+        <v>46.35</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DP14" t="n">
-        <v>13</v>
+        <v>12.92</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.28</v>
+        <v>17.17</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.140000000000001</v>
+        <v>7.74</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.27</v>
+        <v>50.04</v>
       </c>
       <c r="DW14" t="n">
         <v>0.22</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.68</v>
+        <v>12.43</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.32</v>
+        <v>8.26</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.36</v>
+        <v>4.17</v>
       </c>
       <c r="EA14" t="n">
-        <v>22.1</v>
+        <v>22.13</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
       